--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -4804,12 +4804,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -16809,7 +16809,9 @@
         <v>0</v>
       </c>
       <c r="R133" s="37"/>
-      <c r="S133" s="49"/>
+      <c r="S133" s="49">
+        <v>4058133</v>
+      </c>
       <c r="T133" s="49" t="s">
         <v>698</v>
       </c>
@@ -16842,7 +16844,9 @@
         <v>0</v>
       </c>
       <c r="R134" s="37"/>
-      <c r="S134" s="49"/>
+      <c r="S134" s="49">
+        <v>4058134</v>
+      </c>
       <c r="T134" s="49" t="s">
         <v>701</v>
       </c>
@@ -16875,7 +16879,9 @@
         <v>0</v>
       </c>
       <c r="R135" s="37"/>
-      <c r="S135" s="49"/>
+      <c r="S135" s="49">
+        <v>4058135</v>
+      </c>
       <c r="T135" s="49" t="s">
         <v>662</v>
       </c>
@@ -16908,7 +16914,9 @@
         <v>0</v>
       </c>
       <c r="R136" s="37"/>
-      <c r="S136" s="49"/>
+      <c r="S136" s="49">
+        <v>4058136</v>
+      </c>
       <c r="T136" s="49" t="s">
         <v>698</v>
       </c>
@@ -16941,7 +16949,9 @@
         <v>0</v>
       </c>
       <c r="R137" s="37"/>
-      <c r="S137" s="49"/>
+      <c r="S137" s="49">
+        <v>4058137</v>
+      </c>
       <c r="T137" s="49" t="s">
         <v>701</v>
       </c>
@@ -16974,7 +16984,9 @@
         <v>0</v>
       </c>
       <c r="R138" s="37"/>
-      <c r="S138" s="49"/>
+      <c r="S138" s="49">
+        <v>4058138</v>
+      </c>
       <c r="T138" s="49" t="s">
         <v>662</v>
       </c>
@@ -17007,7 +17019,9 @@
         <v>0</v>
       </c>
       <c r="R139" s="37"/>
-      <c r="S139" s="49"/>
+      <c r="S139" s="49">
+        <v>4058139</v>
+      </c>
       <c r="T139" s="49" t="s">
         <v>698</v>
       </c>
@@ -17040,7 +17054,9 @@
         <v>0</v>
       </c>
       <c r="R140" s="37"/>
-      <c r="S140" s="49"/>
+      <c r="S140" s="49">
+        <v>4058140</v>
+      </c>
       <c r="T140" s="49" t="s">
         <v>701</v>
       </c>
@@ -17073,7 +17089,9 @@
         <v>0</v>
       </c>
       <c r="R141" s="37"/>
-      <c r="S141" s="49"/>
+      <c r="S141" s="49">
+        <v>4058141</v>
+      </c>
       <c r="T141" s="49" t="s">
         <v>662</v>
       </c>
@@ -17106,7 +17124,9 @@
         <v>0</v>
       </c>
       <c r="R142" s="37"/>
-      <c r="S142" s="49"/>
+      <c r="S142" s="49">
+        <v>4058142</v>
+      </c>
       <c r="T142" s="49" t="s">
         <v>698</v>
       </c>
@@ -17139,7 +17159,9 @@
         <v>0</v>
       </c>
       <c r="R143" s="37"/>
-      <c r="S143" s="49"/>
+      <c r="S143" s="49">
+        <v>4058143</v>
+      </c>
       <c r="T143" s="49" t="s">
         <v>701</v>
       </c>
@@ -17172,7 +17194,9 @@
         <v>0</v>
       </c>
       <c r="R144" s="37"/>
-      <c r="S144" s="49"/>
+      <c r="S144" s="49">
+        <v>4058144</v>
+      </c>
       <c r="T144" s="49" t="s">
         <v>662</v>
       </c>
@@ -17205,7 +17229,9 @@
         <v>0</v>
       </c>
       <c r="R145" s="37"/>
-      <c r="S145" s="49"/>
+      <c r="S145" s="49">
+        <v>4058145</v>
+      </c>
       <c r="T145" s="49" t="s">
         <v>698</v>
       </c>
@@ -17238,7 +17264,9 @@
         <v>0</v>
       </c>
       <c r="R146" s="37"/>
-      <c r="S146" s="49"/>
+      <c r="S146" s="49">
+        <v>4058146</v>
+      </c>
       <c r="T146" s="49" t="s">
         <v>701</v>
       </c>
@@ -17271,7 +17299,9 @@
         <v>0</v>
       </c>
       <c r="R147" s="37"/>
-      <c r="S147" s="49"/>
+      <c r="S147" s="49">
+        <v>4058147</v>
+      </c>
       <c r="T147" s="49" t="s">
         <v>662</v>
       </c>
@@ -17304,7 +17334,9 @@
         <v>0</v>
       </c>
       <c r="R148" s="37"/>
-      <c r="S148" s="49"/>
+      <c r="S148" s="49">
+        <v>4058148</v>
+      </c>
       <c r="T148" s="49" t="s">
         <v>698</v>
       </c>
@@ -17337,7 +17369,9 @@
         <v>0</v>
       </c>
       <c r="R149" s="37"/>
-      <c r="S149" s="49"/>
+      <c r="S149" s="49">
+        <v>4058149</v>
+      </c>
       <c r="T149" s="49" t="s">
         <v>701</v>
       </c>
@@ -17370,7 +17404,9 @@
         <v>0</v>
       </c>
       <c r="R150" s="37"/>
-      <c r="S150" s="49"/>
+      <c r="S150" s="49">
+        <v>4058150</v>
+      </c>
       <c r="T150" s="49" t="s">
         <v>662</v>
       </c>
@@ -17403,7 +17439,9 @@
         <v>0</v>
       </c>
       <c r="R151" s="37"/>
-      <c r="S151" s="49"/>
+      <c r="S151" s="49">
+        <v>4058151</v>
+      </c>
       <c r="T151" s="49" t="s">
         <v>698</v>
       </c>
@@ -17436,7 +17474,9 @@
         <v>0</v>
       </c>
       <c r="R152" s="37"/>
-      <c r="S152" s="49"/>
+      <c r="S152" s="49">
+        <v>4058152</v>
+      </c>
       <c r="T152" s="49" t="s">
         <v>701</v>
       </c>
@@ -17469,7 +17509,9 @@
         <v>0</v>
       </c>
       <c r="R153" s="37"/>
-      <c r="S153" s="49"/>
+      <c r="S153" s="49">
+        <v>4058153</v>
+      </c>
       <c r="T153" s="49" t="s">
         <v>662</v>
       </c>
@@ -17502,7 +17544,9 @@
         <v>0</v>
       </c>
       <c r="R154" s="37"/>
-      <c r="S154" s="49"/>
+      <c r="S154" s="49">
+        <v>4058154</v>
+      </c>
       <c r="T154" s="49" t="s">
         <v>698</v>
       </c>
@@ -17535,7 +17579,9 @@
         <v>0</v>
       </c>
       <c r="R155" s="37"/>
-      <c r="S155" s="49"/>
+      <c r="S155" s="49">
+        <v>4058155</v>
+      </c>
       <c r="T155" s="49" t="s">
         <v>701</v>
       </c>
@@ -17568,7 +17614,9 @@
         <v>0</v>
       </c>
       <c r="R156" s="37"/>
-      <c r="S156" s="49"/>
+      <c r="S156" s="49">
+        <v>4058156</v>
+      </c>
       <c r="T156" s="49" t="s">
         <v>662</v>
       </c>
@@ -17601,7 +17649,9 @@
         <v>0</v>
       </c>
       <c r="R157" s="37"/>
-      <c r="S157" s="49"/>
+      <c r="S157" s="49">
+        <v>4058157</v>
+      </c>
       <c r="T157" s="49" t="s">
         <v>698</v>
       </c>
@@ -17634,7 +17684,9 @@
         <v>0</v>
       </c>
       <c r="R158" s="37"/>
-      <c r="S158" s="49"/>
+      <c r="S158" s="49">
+        <v>4058158</v>
+      </c>
       <c r="T158" s="49" t="s">
         <v>701</v>
       </c>
@@ -17667,7 +17719,9 @@
         <v>0</v>
       </c>
       <c r="R159" s="37"/>
-      <c r="S159" s="49"/>
+      <c r="S159" s="49">
+        <v>4058159</v>
+      </c>
       <c r="T159" s="49" t="s">
         <v>662</v>
       </c>
@@ -17700,7 +17754,9 @@
         <v>0</v>
       </c>
       <c r="R160" s="37"/>
-      <c r="S160" s="49"/>
+      <c r="S160" s="49">
+        <v>4058160</v>
+      </c>
       <c r="T160" s="49" t="s">
         <v>698</v>
       </c>
@@ -17733,7 +17789,9 @@
         <v>0</v>
       </c>
       <c r="R161" s="37"/>
-      <c r="S161" s="49"/>
+      <c r="S161" s="49">
+        <v>4058161</v>
+      </c>
       <c r="T161" s="49" t="s">
         <v>701</v>
       </c>
@@ -17766,7 +17824,9 @@
         <v>0</v>
       </c>
       <c r="R162" s="37"/>
-      <c r="S162" s="49"/>
+      <c r="S162" s="49">
+        <v>4058162</v>
+      </c>
       <c r="T162" s="49" t="s">
         <v>662</v>
       </c>
@@ -17799,7 +17859,9 @@
         <v>0</v>
       </c>
       <c r="R163" s="37"/>
-      <c r="S163" s="49"/>
+      <c r="S163" s="49">
+        <v>4058163</v>
+      </c>
       <c r="T163" s="49" t="s">
         <v>698</v>
       </c>
@@ -17832,7 +17894,9 @@
         <v>0</v>
       </c>
       <c r="R164" s="37"/>
-      <c r="S164" s="49"/>
+      <c r="S164" s="49">
+        <v>4058164</v>
+      </c>
       <c r="T164" s="49" t="s">
         <v>701</v>
       </c>
@@ -17865,7 +17929,9 @@
         <v>0</v>
       </c>
       <c r="R165" s="37"/>
-      <c r="S165" s="49"/>
+      <c r="S165" s="49">
+        <v>4058165</v>
+      </c>
       <c r="T165" s="49" t="s">
         <v>662</v>
       </c>
@@ -17898,7 +17964,9 @@
         <v>0</v>
       </c>
       <c r="R166" s="37"/>
-      <c r="S166" s="49"/>
+      <c r="S166" s="49">
+        <v>4058166</v>
+      </c>
       <c r="T166" s="49" t="s">
         <v>698</v>
       </c>
@@ -17931,7 +17999,9 @@
         <v>0</v>
       </c>
       <c r="R167" s="37"/>
-      <c r="S167" s="49"/>
+      <c r="S167" s="49">
+        <v>4058167</v>
+      </c>
       <c r="T167" s="49" t="s">
         <v>701</v>
       </c>
@@ -17964,7 +18034,9 @@
         <v>0</v>
       </c>
       <c r="R168" s="37"/>
-      <c r="S168" s="49"/>
+      <c r="S168" s="49">
+        <v>4058168</v>
+      </c>
       <c r="T168" s="49" t="s">
         <v>662</v>
       </c>
@@ -17997,7 +18069,9 @@
         <v>0</v>
       </c>
       <c r="R169" s="37"/>
-      <c r="S169" s="49"/>
+      <c r="S169" s="49">
+        <v>4058169</v>
+      </c>
       <c r="T169" s="49" t="s">
         <v>698</v>
       </c>
@@ -18030,7 +18104,9 @@
         <v>0</v>
       </c>
       <c r="R170" s="37"/>
-      <c r="S170" s="49"/>
+      <c r="S170" s="49">
+        <v>4058170</v>
+      </c>
       <c r="T170" s="49" t="s">
         <v>701</v>
       </c>
@@ -18063,7 +18139,9 @@
         <v>0</v>
       </c>
       <c r="R171" s="37"/>
-      <c r="S171" s="49"/>
+      <c r="S171" s="49">
+        <v>4058171</v>
+      </c>
       <c r="T171" s="49" t="s">
         <v>662</v>
       </c>
@@ -18096,7 +18174,9 @@
         <v>0</v>
       </c>
       <c r="R172" s="37"/>
-      <c r="S172" s="49"/>
+      <c r="S172" s="49">
+        <v>4058172</v>
+      </c>
       <c r="T172" s="49" t="s">
         <v>698</v>
       </c>
@@ -18129,7 +18209,9 @@
         <v>0</v>
       </c>
       <c r="R173" s="37"/>
-      <c r="S173" s="49"/>
+      <c r="S173" s="49">
+        <v>4058173</v>
+      </c>
       <c r="T173" s="49" t="s">
         <v>701</v>
       </c>
@@ -18162,7 +18244,9 @@
         <v>0</v>
       </c>
       <c r="R174" s="37"/>
-      <c r="S174" s="49"/>
+      <c r="S174" s="49">
+        <v>4058174</v>
+      </c>
       <c r="T174" s="49" t="s">
         <v>662</v>
       </c>
@@ -18195,7 +18279,9 @@
         <v>0</v>
       </c>
       <c r="R175" s="37"/>
-      <c r="S175" s="49"/>
+      <c r="S175" s="49">
+        <v>4058175</v>
+      </c>
       <c r="T175" s="49" t="s">
         <v>698</v>
       </c>
@@ -18228,7 +18314,9 @@
         <v>0</v>
       </c>
       <c r="R176" s="37"/>
-      <c r="S176" s="49"/>
+      <c r="S176" s="49">
+        <v>4058176</v>
+      </c>
       <c r="T176" s="49" t="s">
         <v>701</v>
       </c>
@@ -18261,7 +18349,9 @@
         <v>0</v>
       </c>
       <c r="R177" s="37"/>
-      <c r="S177" s="49"/>
+      <c r="S177" s="49">
+        <v>4058177</v>
+      </c>
       <c r="T177" s="49" t="s">
         <v>662</v>
       </c>
@@ -18294,7 +18384,9 @@
         <v>0</v>
       </c>
       <c r="R178" s="37"/>
-      <c r="S178" s="49"/>
+      <c r="S178" s="49">
+        <v>4058178</v>
+      </c>
       <c r="T178" s="49" t="s">
         <v>698</v>
       </c>
@@ -18327,7 +18419,9 @@
         <v>0</v>
       </c>
       <c r="R179" s="37"/>
-      <c r="S179" s="49"/>
+      <c r="S179" s="49">
+        <v>4058179</v>
+      </c>
       <c r="T179" s="49" t="s">
         <v>701</v>
       </c>
@@ -18360,7 +18454,9 @@
         <v>0</v>
       </c>
       <c r="R180" s="37"/>
-      <c r="S180" s="49"/>
+      <c r="S180" s="49">
+        <v>4058180</v>
+      </c>
       <c r="T180" s="49" t="s">
         <v>662</v>
       </c>
@@ -18393,7 +18489,9 @@
         <v>0</v>
       </c>
       <c r="R181" s="37"/>
-      <c r="S181" s="49"/>
+      <c r="S181" s="49">
+        <v>4058181</v>
+      </c>
       <c r="T181" s="49" t="s">
         <v>698</v>
       </c>
@@ -18426,7 +18524,9 @@
         <v>0</v>
       </c>
       <c r="R182" s="37"/>
-      <c r="S182" s="49"/>
+      <c r="S182" s="49">
+        <v>4058182</v>
+      </c>
       <c r="T182" s="49" t="s">
         <v>701</v>
       </c>
@@ -18459,7 +18559,9 @@
         <v>0</v>
       </c>
       <c r="R183" s="37"/>
-      <c r="S183" s="49"/>
+      <c r="S183" s="49">
+        <v>4058183</v>
+      </c>
       <c r="T183" s="49" t="s">
         <v>662</v>
       </c>
@@ -18492,7 +18594,9 @@
         <v>0</v>
       </c>
       <c r="R184" s="37"/>
-      <c r="S184" s="49"/>
+      <c r="S184" s="49">
+        <v>4058184</v>
+      </c>
       <c r="T184" s="49" t="s">
         <v>698</v>
       </c>
@@ -18525,7 +18629,9 @@
         <v>0</v>
       </c>
       <c r="R185" s="37"/>
-      <c r="S185" s="49"/>
+      <c r="S185" s="49">
+        <v>4058185</v>
+      </c>
       <c r="T185" s="49" t="s">
         <v>701</v>
       </c>
@@ -18558,7 +18664,9 @@
         <v>0</v>
       </c>
       <c r="R186" s="37"/>
-      <c r="S186" s="49"/>
+      <c r="S186" s="49">
+        <v>4058186</v>
+      </c>
       <c r="T186" s="49" t="s">
         <v>662</v>
       </c>
@@ -18591,7 +18699,9 @@
         <v>0</v>
       </c>
       <c r="R187" s="37"/>
-      <c r="S187" s="49"/>
+      <c r="S187" s="49">
+        <v>4058187</v>
+      </c>
       <c r="T187" s="49" t="s">
         <v>698</v>
       </c>
@@ -18624,7 +18734,9 @@
         <v>0</v>
       </c>
       <c r="R188" s="37"/>
-      <c r="S188" s="49"/>
+      <c r="S188" s="49">
+        <v>4058188</v>
+      </c>
       <c r="T188" s="49" t="s">
         <v>701</v>
       </c>
@@ -18657,7 +18769,9 @@
         <v>0</v>
       </c>
       <c r="R189" s="37"/>
-      <c r="S189" s="49"/>
+      <c r="S189" s="49">
+        <v>4058189</v>
+      </c>
       <c r="T189" s="49" t="s">
         <v>662</v>
       </c>
@@ -18690,7 +18804,9 @@
         <v>0</v>
       </c>
       <c r="R190" s="37"/>
-      <c r="S190" s="49"/>
+      <c r="S190" s="49">
+        <v>4058190</v>
+      </c>
       <c r="T190" s="49" t="s">
         <v>698</v>
       </c>
@@ -18723,7 +18839,9 @@
         <v>0</v>
       </c>
       <c r="R191" s="37"/>
-      <c r="S191" s="49"/>
+      <c r="S191" s="49">
+        <v>4058191</v>
+      </c>
       <c r="T191" s="49" t="s">
         <v>701</v>
       </c>
@@ -18756,7 +18874,9 @@
         <v>0</v>
       </c>
       <c r="R192" s="37"/>
-      <c r="S192" s="49"/>
+      <c r="S192" s="49">
+        <v>4058192</v>
+      </c>
       <c r="T192" s="49" t="s">
         <v>662</v>
       </c>
@@ -18789,7 +18909,9 @@
         <v>0</v>
       </c>
       <c r="R193" s="37"/>
-      <c r="S193" s="49"/>
+      <c r="S193" s="49">
+        <v>4058193</v>
+      </c>
       <c r="T193" s="49" t="s">
         <v>698</v>
       </c>
@@ -18822,7 +18944,9 @@
         <v>0</v>
       </c>
       <c r="R194" s="37"/>
-      <c r="S194" s="49"/>
+      <c r="S194" s="49">
+        <v>4058194</v>
+      </c>
       <c r="T194" s="49" t="s">
         <v>701</v>
       </c>
@@ -18855,7 +18979,9 @@
         <v>0</v>
       </c>
       <c r="R195" s="37"/>
-      <c r="S195" s="49"/>
+      <c r="S195" s="49">
+        <v>4058195</v>
+      </c>
       <c r="T195" s="49" t="s">
         <v>662</v>
       </c>
@@ -18888,7 +19014,9 @@
         <v>0</v>
       </c>
       <c r="R196" s="37"/>
-      <c r="S196" s="49"/>
+      <c r="S196" s="49">
+        <v>4058196</v>
+      </c>
       <c r="T196" s="49" t="s">
         <v>698</v>
       </c>
@@ -18921,7 +19049,9 @@
         <v>0</v>
       </c>
       <c r="R197" s="37"/>
-      <c r="S197" s="49"/>
+      <c r="S197" s="49">
+        <v>4058197</v>
+      </c>
       <c r="T197" s="49" t="s">
         <v>701</v>
       </c>
@@ -18954,7 +19084,9 @@
         <v>0</v>
       </c>
       <c r="R198" s="37"/>
-      <c r="S198" s="49"/>
+      <c r="S198" s="49">
+        <v>4058198</v>
+      </c>
       <c r="T198" s="49" t="s">
         <v>662</v>
       </c>
@@ -18987,7 +19119,9 @@
         <v>0</v>
       </c>
       <c r="R199" s="37"/>
-      <c r="S199" s="49"/>
+      <c r="S199" s="49">
+        <v>4058199</v>
+      </c>
       <c r="T199" s="49" t="s">
         <v>698</v>
       </c>
@@ -19020,7 +19154,9 @@
         <v>0</v>
       </c>
       <c r="R200" s="37"/>
-      <c r="S200" s="49"/>
+      <c r="S200" s="49">
+        <v>4058200</v>
+      </c>
       <c r="T200" s="49" t="s">
         <v>701</v>
       </c>
@@ -19053,7 +19189,9 @@
         <v>0</v>
       </c>
       <c r="R201" s="37"/>
-      <c r="S201" s="49"/>
+      <c r="S201" s="49">
+        <v>4058201</v>
+      </c>
       <c r="T201" s="49" t="s">
         <v>662</v>
       </c>
@@ -19086,7 +19224,9 @@
         <v>0</v>
       </c>
       <c r="R202" s="37"/>
-      <c r="S202" s="49"/>
+      <c r="S202" s="49">
+        <v>4058202</v>
+      </c>
       <c r="T202" s="49" t="s">
         <v>698</v>
       </c>
@@ -19119,7 +19259,9 @@
         <v>0</v>
       </c>
       <c r="R203" s="37"/>
-      <c r="S203" s="49"/>
+      <c r="S203" s="49">
+        <v>4058203</v>
+      </c>
       <c r="T203" s="49" t="s">
         <v>701</v>
       </c>
@@ -19152,7 +19294,9 @@
         <v>0</v>
       </c>
       <c r="R204" s="37"/>
-      <c r="S204" s="49"/>
+      <c r="S204" s="49">
+        <v>4058204</v>
+      </c>
       <c r="T204" s="49" t="s">
         <v>662</v>
       </c>
@@ -19185,7 +19329,9 @@
         <v>0</v>
       </c>
       <c r="R205" s="37"/>
-      <c r="S205" s="49"/>
+      <c r="S205" s="49">
+        <v>4058205</v>
+      </c>
       <c r="T205" s="49" t="s">
         <v>698</v>
       </c>
@@ -19218,7 +19364,9 @@
         <v>0</v>
       </c>
       <c r="R206" s="37"/>
-      <c r="S206" s="49"/>
+      <c r="S206" s="49">
+        <v>4058206</v>
+      </c>
       <c r="T206" s="49" t="s">
         <v>701</v>
       </c>
@@ -19251,7 +19399,9 @@
         <v>0</v>
       </c>
       <c r="R207" s="37"/>
-      <c r="S207" s="49"/>
+      <c r="S207" s="49">
+        <v>4058207</v>
+      </c>
       <c r="T207" s="49" t="s">
         <v>662</v>
       </c>
@@ -19284,7 +19434,9 @@
         <v>0</v>
       </c>
       <c r="R208" s="37"/>
-      <c r="S208" s="49"/>
+      <c r="S208" s="49">
+        <v>4058208</v>
+      </c>
       <c r="T208" s="49" t="s">
         <v>698</v>
       </c>
@@ -19317,7 +19469,9 @@
         <v>0</v>
       </c>
       <c r="R209" s="37"/>
-      <c r="S209" s="49"/>
+      <c r="S209" s="49">
+        <v>4058209</v>
+      </c>
       <c r="T209" s="49" t="s">
         <v>701</v>
       </c>
@@ -19350,7 +19504,9 @@
         <v>0</v>
       </c>
       <c r="R210" s="37"/>
-      <c r="S210" s="49"/>
+      <c r="S210" s="49">
+        <v>4058210</v>
+      </c>
       <c r="T210" s="49" t="s">
         <v>662</v>
       </c>
@@ -19383,7 +19539,9 @@
         <v>0</v>
       </c>
       <c r="R211" s="37"/>
-      <c r="S211" s="49"/>
+      <c r="S211" s="49">
+        <v>4058211</v>
+      </c>
       <c r="T211" s="49" t="s">
         <v>698</v>
       </c>
@@ -19416,7 +19574,9 @@
         <v>0</v>
       </c>
       <c r="R212" s="37"/>
-      <c r="S212" s="49"/>
+      <c r="S212" s="49">
+        <v>4058212</v>
+      </c>
       <c r="T212" s="49" t="s">
         <v>701</v>
       </c>
@@ -19449,7 +19609,9 @@
         <v>0</v>
       </c>
       <c r="R213" s="37"/>
-      <c r="S213" s="49"/>
+      <c r="S213" s="49">
+        <v>4058213</v>
+      </c>
       <c r="T213" s="49" t="s">
         <v>662</v>
       </c>
@@ -19482,7 +19644,9 @@
         <v>0</v>
       </c>
       <c r="R214" s="37"/>
-      <c r="S214" s="49"/>
+      <c r="S214" s="49">
+        <v>4058214</v>
+      </c>
       <c r="T214" s="49" t="s">
         <v>698</v>
       </c>
@@ -19515,7 +19679,9 @@
         <v>0</v>
       </c>
       <c r="R215" s="37"/>
-      <c r="S215" s="49"/>
+      <c r="S215" s="49">
+        <v>4058215</v>
+      </c>
       <c r="T215" s="49" t="s">
         <v>701</v>
       </c>
@@ -19548,7 +19714,9 @@
         <v>0</v>
       </c>
       <c r="R216" s="37"/>
-      <c r="S216" s="49"/>
+      <c r="S216" s="49">
+        <v>4058216</v>
+      </c>
       <c r="T216" s="49" t="s">
         <v>662</v>
       </c>
@@ -19581,7 +19749,9 @@
         <v>0</v>
       </c>
       <c r="R217" s="37"/>
-      <c r="S217" s="49"/>
+      <c r="S217" s="49">
+        <v>4058217</v>
+      </c>
       <c r="T217" s="49" t="s">
         <v>698</v>
       </c>
@@ -19614,7 +19784,9 @@
         <v>0</v>
       </c>
       <c r="R218" s="37"/>
-      <c r="S218" s="49"/>
+      <c r="S218" s="49">
+        <v>4058218</v>
+      </c>
       <c r="T218" s="49" t="s">
         <v>701</v>
       </c>
@@ -19647,7 +19819,9 @@
         <v>0</v>
       </c>
       <c r="R219" s="37"/>
-      <c r="S219" s="49"/>
+      <c r="S219" s="49">
+        <v>4058219</v>
+      </c>
       <c r="T219" s="49" t="s">
         <v>662</v>
       </c>
@@ -19680,7 +19854,9 @@
         <v>0</v>
       </c>
       <c r="R220" s="37"/>
-      <c r="S220" s="49"/>
+      <c r="S220" s="49">
+        <v>4058220</v>
+      </c>
       <c r="T220" s="49" t="s">
         <v>698</v>
       </c>
@@ -19713,7 +19889,9 @@
         <v>0</v>
       </c>
       <c r="R221" s="37"/>
-      <c r="S221" s="49"/>
+      <c r="S221" s="49">
+        <v>4058221</v>
+      </c>
       <c r="T221" s="49" t="s">
         <v>701</v>
       </c>
@@ -19746,7 +19924,9 @@
         <v>0</v>
       </c>
       <c r="R222" s="37"/>
-      <c r="S222" s="49"/>
+      <c r="S222" s="49">
+        <v>4058222</v>
+      </c>
       <c r="T222" s="49" t="s">
         <v>662</v>
       </c>
@@ -19779,7 +19959,9 @@
         <v>0</v>
       </c>
       <c r="R223" s="37"/>
-      <c r="S223" s="49"/>
+      <c r="S223" s="49">
+        <v>4058223</v>
+      </c>
       <c r="T223" s="49" t="s">
         <v>698</v>
       </c>
@@ -19812,7 +19994,9 @@
         <v>0</v>
       </c>
       <c r="R224" s="37"/>
-      <c r="S224" s="49"/>
+      <c r="S224" s="49">
+        <v>4058224</v>
+      </c>
       <c r="T224" s="49" t="s">
         <v>701</v>
       </c>
@@ -19845,7 +20029,9 @@
         <v>0</v>
       </c>
       <c r="R225" s="37"/>
-      <c r="S225" s="49"/>
+      <c r="S225" s="49">
+        <v>4058225</v>
+      </c>
       <c r="T225" s="49" t="s">
         <v>662</v>
       </c>
@@ -19878,7 +20064,9 @@
         <v>0</v>
       </c>
       <c r="R226" s="37"/>
-      <c r="S226" s="49"/>
+      <c r="S226" s="49">
+        <v>4058226</v>
+      </c>
       <c r="T226" s="49" t="s">
         <v>698</v>
       </c>
@@ -19911,7 +20099,9 @@
         <v>0</v>
       </c>
       <c r="R227" s="37"/>
-      <c r="S227" s="49"/>
+      <c r="S227" s="49">
+        <v>4058227</v>
+      </c>
       <c r="T227" s="49" t="s">
         <v>701</v>
       </c>
@@ -19944,7 +20134,9 @@
         <v>0</v>
       </c>
       <c r="R228" s="37"/>
-      <c r="S228" s="49"/>
+      <c r="S228" s="49">
+        <v>4058228</v>
+      </c>
       <c r="T228" s="49" t="s">
         <v>662</v>
       </c>
@@ -19977,7 +20169,9 @@
         <v>0</v>
       </c>
       <c r="R229" s="37"/>
-      <c r="S229" s="49"/>
+      <c r="S229" s="49">
+        <v>4058229</v>
+      </c>
       <c r="T229" s="49" t="s">
         <v>698</v>
       </c>
@@ -20010,7 +20204,9 @@
         <v>0</v>
       </c>
       <c r="R230" s="37"/>
-      <c r="S230" s="49"/>
+      <c r="S230" s="49">
+        <v>4058230</v>
+      </c>
       <c r="T230" s="49" t="s">
         <v>701</v>
       </c>
@@ -20043,7 +20239,9 @@
         <v>0</v>
       </c>
       <c r="R231" s="37"/>
-      <c r="S231" s="49"/>
+      <c r="S231" s="49">
+        <v>4058231</v>
+      </c>
       <c r="T231" s="49" t="s">
         <v>662</v>
       </c>
@@ -20076,7 +20274,9 @@
         <v>0</v>
       </c>
       <c r="R232" s="37"/>
-      <c r="S232" s="49"/>
+      <c r="S232" s="49">
+        <v>4058232</v>
+      </c>
       <c r="T232" s="49" t="s">
         <v>698</v>
       </c>
@@ -20109,7 +20309,9 @@
         <v>0</v>
       </c>
       <c r="R233" s="37"/>
-      <c r="S233" s="49"/>
+      <c r="S233" s="49">
+        <v>4058233</v>
+      </c>
       <c r="T233" s="49" t="s">
         <v>701</v>
       </c>
@@ -20142,7 +20344,9 @@
         <v>0</v>
       </c>
       <c r="R234" s="37"/>
-      <c r="S234" s="49"/>
+      <c r="S234" s="49">
+        <v>4058234</v>
+      </c>
       <c r="T234" s="49" t="s">
         <v>662</v>
       </c>
@@ -20175,7 +20379,9 @@
         <v>0</v>
       </c>
       <c r="R235" s="37"/>
-      <c r="S235" s="49"/>
+      <c r="S235" s="49">
+        <v>4058235</v>
+      </c>
       <c r="T235" s="49" t="s">
         <v>698</v>
       </c>
@@ -20208,7 +20414,9 @@
         <v>0</v>
       </c>
       <c r="R236" s="37"/>
-      <c r="S236" s="49"/>
+      <c r="S236" s="49">
+        <v>4058236</v>
+      </c>
       <c r="T236" s="49" t="s">
         <v>701</v>
       </c>
@@ -20241,7 +20449,9 @@
         <v>0</v>
       </c>
       <c r="R237" s="37"/>
-      <c r="S237" s="49"/>
+      <c r="S237" s="49">
+        <v>4058237</v>
+      </c>
       <c r="T237" s="49" t="s">
         <v>662</v>
       </c>
@@ -20274,7 +20484,9 @@
         <v>0</v>
       </c>
       <c r="R238" s="37"/>
-      <c r="S238" s="49"/>
+      <c r="S238" s="49">
+        <v>4058238</v>
+      </c>
       <c r="T238" s="49" t="s">
         <v>698</v>
       </c>
@@ -20307,7 +20519,9 @@
         <v>0</v>
       </c>
       <c r="R239" s="37"/>
-      <c r="S239" s="49"/>
+      <c r="S239" s="49">
+        <v>4058239</v>
+      </c>
       <c r="T239" s="49" t="s">
         <v>701</v>
       </c>
@@ -20340,7 +20554,9 @@
         <v>0</v>
       </c>
       <c r="R240" s="37"/>
-      <c r="S240" s="49"/>
+      <c r="S240" s="49">
+        <v>4058240</v>
+      </c>
       <c r="T240" s="49" t="s">
         <v>662</v>
       </c>
@@ -20373,7 +20589,9 @@
         <v>0</v>
       </c>
       <c r="R241" s="37"/>
-      <c r="S241" s="49"/>
+      <c r="S241" s="49">
+        <v>4058241</v>
+      </c>
       <c r="T241" s="49" t="s">
         <v>698</v>
       </c>
@@ -20406,7 +20624,9 @@
         <v>0</v>
       </c>
       <c r="R242" s="37"/>
-      <c r="S242" s="49"/>
+      <c r="S242" s="49">
+        <v>4058242</v>
+      </c>
       <c r="T242" s="49" t="s">
         <v>701</v>
       </c>
@@ -20439,7 +20659,9 @@
         <v>0</v>
       </c>
       <c r="R243" s="37"/>
-      <c r="S243" s="49"/>
+      <c r="S243" s="49">
+        <v>4058243</v>
+      </c>
       <c r="T243" s="49" t="s">
         <v>662</v>
       </c>
@@ -20472,7 +20694,9 @@
         <v>0</v>
       </c>
       <c r="R244" s="37"/>
-      <c r="S244" s="49"/>
+      <c r="S244" s="49">
+        <v>4058244</v>
+      </c>
       <c r="T244" s="49" t="s">
         <v>922</v>
       </c>
@@ -20505,7 +20729,9 @@
         <v>0</v>
       </c>
       <c r="R245" s="37"/>
-      <c r="S245" s="49"/>
+      <c r="S245" s="49">
+        <v>4058245</v>
+      </c>
       <c r="T245" s="49" t="s">
         <v>698</v>
       </c>
@@ -20538,7 +20764,9 @@
         <v>0</v>
       </c>
       <c r="R246" s="37"/>
-      <c r="S246" s="49"/>
+      <c r="S246" s="49">
+        <v>4058246</v>
+      </c>
       <c r="T246" s="49" t="s">
         <v>701</v>
       </c>
@@ -20571,7 +20799,9 @@
         <v>0</v>
       </c>
       <c r="R247" s="37"/>
-      <c r="S247" s="49"/>
+      <c r="S247" s="49">
+        <v>4058247</v>
+      </c>
       <c r="T247" s="49" t="s">
         <v>922</v>
       </c>
@@ -20604,7 +20834,9 @@
         <v>0</v>
       </c>
       <c r="R248" s="37"/>
-      <c r="S248" s="49"/>
+      <c r="S248" s="49">
+        <v>4058248</v>
+      </c>
       <c r="T248" s="49" t="s">
         <v>698</v>
       </c>
@@ -20637,7 +20869,9 @@
         <v>0</v>
       </c>
       <c r="R249" s="37"/>
-      <c r="S249" s="49"/>
+      <c r="S249" s="49">
+        <v>4058249</v>
+      </c>
       <c r="T249" s="49" t="s">
         <v>701</v>
       </c>
@@ -20670,7 +20904,9 @@
         <v>0</v>
       </c>
       <c r="R250" s="37"/>
-      <c r="S250" s="49"/>
+      <c r="S250" s="49">
+        <v>4058250</v>
+      </c>
       <c r="T250" s="49" t="s">
         <v>922</v>
       </c>
@@ -20703,7 +20939,9 @@
         <v>0</v>
       </c>
       <c r="R251" s="37"/>
-      <c r="S251" s="49"/>
+      <c r="S251" s="49">
+        <v>4058251</v>
+      </c>
       <c r="T251" s="49" t="s">
         <v>698</v>
       </c>
@@ -20736,7 +20974,9 @@
         <v>0</v>
       </c>
       <c r="R252" s="37"/>
-      <c r="S252" s="49"/>
+      <c r="S252" s="49">
+        <v>4058252</v>
+      </c>
       <c r="T252" s="49" t="s">
         <v>701</v>
       </c>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -61,6 +61,7 @@
 3. [成就]任务
 4. [多人]任务
 5. [联盟]任务
+6.新手赛季【试炼】任务
 </t>
         </r>
       </text>
@@ -580,7 +581,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="1391">
   <si>
     <t>任务ID</t>
   </si>
@@ -3919,6 +3920,253 @@
   </si>
   <si>
     <t>累计充值金额100</t>
+  </si>
+  <si>
+    <t>试炼任务</t>
+  </si>
+  <si>
+    <t>12601_100300_5_400</t>
+  </si>
+  <si>
+    <t>1960000_50</t>
+  </si>
+  <si>
+    <t>5局收益达到400</t>
+  </si>
+  <si>
+    <t>12601_100300_5_600</t>
+  </si>
+  <si>
+    <t>1960000_100</t>
+  </si>
+  <si>
+    <t>5局收益达到600</t>
+  </si>
+  <si>
+    <t>12601_100300_5_800</t>
+  </si>
+  <si>
+    <t>1960000_200</t>
+  </si>
+  <si>
+    <t>5局收益达到800</t>
+  </si>
+  <si>
+    <t>12602_100300_100_2_1</t>
+  </si>
+  <si>
+    <t>100局触发一次樱桃</t>
+  </si>
+  <si>
+    <t>12602_100300_100_2_2</t>
+  </si>
+  <si>
+    <t>100局触发二次樱桃</t>
+  </si>
+  <si>
+    <t>12602_100300_100_2_3</t>
+  </si>
+  <si>
+    <t>100局触发三次樱桃</t>
+  </si>
+  <si>
+    <t>12603_100300_30_2_1</t>
+  </si>
+  <si>
+    <t>30局触发1次2倍奖励</t>
+  </si>
+  <si>
+    <t>12603_100300_30_2_2</t>
+  </si>
+  <si>
+    <t>30局触发2次2倍奖励</t>
+  </si>
+  <si>
+    <t>12603_100300_30_2_3</t>
+  </si>
+  <si>
+    <t>30局触发3次2倍奖励</t>
+  </si>
+  <si>
+    <t>12604_100300_5_1</t>
+  </si>
+  <si>
+    <t>5局内中奖1次</t>
+  </si>
+  <si>
+    <t>12604_100300_5_2</t>
+  </si>
+  <si>
+    <t>5局内中奖2次</t>
+  </si>
+  <si>
+    <t>12604_100300_5_3</t>
+  </si>
+  <si>
+    <t>5局内中奖3次</t>
+  </si>
+  <si>
+    <t>12603_100300_50_5_1</t>
+  </si>
+  <si>
+    <t>50局触发1次5倍奖励</t>
+  </si>
+  <si>
+    <t>12603_100300_50_5_2</t>
+  </si>
+  <si>
+    <t>50局触发2次5倍奖励</t>
+  </si>
+  <si>
+    <t>12603_100300_50_5_3</t>
+  </si>
+  <si>
+    <t>50局触发3次5倍奖励</t>
+  </si>
+  <si>
+    <t>12605_100300_5_4_1</t>
+  </si>
+  <si>
+    <t>5局出现铃铛图标1次</t>
+  </si>
+  <si>
+    <t>12605_100300_5_4_2</t>
+  </si>
+  <si>
+    <t>5局出现铃铛图标2次</t>
+  </si>
+  <si>
+    <t>12605_100300_5_4_3</t>
+  </si>
+  <si>
+    <t>5局出现铃铛图标3次</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自由搭配，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5局总收益≥800</t>
+    </r>
+  </si>
+  <si>
+    <t>12601_100300_5_1000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自由搭配，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5局总收益≥1000</t>
+    </r>
+  </si>
+  <si>
+    <t>12601_100300_5_1200</t>
+  </si>
+  <si>
+    <t>自由搭配，5局总收益≥1200</t>
+  </si>
+  <si>
+    <t>12606_100300_3_200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内单局最高收益≥200</t>
+    </r>
+  </si>
+  <si>
+    <t>12606_100300_3_300</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内单局最高收益≥300</t>
+    </r>
+  </si>
+  <si>
+    <t>12606_100300_3_400</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内单局最高收益≥400</t>
+    </r>
+  </si>
+  <si>
+    <t>11002_0_5</t>
+  </si>
+  <si>
+    <t>11002_0_10</t>
+  </si>
+  <si>
+    <t>11002_0_20</t>
   </si>
   <si>
     <t>以下游戏可用来配置,【策划看】</t>
@@ -4604,7 +4852,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4804,12 +5052,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5331,7 +5585,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5516,6 +5770,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1">
@@ -6105,7 +6362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ328"/>
+  <dimension ref="A1:AJ354"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="4" customWidth="1"/>
@@ -6394,7 +6651,7 @@
       <c r="AA5" s="39">
         <v>300</v>
       </c>
-      <c r="AB5" s="62" t="s">
+      <c r="AB5" s="63" t="s">
         <v>50</v>
       </c>
       <c r="AC5" s="51">
@@ -6476,7 +6733,7 @@
       <c r="AA6" s="39">
         <v>1400</v>
       </c>
-      <c r="AB6" s="62" t="s">
+      <c r="AB6" s="63" t="s">
         <v>56</v>
       </c>
       <c r="AC6" s="51">
@@ -6558,7 +6815,7 @@
       <c r="AA7" s="39">
         <v>2800</v>
       </c>
-      <c r="AB7" s="62" t="s">
+      <c r="AB7" s="63" t="s">
         <v>62</v>
       </c>
       <c r="AC7" s="51">
@@ -6640,7 +6897,7 @@
       <c r="AA8" s="39">
         <v>8500</v>
       </c>
-      <c r="AB8" s="62" t="s">
+      <c r="AB8" s="63" t="s">
         <v>68</v>
       </c>
       <c r="AC8" s="51">
@@ -6721,7 +6978,7 @@
       <c r="AA9" s="39">
         <v>18700</v>
       </c>
-      <c r="AB9" s="62" t="s">
+      <c r="AB9" s="63" t="s">
         <v>74</v>
       </c>
       <c r="AC9" s="51">
@@ -6800,7 +7057,7 @@
       <c r="AA10" s="39">
         <v>28300</v>
       </c>
-      <c r="AB10" s="62" t="s">
+      <c r="AB10" s="63" t="s">
         <v>80</v>
       </c>
       <c r="AC10" s="51">
@@ -6884,7 +7141,7 @@
       <c r="AA11" s="39">
         <v>144000</v>
       </c>
-      <c r="AB11" s="62" t="s">
+      <c r="AB11" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC11" s="51">
@@ -6976,7 +7233,7 @@
       <c r="AA12" s="39">
         <v>144000</v>
       </c>
-      <c r="AB12" s="62" t="s">
+      <c r="AB12" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC12" s="51">
@@ -7068,7 +7325,7 @@
       <c r="AA13" s="39">
         <v>144000</v>
       </c>
-      <c r="AB13" s="62" t="s">
+      <c r="AB13" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC13" s="51">
@@ -7160,7 +7417,7 @@
       <c r="AA14" s="39">
         <v>144000</v>
       </c>
-      <c r="AB14" s="62" t="s">
+      <c r="AB14" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC14" s="51">
@@ -7252,7 +7509,7 @@
       <c r="AA15" s="39">
         <v>144000</v>
       </c>
-      <c r="AB15" s="62" t="s">
+      <c r="AB15" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC15" s="51">
@@ -7344,7 +7601,7 @@
       <c r="AA16" s="39">
         <v>144000</v>
       </c>
-      <c r="AB16" s="62" t="s">
+      <c r="AB16" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC16" s="51">
@@ -7436,7 +7693,7 @@
       <c r="AA17" s="39">
         <v>144000</v>
       </c>
-      <c r="AB17" s="62" t="s">
+      <c r="AB17" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC17" s="51">
@@ -7528,7 +7785,7 @@
       <c r="AA18" s="39">
         <v>144000</v>
       </c>
-      <c r="AB18" s="62" t="s">
+      <c r="AB18" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC18" s="51">
@@ -7620,7 +7877,7 @@
       <c r="AA19" s="39">
         <v>144000</v>
       </c>
-      <c r="AB19" s="62" t="s">
+      <c r="AB19" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC19" s="51">
@@ -7712,7 +7969,7 @@
       <c r="AA20" s="39">
         <v>144000</v>
       </c>
-      <c r="AB20" s="62" t="s">
+      <c r="AB20" s="63" t="s">
         <v>89</v>
       </c>
       <c r="AC20" s="51">
@@ -7804,7 +8061,7 @@
       <c r="AA21" s="39">
         <v>713000</v>
       </c>
-      <c r="AB21" s="62" t="s">
+      <c r="AB21" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC21" s="51">
@@ -7896,7 +8153,7 @@
       <c r="AA22" s="39">
         <v>713000</v>
       </c>
-      <c r="AB22" s="62" t="s">
+      <c r="AB22" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC22" s="51">
@@ -7988,7 +8245,7 @@
       <c r="AA23" s="39">
         <v>713000</v>
       </c>
-      <c r="AB23" s="62" t="s">
+      <c r="AB23" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC23" s="51">
@@ -8080,7 +8337,7 @@
       <c r="AA24" s="39">
         <v>713000</v>
       </c>
-      <c r="AB24" s="62" t="s">
+      <c r="AB24" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC24" s="51">
@@ -8172,7 +8429,7 @@
       <c r="AA25" s="39">
         <v>713000</v>
       </c>
-      <c r="AB25" s="62" t="s">
+      <c r="AB25" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC25" s="51">
@@ -8263,7 +8520,7 @@
       <c r="AA26" s="39">
         <v>713000</v>
       </c>
-      <c r="AB26" s="62" t="s">
+      <c r="AB26" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC26" s="51">
@@ -8354,7 +8611,7 @@
       <c r="AA27" s="39">
         <v>713000</v>
       </c>
-      <c r="AB27" s="62" t="s">
+      <c r="AB27" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC27" s="51">
@@ -8445,7 +8702,7 @@
       <c r="AA28" s="39">
         <v>713000</v>
       </c>
-      <c r="AB28" s="62" t="s">
+      <c r="AB28" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC28" s="51">
@@ -8536,7 +8793,7 @@
       <c r="AA29" s="39">
         <v>713000</v>
       </c>
-      <c r="AB29" s="62" t="s">
+      <c r="AB29" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC29" s="51">
@@ -8627,7 +8884,7 @@
       <c r="AA30" s="39">
         <v>713000</v>
       </c>
-      <c r="AB30" s="62" t="s">
+      <c r="AB30" s="63" t="s">
         <v>186</v>
       </c>
       <c r="AC30" s="51">
@@ -8720,7 +8977,7 @@
       <c r="AA31" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB31" s="62" t="s">
+      <c r="AB31" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC31" s="51">
@@ -8813,7 +9070,7 @@
       <c r="AA32" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB32" s="62" t="s">
+      <c r="AB32" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC32" s="51">
@@ -8906,7 +9163,7 @@
       <c r="AA33" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB33" s="62" t="s">
+      <c r="AB33" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC33" s="51">
@@ -8999,7 +9256,7 @@
       <c r="AA34" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB34" s="62" t="s">
+      <c r="AB34" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC34" s="51">
@@ -9092,7 +9349,7 @@
       <c r="AA35" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB35" s="62" t="s">
+      <c r="AB35" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC35" s="51">
@@ -9184,7 +9441,7 @@
       <c r="AA36" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB36" s="62" t="s">
+      <c r="AB36" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC36" s="51">
@@ -9276,7 +9533,7 @@
       <c r="AA37" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB37" s="62" t="s">
+      <c r="AB37" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC37" s="51">
@@ -9368,7 +9625,7 @@
       <c r="AA38" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB38" s="62" t="s">
+      <c r="AB38" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC38" s="51">
@@ -9460,7 +9717,7 @@
       <c r="AA39" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB39" s="62" t="s">
+      <c r="AB39" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC39" s="51">
@@ -9552,7 +9809,7 @@
       <c r="AA40" s="39">
         <v>2138000</v>
       </c>
-      <c r="AB40" s="62" t="s">
+      <c r="AB40" s="63" t="s">
         <v>237</v>
       </c>
       <c r="AC40" s="51">
@@ -9644,7 +9901,7 @@
       <c r="AA41" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB41" s="62" t="s">
+      <c r="AB41" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC41" s="51">
@@ -9736,7 +9993,7 @@
       <c r="AA42" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB42" s="62" t="s">
+      <c r="AB42" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC42" s="51">
@@ -9828,7 +10085,7 @@
       <c r="AA43" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB43" s="62" t="s">
+      <c r="AB43" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC43" s="51">
@@ -9920,7 +10177,7 @@
       <c r="AA44" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB44" s="62" t="s">
+      <c r="AB44" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC44" s="51">
@@ -10012,7 +10269,7 @@
       <c r="AA45" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB45" s="62" t="s">
+      <c r="AB45" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC45" s="51">
@@ -10104,7 +10361,7 @@
       <c r="AA46" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB46" s="62" t="s">
+      <c r="AB46" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC46" s="51">
@@ -10196,7 +10453,7 @@
       <c r="AA47" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB47" s="62" t="s">
+      <c r="AB47" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC47" s="51">
@@ -10288,7 +10545,7 @@
       <c r="AA48" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB48" s="62" t="s">
+      <c r="AB48" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC48" s="51">
@@ -10380,7 +10637,7 @@
       <c r="AA49" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB49" s="62" t="s">
+      <c r="AB49" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC49" s="51">
@@ -10472,7 +10729,7 @@
       <c r="AA50" s="39">
         <v>4277000</v>
       </c>
-      <c r="AB50" s="62" t="s">
+      <c r="AB50" s="63" t="s">
         <v>288</v>
       </c>
       <c r="AC50" s="51">
@@ -10563,7 +10820,7 @@
       <c r="AA51" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB51" s="62" t="s">
+      <c r="AB51" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC51" s="51">
@@ -10654,7 +10911,7 @@
       <c r="AA52" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB52" s="62" t="s">
+      <c r="AB52" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC52" s="51">
@@ -10745,7 +11002,7 @@
       <c r="AA53" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB53" s="62" t="s">
+      <c r="AB53" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC53" s="51">
@@ -10836,7 +11093,7 @@
       <c r="AA54" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB54" s="62" t="s">
+      <c r="AB54" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC54" s="51">
@@ -10927,7 +11184,7 @@
       <c r="AA55" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB55" s="62" t="s">
+      <c r="AB55" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC55" s="51">
@@ -11019,7 +11276,7 @@
       <c r="AA56" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB56" s="62" t="s">
+      <c r="AB56" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC56" s="4">
@@ -11111,7 +11368,7 @@
       <c r="AA57" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB57" s="62" t="s">
+      <c r="AB57" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC57" s="4">
@@ -11203,7 +11460,7 @@
       <c r="AA58" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB58" s="62" t="s">
+      <c r="AB58" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC58" s="4">
@@ -11295,7 +11552,7 @@
       <c r="AA59" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB59" s="62" t="s">
+      <c r="AB59" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC59" s="4">
@@ -11387,7 +11644,7 @@
       <c r="AA60" s="39">
         <v>7128000</v>
       </c>
-      <c r="AB60" s="62" t="s">
+      <c r="AB60" s="63" t="s">
         <v>339</v>
       </c>
       <c r="AC60" s="4">
@@ -11477,7 +11734,7 @@
       <c r="AA61" s="39">
         <v>400000</v>
       </c>
-      <c r="AB61" s="62" t="s">
+      <c r="AB61" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC61" s="4">
@@ -11567,7 +11824,7 @@
       <c r="AA62" s="39">
         <v>400000</v>
       </c>
-      <c r="AB62" s="62" t="s">
+      <c r="AB62" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC62" s="4">
@@ -11657,7 +11914,7 @@
       <c r="AA63" s="39">
         <v>400000</v>
       </c>
-      <c r="AB63" s="62" t="s">
+      <c r="AB63" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC63" s="4">
@@ -11747,7 +12004,7 @@
       <c r="AA64" s="39">
         <v>400000</v>
       </c>
-      <c r="AB64" s="62" t="s">
+      <c r="AB64" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC64" s="4">
@@ -11837,7 +12094,7 @@
       <c r="AA65" s="39">
         <v>400000</v>
       </c>
-      <c r="AB65" s="62" t="s">
+      <c r="AB65" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC65" s="4">
@@ -11923,7 +12180,7 @@
       <c r="AA66" s="39">
         <v>400000</v>
       </c>
-      <c r="AB66" s="62" t="s">
+      <c r="AB66" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC66" s="4">
@@ -12009,7 +12266,7 @@
       <c r="AA67" s="39">
         <v>400000</v>
       </c>
-      <c r="AB67" s="62" t="s">
+      <c r="AB67" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC67" s="4">
@@ -12095,7 +12352,7 @@
       <c r="AA68" s="39">
         <v>400000</v>
       </c>
-      <c r="AB68" s="62" t="s">
+      <c r="AB68" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC68" s="4">
@@ -12181,7 +12438,7 @@
       <c r="AA69" s="39">
         <v>400000</v>
       </c>
-      <c r="AB69" s="62" t="s">
+      <c r="AB69" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC69" s="4">
@@ -12267,7 +12524,7 @@
       <c r="AA70" s="39">
         <v>400000</v>
       </c>
-      <c r="AB70" s="62" t="s">
+      <c r="AB70" s="63" t="s">
         <v>391</v>
       </c>
       <c r="AC70" s="4">
@@ -12357,7 +12614,7 @@
       <c r="AA71" s="39">
         <v>800000</v>
       </c>
-      <c r="AB71" s="62" t="s">
+      <c r="AB71" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC71" s="4">
@@ -12447,7 +12704,7 @@
       <c r="AA72" s="39">
         <v>800000</v>
       </c>
-      <c r="AB72" s="62" t="s">
+      <c r="AB72" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC72" s="4">
@@ -12537,7 +12794,7 @@
       <c r="AA73" s="39">
         <v>800000</v>
       </c>
-      <c r="AB73" s="62" t="s">
+      <c r="AB73" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC73" s="4">
@@ -12627,7 +12884,7 @@
       <c r="AA74" s="39">
         <v>800000</v>
       </c>
-      <c r="AB74" s="62" t="s">
+      <c r="AB74" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC74" s="4">
@@ -12717,7 +12974,7 @@
       <c r="AA75" s="39">
         <v>800000</v>
       </c>
-      <c r="AB75" s="62" t="s">
+      <c r="AB75" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC75" s="4">
@@ -12803,7 +13060,7 @@
       <c r="AA76" s="39">
         <v>800000</v>
       </c>
-      <c r="AB76" s="62" t="s">
+      <c r="AB76" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC76" s="4">
@@ -12889,7 +13146,7 @@
       <c r="AA77" s="39">
         <v>800000</v>
       </c>
-      <c r="AB77" s="62" t="s">
+      <c r="AB77" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC77" s="4">
@@ -12975,7 +13232,7 @@
       <c r="AA78" s="39">
         <v>800000</v>
       </c>
-      <c r="AB78" s="62" t="s">
+      <c r="AB78" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC78" s="4">
@@ -13061,7 +13318,7 @@
       <c r="AA79" s="39">
         <v>800000</v>
       </c>
-      <c r="AB79" s="62" t="s">
+      <c r="AB79" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC79" s="4">
@@ -13147,7 +13404,7 @@
       <c r="AA80" s="39">
         <v>800000</v>
       </c>
-      <c r="AB80" s="62" t="s">
+      <c r="AB80" s="63" t="s">
         <v>444</v>
       </c>
       <c r="AC80" s="4">
@@ -13237,7 +13494,7 @@
       <c r="AA81" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB81" s="62" t="s">
+      <c r="AB81" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC81" s="4">
@@ -13327,7 +13584,7 @@
       <c r="AA82" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB82" s="62" t="s">
+      <c r="AB82" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC82" s="4">
@@ -13417,7 +13674,7 @@
       <c r="AA83" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB83" s="62" t="s">
+      <c r="AB83" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC83" s="4">
@@ -13507,7 +13764,7 @@
       <c r="AA84" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB84" s="62" t="s">
+      <c r="AB84" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC84" s="4">
@@ -13597,7 +13854,7 @@
       <c r="AA85" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB85" s="62" t="s">
+      <c r="AB85" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC85" s="4">
@@ -13683,7 +13940,7 @@
       <c r="AA86" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB86" s="62" t="s">
+      <c r="AB86" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC86" s="4">
@@ -13769,7 +14026,7 @@
       <c r="AA87" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB87" s="62" t="s">
+      <c r="AB87" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC87" s="4">
@@ -13855,7 +14112,7 @@
       <c r="AA88" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB88" s="62" t="s">
+      <c r="AB88" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC88" s="4">
@@ -13941,7 +14198,7 @@
       <c r="AA89" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB89" s="62" t="s">
+      <c r="AB89" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC89" s="4">
@@ -14027,7 +14284,7 @@
       <c r="AA90" s="39">
         <v>2000000</v>
       </c>
-      <c r="AB90" s="62" t="s">
+      <c r="AB90" s="63" t="s">
         <v>495</v>
       </c>
       <c r="AC90" s="4">
@@ -14117,7 +14374,7 @@
       <c r="AA91" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB91" s="62" t="s">
+      <c r="AB91" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC91" s="4">
@@ -14207,7 +14464,7 @@
       <c r="AA92" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB92" s="62" t="s">
+      <c r="AB92" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC92" s="4">
@@ -14297,7 +14554,7 @@
       <c r="AA93" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB93" s="62" t="s">
+      <c r="AB93" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC93" s="4">
@@ -14387,7 +14644,7 @@
       <c r="AA94" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB94" s="62" t="s">
+      <c r="AB94" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC94" s="4">
@@ -14477,7 +14734,7 @@
       <c r="AA95" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB95" s="62" t="s">
+      <c r="AB95" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC95" s="4">
@@ -14563,7 +14820,7 @@
       <c r="AA96" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB96" s="62" t="s">
+      <c r="AB96" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC96" s="4">
@@ -14649,7 +14906,7 @@
       <c r="AA97" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB97" s="62" t="s">
+      <c r="AB97" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC97" s="4">
@@ -14735,7 +14992,7 @@
       <c r="AA98" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB98" s="62" t="s">
+      <c r="AB98" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC98" s="4">
@@ -14821,7 +15078,7 @@
       <c r="AA99" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB99" s="62" t="s">
+      <c r="AB99" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC99" s="4">
@@ -14907,7 +15164,7 @@
       <c r="AA100" s="39">
         <v>4000000</v>
       </c>
-      <c r="AB100" s="62" t="s">
+      <c r="AB100" s="63" t="s">
         <v>546</v>
       </c>
       <c r="AC100" s="4">
@@ -14997,7 +15254,7 @@
       <c r="AA101" s="39">
         <v>1000</v>
       </c>
-      <c r="AB101" s="62" t="s">
+      <c r="AB101" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC101" s="4">
@@ -15087,7 +15344,7 @@
       <c r="AA102" s="39">
         <v>1000</v>
       </c>
-      <c r="AB102" s="62" t="s">
+      <c r="AB102" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC102" s="4">
@@ -15177,7 +15434,7 @@
       <c r="AA103" s="39">
         <v>1000</v>
       </c>
-      <c r="AB103" s="62" t="s">
+      <c r="AB103" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC103" s="4">
@@ -15267,7 +15524,7 @@
       <c r="AA104" s="39">
         <v>1000</v>
       </c>
-      <c r="AB104" s="62" t="s">
+      <c r="AB104" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC104" s="4">
@@ -15354,7 +15611,7 @@
       <c r="AA105" s="39">
         <v>1000</v>
       </c>
-      <c r="AB105" s="62" t="s">
+      <c r="AB105" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC105" s="4">
@@ -15440,7 +15697,7 @@
       <c r="AA106" s="39">
         <v>1000</v>
       </c>
-      <c r="AB106" s="62" t="s">
+      <c r="AB106" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC106" s="4">
@@ -15526,7 +15783,7 @@
       <c r="AA107" s="39">
         <v>1000</v>
       </c>
-      <c r="AB107" s="62" t="s">
+      <c r="AB107" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC107" s="4">
@@ -15612,7 +15869,7 @@
       <c r="AA108" s="39">
         <v>1000</v>
       </c>
-      <c r="AB108" s="62" t="s">
+      <c r="AB108" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC108" s="4">
@@ -15698,7 +15955,7 @@
       <c r="AA109" s="39">
         <v>1000</v>
       </c>
-      <c r="AB109" s="62" t="s">
+      <c r="AB109" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC109" s="4">
@@ -15784,7 +16041,7 @@
       <c r="AA110" s="39">
         <v>1000</v>
       </c>
-      <c r="AB110" s="62" t="s">
+      <c r="AB110" s="63" t="s">
         <v>598</v>
       </c>
       <c r="AC110" s="4">
@@ -23762,33 +24019,815 @@
       </c>
     </row>
     <row r="328" spans="1:21">
+      <c r="A328" s="4">
+        <v>100060001</v>
+      </c>
+      <c r="B328" s="4">
+        <v>6</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G328" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I328" s="4" t="s">
+        <v>1115</v>
+      </c>
       <c r="N328" s="37"/>
-      <c r="O328" s="37"/>
+      <c r="O328" s="37">
+        <v>1</v>
+      </c>
       <c r="P328" s="37"/>
-      <c r="Q328" s="37"/>
+      <c r="Q328" t="b">
+        <v>0</v>
+      </c>
       <c r="R328" s="37"/>
+      <c r="S328" s="62">
+        <v>79001</v>
+      </c>
+      <c r="U328" s="4" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="329" spans="1:21">
+      <c r="A329" s="4">
+        <v>100060002</v>
+      </c>
+      <c r="B329" s="4">
+        <v>6</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G329" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I329" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O329" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q329" t="b">
+        <v>0</v>
+      </c>
+      <c r="S329" s="62">
+        <v>79002</v>
+      </c>
+      <c r="U329" s="4" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="330" spans="1:21">
+      <c r="A330" s="4">
+        <v>100060003</v>
+      </c>
+      <c r="B330" s="4">
+        <v>6</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G330" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I330" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O330" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q330" t="b">
+        <v>0</v>
+      </c>
+      <c r="S330" s="62">
+        <v>79003</v>
+      </c>
+      <c r="U330" s="4" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="331" spans="1:21">
+      <c r="A331" s="4">
+        <v>100060004</v>
+      </c>
+      <c r="B331" s="4">
+        <v>6</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="I331" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O331" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q331" t="b">
+        <v>0</v>
+      </c>
+      <c r="S331" s="62">
+        <v>79004</v>
+      </c>
+      <c r="U331" s="4" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="332" spans="1:21">
+      <c r="A332" s="4">
+        <v>100060005</v>
+      </c>
+      <c r="B332" s="4">
+        <v>6</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G332" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I332" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O332" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q332" t="b">
+        <v>0</v>
+      </c>
+      <c r="S332" s="62">
+        <v>79005</v>
+      </c>
+      <c r="U332" s="4" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="333" spans="1:21">
+      <c r="A333" s="4">
+        <v>100060006</v>
+      </c>
+      <c r="B333" s="4">
+        <v>6</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I333" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O333" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q333" t="b">
+        <v>0</v>
+      </c>
+      <c r="S333" s="62">
+        <v>79006</v>
+      </c>
+      <c r="U333" s="4" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="334" spans="1:21">
+      <c r="A334" s="4">
+        <v>100060007</v>
+      </c>
+      <c r="B334" s="4">
+        <v>6</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G334" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I334" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O334" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q334" t="b">
+        <v>0</v>
+      </c>
+      <c r="S334" s="62">
+        <v>79007</v>
+      </c>
+      <c r="U334" s="4" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="335" spans="1:21">
+      <c r="A335" s="4">
+        <v>100060008</v>
+      </c>
+      <c r="B335" s="4">
+        <v>6</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G335" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I335" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O335" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q335" t="b">
+        <v>0</v>
+      </c>
+      <c r="S335" s="62">
+        <v>79008</v>
+      </c>
+      <c r="U335" s="4" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="336" spans="1:21">
+      <c r="A336" s="4">
+        <v>100060009</v>
+      </c>
+      <c r="B336" s="4">
+        <v>6</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I336" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O336" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q336" t="b">
+        <v>0</v>
+      </c>
+      <c r="S336" s="62">
+        <v>79009</v>
+      </c>
+      <c r="U336" s="4" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="337" spans="1:21">
+      <c r="A337" s="4">
+        <v>100060010</v>
+      </c>
+      <c r="B337" s="4">
+        <v>6</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G337" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I337" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O337" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q337" t="b">
+        <v>0</v>
+      </c>
+      <c r="S337" s="62">
+        <v>79010</v>
+      </c>
+      <c r="U337" s="4" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="338" spans="1:21">
+      <c r="A338" s="4">
+        <v>100060011</v>
+      </c>
+      <c r="B338" s="4">
+        <v>6</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O338" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q338" t="b">
+        <v>0</v>
+      </c>
+      <c r="S338" s="62">
+        <v>79011</v>
+      </c>
+      <c r="U338" s="4" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="339" spans="1:21">
+      <c r="A339" s="4">
+        <v>100060012</v>
+      </c>
+      <c r="B339" s="4">
+        <v>6</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I339" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O339" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q339" t="b">
+        <v>0</v>
+      </c>
+      <c r="S339" s="62">
+        <v>79012</v>
+      </c>
+      <c r="U339" s="4" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="340" spans="1:21">
+      <c r="A340" s="4">
+        <v>100060013</v>
+      </c>
+      <c r="B340" s="4">
+        <v>6</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I340" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O340" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q340" t="b">
+        <v>0</v>
+      </c>
+      <c r="S340" s="62">
+        <v>79013</v>
+      </c>
+      <c r="U340" s="4" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="341" spans="1:21">
+      <c r="A341" s="4">
+        <v>100060014</v>
+      </c>
+      <c r="B341" s="4">
+        <v>6</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I341" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O341" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q341" t="b">
+        <v>0</v>
+      </c>
+      <c r="S341" s="62">
+        <v>79014</v>
+      </c>
+      <c r="U341" s="4" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="342" spans="1:21">
+      <c r="A342" s="4">
+        <v>100060015</v>
+      </c>
+      <c r="B342" s="4">
+        <v>6</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I342" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O342" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q342" t="b">
+        <v>0</v>
+      </c>
+      <c r="S342" s="62">
+        <v>79015</v>
+      </c>
+      <c r="U342" s="4" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="343" spans="1:21">
+      <c r="A343" s="4">
+        <v>100060016</v>
+      </c>
+      <c r="B343" s="4">
+        <v>6</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O343" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q343" t="b">
+        <v>0</v>
+      </c>
+      <c r="S343" s="62">
+        <v>79016</v>
+      </c>
+      <c r="U343" s="4" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="344" spans="1:21">
+      <c r="A344" s="4">
+        <v>100060017</v>
+      </c>
+      <c r="B344" s="4">
+        <v>6</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G344" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O344" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q344" t="b">
+        <v>0</v>
+      </c>
+      <c r="S344" s="62">
+        <v>79017</v>
+      </c>
+      <c r="U344" s="4" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="345" spans="1:21">
+      <c r="A345" s="4">
+        <v>100060018</v>
+      </c>
+      <c r="B345" s="4">
+        <v>6</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G345" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I345" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O345" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q345" t="b">
+        <v>0</v>
+      </c>
+      <c r="S345" s="62">
+        <v>79018</v>
+      </c>
+      <c r="U345" s="4" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="346" ht="17.25" spans="1:21">
+      <c r="A346" s="4">
+        <v>100060019</v>
+      </c>
+      <c r="B346" s="4">
+        <v>6</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G346" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I346" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O346" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q346" t="b">
+        <v>0</v>
+      </c>
+      <c r="S346" s="62">
+        <v>79019</v>
+      </c>
+      <c r="U346" s="4" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="347" ht="17.25" spans="1:21">
+      <c r="A347" s="4">
+        <v>100060020</v>
+      </c>
+      <c r="B347" s="4">
+        <v>6</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G347" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I347" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O347" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q347" t="b">
+        <v>0</v>
+      </c>
+      <c r="S347" s="62">
+        <v>79020</v>
+      </c>
+      <c r="U347" s="4" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="348" spans="1:21">
+      <c r="A348" s="4">
+        <v>100060021</v>
+      </c>
+      <c r="B348" s="4">
+        <v>6</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G348" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I348" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O348" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q348" t="b">
+        <v>0</v>
+      </c>
+      <c r="S348" s="62">
+        <v>79021</v>
+      </c>
+      <c r="U348" s="4" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="349" ht="17.25" spans="1:21">
+      <c r="A349" s="4">
+        <v>100060022</v>
+      </c>
+      <c r="B349" s="4">
+        <v>6</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G349" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O349" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q349" t="b">
+        <v>0</v>
+      </c>
+      <c r="S349" s="62">
+        <v>79022</v>
+      </c>
+      <c r="U349" s="4" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="350" ht="17.25" spans="1:21">
+      <c r="A350" s="4">
+        <v>100060023</v>
+      </c>
+      <c r="B350" s="4">
+        <v>6</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G350" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I350" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O350" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q350" t="b">
+        <v>0</v>
+      </c>
+      <c r="S350" s="62">
+        <v>79023</v>
+      </c>
+      <c r="U350" s="4" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="351" ht="17.25" spans="1:21">
+      <c r="A351" s="4">
+        <v>100060024</v>
+      </c>
+      <c r="B351" s="4">
+        <v>6</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G351" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I351" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O351" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q351" t="b">
+        <v>0</v>
+      </c>
+      <c r="S351" s="62">
+        <v>79024</v>
+      </c>
+      <c r="U351" s="4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="352" spans="1:21">
+      <c r="A352" s="4">
+        <v>100060025</v>
+      </c>
+      <c r="B352" s="4">
+        <v>6</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G352" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="O352" s="37">
+        <v>1</v>
+      </c>
+      <c r="Q352" t="b">
+        <v>0</v>
+      </c>
+      <c r="S352" s="62">
+        <v>79025</v>
+      </c>
+      <c r="U352" s="4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="353" spans="1:21">
+      <c r="A353" s="4">
+        <v>100060026</v>
+      </c>
+      <c r="B353" s="4">
+        <v>6</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G353" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="O353" s="49">
+        <v>2</v>
+      </c>
+      <c r="Q353" t="b">
+        <v>0</v>
+      </c>
+      <c r="S353" s="62">
+        <v>79026</v>
+      </c>
+      <c r="U353" s="4" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="354" spans="1:21">
+      <c r="A354" s="4">
+        <v>100060027</v>
+      </c>
+      <c r="B354" s="4">
+        <v>6</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G354" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="I354" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O354" s="49">
+        <v>3</v>
+      </c>
+      <c r="Q354" t="b">
+        <v>0</v>
+      </c>
+      <c r="S354" s="62">
+        <v>79027</v>
+      </c>
+      <c r="U354" s="4" t="s">
+        <v>1106</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A127:A252">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F111:F120">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121:F126">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F127:F252">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S127:S252">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F111:F120">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F121:F126">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F127:F252">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S127:S252">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="S328:S354">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A126 A253:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:S126 S253:S327 S355:S1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S126 S253:S1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -23821,16 +24860,16 @@
   <sheetData>
     <row r="5" spans="2:16">
       <c r="F5" s="18" t="s">
-        <v>1113</v>
+        <v>1167</v>
       </c>
       <c r="J5" s="19">
         <v>502</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>1114</v>
+        <v>1168</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>1115</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -23841,32 +24880,32 @@
         <v>17</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1117</v>
+        <v>1171</v>
       </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22" t="s">
-        <v>1118</v>
+        <v>1172</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>1119</v>
+        <v>1173</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>1120</v>
+        <v>1174</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>1121</v>
+        <v>1175</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>1122</v>
+        <v>1176</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -23874,37 +24913,37 @@
         <v>101</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1123</v>
+        <v>1177</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1124</v>
+        <v>1178</v>
       </c>
       <c r="F7" s="18">
         <v>100100</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>1126</v>
+        <v>1180</v>
       </c>
       <c r="J7" s="18">
         <v>2</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>1127</v>
+        <v>1181</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>1128</v>
+        <v>1182</v>
       </c>
       <c r="N7" s="18">
         <v>1022501</v>
       </c>
       <c r="O7" s="18" t="s">
-        <v>1129</v>
+        <v>1183</v>
       </c>
       <c r="P7" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -23912,37 +24951,37 @@
         <v>102</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>1131</v>
+        <v>1185</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>1124</v>
+        <v>1178</v>
       </c>
       <c r="F8" s="18">
         <v>100300</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>1132</v>
+        <v>1186</v>
       </c>
       <c r="J8" s="18">
         <v>3</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>1134</v>
+        <v>1188</v>
       </c>
       <c r="N8" s="18">
         <v>1022502</v>
       </c>
       <c r="O8" s="18" t="s">
-        <v>1135</v>
+        <v>1189</v>
       </c>
       <c r="P8" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="9" spans="2:16">
@@ -23950,37 +24989,37 @@
         <v>201</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>1136</v>
+        <v>1190</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1137</v>
+        <v>1191</v>
       </c>
       <c r="F9" s="18">
         <v>100700</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>1138</v>
+        <v>1192</v>
       </c>
       <c r="J9" s="18">
         <v>4</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>1139</v>
+        <v>1193</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>1140</v>
+        <v>1194</v>
       </c>
       <c r="N9" s="18">
         <v>1010301</v>
       </c>
       <c r="O9" s="18" t="s">
-        <v>1141</v>
+        <v>1195</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="10" spans="2:16">
@@ -23988,37 +25027,37 @@
         <v>202</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>1142</v>
+        <v>1196</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="F10" s="18">
         <v>101200</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>1144</v>
+        <v>1198</v>
       </c>
       <c r="J10" s="18">
         <v>5</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>1135</v>
+        <v>1189</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>1145</v>
+        <v>1199</v>
       </c>
       <c r="N10" s="18">
         <v>1010302</v>
       </c>
       <c r="O10" s="18" t="s">
-        <v>1146</v>
+        <v>1200</v>
       </c>
       <c r="P10" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="11" spans="2:16">
@@ -24026,37 +25065,37 @@
         <v>203</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>1147</v>
+        <v>1201</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1137</v>
+        <v>1191</v>
       </c>
       <c r="F11" s="18">
         <v>101400</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>1148</v>
+        <v>1202</v>
       </c>
       <c r="J11" s="18">
         <v>6</v>
       </c>
       <c r="K11" s="18" t="s">
-        <v>1149</v>
+        <v>1203</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>1150</v>
+        <v>1204</v>
       </c>
       <c r="N11" s="18">
         <v>1010303</v>
       </c>
       <c r="O11" s="18" t="s">
-        <v>1151</v>
+        <v>1205</v>
       </c>
       <c r="P11" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="12" spans="2:16">
@@ -24064,37 +25103,37 @@
         <v>204</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>1152</v>
+        <v>1206</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="F12" s="18">
         <v>200100</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>1153</v>
+        <v>1207</v>
       </c>
       <c r="J12" s="25">
         <v>12</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>1154</v>
+        <v>1208</v>
       </c>
       <c r="L12" s="25" t="s">
-        <v>1155</v>
+        <v>1209</v>
       </c>
       <c r="N12" s="18">
         <v>1010311</v>
       </c>
       <c r="O12" s="18" t="s">
-        <v>1156</v>
+        <v>1210</v>
       </c>
       <c r="P12" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -24102,19 +25141,19 @@
         <v>301</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>1157</v>
+        <v>1211</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>1158</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="18">
         <v>200101</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>1159</v>
+        <v>1213</v>
       </c>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -24123,10 +25162,10 @@
         <v>1010312</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>1160</v>
+        <v>1214</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -24134,19 +25173,19 @@
         <v>302</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>1161</v>
+        <v>1215</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>1162</v>
+        <v>1216</v>
       </c>
       <c r="F14" s="18">
         <v>200300</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>1163</v>
+        <v>1217</v>
       </c>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -24155,10 +25194,10 @@
         <v>1010313</v>
       </c>
       <c r="O14" s="18" t="s">
-        <v>1164</v>
+        <v>1218</v>
       </c>
       <c r="P14" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -24166,28 +25205,28 @@
         <v>303</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>1165</v>
+        <v>1219</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>1158</v>
+        <v>1212</v>
       </c>
       <c r="F15" s="18">
         <v>200400</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>1166</v>
+        <v>1220</v>
       </c>
       <c r="N15" s="18">
         <v>1010314</v>
       </c>
       <c r="O15" s="18" t="s">
-        <v>1167</v>
+        <v>1221</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -24195,28 +25234,28 @@
         <v>304</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>1168</v>
+        <v>1222</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>1162</v>
+        <v>1216</v>
       </c>
       <c r="F16" s="18">
         <v>200500</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>1169</v>
+        <v>1223</v>
       </c>
       <c r="N16" s="18">
         <v>1010315</v>
       </c>
       <c r="O16" s="18" t="s">
-        <v>1170</v>
+        <v>1224</v>
       </c>
       <c r="P16" s="18" t="s">
-        <v>1130</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -24224,19 +25263,19 @@
         <v>401</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1171</v>
+        <v>1225</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1137</v>
+        <v>1191</v>
       </c>
       <c r="F17" s="18">
         <v>200600</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>1172</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -24244,19 +25283,19 @@
         <v>402</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>1173</v>
+        <v>1227</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1143</v>
+        <v>1197</v>
       </c>
       <c r="F18" s="18">
         <v>200700</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>1174</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -24264,22 +25303,22 @@
         <v>501</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1175</v>
+        <v>1229</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>1176</v>
+        <v>1230</v>
       </c>
       <c r="F19" s="18">
         <v>200800</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>1177</v>
+        <v>1231</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>1178</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="20" spans="2:16">
@@ -24287,28 +25326,28 @@
         <v>502</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>1179</v>
+        <v>1233</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>1180</v>
+        <v>1234</v>
       </c>
       <c r="F20" s="18">
         <v>200900</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>1181</v>
+        <v>1235</v>
       </c>
       <c r="N20" s="24" t="s">
-        <v>1121</v>
+        <v>1175</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>1122</v>
+        <v>1176</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -24316,28 +25355,28 @@
         <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>1182</v>
+        <v>1236</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>1183</v>
+        <v>1237</v>
       </c>
       <c r="F21" s="18">
         <v>201000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>1184</v>
+        <v>1238</v>
       </c>
       <c r="N21" s="18">
         <v>1022501</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>1129</v>
+        <v>1183</v>
       </c>
       <c r="P21" s="18" t="s">
-        <v>1185</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -24345,28 +25384,28 @@
         <v>602</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>1186</v>
+        <v>1240</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>1187</v>
+        <v>1241</v>
       </c>
       <c r="F22" s="18">
         <v>300100</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>1188</v>
+        <v>1242</v>
       </c>
       <c r="N22" s="18">
         <v>1022502</v>
       </c>
       <c r="O22" s="18" t="s">
-        <v>1135</v>
+        <v>1189</v>
       </c>
       <c r="P22" s="18" t="s">
-        <v>1189</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -24374,19 +25413,19 @@
         <v>300200</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1125</v>
+        <v>1179</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>1190</v>
+        <v>1244</v>
       </c>
       <c r="N23" s="18">
         <v>1980000</v>
       </c>
       <c r="O23" s="18" t="s">
-        <v>1191</v>
+        <v>1245</v>
       </c>
       <c r="P23" s="18" t="s">
-        <v>1192</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="24" spans="2:16">
@@ -24394,10 +25433,10 @@
         <v>200100</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>1194</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="25" spans="2:16">
@@ -24405,10 +25444,10 @@
         <v>200101</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>1195</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="26" spans="2:16">
@@ -24416,10 +25455,10 @@
         <v>200300</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>1196</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="27" spans="2:16">
@@ -24427,10 +25466,10 @@
         <v>200400</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>1197</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="28" spans="2:16">
@@ -24438,10 +25477,10 @@
         <v>200500</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>1198</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -24449,10 +25488,10 @@
         <v>200600</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>1199</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -24460,10 +25499,10 @@
         <v>200700</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>1200</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -24471,10 +25510,10 @@
         <v>200800</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>1201</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -24482,10 +25521,10 @@
         <v>200900</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>1202</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -24493,10 +25532,10 @@
         <v>300200</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1193</v>
+        <v>1247</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>1203</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:22">
@@ -24538,19 +25577,19 @@
         <v>19</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>1204</v>
+        <v>1258</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>1205</v>
+        <v>1259</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>1206</v>
+        <v>1260</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>1207</v>
+        <v>1261</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>1208</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:22">
@@ -24565,10 +25604,10 @@
       </c>
       <c r="D39" s="28"/>
       <c r="E39" s="28" t="s">
-        <v>1209</v>
+        <v>1263</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>1209</v>
+        <v>1263</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>21</v>
@@ -24654,7 +25693,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>1210</v>
+        <v>1264</v>
       </c>
       <c r="F42" s="12"/>
       <c r="G42" s="13">
@@ -24667,23 +25706,23 @@
         <v>3002</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>1211</v>
+        <v>1265</v>
       </c>
       <c r="K42" s="8"/>
       <c r="L42" s="8">
         <v>70008</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>1212</v>
+        <v>1266</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="O42" s="4">
         <v>10</v>
       </c>
       <c r="P42" t="s">
-        <v>1129</v>
+        <v>1183</v>
       </c>
       <c r="Q42">
         <v>0.25</v>
@@ -24719,7 +25758,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>1213</v>
+        <v>1267</v>
       </c>
       <c r="F43" s="12"/>
       <c r="G43" s="13">
@@ -24732,23 +25771,23 @@
         <v>3002</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>1211</v>
+        <v>1265</v>
       </c>
       <c r="K43" s="8"/>
       <c r="L43" s="8" t="s">
-        <v>1214</v>
+        <v>1268</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>1215</v>
+        <v>1269</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="O43" s="4">
         <v>30</v>
       </c>
       <c r="P43" t="s">
-        <v>1129</v>
+        <v>1183</v>
       </c>
       <c r="Q43">
         <v>0.25</v>
@@ -24784,7 +25823,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>1216</v>
+        <v>1270</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="13">
@@ -24797,23 +25836,23 @@
         <v>3002</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>1211</v>
+        <v>1265</v>
       </c>
       <c r="K44" s="8"/>
       <c r="L44" s="8" t="s">
-        <v>1217</v>
+        <v>1271</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>1218</v>
+        <v>1272</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="O44" s="4">
         <v>100</v>
       </c>
       <c r="P44" t="s">
-        <v>1129</v>
+        <v>1183</v>
       </c>
       <c r="Q44">
         <v>0.25</v>
@@ -24848,7 +25887,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>1219</v>
+        <v>1273</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="13">
@@ -24861,17 +25900,17 @@
         <v>2003</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="K45" s="8"/>
       <c r="L45" s="8" t="s">
-        <v>1221</v>
+        <v>1275</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>1222</v>
+        <v>1276</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="O45" s="4">
         <v>2</v>
@@ -24910,7 +25949,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1224</v>
+        <v>1278</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="13">
@@ -24923,17 +25962,17 @@
         <v>2003</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="K46" s="8"/>
       <c r="L46" s="8" t="s">
-        <v>1225</v>
+        <v>1279</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>1226</v>
+        <v>1280</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="O46" s="4">
         <v>1</v>
@@ -24972,7 +26011,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1227</v>
+        <v>1281</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="13">
@@ -24985,17 +26024,17 @@
         <v>2003</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8" t="s">
-        <v>1228</v>
+        <v>1282</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>1229</v>
+        <v>1283</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -25034,7 +26073,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1230</v>
+        <v>1284</v>
       </c>
       <c r="F48" s="12"/>
       <c r="G48" s="13">
@@ -25047,17 +26086,17 @@
         <v>2003</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="K48" s="8"/>
       <c r="L48" s="8" t="s">
-        <v>1231</v>
+        <v>1285</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="O48" s="4">
         <v>1</v>
@@ -25082,16 +26121,16 @@
     </row>
     <row r="54" spans="4:14">
       <c r="D54" s="18" t="s">
-        <v>1233</v>
+        <v>1287</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>1234</v>
+        <v>1288</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>1235</v>
+        <v>1289</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>1236</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="55" spans="4:14">
@@ -27199,7 +28238,7 @@
         <v>70001</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1222</v>
+        <v>1276</v>
       </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
@@ -27209,7 +28248,7 @@
         <v>70002</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1237</v>
+        <v>1291</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9"/>
@@ -27219,7 +28258,7 @@
         <v>70003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1238</v>
+        <v>1292</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -27229,7 +28268,7 @@
         <v>70004</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1239</v>
+        <v>1293</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -27239,10 +28278,10 @@
         <v>70005</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1240</v>
+        <v>1294</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L5" s="10" t="e">
         <f>_xlfn.XLOOKUP(K5,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27254,10 +28293,10 @@
         <v>70006</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1242</v>
+        <v>1296</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L6" s="10" t="e">
         <f>_xlfn.XLOOKUP(K6,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27269,10 +28308,10 @@
         <v>70007</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1243</v>
+        <v>1297</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L7" s="10" t="e">
         <f>_xlfn.XLOOKUP(K7,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27284,10 +28323,10 @@
         <v>70008</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1212</v>
+        <v>1266</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L8" s="10" t="e">
         <f>_xlfn.XLOOKUP(K8,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27299,10 +28338,10 @@
         <v>70009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1244</v>
+        <v>1298</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L9" s="10" t="e">
         <f>_xlfn.XLOOKUP(K9,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27314,10 +28353,10 @@
         <v>70010</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1245</v>
+        <v>1299</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L10" s="10" t="e">
         <f>_xlfn.XLOOKUP(K10,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27329,10 +28368,10 @@
         <v>70101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1246</v>
+        <v>1300</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>1241</v>
+        <v>1295</v>
       </c>
       <c r="L11" s="10" t="e">
         <f>_xlfn.XLOOKUP(K11,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27344,10 +28383,10 @@
         <v>70102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1247</v>
+        <v>1301</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="L12" s="10" t="e">
         <f>_xlfn.XLOOKUP(K12,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27359,10 +28398,10 @@
         <v>70103</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1249</v>
+        <v>1303</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="L13" s="10" t="e">
         <f>_xlfn.XLOOKUP(K13,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27374,7 +28413,7 @@
         <v>70104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1250</v>
+        <v>1304</v>
       </c>
       <c r="K14" s="10" t="s">
         <v>88</v>
@@ -27389,7 +28428,7 @@
         <v>70301</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1251</v>
+        <v>1305</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>99</v>
@@ -27404,10 +28443,10 @@
         <v>70302</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1252</v>
+        <v>1306</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="L16" s="10" t="e">
         <f>_xlfn.XLOOKUP(K16,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27419,7 +28458,7 @@
         <v>70303</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1253</v>
+        <v>1307</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>99</v>
@@ -27434,7 +28473,7 @@
         <v>70304</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1254</v>
+        <v>1308</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>99</v>
@@ -27449,7 +28488,7 @@
         <v>70305</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1255</v>
+        <v>1309</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>99</v>
@@ -27464,7 +28503,7 @@
         <v>70306</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1256</v>
+        <v>1310</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>88</v>
@@ -27479,7 +28518,7 @@
         <v>70307</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1257</v>
+        <v>1311</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>88</v>
@@ -27494,7 +28533,7 @@
         <v>70308</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1258</v>
+        <v>1312</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>88</v>
@@ -27509,7 +28548,7 @@
         <v>70309</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1259</v>
+        <v>1313</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>108</v>
@@ -27524,7 +28563,7 @@
         <v>70310</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1260</v>
+        <v>1314</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>108</v>
@@ -27539,7 +28578,7 @@
         <v>70311</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1261</v>
+        <v>1315</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>108</v>
@@ -27554,7 +28593,7 @@
         <v>70312</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1262</v>
+        <v>1316</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>117</v>
@@ -27569,7 +28608,7 @@
         <v>70381</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1263</v>
+        <v>1317</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>117</v>
@@ -27584,7 +28623,7 @@
         <v>70382</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1264</v>
+        <v>1318</v>
       </c>
       <c r="K28" s="10" t="s">
         <v>117</v>
@@ -27599,7 +28638,7 @@
         <v>70383</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1265</v>
+        <v>1319</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>108</v>
@@ -27614,7 +28653,7 @@
         <v>70391</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1266</v>
+        <v>1320</v>
       </c>
       <c r="K30" s="10" t="s">
         <v>108</v>
@@ -27629,7 +28668,7 @@
         <v>70392</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1267</v>
+        <v>1321</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>108</v>
@@ -27644,7 +28683,7 @@
         <v>70393</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1268</v>
+        <v>1322</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>108</v>
@@ -27659,10 +28698,10 @@
         <v>71101</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1226</v>
+        <v>1280</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>1269</v>
+        <v>1323</v>
       </c>
       <c r="L33" s="10" t="e">
         <f>_xlfn.XLOOKUP(K33,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27674,10 +28713,10 @@
         <v>71102</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1229</v>
+        <v>1283</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>1269</v>
+        <v>1323</v>
       </c>
       <c r="L34" s="10" t="e">
         <f>_xlfn.XLOOKUP(K34,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27689,10 +28728,10 @@
         <v>71103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1232</v>
+        <v>1286</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>1269</v>
+        <v>1323</v>
       </c>
       <c r="L35" s="10" t="e">
         <f>_xlfn.XLOOKUP(K35,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27704,10 +28743,10 @@
         <v>71201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1270</v>
+        <v>1324</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>1269</v>
+        <v>1323</v>
       </c>
       <c r="L36" s="10" t="e">
         <f>_xlfn.XLOOKUP(K36,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27719,10 +28758,10 @@
         <v>71202</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1271</v>
+        <v>1325</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="L37" s="10" t="e">
         <f>_xlfn.XLOOKUP(K37,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27734,10 +28773,10 @@
         <v>72011</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1272</v>
+        <v>1326</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="L38" s="10" t="e">
         <f>_xlfn.XLOOKUP(K38,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27749,10 +28788,10 @@
         <v>72012</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1273</v>
+        <v>1327</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="L39" s="10" t="e">
         <f>_xlfn.XLOOKUP(K39,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27764,10 +28803,10 @@
         <v>72101</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1215</v>
+        <v>1269</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="L40" s="10" t="e">
         <f>_xlfn.XLOOKUP(K40,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
@@ -27779,7 +28818,7 @@
         <v>72102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1218</v>
+        <v>1272</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>99</v>
@@ -27910,7 +28949,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1274</v>
+        <v>1328</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" s="13">
@@ -27923,17 +28962,17 @@
         <v>2001</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>1275</v>
+        <v>1329</v>
       </c>
       <c r="K59" s="8"/>
       <c r="L59" s="8">
         <v>70007</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>1243</v>
+        <v>1297</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>1276</v>
+        <v>1330</v>
       </c>
       <c r="O59" s="3">
         <v>1000</v>
@@ -27969,7 +29008,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>1277</v>
+        <v>1331</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" s="13">
@@ -27982,17 +29021,17 @@
         <v>2001</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>1275</v>
+        <v>1329</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8" t="s">
-        <v>1278</v>
+        <v>1332</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>1263</v>
+        <v>1317</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>1276</v>
+        <v>1330</v>
       </c>
       <c r="O60" s="3">
         <v>7000</v>
@@ -28030,7 +29069,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>1279</v>
+        <v>1333</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13">
@@ -28043,17 +29082,17 @@
         <v>2001</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>1275</v>
+        <v>1329</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8" t="s">
-        <v>1280</v>
+        <v>1334</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>1264</v>
+        <v>1318</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>1276</v>
+        <v>1330</v>
       </c>
       <c r="O61" s="3">
         <v>70000</v>
@@ -28091,7 +29130,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>1281</v>
+        <v>1335</v>
       </c>
       <c r="F62" s="12"/>
       <c r="G62" s="13">
@@ -28104,17 +29143,17 @@
         <v>2001</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>1275</v>
+        <v>1329</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8" t="s">
-        <v>1282</v>
+        <v>1336</v>
       </c>
       <c r="M62" s="4" t="s">
-        <v>1265</v>
+        <v>1319</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>1276</v>
+        <v>1330</v>
       </c>
       <c r="O62" s="3">
         <v>700000</v>
@@ -28151,7 +29190,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>1274</v>
+        <v>1328</v>
       </c>
       <c r="F63" s="14"/>
       <c r="G63" s="15">
@@ -28164,16 +29203,16 @@
         <v>2002</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>1275</v>
+        <v>1329</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L63" s="16">
         <v>70007</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>1243</v>
+        <v>1297</v>
       </c>
       <c r="P63" s="4"/>
     </row>
@@ -28192,7 +29231,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>1284</v>
+        <v>1338</v>
       </c>
       <c r="F65" s="14"/>
       <c r="G65" s="15">
@@ -28205,16 +29244,16 @@
         <v>1001</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>1285</v>
+        <v>1339</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>1286</v>
+        <v>1340</v>
       </c>
       <c r="L65" s="16">
         <v>70001</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>1222</v>
+        <v>1276</v>
       </c>
       <c r="V65" s="4">
         <f>ROUND(MAX(S65/100,T65/100,U65),0)</f>
@@ -28236,7 +29275,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>1287</v>
+        <v>1341</v>
       </c>
       <c r="F66" s="14"/>
       <c r="G66" s="15">
@@ -28249,16 +29288,16 @@
         <v>2001</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>1285</v>
+        <v>1339</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L66" s="16">
         <v>70002</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>1288</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="67" s="4" customFormat="1" spans="1:22">
@@ -28276,7 +29315,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>1289</v>
+        <v>1343</v>
       </c>
       <c r="F67" s="14"/>
       <c r="G67" s="15">
@@ -28289,16 +29328,16 @@
         <v>2002</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>1290</v>
+        <v>1344</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L67" s="16">
         <v>70003</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>1238</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="68" s="4" customFormat="1" spans="1:22">
@@ -28316,7 +29355,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>1291</v>
+        <v>1345</v>
       </c>
       <c r="F68" s="14"/>
       <c r="G68" s="15">
@@ -28329,16 +29368,16 @@
         <v>2003</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>1292</v>
+        <v>1346</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L68" s="16">
         <v>70004</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>1239</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="69" s="4" customFormat="1" spans="1:22">
@@ -28356,7 +29395,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>1293</v>
+        <v>1347</v>
       </c>
       <c r="F69" s="14"/>
       <c r="G69" s="15">
@@ -28369,16 +29408,16 @@
         <v>1001</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>1290</v>
+        <v>1344</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L69" s="16">
         <v>70005</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>1240</v>
+        <v>1294</v>
       </c>
       <c r="N69" s="17"/>
     </row>
@@ -28410,16 +29449,16 @@
         <v>2001</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>1292</v>
+        <v>1346</v>
       </c>
       <c r="K70" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L70" s="16">
         <v>70006</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>1294</v>
+        <v>1348</v>
       </c>
       <c r="N70" s="17"/>
     </row>
@@ -28438,7 +29477,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>1210</v>
+        <v>1264</v>
       </c>
       <c r="F71" s="14"/>
       <c r="G71" s="15">
@@ -28451,16 +29490,16 @@
         <v>2003</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>1295</v>
+        <v>1349</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L71" s="16">
         <v>70008</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>1212</v>
+        <v>1266</v>
       </c>
       <c r="N71" s="17"/>
     </row>
@@ -28479,7 +29518,7 @@
         <v>1</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>1296</v>
+        <v>1350</v>
       </c>
       <c r="F72" s="14"/>
       <c r="G72" s="15">
@@ -28492,16 +29531,16 @@
         <v>1001</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>1297</v>
+        <v>1351</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L72" s="16">
         <v>70009</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>1244</v>
+        <v>1298</v>
       </c>
       <c r="N72" s="17"/>
     </row>
@@ -28520,7 +29559,7 @@
         <v>1</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>1298</v>
+        <v>1352</v>
       </c>
       <c r="F73" s="14"/>
       <c r="G73" s="15">
@@ -28533,16 +29572,16 @@
         <v>2001</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>1297</v>
+        <v>1351</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>1283</v>
+        <v>1337</v>
       </c>
       <c r="L73" s="16">
         <v>70010</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>1299</v>
+        <v>1353</v>
       </c>
     </row>
   </sheetData>
@@ -28572,18 +29611,18 @@
         <v>27</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1300</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>1248</v>
+        <v>1302</v>
       </c>
       <c r="B2" s="1">
         <v>100100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1301</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -28687,145 +29726,145 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>1302</v>
+        <v>1356</v>
       </c>
       <c r="B12" s="1">
         <v>102500</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1303</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>1304</v>
+        <v>1358</v>
       </c>
       <c r="B13" s="1">
         <v>200100</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1305</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>1306</v>
+        <v>1360</v>
       </c>
       <c r="B14" s="1">
         <v>200101</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1307</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>1308</v>
+        <v>1362</v>
       </c>
       <c r="B15" s="1">
         <v>200300</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1309</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>1310</v>
+        <v>1364</v>
       </c>
       <c r="B16" s="1">
         <v>200400</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1311</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>1312</v>
+        <v>1366</v>
       </c>
       <c r="B17" s="1">
         <v>200500</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1313</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>1314</v>
+        <v>1368</v>
       </c>
       <c r="B18" s="1">
         <v>200600</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1315</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>1316</v>
+        <v>1370</v>
       </c>
       <c r="B19" s="1">
         <v>200700</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1317</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>1318</v>
+        <v>1372</v>
       </c>
       <c r="B20" s="1">
         <v>200800</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1319</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>1320</v>
+        <v>1374</v>
       </c>
       <c r="B21" s="1">
         <v>200900</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1321</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>1322</v>
+        <v>1376</v>
       </c>
       <c r="B22" s="1">
         <v>300100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1323</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>1324</v>
+        <v>1378</v>
       </c>
       <c r="B23" s="1">
         <v>300200</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1325</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>1223</v>
+        <v>1277</v>
       </c>
       <c r="B24" s="1">
         <v>500000</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1220</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -28841,29 +29880,29 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>1326</v>
+        <v>1380</v>
       </c>
       <c r="B26" s="1">
         <v>500002</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1327</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>1328</v>
+        <v>1382</v>
       </c>
       <c r="B27" s="1">
         <v>500003</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1329</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>1330</v>
+        <v>1384</v>
       </c>
       <c r="B28" s="1">
         <v>500004</v>
@@ -28874,13 +29913,13 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>1331</v>
+        <v>1385</v>
       </c>
       <c r="B29" s="1">
         <v>500005</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1332</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -28907,46 +29946,46 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>1133</v>
+        <v>1187</v>
       </c>
       <c r="B32" s="1">
         <v>600000</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1211</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>1139</v>
+        <v>1193</v>
       </c>
       <c r="B33" s="1">
         <v>600001</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1333</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>1334</v>
+        <v>1388</v>
       </c>
       <c r="B34" s="1">
         <v>600002</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1335</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>1135</v>
+        <v>1189</v>
       </c>
       <c r="B35" s="1">
         <v>600003</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1336</v>
+        <v>1390</v>
       </c>
     </row>
   </sheetData>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -16193,7 +16193,9 @@
       </c>
       <c r="J111" s="12"/>
       <c r="K111" s="13"/>
-      <c r="L111" s="10"/>
+      <c r="L111" s="10">
+        <v>11003</v>
+      </c>
       <c r="M111" s="10" t="s">
         <v>177</v>
       </c>
@@ -16237,7 +16239,9 @@
       </c>
       <c r="J112" s="12"/>
       <c r="K112" s="13"/>
-      <c r="L112" s="10"/>
+      <c r="L112" s="10">
+        <v>11003</v>
+      </c>
       <c r="M112" s="10" t="s">
         <v>177</v>
       </c>
@@ -16327,7 +16331,9 @@
       </c>
       <c r="J114" s="12"/>
       <c r="K114" s="13"/>
-      <c r="L114" s="10"/>
+      <c r="L114" s="10">
+        <v>11012</v>
+      </c>
       <c r="M114" s="10" t="s">
         <v>177</v>
       </c>
@@ -16371,7 +16377,9 @@
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="13"/>
-      <c r="L115" s="10"/>
+      <c r="L115" s="10">
+        <v>11012</v>
+      </c>
       <c r="M115" s="10" t="s">
         <v>177</v>
       </c>
@@ -16415,7 +16423,9 @@
       </c>
       <c r="J116" s="12"/>
       <c r="K116" s="13"/>
-      <c r="L116" s="10"/>
+      <c r="L116" s="10">
+        <v>11012</v>
+      </c>
       <c r="M116" s="10" t="s">
         <v>177</v>
       </c>
@@ -16461,7 +16471,9 @@
       </c>
       <c r="J117" s="12"/>
       <c r="K117" s="13"/>
-      <c r="L117" s="10"/>
+      <c r="L117" s="10">
+        <v>11012</v>
+      </c>
       <c r="M117" s="10" t="s">
         <v>177</v>
       </c>
@@ -16505,7 +16517,9 @@
       </c>
       <c r="J118" s="12"/>
       <c r="K118" s="13"/>
-      <c r="L118" s="10"/>
+      <c r="L118" s="10">
+        <v>11012</v>
+      </c>
       <c r="M118" s="10" t="s">
         <v>177</v>
       </c>
@@ -16549,7 +16563,9 @@
       </c>
       <c r="J119" s="12"/>
       <c r="K119" s="13"/>
-      <c r="L119" s="10"/>
+      <c r="L119" s="10">
+        <v>11012</v>
+      </c>
       <c r="M119" s="10" t="s">
         <v>177</v>
       </c>
@@ -16593,7 +16609,9 @@
       </c>
       <c r="J120" s="12"/>
       <c r="K120" s="13"/>
-      <c r="L120" s="10"/>
+      <c r="L120" s="10">
+        <v>11012</v>
+      </c>
       <c r="M120" s="10" t="s">
         <v>177</v>
       </c>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2461,7 +2461,7 @@
     <t>No jogo [any game], foram acumuladas 1,000  rodadas.</t>
   </si>
   <si>
-    <t>12001_101700_1_1000</t>
+    <t>12001_101700_1000</t>
   </si>
   <si>
     <t>在[圣诞狂欢夜]電子遊戲中，累積旋轉 1,000 次</t>
@@ -2476,7 +2476,7 @@
     <t>No jogo [Christmas Eve Party ], foram acumuladas 1,000  rodadas.</t>
   </si>
   <si>
-    <t>12001_102100_1_1000</t>
+    <t>12001_102100_1000</t>
   </si>
   <si>
     <t>在[杰克船长]電子遊戲中，累積旋轉 1,000 次</t>
@@ -2491,7 +2491,7 @@
     <t>No jogo [Captain Jack], foram acumuladas 1,000  rodadas.</t>
   </si>
   <si>
-    <t>12001_102200_1_1000</t>
+    <t>12001_102200_1000</t>
   </si>
   <si>
     <t>在[雷神]電子遊戲中，累積旋轉 1,000 次</t>
@@ -2506,7 +2506,7 @@
     <t>No jogo [Thor], foram acumuladas 1,000  rodadas.</t>
   </si>
   <si>
-    <t>12001_102300_1_1000</t>
+    <t>12001_102300_1000</t>
   </si>
   <si>
     <t>在[蒸汽时代]電子遊戲中，累積旋轉 1,000 次</t>
@@ -2521,7 +2521,7 @@
     <t>No jogo [Steam Era], foram acumuladas 1,000  rodadas.</t>
   </si>
   <si>
-    <t>12001_102400_1_1000</t>
+    <t>12001_102400_1000</t>
   </si>
   <si>
     <t>在[财富银行]電子遊戲中，累積旋轉 1,000 次</t>
@@ -6186,14 +6186,29 @@
             <v>跳转ID</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="F1" t="str">
+            <v>打开界面需要导入的脚本</v>
+          </cell>
+        </row>
         <row r="2">
           <cell r="A2" t="str">
             <v>int</v>
           </cell>
         </row>
+        <row r="2">
+          <cell r="F2" t="str">
+            <v>string</v>
+          </cell>
+        </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>id</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="F3" t="str">
+            <v>jumpRequire</v>
           </cell>
         </row>
         <row r="5">
@@ -6399,6 +6414,76 @@
         <row r="45">
           <cell r="A45">
             <v>3007</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>3011</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46" t="str">
+            <v>PlatformHall/UIHall/MVCHead</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>3012</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47" t="str">
+            <v>PlatformHall/UIHall/MVCHead</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>3013</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48" t="str">
+            <v>PlatformHall/UIFriends/MVCHead</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>3014</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="F49" t="str">
+            <v>PlatformHall/Alliance/MVCHead</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>3015</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="F50" t="str">
+            <v>PlatformHall/UISeason/MVCHead</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>3016</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="F51" t="str">
+            <v>PlatformHall/UIActivities/UISignIn/MVCHead</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>3017</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="F52" t="str">
+            <v>PlatformHall/SimulationGame/MVCHead</v>
           </cell>
         </row>
       </sheetData>
@@ -30872,72 +30957,72 @@
     </row>
     <row r="46" spans="1:12">
       <c r="K46" s="11"/>
-      <c r="L46" s="10" t="str">
+      <c r="L46" s="10">
         <f>_xlfn.XLOOKUP(K46,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="K47" s="11"/>
-      <c r="L47" s="10" t="str">
+      <c r="L47" s="10">
         <f>_xlfn.XLOOKUP(K47,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="K48" s="11"/>
-      <c r="L48" s="10" t="str">
+      <c r="L48" s="10">
         <f>_xlfn.XLOOKUP(K48,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:22">
       <c r="K49" s="11"/>
-      <c r="L49" s="10" t="str">
+      <c r="L49" s="10">
         <f>_xlfn.XLOOKUP(K49,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="K50" s="11"/>
-      <c r="L50" s="10" t="str">
+      <c r="L50" s="10">
         <f>_xlfn.XLOOKUP(K50,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:22">
       <c r="K51" s="11"/>
-      <c r="L51" s="10" t="str">
+      <c r="L51" s="10">
         <f>_xlfn.XLOOKUP(K51,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="K52" s="11"/>
-      <c r="L52" s="10" t="str">
+      <c r="L52" s="10">
         <f>_xlfn.XLOOKUP(K52,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:22">
       <c r="K53" s="11"/>
-      <c r="L53" s="10" t="str">
+      <c r="L53" s="10">
         <f>_xlfn.XLOOKUP(K53,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="K54" s="11"/>
-      <c r="L54" s="10" t="str">
+      <c r="L54" s="10">
         <f>_xlfn.XLOOKUP(K54,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:22">
       <c r="K55" s="11"/>
-      <c r="L55" s="10" t="str">
+      <c r="L55" s="10">
         <f>_xlfn.XLOOKUP(K55,[1]jumpData!$F:$F,[1]jumpData!$A:$A)</f>
-        <v>跳转ID</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" spans="1:22">

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -3274,7 +3274,7 @@
     <t>12501_100300_120_2_2</t>
   </si>
   <si>
-    <t>1990000_100</t>
+    <t>1024013_1|1024014_1</t>
   </si>
   <si>
     <t>在[超级明星]游戏中120次旋转内中2次樱桃符号</t>
@@ -3283,7 +3283,7 @@
     <t>12501_100300_240_2_5</t>
   </si>
   <si>
-    <t>1990000_200</t>
+    <t>1024013_2|1024014_2</t>
   </si>
   <si>
     <t>在[超级明星]游戏中240次旋转内中5次樱桃符号</t>
@@ -3292,7 +3292,7 @@
     <t>12501_100300_360_2_10</t>
   </si>
   <si>
-    <t>1990000_300</t>
+    <t>1024013_3|1024014_3</t>
   </si>
   <si>
     <t>在[超级明星]游戏中360次旋转内中10次樱桃符号</t>
@@ -21708,7 +21708,7 @@
         <v>973</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="N231" s="37"/>
       <c r="O231" s="37">
@@ -21744,7 +21744,7 @@
         <v>975</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="N232" s="37"/>
       <c r="O232" s="37">
@@ -21780,7 +21780,7 @@
         <v>977</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="N233" s="37"/>
       <c r="O233" s="37">
@@ -21852,7 +21852,7 @@
         <v>981</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="N235" s="37"/>
       <c r="O235" s="37">
@@ -21888,7 +21888,7 @@
         <v>983</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="N236" s="37"/>
       <c r="O236" s="37">
@@ -21924,7 +21924,7 @@
         <v>985</v>
       </c>
       <c r="I237" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N237" s="37"/>
       <c r="O237" s="37">
@@ -22032,7 +22032,7 @@
         <v>991</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="N240" s="37"/>
       <c r="O240" s="37">
@@ -22068,7 +22068,7 @@
         <v>993</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="N241" s="37"/>
       <c r="O241" s="37">
@@ -22104,7 +22104,7 @@
         <v>995</v>
       </c>
       <c r="I242" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="N242" s="37"/>
       <c r="O242" s="37">
@@ -22176,7 +22176,7 @@
         <v>999</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="N244" s="37"/>
       <c r="O244" s="37">
@@ -22212,7 +22212,7 @@
         <v>1001</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="N245" s="37"/>
       <c r="O245" s="37">
@@ -22248,7 +22248,7 @@
         <v>1003</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N246" s="37"/>
       <c r="O246" s="37">
@@ -22356,7 +22356,7 @@
         <v>1009</v>
       </c>
       <c r="I249" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="N249" s="37"/>
       <c r="O249" s="37">
@@ -22392,7 +22392,7 @@
         <v>1011</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="N250" s="37"/>
       <c r="O250" s="37">
@@ -22428,7 +22428,7 @@
         <v>1013</v>
       </c>
       <c r="I251" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="N251" s="37"/>
       <c r="O251" s="37">
@@ -22500,7 +22500,7 @@
         <v>1017</v>
       </c>
       <c r="I253" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="N253" s="37"/>
       <c r="O253" s="37">
@@ -22536,7 +22536,7 @@
         <v>1019</v>
       </c>
       <c r="I254" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="N254" s="37"/>
       <c r="O254" s="37">
@@ -22572,7 +22572,7 @@
         <v>1021</v>
       </c>
       <c r="I255" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N255" s="37"/>
       <c r="O255" s="37">
@@ -22644,7 +22644,7 @@
         <v>1025</v>
       </c>
       <c r="I257" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="N257" s="37"/>
       <c r="O257" s="37">
@@ -22716,7 +22716,7 @@
         <v>1029</v>
       </c>
       <c r="I259" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="N259" s="37"/>
       <c r="O259" s="37">
@@ -22752,7 +22752,7 @@
         <v>1031</v>
       </c>
       <c r="I260" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="N260" s="37"/>
       <c r="O260" s="37">
@@ -22788,7 +22788,7 @@
         <v>1033</v>
       </c>
       <c r="I261" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N261" s="37"/>
       <c r="O261" s="37">
@@ -22896,7 +22896,7 @@
         <v>1039</v>
       </c>
       <c r="I264" s="4" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="N264" s="37"/>
       <c r="O264" s="37">
@@ -22932,7 +22932,7 @@
         <v>1041</v>
       </c>
       <c r="I265" s="4" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="N265" s="37"/>
       <c r="O265" s="37">
@@ -22968,7 +22968,7 @@
         <v>1043</v>
       </c>
       <c r="I266" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="N266" s="37"/>
       <c r="O266" s="37">
@@ -23040,7 +23040,7 @@
         <v>1047</v>
       </c>
       <c r="I268" s="4" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="N268" s="37"/>
       <c r="O268" s="37">
@@ -23076,7 +23076,7 @@
         <v>1049</v>
       </c>
       <c r="I269" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="N269" s="37"/>
       <c r="O269" s="37">
@@ -23112,7 +23112,7 @@
         <v>1051</v>
       </c>
       <c r="I270" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="N270" s="37"/>
       <c r="O270" s="37">

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -3102,19 +3102,19 @@
     <t>1150017.png</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;1个1星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;1个1星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>12212_10_2_1</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;2个1星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;2个1星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>1150017_1|1980000_600</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;1个2星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;1个2星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>12212_10_1_3</t>
@@ -3123,13 +3123,13 @@
     <t>1150018.png</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;1个3星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;1个3星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>12212_10_1_4</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;1个4星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;1个4星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>12212_10_1_5</t>
@@ -3138,7 +3138,7 @@
     <t>1150018_1|1980000_1200</t>
   </si>
   <si>
-    <t>拥有&lt;color=#00bfff&gt;1个5星导航员&lt;/color&gt;</t>
+    <t>拥有&lt;color=#00bfff&gt;1个5星游戏经理&lt;/color&gt;</t>
   </si>
   <si>
     <t>12303_20001_2</t>
@@ -16980,7 +16980,9 @@
       </c>
       <c r="K112" s="12"/>
       <c r="L112" s="13"/>
-      <c r="M112" s="10"/>
+      <c r="M112" s="10">
+        <v>3011</v>
+      </c>
       <c r="N112" s="10" t="str">
         <f t="shared" ref="N112:N133" si="0">LEFT(G112,FIND("_",G112)-1)&amp;".png"</f>
         <v>12216.png</v>
@@ -17028,7 +17030,9 @@
       </c>
       <c r="K113" s="12"/>
       <c r="L113" s="13"/>
-      <c r="M113" s="10"/>
+      <c r="M113" s="10">
+        <v>3017</v>
+      </c>
       <c r="N113" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12214.png</v>
@@ -17076,7 +17080,9 @@
       </c>
       <c r="K114" s="12"/>
       <c r="L114" s="13"/>
-      <c r="M114" s="10"/>
+      <c r="M114" s="10">
+        <v>3012</v>
+      </c>
       <c r="N114" s="10" t="str">
         <f t="shared" si="0"/>
         <v>10001.png</v>
@@ -17172,7 +17178,9 @@
       </c>
       <c r="K116" s="12"/>
       <c r="L116" s="13"/>
-      <c r="M116" s="10"/>
+      <c r="M116" s="10">
+        <v>3012</v>
+      </c>
       <c r="N116" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12202.png</v>
@@ -17268,7 +17276,9 @@
       </c>
       <c r="K118" s="12"/>
       <c r="L118" s="13"/>
-      <c r="M118" s="10"/>
+      <c r="M118" s="10">
+        <v>3011</v>
+      </c>
       <c r="N118" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12304.png</v>
@@ -17316,7 +17326,9 @@
       </c>
       <c r="K119" s="12"/>
       <c r="L119" s="13"/>
-      <c r="M119" s="10"/>
+      <c r="M119" s="10">
+        <v>3017</v>
+      </c>
       <c r="N119" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12303.png</v>
@@ -17364,7 +17376,9 @@
       </c>
       <c r="K120" s="12"/>
       <c r="L120" s="13"/>
-      <c r="M120" s="10"/>
+      <c r="M120" s="10">
+        <v>3017</v>
+      </c>
       <c r="N120" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12303.png</v>
@@ -17412,7 +17426,9 @@
       </c>
       <c r="K121" s="12"/>
       <c r="L121" s="13"/>
-      <c r="M121" s="10"/>
+      <c r="M121" s="10">
+        <v>3017</v>
+      </c>
       <c r="N121" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12212.png</v>
@@ -17460,7 +17476,9 @@
       </c>
       <c r="K122" s="12"/>
       <c r="L122" s="13"/>
-      <c r="M122" s="10"/>
+      <c r="M122" s="10">
+        <v>3014</v>
+      </c>
       <c r="N122" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12305.png</v>
@@ -17556,7 +17574,9 @@
       </c>
       <c r="K124" s="12"/>
       <c r="L124" s="13"/>
-      <c r="M124" s="10"/>
+      <c r="M124" s="10">
+        <v>3017</v>
+      </c>
       <c r="N124" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12211.png</v>
@@ -17796,7 +17816,9 @@
       </c>
       <c r="K129" s="12"/>
       <c r="L129" s="13"/>
-      <c r="M129" s="10"/>
+      <c r="M129" s="10">
+        <v>3012</v>
+      </c>
       <c r="N129" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12201.png</v>
@@ -17892,7 +17914,9 @@
       </c>
       <c r="K131" s="12"/>
       <c r="L131" s="13"/>
-      <c r="M131" s="10"/>
+      <c r="M131" s="10">
+        <v>3012</v>
+      </c>
       <c r="N131" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12203.png</v>
@@ -17940,7 +17964,9 @@
       </c>
       <c r="K132" s="12"/>
       <c r="L132" s="13"/>
-      <c r="M132" s="10"/>
+      <c r="M132" s="10">
+        <v>3012</v>
+      </c>
       <c r="N132" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12204.png</v>
@@ -17988,7 +18014,9 @@
       </c>
       <c r="K133" s="12"/>
       <c r="L133" s="13"/>
-      <c r="M133" s="10"/>
+      <c r="M133" s="10">
+        <v>3012</v>
+      </c>
       <c r="N133" s="10" t="str">
         <f t="shared" si="0"/>
         <v>12205.png</v>
@@ -18330,7 +18358,9 @@
       </c>
       <c r="K140" s="53"/>
       <c r="L140" s="54"/>
-      <c r="M140" s="55"/>
+      <c r="M140" s="55">
+        <v>3012</v>
+      </c>
       <c r="N140" s="55" t="s">
         <v>743</v>
       </c>
@@ -18379,7 +18409,9 @@
       </c>
       <c r="K141" s="53"/>
       <c r="L141" s="54"/>
-      <c r="M141" s="55"/>
+      <c r="M141" s="55">
+        <v>3012</v>
+      </c>
       <c r="N141" s="55" t="s">
         <v>743</v>
       </c>
@@ -18428,7 +18460,9 @@
       </c>
       <c r="K142" s="53"/>
       <c r="L142" s="54"/>
-      <c r="M142" s="55"/>
+      <c r="M142" s="55">
+        <v>3012</v>
+      </c>
       <c r="N142" s="55" t="s">
         <v>743</v>
       </c>
@@ -18477,7 +18511,9 @@
       </c>
       <c r="K143" s="53"/>
       <c r="L143" s="54"/>
-      <c r="M143" s="55"/>
+      <c r="M143" s="55">
+        <v>3012</v>
+      </c>
       <c r="N143" s="55" t="s">
         <v>749</v>
       </c>
@@ -18526,7 +18562,9 @@
       </c>
       <c r="K144" s="53"/>
       <c r="L144" s="54"/>
-      <c r="M144" s="55"/>
+      <c r="M144" s="55">
+        <v>3012</v>
+      </c>
       <c r="N144" s="55" t="s">
         <v>749</v>
       </c>
@@ -18573,7 +18611,9 @@
       </c>
       <c r="K145" s="53"/>
       <c r="L145" s="54"/>
-      <c r="M145" s="55"/>
+      <c r="M145" s="55">
+        <v>3012</v>
+      </c>
       <c r="N145" s="55" t="s">
         <v>749</v>
       </c>
@@ -18623,7 +18663,9 @@
       </c>
       <c r="K146" s="53"/>
       <c r="L146" s="54"/>
-      <c r="M146" s="55"/>
+      <c r="M146" s="55">
+        <v>3012</v>
+      </c>
       <c r="N146" s="55" t="s">
         <v>757</v>
       </c>
@@ -18673,7 +18715,9 @@
       </c>
       <c r="K147" s="53"/>
       <c r="L147" s="54"/>
-      <c r="M147" s="55"/>
+      <c r="M147" s="55">
+        <v>3012</v>
+      </c>
       <c r="N147" s="55" t="s">
         <v>757</v>
       </c>
@@ -18723,7 +18767,9 @@
       </c>
       <c r="K148" s="53"/>
       <c r="L148" s="54"/>
-      <c r="M148" s="55"/>
+      <c r="M148" s="55">
+        <v>3012</v>
+      </c>
       <c r="N148" s="55" t="s">
         <v>757</v>
       </c>
@@ -18773,7 +18819,9 @@
       </c>
       <c r="K149" s="53"/>
       <c r="L149" s="54"/>
-      <c r="M149" s="55"/>
+      <c r="M149" s="55">
+        <v>3012</v>
+      </c>
       <c r="N149" s="55" t="s">
         <v>765</v>
       </c>
@@ -18823,7 +18871,9 @@
       </c>
       <c r="K150" s="53"/>
       <c r="L150" s="54"/>
-      <c r="M150" s="55"/>
+      <c r="M150" s="55">
+        <v>3012</v>
+      </c>
       <c r="N150" s="55" t="s">
         <v>765</v>
       </c>
@@ -18870,7 +18920,9 @@
       </c>
       <c r="K151" s="53"/>
       <c r="L151" s="54"/>
-      <c r="M151" s="55"/>
+      <c r="M151" s="55">
+        <v>3012</v>
+      </c>
       <c r="N151" s="55" t="s">
         <v>765</v>
       </c>
@@ -18920,7 +18972,9 @@
       </c>
       <c r="K152" s="53"/>
       <c r="L152" s="54"/>
-      <c r="M152" s="55"/>
+      <c r="M152" s="55">
+        <v>3012</v>
+      </c>
       <c r="N152" s="55" t="s">
         <v>773</v>
       </c>
@@ -18970,7 +19024,9 @@
       </c>
       <c r="K153" s="53"/>
       <c r="L153" s="54"/>
-      <c r="M153" s="55"/>
+      <c r="M153" s="55">
+        <v>3012</v>
+      </c>
       <c r="N153" s="55" t="s">
         <v>773</v>
       </c>
@@ -19020,7 +19076,9 @@
       </c>
       <c r="K154" s="53"/>
       <c r="L154" s="54"/>
-      <c r="M154" s="55"/>
+      <c r="M154" s="55">
+        <v>3012</v>
+      </c>
       <c r="N154" s="55" t="s">
         <v>773</v>
       </c>
@@ -19070,7 +19128,9 @@
       </c>
       <c r="K155" s="53"/>
       <c r="L155" s="54"/>
-      <c r="M155" s="55"/>
+      <c r="M155" s="55">
+        <v>3012</v>
+      </c>
       <c r="N155" s="55" t="s">
         <v>781</v>
       </c>
@@ -19120,7 +19180,9 @@
       </c>
       <c r="K156" s="53"/>
       <c r="L156" s="54"/>
-      <c r="M156" s="55"/>
+      <c r="M156" s="55">
+        <v>3012</v>
+      </c>
       <c r="N156" s="55" t="s">
         <v>781</v>
       </c>
@@ -19167,7 +19229,9 @@
       </c>
       <c r="K157" s="53"/>
       <c r="L157" s="54"/>
-      <c r="M157" s="55"/>
+      <c r="M157" s="55">
+        <v>3012</v>
+      </c>
       <c r="N157" s="55" t="s">
         <v>781</v>
       </c>
@@ -19217,7 +19281,9 @@
       </c>
       <c r="K158" s="53"/>
       <c r="L158" s="54"/>
-      <c r="M158" s="55"/>
+      <c r="M158" s="55">
+        <v>3012</v>
+      </c>
       <c r="N158" s="55" t="s">
         <v>788</v>
       </c>
@@ -19267,7 +19333,9 @@
       </c>
       <c r="K159" s="53"/>
       <c r="L159" s="54"/>
-      <c r="M159" s="55"/>
+      <c r="M159" s="55">
+        <v>3012</v>
+      </c>
       <c r="N159" s="55" t="s">
         <v>788</v>
       </c>
@@ -19317,7 +19385,9 @@
       </c>
       <c r="K160" s="53"/>
       <c r="L160" s="54"/>
-      <c r="M160" s="55"/>
+      <c r="M160" s="55">
+        <v>3012</v>
+      </c>
       <c r="N160" s="55" t="s">
         <v>788</v>
       </c>
@@ -19367,7 +19437,9 @@
       </c>
       <c r="K161" s="53"/>
       <c r="L161" s="54"/>
-      <c r="M161" s="55"/>
+      <c r="M161" s="55">
+        <v>3012</v>
+      </c>
       <c r="N161" s="55" t="s">
         <v>795</v>
       </c>
@@ -19417,7 +19489,9 @@
       </c>
       <c r="K162" s="53"/>
       <c r="L162" s="54"/>
-      <c r="M162" s="55"/>
+      <c r="M162" s="55">
+        <v>3012</v>
+      </c>
       <c r="N162" s="55" t="s">
         <v>795</v>
       </c>
@@ -19464,7 +19538,9 @@
       </c>
       <c r="K163" s="53"/>
       <c r="L163" s="54"/>
-      <c r="M163" s="55"/>
+      <c r="M163" s="55">
+        <v>3012</v>
+      </c>
       <c r="N163" s="55" t="s">
         <v>795</v>
       </c>
@@ -20108,7 +20184,9 @@
       </c>
       <c r="K176" s="53"/>
       <c r="L176" s="54"/>
-      <c r="M176" s="55"/>
+      <c r="M176" s="55">
+        <v>3017</v>
+      </c>
       <c r="N176" s="55" t="s">
         <v>831</v>
       </c>
@@ -20158,7 +20236,9 @@
       </c>
       <c r="K177" s="53"/>
       <c r="L177" s="54"/>
-      <c r="M177" s="55"/>
+      <c r="M177" s="55">
+        <v>3017</v>
+      </c>
       <c r="N177" s="55" t="s">
         <v>831</v>
       </c>
@@ -20208,7 +20288,9 @@
       </c>
       <c r="K178" s="53"/>
       <c r="L178" s="54"/>
-      <c r="M178" s="55"/>
+      <c r="M178" s="55">
+        <v>3017</v>
+      </c>
       <c r="N178" s="55" t="s">
         <v>831</v>
       </c>
@@ -20258,7 +20340,9 @@
       </c>
       <c r="K179" s="53"/>
       <c r="L179" s="54"/>
-      <c r="M179" s="55"/>
+      <c r="M179" s="55">
+        <v>3017</v>
+      </c>
       <c r="N179" s="55" t="s">
         <v>838</v>
       </c>
@@ -20308,7 +20392,9 @@
       </c>
       <c r="K180" s="53"/>
       <c r="L180" s="54"/>
-      <c r="M180" s="55"/>
+      <c r="M180" s="55">
+        <v>3017</v>
+      </c>
       <c r="N180" s="55" t="s">
         <v>838</v>
       </c>
@@ -20355,7 +20441,9 @@
       </c>
       <c r="K181" s="53"/>
       <c r="L181" s="54"/>
-      <c r="M181" s="55"/>
+      <c r="M181" s="55">
+        <v>3017</v>
+      </c>
       <c r="N181" s="55" t="s">
         <v>838</v>
       </c>
@@ -20405,7 +20493,9 @@
       </c>
       <c r="K182" s="53"/>
       <c r="L182" s="54"/>
-      <c r="M182" s="55"/>
+      <c r="M182" s="55">
+        <v>3017</v>
+      </c>
       <c r="N182" s="55" t="s">
         <v>846</v>
       </c>
@@ -20455,7 +20545,9 @@
       </c>
       <c r="K183" s="53"/>
       <c r="L183" s="54"/>
-      <c r="M183" s="55"/>
+      <c r="M183" s="55">
+        <v>3017</v>
+      </c>
       <c r="N183" s="55" t="s">
         <v>846</v>
       </c>
@@ -20505,7 +20597,9 @@
       </c>
       <c r="K184" s="53"/>
       <c r="L184" s="54"/>
-      <c r="M184" s="55"/>
+      <c r="M184" s="55">
+        <v>3017</v>
+      </c>
       <c r="N184" s="55" t="s">
         <v>846</v>
       </c>
@@ -20555,7 +20649,9 @@
       </c>
       <c r="K185" s="53"/>
       <c r="L185" s="54"/>
-      <c r="M185" s="55"/>
+      <c r="M185" s="55">
+        <v>3017</v>
+      </c>
       <c r="N185" s="55" t="s">
         <v>854</v>
       </c>
@@ -20605,7 +20701,9 @@
       </c>
       <c r="K186" s="53"/>
       <c r="L186" s="54"/>
-      <c r="M186" s="55"/>
+      <c r="M186" s="55">
+        <v>3017</v>
+      </c>
       <c r="N186" s="55" t="s">
         <v>854</v>
       </c>
@@ -20652,7 +20750,9 @@
       </c>
       <c r="K187" s="53"/>
       <c r="L187" s="54"/>
-      <c r="M187" s="55"/>
+      <c r="M187" s="55">
+        <v>3017</v>
+      </c>
       <c r="N187" s="55" t="s">
         <v>854</v>
       </c>
@@ -20702,7 +20802,9 @@
       </c>
       <c r="K188" s="53"/>
       <c r="L188" s="54"/>
-      <c r="M188" s="55"/>
+      <c r="M188" s="55">
+        <v>3017</v>
+      </c>
       <c r="N188" s="55" t="s">
         <v>862</v>
       </c>
@@ -20752,7 +20854,9 @@
       </c>
       <c r="K189" s="53"/>
       <c r="L189" s="54"/>
-      <c r="M189" s="55"/>
+      <c r="M189" s="55">
+        <v>3017</v>
+      </c>
       <c r="N189" s="55" t="s">
         <v>862</v>
       </c>
@@ -20802,7 +20906,9 @@
       </c>
       <c r="K190" s="53"/>
       <c r="L190" s="54"/>
-      <c r="M190" s="55"/>
+      <c r="M190" s="55">
+        <v>3017</v>
+      </c>
       <c r="N190" s="55" t="s">
         <v>862</v>
       </c>
@@ -20852,7 +20958,9 @@
       </c>
       <c r="K191" s="53"/>
       <c r="L191" s="54"/>
-      <c r="M191" s="55"/>
+      <c r="M191" s="55">
+        <v>3017</v>
+      </c>
       <c r="N191" s="55" t="s">
         <v>870</v>
       </c>
@@ -20902,7 +21010,9 @@
       </c>
       <c r="K192" s="53"/>
       <c r="L192" s="54"/>
-      <c r="M192" s="55"/>
+      <c r="M192" s="55">
+        <v>3017</v>
+      </c>
       <c r="N192" s="55" t="s">
         <v>870</v>
       </c>
@@ -20949,7 +21059,9 @@
       </c>
       <c r="K193" s="53"/>
       <c r="L193" s="54"/>
-      <c r="M193" s="55"/>
+      <c r="M193" s="55">
+        <v>3017</v>
+      </c>
       <c r="N193" s="55" t="s">
         <v>870</v>
       </c>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -17999,9 +17999,7 @@
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="12"/>
-      <c r="F133" s="12">
-        <v>100020024</v>
-      </c>
+      <c r="F133" s="12"/>
       <c r="G133" s="12" t="s">
         <v>719</v>
       </c>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2902,6 +2902,9 @@
     <t>1990000_400000|1980000_400</t>
   </si>
   <si>
+    <t>1150032.png</t>
+  </si>
+  <si>
     <t>累积登陆&lt;color=#00bfff&gt;2天&lt;/color&gt;</t>
   </si>
   <si>
@@ -2918,9 +2921,6 @@
   </si>
   <si>
     <t>1990000_600000|1980000_800</t>
-  </si>
-  <si>
-    <t>1150032.png</t>
   </si>
   <si>
     <t>累积登陆&lt;color=#00bfff&gt;4天&lt;/color&gt;</t>
@@ -18671,7 +18671,7 @@
         <v>654</v>
       </c>
       <c r="M152" s="55" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="N152" s="56"/>
       <c r="O152" s="57"/>
@@ -18686,7 +18686,7 @@
       <c r="T152" s="57"/>
       <c r="U152" s="57"/>
       <c r="V152" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="153" spans="1:22">
@@ -18707,11 +18707,11 @@
         <v>100030004</v>
       </c>
       <c r="G153" s="53" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H153" s="53"/>
       <c r="I153" s="53" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="J153" s="53"/>
       <c r="K153" s="54"/>
@@ -18719,7 +18719,7 @@
         <v>654</v>
       </c>
       <c r="M153" s="55" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="N153" s="56"/>
       <c r="O153" s="57"/>
@@ -18734,7 +18734,7 @@
       <c r="T153" s="57"/>
       <c r="U153" s="57"/>
       <c r="V153" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="154" spans="1:22">
@@ -18755,11 +18755,11 @@
         <v>100030005</v>
       </c>
       <c r="G154" s="53" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H154" s="53"/>
       <c r="I154" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J154" s="53"/>
       <c r="K154" s="54"/>
@@ -18767,7 +18767,7 @@
         <v>654</v>
       </c>
       <c r="M154" s="55" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="N154" s="56"/>
       <c r="O154" s="57"/>
@@ -18815,7 +18815,7 @@
         <v>654</v>
       </c>
       <c r="M155" s="55" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="N155" s="56"/>
       <c r="O155" s="57"/>
@@ -18861,7 +18861,7 @@
         <v>654</v>
       </c>
       <c r="M156" s="55" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="N156" s="56"/>
       <c r="O156" s="57"/>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="H160" s="53"/>
       <c r="I160" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J160" s="53"/>
       <c r="K160" s="54"/>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="H166" s="53"/>
       <c r="I166" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J166" s="53"/>
       <c r="K166" s="54"/>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="H172" s="53"/>
       <c r="I172" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J172" s="53"/>
       <c r="K172" s="54"/>
@@ -19917,7 +19917,7 @@
       </c>
       <c r="H178" s="53"/>
       <c r="I178" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J178" s="53"/>
       <c r="K178" s="54"/>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="H184" s="53"/>
       <c r="I184" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J184" s="53"/>
       <c r="K184" s="54"/>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="H190" s="53"/>
       <c r="I190" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J190" s="53"/>
       <c r="K190" s="54"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="H196" s="53"/>
       <c r="I196" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J196" s="53"/>
       <c r="K196" s="54"/>
@@ -21081,7 +21081,7 @@
       </c>
       <c r="H202" s="53"/>
       <c r="I202" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J202" s="53"/>
       <c r="K202" s="54"/>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="H208" s="53"/>
       <c r="I208" s="53" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J208" s="53"/>
       <c r="K208" s="54"/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2584,7 +2584,7 @@
     <t>1990000_120000|1980000_350</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级2次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级2次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12202_0_1024005_5</t>
@@ -3136,13 +3136,13 @@
     <t>1150016.png</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级5次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级5次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12255_0_10</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级10次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级10次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12255_0_20</t>
@@ -3151,7 +3151,7 @@
     <t>1150016_1|1980000_600</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级20次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级20次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12255_0_30</t>
@@ -3160,13 +3160,13 @@
     <t>1150029.png</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级30次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级30次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12255_0_40</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级40次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级40次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12255_0_60</t>
@@ -3175,7 +3175,7 @@
     <t>1150029_1|1980000_1200</t>
   </si>
   <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级60次&lt;/color&gt;</t>
+    <t>任意建筑&lt;color=#00bfff&gt;升级60次大等级&lt;/color&gt;</t>
   </si>
   <si>
     <t>12257_1</t>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -2547,7 +2547,7 @@
     <t>12218_1</t>
   </si>
   <si>
-    <t>1990000_20000|1024005_100|1024007_5</t>
+    <t>1990000_20000|1024005_5|1024007_5</t>
   </si>
   <si>
     <t/>
@@ -2556,10 +2556,46 @@
     <t>登陆&lt;color=#00bfff&gt;1天&lt;/color&gt;</t>
   </si>
   <si>
+    <t>12221_0_1</t>
+  </si>
+  <si>
+    <t>1990000_80000|1980000_100</t>
+  </si>
+  <si>
+    <t>在任意SLOT游戏中投注&lt;color=#00bfff&gt;1次&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>12206_0_1</t>
+  </si>
+  <si>
+    <t>1990000_100000|1980000_100|1024013_2</t>
+  </si>
+  <si>
+    <t>任意建筑&lt;color=#00bfff&gt;升级1次大等级&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>12303_10002_1</t>
+  </si>
+  <si>
+    <t>1990000_100000|1980000_150|1125102_60</t>
+  </si>
+  <si>
+    <t>在&lt;color=#00bfff&gt;游客&lt;/color&gt;卡池抽奖&lt;color=#00bfff&gt;1次&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>12202_0_1024005_1</t>
+  </si>
+  <si>
+    <t>1990000_120000|1980000_150|1024007_5</t>
+  </si>
+  <si>
+    <t>在任意SLOT游戏中旋转获得&lt;color=#00bfff&gt;1个研究点&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>12263_2</t>
   </si>
   <si>
-    <t>1024013_5|1125101_100|1024007_5|1125402_100</t>
+    <t>1024013_5|1125101_100|1024007_5|1125402_60</t>
   </si>
   <si>
     <t>累积研发&lt;color=#00bfff&gt;2个SLOT游戏&lt;/color&gt;</t>
@@ -2568,39 +2604,12 @@
     <t>12261_1_2</t>
   </si>
   <si>
-    <t>1024014_5|1980000_100|1024007_5|1126101_100</t>
+    <t>1024014_5|1980000_100|1024007_5|1126101_60</t>
   </si>
   <si>
     <t>拥有&lt;color=#00bfff&gt;1个2星的游客&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12221_0_1</t>
-  </si>
-  <si>
-    <t>1990000_80000|1980000_100</t>
-  </si>
-  <si>
-    <t>在任意SLOT游戏中投注&lt;color=#00bfff&gt;1次&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>12206_0_1</t>
-  </si>
-  <si>
-    <t>1990000_100000|1980000_100</t>
-  </si>
-  <si>
-    <t>任意建筑&lt;color=#00bfff&gt;升级1次大等级&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>12202_0_1024005_1</t>
-  </si>
-  <si>
-    <t>1990000_120000|1980000_150|1024007_5</t>
-  </si>
-  <si>
-    <t>在任意SLOT游戏中旋转获得&lt;color=#00bfff&gt;1个研究点&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>12268_1_2</t>
   </si>
   <si>
@@ -2626,15 +2635,6 @@
   </si>
   <si>
     <t>在&lt;color=#00bfff&gt;研究院&lt;/color&gt;中对任意游戏的技能升级&lt;color=#00bfff&gt;1次&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>12303_10002_1</t>
-  </si>
-  <si>
-    <t>1024007_5|1980000_150|1125102_100</t>
-  </si>
-  <si>
-    <t>在&lt;color=#00bfff&gt;游客&lt;/color&gt;卡池抽奖&lt;color=#00bfff&gt;1次&lt;/color&gt;</t>
   </si>
   <si>
     <t>12261_2_1</t>
@@ -16900,11 +16900,11 @@
       <c r="J112" s="12"/>
       <c r="K112" s="13"/>
       <c r="L112" s="10">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="M112" s="10" t="str">
         <f t="shared" ref="M112:M143" si="0">LEFT(G112,FIND("_",G112)-1)&amp;".png"</f>
-        <v>12263.png</v>
+        <v>12221.png</v>
       </c>
       <c r="N112" s="8"/>
       <c r="O112" s="6"/>
@@ -16946,12 +16946,12 @@
       </c>
       <c r="J113" s="12"/>
       <c r="K113" s="13"/>
-      <c r="L113" s="10">
-        <v>3017</v>
+      <c r="L113" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="M113" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12261.png</v>
+        <v>12206.png</v>
       </c>
       <c r="N113" s="8"/>
       <c r="O113" s="6"/>
@@ -16994,11 +16994,11 @@
       <c r="J114" s="12"/>
       <c r="K114" s="13"/>
       <c r="L114" s="10">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="M114" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12221.png</v>
+        <v>12303.png</v>
       </c>
       <c r="N114" s="8"/>
       <c r="O114" s="6"/>
@@ -17040,12 +17040,12 @@
       </c>
       <c r="J115" s="12"/>
       <c r="K115" s="13"/>
-      <c r="L115" s="10" t="s">
-        <v>654</v>
+      <c r="L115" s="10">
+        <v>3012</v>
       </c>
       <c r="M115" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12206.png</v>
+        <v>12202.png</v>
       </c>
       <c r="N115" s="8"/>
       <c r="O115" s="6"/>
@@ -17088,11 +17088,11 @@
       <c r="J116" s="12"/>
       <c r="K116" s="13"/>
       <c r="L116" s="10">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="M116" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12202.png</v>
+        <v>12263.png</v>
       </c>
       <c r="N116" s="8"/>
       <c r="O116" s="6"/>
@@ -17135,11 +17135,11 @@
       <c r="J117" s="12"/>
       <c r="K117" s="13"/>
       <c r="L117" s="10">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="M117" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12268.png</v>
+        <v>12261.png</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="6"/>
@@ -17181,12 +17181,12 @@
       </c>
       <c r="J118" s="12"/>
       <c r="K118" s="13"/>
-      <c r="L118" s="10" t="s">
-        <v>654</v>
+      <c r="L118" s="10">
+        <v>3012</v>
       </c>
       <c r="M118" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12209.png</v>
+        <v>12268.png</v>
       </c>
       <c r="N118" s="8"/>
       <c r="O118" s="6"/>
@@ -17228,12 +17228,12 @@
       </c>
       <c r="J119" s="12"/>
       <c r="K119" s="13"/>
-      <c r="L119" s="10">
-        <v>3011</v>
+      <c r="L119" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="M119" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12304.png</v>
+        <v>12209.png</v>
       </c>
       <c r="N119" s="8"/>
       <c r="O119" s="6"/>
@@ -17276,11 +17276,11 @@
       <c r="J120" s="12"/>
       <c r="K120" s="13"/>
       <c r="L120" s="10">
-        <v>3017</v>
+        <v>3011</v>
       </c>
       <c r="M120" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>12303.png</v>
+        <v>12304.png</v>
       </c>
       <c r="N120" s="8"/>
       <c r="O120" s="6"/>
@@ -18487,7 +18487,7 @@
         <v>100020037</v>
       </c>
       <c r="G146" s="12" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="12" t="s">
@@ -18515,7 +18515,7 @@
       <c r="T146" s="6"/>
       <c r="U146" s="6"/>
       <c r="V146" s="4" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="147" spans="1:22">
@@ -18863,7 +18863,7 @@
         <v>100020045</v>
       </c>
       <c r="G154" s="12" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H154" s="12"/>
       <c r="I154" s="12" t="s">
@@ -18891,7 +18891,7 @@
       <c r="T154" s="6"/>
       <c r="U154" s="6"/>
       <c r="V154" s="4" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="155" spans="1:22">
@@ -19220,7 +19220,7 @@
       <c r="T161" s="6"/>
       <c r="U161" s="6"/>
       <c r="V161" s="4" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="162" spans="1:22">
@@ -19596,7 +19596,7 @@
       <c r="T169" s="6"/>
       <c r="U169" s="6"/>
       <c r="V169" s="4" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="170" spans="1:22">
@@ -19996,7 +19996,7 @@
         <v>100030013</v>
       </c>
       <c r="G178" s="53" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="H178" s="53"/>
       <c r="I178" s="53" t="s">
@@ -20023,7 +20023,7 @@
       <c r="T178" s="57"/>
       <c r="U178" s="57"/>
       <c r="V178" s="4" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="179" spans="1:22">
@@ -20553,7 +20553,7 @@
       <c r="T189" s="57"/>
       <c r="U189" s="57"/>
       <c r="V189" s="4" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="190" spans="1:22">
@@ -21135,7 +21135,7 @@
       <c r="T201" s="57"/>
       <c r="U201" s="57"/>
       <c r="V201" s="4" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="202" spans="1:22">
@@ -21426,7 +21426,7 @@
       <c r="T207" s="57"/>
       <c r="U207" s="57"/>
       <c r="V207" s="4" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
     </row>
     <row r="208" spans="1:22">
@@ -22272,7 +22272,7 @@
         <v>100030092</v>
       </c>
       <c r="G225" s="53" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="H225" s="53"/>
       <c r="I225" s="53" t="s">
@@ -22299,7 +22299,7 @@
       <c r="T225" s="57"/>
       <c r="U225" s="57"/>
       <c r="V225" s="4" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
     </row>
     <row r="226" spans="1:22">

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -6332,7 +6332,7 @@
     <t>[象财神]游戏&lt;color=#00bfff&gt;技能战力达到70000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_102700_94000</t>
+    <t>12269_102700_90000</t>
   </si>
   <si>
     <t>[象财神]游戏&lt;color=#00bfff&gt;技能战力达到94000以上&lt;/color&gt;</t>
@@ -6596,7 +6596,7 @@
     <t>[超级明星]游戏&lt;color=#00bfff&gt;技能战力达到60000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_100300_86000</t>
+    <t>12269_100300_80000</t>
   </si>
   <si>
     <t>[超级明星]游戏&lt;color=#00bfff&gt;技能战力达到86000以上&lt;/color&gt;</t>
@@ -6857,7 +6857,7 @@
     <t>[财神来了]游戏&lt;color=#00bfff&gt;技能战力达到35000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_101200_66000</t>
+    <t>12269_101200_60000</t>
   </si>
   <si>
     <t>[财神来了]游戏&lt;color=#00bfff&gt;技能战力达到66000以上&lt;/color&gt;</t>
@@ -6935,37 +6935,37 @@
     <t>在[财神来了]SLOT游戏中&lt;color=#00bfff&gt;投注10000次&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_1</t>
+    <t>12275_1</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发1次财神到模式&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_2</t>
+    <t>12275_2</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发2次财神到模式&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_5</t>
+    <t>12275_5</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发5次财神到模式&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_10</t>
+    <t>12275_10</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发10次财神到模式&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_20</t>
+    <t>12275_20</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发20次财神到模式&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12275_101200_50</t>
+    <t>12275_50</t>
   </si>
   <si>
     <t>在[财神来了]SLOT游戏中旋转&lt;color=#00bfff&gt;触发50次财神到模式&lt;/color&gt;</t>
@@ -7682,7 +7682,7 @@
     <t>[篮球巨星]游戏&lt;color=#00bfff&gt;技能战力达到70000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_101800_105000</t>
+    <t>12269_101800_100000</t>
   </si>
   <si>
     <t>[篮球巨星]游戏&lt;color=#00bfff&gt;技能战力达到105000以上&lt;/color&gt;</t>
@@ -8255,7 +8255,7 @@
     <t>[狼月]游戏&lt;color=#00bfff&gt;技能战力达到120000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_101500_155000</t>
+    <t>12269_101500_150000</t>
   </si>
   <si>
     <t>[狼月]游戏&lt;color=#00bfff&gt;技能战力达到155000以上&lt;/color&gt;</t>
@@ -8555,7 +8555,7 @@
     <t>[麻将胡了]游戏&lt;color=#00bfff&gt;技能战力达到70000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_100700_95000</t>
+    <t>12269_100700_90000</t>
   </si>
   <si>
     <t>[麻将胡了]游戏&lt;color=#00bfff&gt;技能战力达到95000以上&lt;/color&gt;</t>
@@ -8819,7 +8819,7 @@
     <t>[雷神]游戏&lt;color=#00bfff&gt;技能战力达到70000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_102200_95000</t>
+    <t>12269_102200_90000</t>
   </si>
   <si>
     <t>[雷神]游戏&lt;color=#00bfff&gt;技能战力达到95000以上&lt;/color&gt;</t>
@@ -9089,7 +9089,7 @@
     <t>[杰克船长]游戏&lt;color=#00bfff&gt;技能战力达到100000以上&lt;/color&gt;</t>
   </si>
   <si>
-    <t>12269_102100_135000</t>
+    <t>12269_102100_125000</t>
   </si>
   <si>
     <t>[杰克船长]游戏&lt;color=#00bfff&gt;技能战力达到135000以上&lt;/color&gt;</t>
@@ -10228,12 +10228,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -11731,17 +11731,17 @@
         </row>
         <row r="97">
           <cell r="A97">
-            <v>3301</v>
+            <v>3554</v>
           </cell>
         </row>
         <row r="97">
           <cell r="F97" t="str">
-            <v>PlatformHall/UIHall/MVCHead</v>
+            <v>PlatformHall/SimulationGame/MVCHead</v>
           </cell>
         </row>
         <row r="98">
           <cell r="A98">
-            <v>3302</v>
+            <v>3301</v>
           </cell>
         </row>
         <row r="98">
@@ -11751,7 +11751,7 @@
         </row>
         <row r="99">
           <cell r="A99">
-            <v>3303</v>
+            <v>3302</v>
           </cell>
         </row>
         <row r="99">
@@ -11761,7 +11761,7 @@
         </row>
         <row r="100">
           <cell r="A100">
-            <v>3304</v>
+            <v>3303</v>
           </cell>
         </row>
         <row r="100">
@@ -11771,7 +11771,7 @@
         </row>
         <row r="101">
           <cell r="A101">
-            <v>3305</v>
+            <v>3304</v>
           </cell>
         </row>
         <row r="101">
@@ -11781,7 +11781,7 @@
         </row>
         <row r="102">
           <cell r="A102">
-            <v>3306</v>
+            <v>3305</v>
           </cell>
         </row>
         <row r="102">
@@ -11791,7 +11791,7 @@
         </row>
         <row r="103">
           <cell r="A103">
-            <v>3307</v>
+            <v>3306</v>
           </cell>
         </row>
         <row r="103">
@@ -11801,7 +11801,7 @@
         </row>
         <row r="104">
           <cell r="A104">
-            <v>3308</v>
+            <v>3307</v>
           </cell>
         </row>
         <row r="104">
@@ -11811,7 +11811,7 @@
         </row>
         <row r="105">
           <cell r="A105">
-            <v>3309</v>
+            <v>3308</v>
           </cell>
         </row>
         <row r="105">
@@ -11821,7 +11821,7 @@
         </row>
         <row r="106">
           <cell r="A106">
-            <v>3310</v>
+            <v>3309</v>
           </cell>
         </row>
         <row r="106">
@@ -11831,7 +11831,7 @@
         </row>
         <row r="107">
           <cell r="A107">
-            <v>3311</v>
+            <v>3310</v>
           </cell>
         </row>
         <row r="107">
@@ -11841,7 +11841,7 @@
         </row>
         <row r="108">
           <cell r="A108">
-            <v>3312</v>
+            <v>3311</v>
           </cell>
         </row>
         <row r="108">
@@ -11851,76 +11851,86 @@
         </row>
         <row r="109">
           <cell r="A109">
-            <v>3401</v>
+            <v>3312</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="F109" t="str">
+            <v>PlatformHall/UIHall/MVCHead</v>
           </cell>
         </row>
         <row r="110">
           <cell r="A110">
-            <v>3402</v>
+            <v>3401</v>
           </cell>
         </row>
         <row r="111">
           <cell r="A111">
-            <v>3403</v>
+            <v>3402</v>
           </cell>
         </row>
         <row r="112">
           <cell r="A112">
-            <v>3404</v>
+            <v>3403</v>
           </cell>
         </row>
         <row r="113">
           <cell r="A113">
-            <v>3405</v>
+            <v>3404</v>
           </cell>
         </row>
         <row r="114">
           <cell r="A114">
-            <v>3406</v>
+            <v>3405</v>
           </cell>
         </row>
         <row r="115">
           <cell r="A115">
-            <v>3407</v>
+            <v>3406</v>
           </cell>
         </row>
         <row r="116">
           <cell r="A116">
-            <v>3408</v>
+            <v>3407</v>
           </cell>
         </row>
         <row r="117">
           <cell r="A117">
-            <v>3409</v>
+            <v>3408</v>
           </cell>
         </row>
         <row r="118">
           <cell r="A118">
-            <v>3410</v>
+            <v>3409</v>
           </cell>
         </row>
         <row r="119">
           <cell r="A119">
-            <v>3411</v>
+            <v>3410</v>
           </cell>
         </row>
         <row r="120">
           <cell r="A120">
-            <v>3412</v>
+            <v>3411</v>
           </cell>
         </row>
         <row r="121">
           <cell r="A121">
-            <v>3501</v>
+            <v>3412</v>
           </cell>
         </row>
         <row r="122">
           <cell r="A122">
-            <v>3502</v>
+            <v>3501</v>
           </cell>
         </row>
         <row r="123">
           <cell r="A123">
+            <v>3502</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
             <v>3503</v>
           </cell>
         </row>
@@ -34678,12 +34688,14 @@
         <v>100030001</v>
       </c>
       <c r="B375" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C375" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D375" s="55"/>
+      <c r="D375" s="55">
+        <v>13</v>
+      </c>
       <c r="E375" s="55"/>
       <c r="F375" s="55">
         <v>30001</v>
@@ -34731,12 +34743,14 @@
         <v>100030002</v>
       </c>
       <c r="B376" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C376" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D376" s="55"/>
+      <c r="D376" s="55">
+        <v>13</v>
+      </c>
       <c r="E376" s="55"/>
       <c r="F376" s="55">
         <v>30001</v>
@@ -34784,12 +34798,14 @@
         <v>100030003</v>
       </c>
       <c r="B377" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C377" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D377" s="55"/>
+      <c r="D377" s="55">
+        <v>13</v>
+      </c>
       <c r="E377" s="55"/>
       <c r="F377" s="55">
         <v>30001</v>
@@ -34837,12 +34853,14 @@
         <v>100030004</v>
       </c>
       <c r="B378" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C378" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D378" s="55"/>
+      <c r="D378" s="55">
+        <v>13</v>
+      </c>
       <c r="E378" s="55"/>
       <c r="F378" s="55">
         <v>30001</v>
@@ -34890,12 +34908,14 @@
         <v>100030005</v>
       </c>
       <c r="B379" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C379" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D379" s="55"/>
+      <c r="D379" s="55">
+        <v>13</v>
+      </c>
       <c r="E379" s="55"/>
       <c r="F379" s="55">
         <v>30001</v>
@@ -34943,12 +34963,14 @@
         <v>100030006</v>
       </c>
       <c r="B380" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C380" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D380" s="55"/>
+      <c r="D380" s="55">
+        <v>13</v>
+      </c>
       <c r="E380" s="55"/>
       <c r="F380" s="55">
         <v>30001</v>
@@ -34994,12 +35016,14 @@
         <v>100030011</v>
       </c>
       <c r="B381" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C381" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D381" s="55"/>
+      <c r="D381" s="55">
+        <v>14</v>
+      </c>
       <c r="E381" s="55"/>
       <c r="F381" s="55">
         <v>30011</v>
@@ -35047,12 +35071,14 @@
         <v>100030012</v>
       </c>
       <c r="B382" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C382" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D382" s="55"/>
+      <c r="D382" s="55">
+        <v>14</v>
+      </c>
       <c r="E382" s="55"/>
       <c r="F382" s="55">
         <v>30011</v>
@@ -35100,12 +35126,14 @@
         <v>100030013</v>
       </c>
       <c r="B383" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C383" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D383" s="55"/>
+      <c r="D383" s="55">
+        <v>14</v>
+      </c>
       <c r="E383" s="55"/>
       <c r="F383" s="55">
         <v>30011</v>
@@ -35153,12 +35181,14 @@
         <v>100030014</v>
       </c>
       <c r="B384" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C384" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D384" s="55"/>
+      <c r="D384" s="55">
+        <v>14</v>
+      </c>
       <c r="E384" s="55"/>
       <c r="F384" s="55">
         <v>30011</v>
@@ -35206,12 +35236,14 @@
         <v>100030015</v>
       </c>
       <c r="B385" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C385" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D385" s="55"/>
+      <c r="D385" s="55">
+        <v>14</v>
+      </c>
       <c r="E385" s="55"/>
       <c r="F385" s="55">
         <v>30011</v>
@@ -35259,12 +35291,14 @@
         <v>100030016</v>
       </c>
       <c r="B386" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C386" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D386" s="55"/>
+      <c r="D386" s="55">
+        <v>14</v>
+      </c>
       <c r="E386" s="55"/>
       <c r="F386" s="55">
         <v>30011</v>
@@ -35310,12 +35344,14 @@
         <v>100030051</v>
       </c>
       <c r="B387" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C387" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D387" s="55"/>
+      <c r="D387" s="55">
+        <v>15</v>
+      </c>
       <c r="E387" s="55"/>
       <c r="F387" s="55">
         <v>30051</v>
@@ -35364,12 +35400,14 @@
         <v>100030052</v>
       </c>
       <c r="B388" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C388" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D388" s="55"/>
+      <c r="D388" s="55">
+        <v>15</v>
+      </c>
       <c r="E388" s="55"/>
       <c r="F388" s="55">
         <v>30051</v>
@@ -35418,12 +35456,14 @@
         <v>100030053</v>
       </c>
       <c r="B389" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C389" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D389" s="55"/>
+      <c r="D389" s="55">
+        <v>15</v>
+      </c>
       <c r="E389" s="55"/>
       <c r="F389" s="55">
         <v>30051</v>
@@ -35472,12 +35512,14 @@
         <v>100030054</v>
       </c>
       <c r="B390" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C390" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D390" s="55"/>
+      <c r="D390" s="55">
+        <v>15</v>
+      </c>
       <c r="E390" s="55"/>
       <c r="F390" s="55">
         <v>30051</v>
@@ -35526,12 +35568,14 @@
         <v>100030055</v>
       </c>
       <c r="B391" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C391" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D391" s="55"/>
+      <c r="D391" s="55">
+        <v>15</v>
+      </c>
       <c r="E391" s="55"/>
       <c r="F391" s="55">
         <v>30051</v>
@@ -35580,12 +35624,14 @@
         <v>100030056</v>
       </c>
       <c r="B392" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C392" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D392" s="55"/>
+      <c r="D392" s="55">
+        <v>15</v>
+      </c>
       <c r="E392" s="55"/>
       <c r="F392" s="55">
         <v>30051</v>
@@ -35631,12 +35677,14 @@
         <v>100030061</v>
       </c>
       <c r="B393" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C393" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D393" s="55"/>
+      <c r="D393" s="55">
+        <v>16</v>
+      </c>
       <c r="E393" s="55"/>
       <c r="F393" s="55">
         <v>30061</v>
@@ -35685,12 +35733,14 @@
         <v>100030062</v>
       </c>
       <c r="B394" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C394" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D394" s="55"/>
+      <c r="D394" s="55">
+        <v>16</v>
+      </c>
       <c r="E394" s="55"/>
       <c r="F394" s="55">
         <v>30061</v>
@@ -35739,12 +35789,14 @@
         <v>100030063</v>
       </c>
       <c r="B395" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C395" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D395" s="55"/>
+      <c r="D395" s="55">
+        <v>16</v>
+      </c>
       <c r="E395" s="55"/>
       <c r="F395" s="55">
         <v>30061</v>
@@ -35793,12 +35845,14 @@
         <v>100030064</v>
       </c>
       <c r="B396" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C396" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D396" s="55"/>
+      <c r="D396" s="55">
+        <v>16</v>
+      </c>
       <c r="E396" s="55"/>
       <c r="F396" s="55">
         <v>30061</v>
@@ -35847,12 +35901,14 @@
         <v>100030065</v>
       </c>
       <c r="B397" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C397" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D397" s="55"/>
+      <c r="D397" s="55">
+        <v>16</v>
+      </c>
       <c r="E397" s="55"/>
       <c r="F397" s="55">
         <v>30061</v>
@@ -35901,12 +35957,14 @@
         <v>100030066</v>
       </c>
       <c r="B398" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C398" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D398" s="55"/>
+      <c r="D398" s="55">
+        <v>16</v>
+      </c>
       <c r="E398" s="55"/>
       <c r="F398" s="55">
         <v>30061</v>
@@ -35952,12 +36010,14 @@
         <v>100030071</v>
       </c>
       <c r="B399" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C399" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D399" s="55"/>
+      <c r="D399" s="55">
+        <v>17</v>
+      </c>
       <c r="E399" s="55"/>
       <c r="F399" s="55">
         <v>30071</v>
@@ -36004,12 +36064,14 @@
         <v>100030072</v>
       </c>
       <c r="B400" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C400" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D400" s="55"/>
+      <c r="D400" s="55">
+        <v>17</v>
+      </c>
       <c r="E400" s="55"/>
       <c r="F400" s="55">
         <v>30071</v>
@@ -36056,12 +36118,14 @@
         <v>100030073</v>
       </c>
       <c r="B401" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C401" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D401" s="55"/>
+      <c r="D401" s="55">
+        <v>17</v>
+      </c>
       <c r="E401" s="55"/>
       <c r="F401" s="55">
         <v>30071</v>
@@ -36108,12 +36172,14 @@
         <v>100030074</v>
       </c>
       <c r="B402" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C402" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D402" s="55"/>
+      <c r="D402" s="55">
+        <v>17</v>
+      </c>
       <c r="E402" s="55"/>
       <c r="F402" s="55">
         <v>30071</v>
@@ -36160,12 +36226,14 @@
         <v>100030075</v>
       </c>
       <c r="B403" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C403" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D403" s="55"/>
+      <c r="D403" s="55">
+        <v>17</v>
+      </c>
       <c r="E403" s="55"/>
       <c r="F403" s="55">
         <v>30071</v>
@@ -36212,12 +36280,14 @@
         <v>100030076</v>
       </c>
       <c r="B404" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C404" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D404" s="55"/>
+      <c r="D404" s="55">
+        <v>17</v>
+      </c>
       <c r="E404" s="55"/>
       <c r="F404" s="55">
         <v>30071</v>
@@ -36261,12 +36331,14 @@
         <v>100030091</v>
       </c>
       <c r="B405" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C405" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D405" s="55"/>
+      <c r="D405" s="55">
+        <v>18</v>
+      </c>
       <c r="E405" s="55"/>
       <c r="F405" s="55">
         <v>30091</v>
@@ -36315,12 +36387,14 @@
         <v>100030092</v>
       </c>
       <c r="B406" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C406" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D406" s="55"/>
+      <c r="D406" s="55">
+        <v>18</v>
+      </c>
       <c r="E406" s="55"/>
       <c r="F406" s="55">
         <v>30091</v>
@@ -36369,12 +36443,14 @@
         <v>100030093</v>
       </c>
       <c r="B407" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C407" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D407" s="55"/>
+      <c r="D407" s="55">
+        <v>18</v>
+      </c>
       <c r="E407" s="55"/>
       <c r="F407" s="55">
         <v>30091</v>
@@ -36423,12 +36499,14 @@
         <v>100030094</v>
       </c>
       <c r="B408" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C408" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D408" s="55"/>
+      <c r="D408" s="55">
+        <v>18</v>
+      </c>
       <c r="E408" s="55"/>
       <c r="F408" s="55">
         <v>30091</v>
@@ -36477,12 +36555,14 @@
         <v>100030095</v>
       </c>
       <c r="B409" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C409" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D409" s="55"/>
+      <c r="D409" s="55">
+        <v>18</v>
+      </c>
       <c r="E409" s="55"/>
       <c r="F409" s="55">
         <v>30091</v>
@@ -36531,12 +36611,14 @@
         <v>100030096</v>
       </c>
       <c r="B410" s="55">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C410" s="55" t="s">
         <v>1241</v>
       </c>
-      <c r="D410" s="55"/>
+      <c r="D410" s="55">
+        <v>18</v>
+      </c>
       <c r="E410" s="55"/>
       <c r="F410" s="55">
         <v>30091</v>
@@ -43286,6 +43368,12 @@
       <c r="K591" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N591" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U591" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y591" s="4" t="s">
         <v>1748</v>
       </c>
@@ -43319,6 +43407,12 @@
       <c r="K592" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N592" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U592" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y592" s="4" t="s">
         <v>1751</v>
       </c>
@@ -43352,6 +43446,12 @@
       <c r="K593" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N593" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U593" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y593" s="4" t="s">
         <v>1754</v>
       </c>
@@ -43385,6 +43485,12 @@
       <c r="K594" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N594" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U594" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y594" s="4" t="s">
         <v>1757</v>
       </c>
@@ -43418,6 +43524,12 @@
       <c r="K595" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N595" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U595" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y595" s="4" t="s">
         <v>1760</v>
       </c>
@@ -43447,6 +43559,12 @@
       <c r="K596" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N596" s="38">
+        <v>3201</v>
+      </c>
+      <c r="U596" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y596" s="4" t="s">
         <v>1763</v>
       </c>
@@ -43477,6 +43595,12 @@
       <c r="K597" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N597" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U597" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y597" s="4" t="s">
         <v>1765</v>
       </c>
@@ -43507,6 +43631,12 @@
       <c r="K598" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N598" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U598" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y598" s="4" t="s">
         <v>1767</v>
       </c>
@@ -43537,6 +43667,12 @@
       <c r="K599" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N599" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U599" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y599" s="4" t="s">
         <v>1769</v>
       </c>
@@ -43567,6 +43703,12 @@
       <c r="K600" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N600" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U600" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y600" s="4" t="s">
         <v>1771</v>
       </c>
@@ -43597,6 +43739,12 @@
       <c r="K601" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N601" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U601" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y601" s="4" t="s">
         <v>1773</v>
       </c>
@@ -43623,6 +43771,12 @@
       <c r="K602" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N602" s="38">
+        <v>3301</v>
+      </c>
+      <c r="U602" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y602" s="4" t="s">
         <v>1775</v>
       </c>
@@ -43653,6 +43807,12 @@
       <c r="K603" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N603" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U603" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y603" s="4" t="s">
         <v>1777</v>
       </c>
@@ -43683,6 +43843,12 @@
       <c r="K604" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N604" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U604" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y604" s="4" t="s">
         <v>1779</v>
       </c>
@@ -43713,6 +43879,12 @@
       <c r="K605" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N605" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U605" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y605" s="4" t="s">
         <v>1781</v>
       </c>
@@ -43743,6 +43915,12 @@
       <c r="K606" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N606" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U606" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y606" s="4" t="s">
         <v>1783</v>
       </c>
@@ -43773,6 +43951,12 @@
       <c r="K607" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N607" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U607" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y607" s="4" t="s">
         <v>1785</v>
       </c>
@@ -43799,6 +43983,12 @@
       <c r="K608" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N608" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U608" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y608" s="4" t="s">
         <v>1787</v>
       </c>
@@ -43829,6 +44019,12 @@
       <c r="K609" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N609" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U609" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y609" s="4" t="s">
         <v>1789</v>
       </c>
@@ -43859,6 +44055,12 @@
       <c r="K610" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N610" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U610" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y610" s="4" t="s">
         <v>1791</v>
       </c>
@@ -43889,6 +44091,12 @@
       <c r="K611" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N611" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U611" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y611" s="4" t="s">
         <v>1793</v>
       </c>
@@ -43919,6 +44127,12 @@
       <c r="K612" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N612" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U612" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y612" s="4" t="s">
         <v>1795</v>
       </c>
@@ -43949,6 +44163,12 @@
       <c r="K613" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N613" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U613" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y613" s="4" t="s">
         <v>1797</v>
       </c>
@@ -43975,6 +44195,12 @@
       <c r="K614" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N614" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U614" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y614" s="4" t="s">
         <v>1799</v>
       </c>
@@ -44005,6 +44231,12 @@
       <c r="K615" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N615" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U615" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y615" s="4" t="s">
         <v>1801</v>
       </c>
@@ -44035,6 +44267,12 @@
       <c r="K616" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N616" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U616" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y616" s="4" t="s">
         <v>1803</v>
       </c>
@@ -44065,6 +44303,12 @@
       <c r="K617" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N617" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U617" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y617" s="4" t="s">
         <v>1805</v>
       </c>
@@ -44095,6 +44339,12 @@
       <c r="K618" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N618" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U618" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y618" s="4" t="s">
         <v>1807</v>
       </c>
@@ -44125,6 +44375,12 @@
       <c r="K619" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N619" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U619" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y619" s="4" t="s">
         <v>1809</v>
       </c>
@@ -44151,6 +44407,12 @@
       <c r="K620" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N620" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U620" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y620" s="4" t="s">
         <v>1811</v>
       </c>
@@ -44181,6 +44443,12 @@
       <c r="K621" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N621" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U621" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y621" s="4" t="s">
         <v>1813</v>
       </c>
@@ -44211,6 +44479,12 @@
       <c r="K622" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N622" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U622" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y622" s="4" t="s">
         <v>1815</v>
       </c>
@@ -44241,6 +44515,12 @@
       <c r="K623" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N623" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U623" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y623" s="4" t="s">
         <v>1817</v>
       </c>
@@ -44271,6 +44551,12 @@
       <c r="K624" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N624" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U624" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y624" s="4" t="s">
         <v>1819</v>
       </c>
@@ -44301,6 +44587,12 @@
       <c r="K625" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N625" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U625" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y625" s="4" t="s">
         <v>1821</v>
       </c>
@@ -44327,6 +44619,12 @@
       <c r="K626" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N626" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U626" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y626" s="4" t="s">
         <v>1823</v>
       </c>
@@ -44357,6 +44655,12 @@
       <c r="K627" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N627" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U627" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y627" s="4" t="s">
         <v>1825</v>
       </c>
@@ -44387,6 +44691,12 @@
       <c r="K628" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N628" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U628" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y628" s="4" t="s">
         <v>1827</v>
       </c>
@@ -44417,6 +44727,12 @@
       <c r="K629" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N629" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U629" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y629" s="4" t="s">
         <v>1830</v>
       </c>
@@ -44447,6 +44763,12 @@
       <c r="K630" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N630" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U630" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y630" s="4" t="s">
         <v>1832</v>
       </c>
@@ -44477,6 +44799,12 @@
       <c r="K631" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N631" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U631" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y631" s="4" t="s">
         <v>1835</v>
       </c>
@@ -44507,6 +44835,12 @@
       <c r="K632" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N632" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U632" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y632" s="4" t="s">
         <v>1838</v>
       </c>
@@ -44537,6 +44871,12 @@
       <c r="K633" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N633" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U633" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y633" s="4" t="s">
         <v>1841</v>
       </c>
@@ -44563,6 +44903,12 @@
       <c r="K634" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N634" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U634" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y634" s="4" t="s">
         <v>1843</v>
       </c>
@@ -44593,6 +44939,12 @@
       <c r="K635" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N635" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U635" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y635" s="4" t="s">
         <v>1845</v>
       </c>
@@ -44623,6 +44975,12 @@
       <c r="K636" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N636" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U636" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y636" s="4" t="s">
         <v>1847</v>
       </c>
@@ -44653,6 +45011,12 @@
       <c r="K637" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N637" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U637" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y637" s="4" t="s">
         <v>1849</v>
       </c>
@@ -44683,6 +45047,12 @@
       <c r="K638" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N638" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U638" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y638" s="4" t="s">
         <v>1851</v>
       </c>
@@ -44713,6 +45083,12 @@
       <c r="K639" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N639" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U639" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y639" s="4" t="s">
         <v>1853</v>
       </c>
@@ -44739,6 +45115,12 @@
       <c r="K640" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N640" s="38">
+        <v>11041</v>
+      </c>
+      <c r="U640" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y640" s="4" t="s">
         <v>1855</v>
       </c>
@@ -44772,6 +45154,12 @@
       <c r="K641" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N641" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U641" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y641" s="4" t="s">
         <v>1858</v>
       </c>
@@ -44805,6 +45193,12 @@
       <c r="K642" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N642" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U642" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y642" s="4" t="s">
         <v>1860</v>
       </c>
@@ -44838,6 +45232,12 @@
       <c r="K643" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N643" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U643" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y643" s="4" t="s">
         <v>1862</v>
       </c>
@@ -44871,6 +45271,12 @@
       <c r="K644" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N644" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U644" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y644" s="4" t="s">
         <v>1864</v>
       </c>
@@ -44904,6 +45310,12 @@
       <c r="K645" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N645" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U645" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y645" s="4" t="s">
         <v>1866</v>
       </c>
@@ -44933,6 +45345,12 @@
       <c r="K646" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N646" s="38">
+        <v>3202</v>
+      </c>
+      <c r="U646" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y646" s="4" t="s">
         <v>1868</v>
       </c>
@@ -44963,6 +45381,12 @@
       <c r="K647" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N647" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U647" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y647" s="4" t="s">
         <v>1870</v>
       </c>
@@ -44993,6 +45417,12 @@
       <c r="K648" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N648" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U648" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y648" s="4" t="s">
         <v>1872</v>
       </c>
@@ -45023,6 +45453,12 @@
       <c r="K649" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N649" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U649" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y649" s="4" t="s">
         <v>1874</v>
       </c>
@@ -45053,6 +45489,12 @@
       <c r="K650" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N650" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U650" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y650" s="4" t="s">
         <v>1876</v>
       </c>
@@ -45083,6 +45525,12 @@
       <c r="K651" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N651" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U651" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y651" s="4" t="s">
         <v>1878</v>
       </c>
@@ -45109,6 +45557,12 @@
       <c r="K652" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N652" s="38">
+        <v>3302</v>
+      </c>
+      <c r="U652" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y652" s="4" t="s">
         <v>1880</v>
       </c>
@@ -45139,6 +45593,12 @@
       <c r="K653" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N653" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U653" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y653" s="4" t="s">
         <v>1882</v>
       </c>
@@ -45169,6 +45629,12 @@
       <c r="K654" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N654" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U654" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y654" s="4" t="s">
         <v>1884</v>
       </c>
@@ -45199,6 +45665,12 @@
       <c r="K655" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N655" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U655" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y655" s="4" t="s">
         <v>1886</v>
       </c>
@@ -45229,6 +45701,12 @@
       <c r="K656" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N656" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U656" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y656" s="4" t="s">
         <v>1888</v>
       </c>
@@ -45259,6 +45737,12 @@
       <c r="K657" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N657" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U657" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y657" s="4" t="s">
         <v>1890</v>
       </c>
@@ -45285,6 +45769,12 @@
       <c r="K658" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N658" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U658" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y658" s="4" t="s">
         <v>1892</v>
       </c>
@@ -45315,6 +45805,12 @@
       <c r="K659" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N659" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U659" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y659" s="4" t="s">
         <v>1894</v>
       </c>
@@ -45345,6 +45841,12 @@
       <c r="K660" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N660" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U660" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y660" s="4" t="s">
         <v>1896</v>
       </c>
@@ -45375,6 +45877,12 @@
       <c r="K661" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N661" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U661" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y661" s="4" t="s">
         <v>1898</v>
       </c>
@@ -45405,6 +45913,12 @@
       <c r="K662" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N662" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U662" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y662" s="4" t="s">
         <v>1900</v>
       </c>
@@ -45435,6 +45949,12 @@
       <c r="K663" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N663" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U663" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y663" s="4" t="s">
         <v>1902</v>
       </c>
@@ -45461,6 +45981,12 @@
       <c r="K664" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N664" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U664" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y664" s="4" t="s">
         <v>1904</v>
       </c>
@@ -45491,6 +46017,12 @@
       <c r="K665" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N665" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U665" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y665" s="4" t="s">
         <v>1906</v>
       </c>
@@ -45521,6 +46053,12 @@
       <c r="K666" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N666" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U666" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y666" s="4" t="s">
         <v>1908</v>
       </c>
@@ -45551,6 +46089,12 @@
       <c r="K667" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N667" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U667" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y667" s="4" t="s">
         <v>1910</v>
       </c>
@@ -45581,6 +46125,12 @@
       <c r="K668" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N668" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U668" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y668" s="4" t="s">
         <v>1912</v>
       </c>
@@ -45611,6 +46161,12 @@
       <c r="K669" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N669" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U669" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y669" s="4" t="s">
         <v>1914</v>
       </c>
@@ -45637,6 +46193,12 @@
       <c r="K670" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N670" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U670" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y670" s="4" t="s">
         <v>1916</v>
       </c>
@@ -45667,6 +46229,12 @@
       <c r="K671" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N671" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U671" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y671" s="4" t="s">
         <v>1918</v>
       </c>
@@ -45697,6 +46265,12 @@
       <c r="K672" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N672" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U672" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y672" s="4" t="s">
         <v>1920</v>
       </c>
@@ -45727,6 +46301,12 @@
       <c r="K673" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N673" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U673" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y673" s="4" t="s">
         <v>1922</v>
       </c>
@@ -45757,6 +46337,12 @@
       <c r="K674" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N674" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U674" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y674" s="4" t="s">
         <v>1924</v>
       </c>
@@ -45787,6 +46373,12 @@
       <c r="K675" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N675" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U675" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y675" s="4" t="s">
         <v>1926</v>
       </c>
@@ -45813,6 +46405,12 @@
       <c r="K676" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N676" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U676" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y676" s="4" t="s">
         <v>1928</v>
       </c>
@@ -45843,6 +46441,12 @@
       <c r="K677" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N677" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U677" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y677" s="4" t="s">
         <v>1930</v>
       </c>
@@ -45873,6 +46477,12 @@
       <c r="K678" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N678" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U678" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y678" s="4" t="s">
         <v>1932</v>
       </c>
@@ -45903,6 +46513,12 @@
       <c r="K679" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N679" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U679" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y679" s="4" t="s">
         <v>1934</v>
       </c>
@@ -45933,6 +46549,12 @@
       <c r="K680" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N680" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U680" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y680" s="4" t="s">
         <v>1936</v>
       </c>
@@ -45963,6 +46585,12 @@
       <c r="K681" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N681" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U681" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y681" s="4" t="s">
         <v>1938</v>
       </c>
@@ -45993,6 +46621,12 @@
       <c r="K682" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N682" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U682" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y682" s="4" t="s">
         <v>1940</v>
       </c>
@@ -46023,6 +46657,12 @@
       <c r="K683" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N683" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U683" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y683" s="4" t="s">
         <v>1942</v>
       </c>
@@ -46049,6 +46689,12 @@
       <c r="K684" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N684" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U684" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y684" s="4" t="s">
         <v>1944</v>
       </c>
@@ -46079,6 +46725,12 @@
       <c r="K685" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N685" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U685" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y685" s="4" t="s">
         <v>1946</v>
       </c>
@@ -46109,6 +46761,12 @@
       <c r="K686" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N686" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U686" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y686" s="4" t="s">
         <v>1948</v>
       </c>
@@ -46139,6 +46797,12 @@
       <c r="K687" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N687" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U687" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y687" s="4" t="s">
         <v>1950</v>
       </c>
@@ -46169,6 +46833,12 @@
       <c r="K688" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N688" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U688" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y688" s="4" t="s">
         <v>1952</v>
       </c>
@@ -46199,6 +46869,12 @@
       <c r="K689" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N689" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U689" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y689" s="4" t="s">
         <v>1954</v>
       </c>
@@ -46225,6 +46901,12 @@
       <c r="K690" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N690" s="38">
+        <v>11042</v>
+      </c>
+      <c r="U690" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y690" s="4" t="s">
         <v>1956</v>
       </c>
@@ -46258,6 +46940,12 @@
       <c r="K691" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N691" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U691" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y691" s="4" t="s">
         <v>1006</v>
       </c>
@@ -46291,6 +46979,12 @@
       <c r="K692" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N692" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U692" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y692" s="4" t="s">
         <v>1016</v>
       </c>
@@ -46324,6 +47018,12 @@
       <c r="K693" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N693" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U693" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y693" s="4" t="s">
         <v>1027</v>
       </c>
@@ -46357,6 +47057,12 @@
       <c r="K694" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N694" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U694" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y694" s="4" t="s">
         <v>1034</v>
       </c>
@@ -46390,6 +47096,12 @@
       <c r="K695" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N695" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U695" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y695" s="4" t="s">
         <v>1958</v>
       </c>
@@ -46419,6 +47131,12 @@
       <c r="K696" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N696" s="38">
+        <v>3205</v>
+      </c>
+      <c r="U696" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y696" s="4" t="s">
         <v>1960</v>
       </c>
@@ -46449,6 +47167,12 @@
       <c r="K697" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N697" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U697" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y697" s="4" t="s">
         <v>1008</v>
       </c>
@@ -46479,6 +47203,12 @@
       <c r="K698" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N698" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U698" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y698" s="4" t="s">
         <v>1962</v>
       </c>
@@ -46509,6 +47239,12 @@
       <c r="K699" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N699" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U699" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y699" s="4" t="s">
         <v>1023</v>
       </c>
@@ -46539,6 +47275,12 @@
       <c r="K700" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N700" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U700" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y700" s="4" t="s">
         <v>1964</v>
       </c>
@@ -46569,6 +47311,12 @@
       <c r="K701" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N701" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U701" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y701" s="4" t="s">
         <v>1966</v>
       </c>
@@ -46595,6 +47343,12 @@
       <c r="K702" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N702" s="38">
+        <v>3308</v>
+      </c>
+      <c r="U702" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y702" s="4" t="s">
         <v>1968</v>
       </c>
@@ -46625,6 +47379,12 @@
       <c r="K703" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N703" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U703" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y703" s="4" t="s">
         <v>1970</v>
       </c>
@@ -46655,6 +47415,12 @@
       <c r="K704" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N704" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U704" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y704" s="4" t="s">
         <v>1972</v>
       </c>
@@ -46685,6 +47451,12 @@
       <c r="K705" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N705" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U705" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y705" s="4" t="s">
         <v>1974</v>
       </c>
@@ -46715,6 +47487,12 @@
       <c r="K706" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N706" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U706" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y706" s="4" t="s">
         <v>1976</v>
       </c>
@@ -46745,6 +47523,12 @@
       <c r="K707" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N707" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U707" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y707" s="4" t="s">
         <v>1978</v>
       </c>
@@ -46771,6 +47555,12 @@
       <c r="K708" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N708" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U708" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y708" s="4" t="s">
         <v>1980</v>
       </c>
@@ -46801,6 +47591,12 @@
       <c r="K709" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N709" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U709" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y709" s="4" t="s">
         <v>1982</v>
       </c>
@@ -46831,6 +47627,12 @@
       <c r="K710" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N710" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U710" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y710" s="4" t="s">
         <v>1984</v>
       </c>
@@ -46861,6 +47663,12 @@
       <c r="K711" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N711" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U711" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y711" s="4" t="s">
         <v>1986</v>
       </c>
@@ -46891,6 +47699,12 @@
       <c r="K712" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N712" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U712" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y712" s="4" t="s">
         <v>1988</v>
       </c>
@@ -46921,6 +47735,12 @@
       <c r="K713" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N713" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U713" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y713" s="4" t="s">
         <v>1990</v>
       </c>
@@ -46947,6 +47767,12 @@
       <c r="K714" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N714" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U714" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y714" s="4" t="s">
         <v>1992</v>
       </c>
@@ -46977,6 +47803,12 @@
       <c r="K715" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N715" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U715" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y715" s="4" t="s">
         <v>1994</v>
       </c>
@@ -47007,6 +47839,12 @@
       <c r="K716" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N716" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U716" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y716" s="4" t="s">
         <v>1996</v>
       </c>
@@ -47037,6 +47875,12 @@
       <c r="K717" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N717" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U717" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y717" s="4" t="s">
         <v>1998</v>
       </c>
@@ -47067,6 +47911,12 @@
       <c r="K718" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N718" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U718" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y718" s="4" t="s">
         <v>2000</v>
       </c>
@@ -47097,6 +47947,12 @@
       <c r="K719" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N719" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U719" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y719" s="4" t="s">
         <v>2002</v>
       </c>
@@ -47123,6 +47979,12 @@
       <c r="K720" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N720" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U720" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y720" s="4" t="s">
         <v>2004</v>
       </c>
@@ -47153,6 +48015,12 @@
       <c r="K721" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N721" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U721" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y721" s="4" t="s">
         <v>2006</v>
       </c>
@@ -47183,6 +48051,12 @@
       <c r="K722" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N722" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U722" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y722" s="4" t="s">
         <v>2008</v>
       </c>
@@ -47213,6 +48087,12 @@
       <c r="K723" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N723" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U723" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y723" s="4" t="s">
         <v>2010</v>
       </c>
@@ -47243,6 +48123,12 @@
       <c r="K724" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N724" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U724" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y724" s="4" t="s">
         <v>2012</v>
       </c>
@@ -47273,6 +48159,12 @@
       <c r="K725" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N725" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U725" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y725" s="4" t="s">
         <v>2014</v>
       </c>
@@ -47299,6 +48191,12 @@
       <c r="K726" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N726" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U726" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y726" s="4" t="s">
         <v>2016</v>
       </c>
@@ -47329,6 +48227,12 @@
       <c r="K727" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N727" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U727" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y727" s="4" t="s">
         <v>2018</v>
       </c>
@@ -47359,6 +48263,12 @@
       <c r="K728" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N728" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U728" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y728" s="4" t="s">
         <v>2020</v>
       </c>
@@ -47389,6 +48299,12 @@
       <c r="K729" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N729" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U729" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y729" s="4" t="s">
         <v>2022</v>
       </c>
@@ -47419,6 +48335,12 @@
       <c r="K730" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N730" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U730" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y730" s="4" t="s">
         <v>2024</v>
       </c>
@@ -47449,6 +48371,12 @@
       <c r="K731" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N731" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U731" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y731" s="4" t="s">
         <v>2026</v>
       </c>
@@ -47479,6 +48407,12 @@
       <c r="K732" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N732" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U732" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y732" s="4" t="s">
         <v>2028</v>
       </c>
@@ -47509,6 +48443,12 @@
       <c r="K733" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N733" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U733" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y733" s="4" t="s">
         <v>2030</v>
       </c>
@@ -47535,6 +48475,12 @@
       <c r="K734" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N734" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U734" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y734" s="4" t="s">
         <v>2032</v>
       </c>
@@ -47565,6 +48511,12 @@
       <c r="K735" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N735" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U735" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y735" s="4" t="s">
         <v>2034</v>
       </c>
@@ -47595,6 +48547,12 @@
       <c r="K736" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N736" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U736" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y736" s="4" t="s">
         <v>2036</v>
       </c>
@@ -47625,6 +48583,12 @@
       <c r="K737" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N737" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U737" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y737" s="4" t="s">
         <v>2038</v>
       </c>
@@ -47655,6 +48619,12 @@
       <c r="K738" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N738" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U738" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y738" s="4" t="s">
         <v>2040</v>
       </c>
@@ -47685,6 +48655,12 @@
       <c r="K739" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N739" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U739" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y739" s="4" t="s">
         <v>2042</v>
       </c>
@@ -47711,6 +48687,12 @@
       <c r="K740" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N740" s="38">
+        <v>11003</v>
+      </c>
+      <c r="U740" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y740" s="4" t="s">
         <v>2044</v>
       </c>
@@ -47744,6 +48726,12 @@
       <c r="K741" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N741" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U741" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y741" s="4" t="s">
         <v>955</v>
       </c>
@@ -47777,6 +48765,12 @@
       <c r="K742" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N742" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U742" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y742" s="4" t="s">
         <v>965</v>
       </c>
@@ -47810,6 +48804,12 @@
       <c r="K743" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N743" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U743" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y743" s="4" t="s">
         <v>976</v>
       </c>
@@ -47843,6 +48843,12 @@
       <c r="K744" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N744" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U744" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y744" s="4" t="s">
         <v>983</v>
       </c>
@@ -47876,6 +48882,12 @@
       <c r="K745" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N745" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U745" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y745" s="4" t="s">
         <v>2047</v>
       </c>
@@ -47905,6 +48917,12 @@
       <c r="K746" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N746" s="38">
+        <v>3206</v>
+      </c>
+      <c r="U746" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y746" s="4" t="s">
         <v>2049</v>
       </c>
@@ -47935,6 +48953,12 @@
       <c r="K747" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N747" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U747" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y747" s="4" t="s">
         <v>957</v>
       </c>
@@ -47965,6 +48989,12 @@
       <c r="K748" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N748" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U748" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y748" s="4" t="s">
         <v>2051</v>
       </c>
@@ -47995,6 +49025,12 @@
       <c r="K749" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N749" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U749" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y749" s="4" t="s">
         <v>972</v>
       </c>
@@ -48025,6 +49061,12 @@
       <c r="K750" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N750" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U750" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y750" s="4" t="s">
         <v>2053</v>
       </c>
@@ -48055,6 +49097,12 @@
       <c r="K751" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N751" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U751" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y751" s="4" t="s">
         <v>985</v>
       </c>
@@ -48081,6 +49129,12 @@
       <c r="K752" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N752" s="38">
+        <v>3307</v>
+      </c>
+      <c r="U752" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y752" s="4" t="s">
         <v>2055</v>
       </c>
@@ -48111,6 +49165,12 @@
       <c r="K753" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N753" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U753" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y753" s="4" t="s">
         <v>2057</v>
       </c>
@@ -48141,6 +49201,12 @@
       <c r="K754" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N754" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U754" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y754" s="4" t="s">
         <v>2059</v>
       </c>
@@ -48171,6 +49237,12 @@
       <c r="K755" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N755" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U755" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y755" s="4" t="s">
         <v>2061</v>
       </c>
@@ -48201,6 +49273,12 @@
       <c r="K756" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N756" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U756" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y756" s="4" t="s">
         <v>2063</v>
       </c>
@@ -48231,6 +49309,12 @@
       <c r="K757" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N757" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U757" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y757" s="4" t="s">
         <v>2065</v>
       </c>
@@ -48257,6 +49341,12 @@
       <c r="K758" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N758" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U758" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y758" s="4" t="s">
         <v>2067</v>
       </c>
@@ -48287,6 +49377,12 @@
       <c r="K759" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N759" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U759" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y759" s="4" t="s">
         <v>2069</v>
       </c>
@@ -48317,6 +49413,12 @@
       <c r="K760" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N760" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U760" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y760" s="4" t="s">
         <v>2071</v>
       </c>
@@ -48347,6 +49449,12 @@
       <c r="K761" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N761" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U761" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y761" s="4" t="s">
         <v>2073</v>
       </c>
@@ -48377,6 +49485,12 @@
       <c r="K762" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N762" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U762" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y762" s="4" t="s">
         <v>2075</v>
       </c>
@@ -48407,6 +49521,12 @@
       <c r="K763" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N763" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U763" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y763" s="4" t="s">
         <v>2077</v>
       </c>
@@ -48433,6 +49553,12 @@
       <c r="K764" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N764" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U764" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y764" s="4" t="s">
         <v>2079</v>
       </c>
@@ -48463,6 +49589,12 @@
       <c r="K765" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N765" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U765" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y765" s="4" t="s">
         <v>2081</v>
       </c>
@@ -48493,6 +49625,12 @@
       <c r="K766" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N766" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U766" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y766" s="4" t="s">
         <v>2083</v>
       </c>
@@ -48523,6 +49661,12 @@
       <c r="K767" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N767" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U767" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y767" s="4" t="s">
         <v>2085</v>
       </c>
@@ -48553,6 +49697,12 @@
       <c r="K768" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N768" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U768" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y768" s="4" t="s">
         <v>2087</v>
       </c>
@@ -48583,6 +49733,12 @@
       <c r="K769" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N769" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U769" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y769" s="4" t="s">
         <v>2089</v>
       </c>
@@ -48609,6 +49765,12 @@
       <c r="K770" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N770" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U770" s="50">
+        <v>76010</v>
+      </c>
       <c r="Y770" s="4" t="s">
         <v>2091</v>
       </c>
@@ -48639,6 +49801,12 @@
       <c r="K771" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N771" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U771" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y771" s="4" t="s">
         <v>2093</v>
       </c>
@@ -48669,6 +49837,12 @@
       <c r="K772" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N772" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U772" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y772" s="4" t="s">
         <v>2095</v>
       </c>
@@ -48699,6 +49873,12 @@
       <c r="K773" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N773" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U773" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y773" s="4" t="s">
         <v>2097</v>
       </c>
@@ -48729,6 +49909,12 @@
       <c r="K774" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N774" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U774" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y774" s="4" t="s">
         <v>2099</v>
       </c>
@@ -48759,6 +49945,12 @@
       <c r="K775" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N775" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U775" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y775" s="4" t="s">
         <v>2101</v>
       </c>
@@ -48785,6 +49977,12 @@
       <c r="K776" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N776" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U776" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y776" s="4" t="s">
         <v>2103</v>
       </c>
@@ -48815,6 +50013,12 @@
       <c r="K777" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N777" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U777" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y777" s="4" t="s">
         <v>2105</v>
       </c>
@@ -48845,6 +50049,12 @@
       <c r="K778" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N778" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U778" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y778" s="4" t="s">
         <v>2107</v>
       </c>
@@ -48875,6 +50085,12 @@
       <c r="K779" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N779" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U779" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y779" s="4" t="s">
         <v>2109</v>
       </c>
@@ -48905,6 +50121,12 @@
       <c r="K780" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N780" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U780" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y780" s="4" t="s">
         <v>2111</v>
       </c>
@@ -48935,6 +50157,12 @@
       <c r="K781" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N781" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U781" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y781" s="4" t="s">
         <v>2113</v>
       </c>
@@ -48965,6 +50193,12 @@
       <c r="K782" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N782" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U782" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y782" s="4" t="s">
         <v>2115</v>
       </c>
@@ -48995,6 +50229,12 @@
       <c r="K783" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N783" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U783" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y783" s="4" t="s">
         <v>2117</v>
       </c>
@@ -49021,6 +50261,12 @@
       <c r="K784" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N784" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U784" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y784" s="4" t="s">
         <v>2119</v>
       </c>
@@ -49051,6 +50297,12 @@
       <c r="K785" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N785" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U785" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y785" s="4" t="s">
         <v>2121</v>
       </c>
@@ -49081,6 +50333,12 @@
       <c r="K786" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N786" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U786" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y786" s="4" t="s">
         <v>2123</v>
       </c>
@@ -49111,6 +50369,12 @@
       <c r="K787" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N787" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U787" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y787" s="4" t="s">
         <v>2125</v>
       </c>
@@ -49141,6 +50405,12 @@
       <c r="K788" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N788" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U788" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y788" s="4" t="s">
         <v>2127</v>
       </c>
@@ -49171,6 +50441,12 @@
       <c r="K789" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N789" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U789" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y789" s="4" t="s">
         <v>2129</v>
       </c>
@@ -49197,6 +50473,12 @@
       <c r="K790" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N790" s="38">
+        <v>11012</v>
+      </c>
+      <c r="U790" s="50">
+        <v>76009</v>
+      </c>
       <c r="Y790" s="4" t="s">
         <v>2131</v>
       </c>
@@ -49230,6 +50512,12 @@
       <c r="K791" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N791" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U791" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y791" s="4" t="s">
         <v>904</v>
       </c>
@@ -49263,6 +50551,12 @@
       <c r="K792" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N792" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U792" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y792" s="4" t="s">
         <v>914</v>
       </c>
@@ -49296,6 +50590,12 @@
       <c r="K793" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N793" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U793" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y793" s="4" t="s">
         <v>925</v>
       </c>
@@ -49329,6 +50629,12 @@
       <c r="K794" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N794" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U794" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y794" s="4" t="s">
         <v>932</v>
       </c>
@@ -49362,6 +50668,12 @@
       <c r="K795" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N795" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U795" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y795" s="4" t="s">
         <v>2134</v>
       </c>
@@ -49391,6 +50703,12 @@
       <c r="K796" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N796" s="38">
+        <v>3207</v>
+      </c>
+      <c r="U796" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y796" s="4" t="s">
         <v>2136</v>
       </c>
@@ -49421,6 +50739,12 @@
       <c r="K797" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N797" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U797" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y797" s="4" t="s">
         <v>906</v>
       </c>
@@ -49451,6 +50775,12 @@
       <c r="K798" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N798" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U798" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y798" s="4" t="s">
         <v>2138</v>
       </c>
@@ -49481,6 +50811,12 @@
       <c r="K799" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N799" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U799" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y799" s="4" t="s">
         <v>921</v>
       </c>
@@ -49511,6 +50847,12 @@
       <c r="K800" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N800" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U800" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y800" s="4" t="s">
         <v>2140</v>
       </c>
@@ -49541,6 +50883,12 @@
       <c r="K801" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N801" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U801" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y801" s="4" t="s">
         <v>2142</v>
       </c>
@@ -49567,6 +50915,12 @@
       <c r="K802" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N802" s="38">
+        <v>3306</v>
+      </c>
+      <c r="U802" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y802" s="4" t="s">
         <v>2144</v>
       </c>
@@ -49597,6 +50951,12 @@
       <c r="K803" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N803" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U803" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y803" s="4" t="s">
         <v>2146</v>
       </c>
@@ -49627,6 +50987,12 @@
       <c r="K804" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N804" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U804" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y804" s="4" t="s">
         <v>2148</v>
       </c>
@@ -49657,6 +51023,12 @@
       <c r="K805" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N805" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U805" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y805" s="4" t="s">
         <v>2150</v>
       </c>
@@ -49687,6 +51059,12 @@
       <c r="K806" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N806" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U806" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y806" s="4" t="s">
         <v>2152</v>
       </c>
@@ -49717,6 +51095,12 @@
       <c r="K807" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N807" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U807" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y807" s="4" t="s">
         <v>2154</v>
       </c>
@@ -49743,6 +51127,12 @@
       <c r="K808" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N808" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U808" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y808" s="4" t="s">
         <v>2156</v>
       </c>
@@ -49773,6 +51163,12 @@
       <c r="K809" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N809" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U809" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y809" s="4" t="s">
         <v>2158</v>
       </c>
@@ -49803,6 +51199,12 @@
       <c r="K810" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N810" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U810" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y810" s="4" t="s">
         <v>2160</v>
       </c>
@@ -49833,6 +51235,12 @@
       <c r="K811" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N811" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U811" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y811" s="4" t="s">
         <v>2162</v>
       </c>
@@ -49863,6 +51271,12 @@
       <c r="K812" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N812" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U812" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y812" s="4" t="s">
         <v>2164</v>
       </c>
@@ -49893,6 +51307,12 @@
       <c r="K813" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N813" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U813" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y813" s="4" t="s">
         <v>2166</v>
       </c>
@@ -49919,6 +51339,12 @@
       <c r="K814" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N814" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U814" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y814" s="4" t="s">
         <v>2168</v>
       </c>
@@ -49949,6 +51375,12 @@
       <c r="K815" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N815" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U815" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y815" s="4" t="s">
         <v>2170</v>
       </c>
@@ -49979,6 +51411,12 @@
       <c r="K816" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N816" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U816" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y816" s="4" t="s">
         <v>2172</v>
       </c>
@@ -50009,6 +51447,12 @@
       <c r="K817" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N817" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U817" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y817" s="4" t="s">
         <v>2174</v>
       </c>
@@ -50039,6 +51483,12 @@
       <c r="K818" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N818" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U818" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y818" s="4" t="s">
         <v>2176</v>
       </c>
@@ -50069,6 +51519,12 @@
       <c r="K819" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N819" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U819" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y819" s="4" t="s">
         <v>2178</v>
       </c>
@@ -50095,6 +51551,12 @@
       <c r="K820" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N820" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U820" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y820" s="4" t="s">
         <v>2180</v>
       </c>
@@ -50125,6 +51587,12 @@
       <c r="K821" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N821" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U821" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y821" s="4" t="s">
         <v>2182</v>
       </c>
@@ -50155,6 +51623,12 @@
       <c r="K822" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N822" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U822" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y822" s="4" t="s">
         <v>2184</v>
       </c>
@@ -50185,6 +51659,12 @@
       <c r="K823" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N823" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U823" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y823" s="4" t="s">
         <v>2186</v>
       </c>
@@ -50215,6 +51695,12 @@
       <c r="K824" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N824" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U824" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y824" s="4" t="s">
         <v>2188</v>
       </c>
@@ -50245,6 +51731,12 @@
       <c r="K825" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N825" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U825" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y825" s="4" t="s">
         <v>2190</v>
       </c>
@@ -50271,6 +51763,12 @@
       <c r="K826" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N826" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U826" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y826" s="4" t="s">
         <v>2192</v>
       </c>
@@ -50301,6 +51799,12 @@
       <c r="K827" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N827" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U827" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y827" s="4" t="s">
         <v>2194</v>
       </c>
@@ -50331,6 +51835,12 @@
       <c r="K828" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N828" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U828" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y828" s="4" t="s">
         <v>2196</v>
       </c>
@@ -50361,6 +51871,12 @@
       <c r="K829" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N829" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U829" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y829" s="4" t="s">
         <v>2198</v>
       </c>
@@ -50391,6 +51907,12 @@
       <c r="K830" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N830" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U830" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y830" s="4" t="s">
         <v>2200</v>
       </c>
@@ -50421,6 +51943,12 @@
       <c r="K831" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N831" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U831" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y831" s="4" t="s">
         <v>2202</v>
       </c>
@@ -50451,6 +51979,12 @@
       <c r="K832" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N832" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U832" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y832" s="4" t="s">
         <v>2204</v>
       </c>
@@ -50481,6 +52015,12 @@
       <c r="K833" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N833" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U833" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y833" s="4" t="s">
         <v>2206</v>
       </c>
@@ -50507,6 +52047,12 @@
       <c r="K834" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N834" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U834" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y834" s="4" t="s">
         <v>2208</v>
       </c>
@@ -50537,6 +52083,12 @@
       <c r="K835" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N835" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U835" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y835" s="4" t="s">
         <v>2210</v>
       </c>
@@ -50567,6 +52119,12 @@
       <c r="K836" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N836" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U836" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y836" s="4" t="s">
         <v>2212</v>
       </c>
@@ -50597,6 +52155,12 @@
       <c r="K837" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N837" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U837" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y837" s="4" t="s">
         <v>2214</v>
       </c>
@@ -50627,6 +52191,12 @@
       <c r="K838" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N838" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U838" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y838" s="4" t="s">
         <v>2216</v>
       </c>
@@ -50657,6 +52227,12 @@
       <c r="K839" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N839" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U839" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y839" s="4" t="s">
         <v>2218</v>
       </c>
@@ -50683,6 +52259,12 @@
       <c r="K840" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N840" s="38">
+        <v>11028</v>
+      </c>
+      <c r="U840" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y840" s="4" t="s">
         <v>2220</v>
       </c>
@@ -50716,6 +52298,12 @@
       <c r="K841" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N841" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U841" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y841" s="4" t="s">
         <v>853</v>
       </c>
@@ -50749,6 +52337,12 @@
       <c r="K842" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N842" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U842" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y842" s="4" t="s">
         <v>863</v>
       </c>
@@ -50782,6 +52376,12 @@
       <c r="K843" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N843" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U843" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y843" s="4" t="s">
         <v>874</v>
       </c>
@@ -50815,6 +52415,12 @@
       <c r="K844" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N844" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U844" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y844" s="4" t="s">
         <v>881</v>
       </c>
@@ -50848,6 +52454,12 @@
       <c r="K845" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N845" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U845" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y845" s="4" t="s">
         <v>2223</v>
       </c>
@@ -50877,6 +52489,12 @@
       <c r="K846" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N846" s="38">
+        <v>3208</v>
+      </c>
+      <c r="U846" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y846" s="4" t="s">
         <v>2225</v>
       </c>
@@ -50907,6 +52525,12 @@
       <c r="K847" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N847" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U847" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y847" s="4" t="s">
         <v>855</v>
       </c>
@@ -50937,6 +52561,12 @@
       <c r="K848" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N848" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U848" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y848" s="4" t="s">
         <v>2227</v>
       </c>
@@ -50967,6 +52597,12 @@
       <c r="K849" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N849" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U849" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y849" s="4" t="s">
         <v>2229</v>
       </c>
@@ -50997,6 +52633,12 @@
       <c r="K850" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N850" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U850" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y850" s="4" t="s">
         <v>2231</v>
       </c>
@@ -51027,6 +52669,12 @@
       <c r="K851" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N851" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U851" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y851" s="4" t="s">
         <v>2233</v>
       </c>
@@ -51053,6 +52701,12 @@
       <c r="K852" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N852" s="38">
+        <v>3305</v>
+      </c>
+      <c r="U852" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y852" s="4" t="s">
         <v>2235</v>
       </c>
@@ -51083,6 +52737,12 @@
       <c r="K853" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N853" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U853" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y853" s="4" t="s">
         <v>2237</v>
       </c>
@@ -51113,6 +52773,12 @@
       <c r="K854" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N854" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U854" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y854" s="4" t="s">
         <v>2239</v>
       </c>
@@ -51143,6 +52809,12 @@
       <c r="K855" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N855" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U855" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y855" s="4" t="s">
         <v>2241</v>
       </c>
@@ -51173,6 +52845,12 @@
       <c r="K856" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N856" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U856" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y856" s="4" t="s">
         <v>2243</v>
       </c>
@@ -51203,6 +52881,12 @@
       <c r="K857" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N857" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U857" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y857" s="4" t="s">
         <v>2245</v>
       </c>
@@ -51229,6 +52913,12 @@
       <c r="K858" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N858" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U858" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y858" s="4" t="s">
         <v>2247</v>
       </c>
@@ -51259,6 +52949,12 @@
       <c r="K859" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N859" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U859" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y859" s="4" t="s">
         <v>2249</v>
       </c>
@@ -51289,6 +52985,12 @@
       <c r="K860" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N860" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U860" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y860" s="4" t="s">
         <v>2251</v>
       </c>
@@ -51319,6 +53021,12 @@
       <c r="K861" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N861" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U861" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y861" s="4" t="s">
         <v>2253</v>
       </c>
@@ -51349,6 +53057,12 @@
       <c r="K862" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N862" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U862" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y862" s="4" t="s">
         <v>2255</v>
       </c>
@@ -51379,6 +53093,12 @@
       <c r="K863" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N863" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U863" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y863" s="4" t="s">
         <v>2257</v>
       </c>
@@ -51405,6 +53125,12 @@
       <c r="K864" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N864" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U864" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y864" s="4" t="s">
         <v>2259</v>
       </c>
@@ -51435,6 +53161,12 @@
       <c r="K865" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N865" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U865" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y865" s="4" t="s">
         <v>2261</v>
       </c>
@@ -51465,6 +53197,12 @@
       <c r="K866" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N866" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U866" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y866" s="4" t="s">
         <v>2263</v>
       </c>
@@ -51495,6 +53233,12 @@
       <c r="K867" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N867" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U867" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y867" s="4" t="s">
         <v>2265</v>
       </c>
@@ -51525,6 +53269,12 @@
       <c r="K868" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N868" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U868" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y868" s="4" t="s">
         <v>2267</v>
       </c>
@@ -51555,6 +53305,12 @@
       <c r="K869" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N869" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U869" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y869" s="4" t="s">
         <v>2269</v>
       </c>
@@ -51581,6 +53337,12 @@
       <c r="K870" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N870" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U870" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y870" s="4" t="s">
         <v>2271</v>
       </c>
@@ -51611,6 +53373,12 @@
       <c r="K871" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N871" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U871" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y871" s="4" t="s">
         <v>2273</v>
       </c>
@@ -51641,6 +53409,12 @@
       <c r="K872" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N872" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U872" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y872" s="4" t="s">
         <v>2275</v>
       </c>
@@ -51671,6 +53445,12 @@
       <c r="K873" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N873" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U873" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y873" s="4" t="s">
         <v>2277</v>
       </c>
@@ -51701,6 +53481,12 @@
       <c r="K874" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N874" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U874" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y874" s="4" t="s">
         <v>2279</v>
       </c>
@@ -51731,6 +53517,12 @@
       <c r="K875" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N875" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U875" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y875" s="4" t="s">
         <v>2281</v>
       </c>
@@ -51757,6 +53549,12 @@
       <c r="K876" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N876" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U876" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y876" s="4" t="s">
         <v>2283</v>
       </c>
@@ -51787,6 +53585,12 @@
       <c r="K877" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N877" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U877" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y877" s="4" t="s">
         <v>2285</v>
       </c>
@@ -51817,6 +53621,12 @@
       <c r="K878" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N878" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U878" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y878" s="4" t="s">
         <v>2287</v>
       </c>
@@ -51847,6 +53657,12 @@
       <c r="K879" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N879" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U879" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y879" s="4" t="s">
         <v>2289</v>
       </c>
@@ -51877,6 +53693,12 @@
       <c r="K880" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N880" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U880" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y880" s="4" t="s">
         <v>2291</v>
       </c>
@@ -51907,6 +53729,12 @@
       <c r="K881" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N881" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U881" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y881" s="4" t="s">
         <v>2293</v>
       </c>
@@ -51937,6 +53765,12 @@
       <c r="K882" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N882" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U882" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y882" s="4" t="s">
         <v>2295</v>
       </c>
@@ -51967,6 +53801,12 @@
       <c r="K883" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N883" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U883" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y883" s="4" t="s">
         <v>2297</v>
       </c>
@@ -51993,6 +53833,12 @@
       <c r="K884" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N884" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U884" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y884" s="4" t="s">
         <v>2299</v>
       </c>
@@ -52023,6 +53869,12 @@
       <c r="K885" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N885" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U885" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y885" s="4" t="s">
         <v>2301</v>
       </c>
@@ -52053,6 +53905,12 @@
       <c r="K886" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N886" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U886" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y886" s="4" t="s">
         <v>2303</v>
       </c>
@@ -52083,6 +53941,12 @@
       <c r="K887" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N887" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U887" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y887" s="4" t="s">
         <v>2305</v>
       </c>
@@ -52113,6 +53977,12 @@
       <c r="K888" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N888" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U888" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y888" s="4" t="s">
         <v>2307</v>
       </c>
@@ -52143,6 +54013,12 @@
       <c r="K889" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N889" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U889" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y889" s="4" t="s">
         <v>2309</v>
       </c>
@@ -52169,6 +54045,12 @@
       <c r="K890" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N890" s="38">
+        <v>11043</v>
+      </c>
+      <c r="U890" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y890" s="4" t="s">
         <v>2311</v>
       </c>
@@ -52202,6 +54084,12 @@
       <c r="K891" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N891" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U891" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y891" s="4" t="s">
         <v>811</v>
       </c>
@@ -52235,6 +54123,12 @@
       <c r="K892" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N892" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U892" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y892" s="4" t="s">
         <v>2314</v>
       </c>
@@ -52268,6 +54162,12 @@
       <c r="K893" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N893" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U893" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y893" s="4" t="s">
         <v>2316</v>
       </c>
@@ -52301,6 +54201,12 @@
       <c r="K894" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N894" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U894" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y894" s="4" t="s">
         <v>2318</v>
       </c>
@@ -52334,6 +54240,12 @@
       <c r="K895" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N895" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U895" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y895" s="4" t="s">
         <v>2320</v>
       </c>
@@ -52363,6 +54275,12 @@
       <c r="K896" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N896" s="38">
+        <v>3204</v>
+      </c>
+      <c r="U896" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y896" s="4" t="s">
         <v>2322</v>
       </c>
@@ -52393,6 +54311,12 @@
       <c r="K897" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N897" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U897" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y897" s="4" t="s">
         <v>816</v>
       </c>
@@ -52423,6 +54347,12 @@
       <c r="K898" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N898" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U898" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y898" s="4" t="s">
         <v>826</v>
       </c>
@@ -52453,6 +54383,12 @@
       <c r="K899" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N899" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U899" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y899" s="4" t="s">
         <v>2324</v>
       </c>
@@ -52483,6 +54419,12 @@
       <c r="K900" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N900" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U900" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y900" s="4" t="s">
         <v>2326</v>
       </c>
@@ -52513,6 +54455,12 @@
       <c r="K901" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N901" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U901" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y901" s="4" t="s">
         <v>2328</v>
       </c>
@@ -52539,6 +54487,12 @@
       <c r="K902" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N902" s="38">
+        <v>3304</v>
+      </c>
+      <c r="U902" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y902" s="4" t="s">
         <v>2330</v>
       </c>
@@ -52569,6 +54523,12 @@
       <c r="K903" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N903" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U903" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y903" s="4" t="s">
         <v>2332</v>
       </c>
@@ -52599,6 +54559,12 @@
       <c r="K904" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N904" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U904" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y904" s="4" t="s">
         <v>2334</v>
       </c>
@@ -52629,6 +54595,12 @@
       <c r="K905" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N905" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U905" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y905" s="4" t="s">
         <v>2336</v>
       </c>
@@ -52659,6 +54631,12 @@
       <c r="K906" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N906" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U906" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y906" s="4" t="s">
         <v>2338</v>
       </c>
@@ -52689,6 +54667,12 @@
       <c r="K907" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N907" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U907" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y907" s="4" t="s">
         <v>2340</v>
       </c>
@@ -52715,6 +54699,12 @@
       <c r="K908" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N908" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U908" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y908" s="4" t="s">
         <v>2342</v>
       </c>
@@ -52745,6 +54735,12 @@
       <c r="K909" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N909" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U909" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y909" s="4" t="s">
         <v>2344</v>
       </c>
@@ -52775,6 +54771,12 @@
       <c r="K910" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N910" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U910" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y910" s="4" t="s">
         <v>2346</v>
       </c>
@@ -52805,6 +54807,12 @@
       <c r="K911" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N911" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U911" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y911" s="4" t="s">
         <v>2348</v>
       </c>
@@ -52835,6 +54843,12 @@
       <c r="K912" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N912" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U912" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y912" s="4" t="s">
         <v>2350</v>
       </c>
@@ -52865,6 +54879,12 @@
       <c r="K913" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N913" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U913" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y913" s="4" t="s">
         <v>2352</v>
       </c>
@@ -52891,6 +54911,12 @@
       <c r="K914" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N914" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U914" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y914" s="4" t="s">
         <v>2354</v>
       </c>
@@ -52921,6 +54947,12 @@
       <c r="K915" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N915" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U915" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y915" s="4" t="s">
         <v>2356</v>
       </c>
@@ -52951,6 +54983,12 @@
       <c r="K916" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N916" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U916" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y916" s="4" t="s">
         <v>2358</v>
       </c>
@@ -52981,6 +55019,12 @@
       <c r="K917" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N917" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U917" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y917" s="4" t="s">
         <v>2360</v>
       </c>
@@ -53011,6 +55055,12 @@
       <c r="K918" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N918" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U918" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y918" s="4" t="s">
         <v>2362</v>
       </c>
@@ -53041,6 +55091,12 @@
       <c r="K919" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N919" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U919" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y919" s="4" t="s">
         <v>2364</v>
       </c>
@@ -53067,6 +55123,12 @@
       <c r="K920" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N920" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U920" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y920" s="4" t="s">
         <v>2366</v>
       </c>
@@ -53097,6 +55159,12 @@
       <c r="K921" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N921" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U921" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y921" s="4" t="s">
         <v>2368</v>
       </c>
@@ -53127,6 +55195,12 @@
       <c r="K922" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N922" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U922" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y922" s="4" t="s">
         <v>2370</v>
       </c>
@@ -53157,6 +55231,12 @@
       <c r="K923" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N923" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U923" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y923" s="4" t="s">
         <v>2372</v>
       </c>
@@ -53187,6 +55267,12 @@
       <c r="K924" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N924" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U924" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y924" s="4" t="s">
         <v>2374</v>
       </c>
@@ -53217,6 +55303,12 @@
       <c r="K925" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N925" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U925" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y925" s="4" t="s">
         <v>2376</v>
       </c>
@@ -53243,6 +55335,12 @@
       <c r="K926" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N926" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U926" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y926" s="4" t="s">
         <v>2378</v>
       </c>
@@ -53273,6 +55371,12 @@
       <c r="K927" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N927" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U927" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y927" s="4" t="s">
         <v>2380</v>
       </c>
@@ -53303,6 +55407,12 @@
       <c r="K928" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N928" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U928" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y928" s="4" t="s">
         <v>2382</v>
       </c>
@@ -53333,6 +55443,12 @@
       <c r="K929" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N929" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U929" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y929" s="4" t="s">
         <v>2384</v>
       </c>
@@ -53363,6 +55479,12 @@
       <c r="K930" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N930" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U930" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y930" s="4" t="s">
         <v>2386</v>
       </c>
@@ -53393,6 +55515,12 @@
       <c r="K931" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N931" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U931" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y931" s="4" t="s">
         <v>2388</v>
       </c>
@@ -53423,6 +55551,12 @@
       <c r="K932" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N932" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U932" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y932" s="4" t="s">
         <v>2390</v>
       </c>
@@ -53453,6 +55587,12 @@
       <c r="K933" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N933" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U933" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y933" s="4" t="s">
         <v>2392</v>
       </c>
@@ -53479,6 +55619,12 @@
       <c r="K934" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N934" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U934" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y934" s="4" t="s">
         <v>2394</v>
       </c>
@@ -53509,6 +55655,12 @@
       <c r="K935" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N935" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U935" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y935" s="4" t="s">
         <v>2396</v>
       </c>
@@ -53539,6 +55691,12 @@
       <c r="K936" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N936" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U936" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y936" s="4" t="s">
         <v>2398</v>
       </c>
@@ -53569,6 +55727,12 @@
       <c r="K937" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N937" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U937" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y937" s="4" t="s">
         <v>2400</v>
       </c>
@@ -53599,6 +55763,12 @@
       <c r="K938" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N938" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U938" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y938" s="4" t="s">
         <v>2402</v>
       </c>
@@ -53629,6 +55799,12 @@
       <c r="K939" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N939" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U939" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y939" s="4" t="s">
         <v>2404</v>
       </c>
@@ -53655,6 +55831,12 @@
       <c r="K940" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N940" s="38">
+        <v>11027</v>
+      </c>
+      <c r="U940" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y940" s="4" t="s">
         <v>2406</v>
       </c>
@@ -53688,6 +55870,12 @@
       <c r="K941" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N941" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U941" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y941" s="4" t="s">
         <v>2408</v>
       </c>
@@ -53721,6 +55909,12 @@
       <c r="K942" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N942" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U942" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y942" s="4" t="s">
         <v>2409</v>
       </c>
@@ -53754,6 +55948,12 @@
       <c r="K943" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N943" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U943" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y943" s="4" t="s">
         <v>2410</v>
       </c>
@@ -53787,6 +55987,12 @@
       <c r="K944" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N944" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U944" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y944" s="4" t="s">
         <v>2411</v>
       </c>
@@ -53820,6 +56026,12 @@
       <c r="K945" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N945" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U945" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y945" s="4" t="s">
         <v>2413</v>
       </c>
@@ -53849,6 +56061,12 @@
       <c r="K946" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N946" s="38">
+        <v>3211</v>
+      </c>
+      <c r="U946" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y946" s="4" t="s">
         <v>2415</v>
       </c>
@@ -53879,6 +56097,12 @@
       <c r="K947" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N947" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U947" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y947" s="4" t="s">
         <v>2416</v>
       </c>
@@ -53909,6 +56133,12 @@
       <c r="K948" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N948" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U948" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y948" s="4" t="s">
         <v>2418</v>
       </c>
@@ -53939,6 +56169,12 @@
       <c r="K949" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N949" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U949" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y949" s="4" t="s">
         <v>2420</v>
       </c>
@@ -53969,6 +56205,12 @@
       <c r="K950" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N950" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U950" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y950" s="4" t="s">
         <v>2421</v>
       </c>
@@ -53999,6 +56241,12 @@
       <c r="K951" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N951" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U951" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y951" s="4" t="s">
         <v>2423</v>
       </c>
@@ -54025,6 +56273,12 @@
       <c r="K952" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N952" s="38">
+        <v>3310</v>
+      </c>
+      <c r="U952" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y952" s="4" t="s">
         <v>2425</v>
       </c>
@@ -54055,6 +56309,12 @@
       <c r="K953" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N953" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U953" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y953" s="4" t="s">
         <v>2427</v>
       </c>
@@ -54085,6 +56345,12 @@
       <c r="K954" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N954" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U954" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y954" s="4" t="s">
         <v>2429</v>
       </c>
@@ -54115,6 +56381,12 @@
       <c r="K955" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N955" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U955" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y955" s="4" t="s">
         <v>2431</v>
       </c>
@@ -54145,6 +56417,12 @@
       <c r="K956" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N956" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U956" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y956" s="4" t="s">
         <v>2433</v>
       </c>
@@ -54175,6 +56453,12 @@
       <c r="K957" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N957" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U957" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y957" s="4" t="s">
         <v>2435</v>
       </c>
@@ -54201,6 +56485,12 @@
       <c r="K958" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N958" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U958" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y958" s="4" t="s">
         <v>2437</v>
       </c>
@@ -54231,6 +56521,12 @@
       <c r="K959" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N959" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U959" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y959" s="4" t="s">
         <v>2439</v>
       </c>
@@ -54261,6 +56557,12 @@
       <c r="K960" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N960" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U960" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y960" s="4" t="s">
         <v>2441</v>
       </c>
@@ -54291,6 +56593,12 @@
       <c r="K961" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N961" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U961" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y961" s="4" t="s">
         <v>2443</v>
       </c>
@@ -54321,6 +56629,12 @@
       <c r="K962" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N962" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U962" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y962" s="4" t="s">
         <v>2445</v>
       </c>
@@ -54351,6 +56665,12 @@
       <c r="K963" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N963" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U963" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y963" s="4" t="s">
         <v>2447</v>
       </c>
@@ -54377,6 +56697,12 @@
       <c r="K964" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N964" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U964" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y964" s="4" t="s">
         <v>2449</v>
       </c>
@@ -54407,6 +56733,12 @@
       <c r="K965" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N965" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U965" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y965" s="4" t="s">
         <v>2451</v>
       </c>
@@ -54437,6 +56769,12 @@
       <c r="K966" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N966" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U966" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y966" s="4" t="s">
         <v>2453</v>
       </c>
@@ -54467,6 +56805,12 @@
       <c r="K967" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N967" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U967" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y967" s="4" t="s">
         <v>2455</v>
       </c>
@@ -54497,6 +56841,12 @@
       <c r="K968" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N968" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U968" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y968" s="4" t="s">
         <v>2457</v>
       </c>
@@ -54527,6 +56877,12 @@
       <c r="K969" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N969" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U969" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y969" s="4" t="s">
         <v>2459</v>
       </c>
@@ -54553,6 +56909,12 @@
       <c r="K970" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N970" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U970" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y970" s="4" t="s">
         <v>2461</v>
       </c>
@@ -54583,6 +56945,12 @@
       <c r="K971" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N971" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U971" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y971" s="4" t="s">
         <v>2463</v>
       </c>
@@ -54613,6 +56981,12 @@
       <c r="K972" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N972" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U972" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y972" s="4" t="s">
         <v>2465</v>
       </c>
@@ -54643,6 +57017,12 @@
       <c r="K973" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N973" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U973" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y973" s="4" t="s">
         <v>2467</v>
       </c>
@@ -54673,6 +57053,12 @@
       <c r="K974" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N974" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U974" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y974" s="4" t="s">
         <v>2469</v>
       </c>
@@ -54703,6 +57089,12 @@
       <c r="K975" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N975" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U975" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y975" s="4" t="s">
         <v>2471</v>
       </c>
@@ -54729,6 +57121,12 @@
       <c r="K976" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N976" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U976" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y976" s="4" t="s">
         <v>2473</v>
       </c>
@@ -54759,6 +57157,12 @@
       <c r="K977" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N977" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U977" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y977" s="4" t="s">
         <v>2475</v>
       </c>
@@ -54789,6 +57193,12 @@
       <c r="K978" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N978" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U978" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y978" s="4" t="s">
         <v>2477</v>
       </c>
@@ -54819,6 +57229,12 @@
       <c r="K979" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N979" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U979" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y979" s="4" t="s">
         <v>2479</v>
       </c>
@@ -54849,6 +57265,12 @@
       <c r="K980" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N980" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U980" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y980" s="4" t="s">
         <v>2481</v>
       </c>
@@ -54879,6 +57301,12 @@
       <c r="K981" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N981" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U981" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y981" s="4" t="s">
         <v>2483</v>
       </c>
@@ -54909,6 +57337,12 @@
       <c r="K982" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N982" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U982" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y982" s="4" t="s">
         <v>2485</v>
       </c>
@@ -54939,6 +57373,12 @@
       <c r="K983" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N983" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U983" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y983" s="4" t="s">
         <v>2487</v>
       </c>
@@ -54965,6 +57405,12 @@
       <c r="K984" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N984" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U984" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y984" s="4" t="s">
         <v>2489</v>
       </c>
@@ -54995,6 +57441,12 @@
       <c r="K985" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N985" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U985" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y985" s="4" t="s">
         <v>2491</v>
       </c>
@@ -55025,6 +57477,12 @@
       <c r="K986" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N986" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U986" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y986" s="4" t="s">
         <v>2493</v>
       </c>
@@ -55055,6 +57513,12 @@
       <c r="K987" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N987" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U987" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y987" s="4" t="s">
         <v>2495</v>
       </c>
@@ -55085,6 +57549,12 @@
       <c r="K988" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N988" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U988" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y988" s="4" t="s">
         <v>2497</v>
       </c>
@@ -55115,6 +57585,12 @@
       <c r="K989" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N989" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U989" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y989" s="4" t="s">
         <v>2499</v>
       </c>
@@ -55141,6 +57617,12 @@
       <c r="K990" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N990" s="38">
+        <v>11045</v>
+      </c>
+      <c r="U990" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y990" s="4" t="s">
         <v>2501</v>
       </c>
@@ -55174,6 +57656,12 @@
       <c r="K991" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N991" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U991" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y991" s="4" t="s">
         <v>1057</v>
       </c>
@@ -55207,6 +57695,12 @@
       <c r="K992" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N992" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U992" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y992" s="4" t="s">
         <v>1067</v>
       </c>
@@ -55240,6 +57734,12 @@
       <c r="K993" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N993" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U993" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y993" s="4" t="s">
         <v>1078</v>
       </c>
@@ -55273,6 +57773,12 @@
       <c r="K994" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N994" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U994" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y994" s="4" t="s">
         <v>1085</v>
       </c>
@@ -55306,6 +57812,12 @@
       <c r="K995" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N995" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U995" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y995" s="4" t="s">
         <v>2504</v>
       </c>
@@ -55335,6 +57847,12 @@
       <c r="K996" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N996" s="38">
+        <v>3212</v>
+      </c>
+      <c r="U996" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y996" s="4" t="s">
         <v>2506</v>
       </c>
@@ -55365,6 +57883,12 @@
       <c r="K997" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N997" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U997" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y997" s="4" t="s">
         <v>1059</v>
       </c>
@@ -55395,6 +57919,12 @@
       <c r="K998" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N998" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U998" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y998" s="4" t="s">
         <v>1074</v>
       </c>
@@ -55425,6 +57955,12 @@
       <c r="K999" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N999" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U999" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y999" s="4" t="s">
         <v>1087</v>
       </c>
@@ -55455,6 +57991,12 @@
       <c r="K1000" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1000" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U1000" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1000" s="4" t="s">
         <v>2508</v>
       </c>
@@ -55485,6 +58027,12 @@
       <c r="K1001" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1001" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U1001" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1001" s="4" t="s">
         <v>2510</v>
       </c>
@@ -55511,6 +58059,12 @@
       <c r="K1002" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1002" s="38">
+        <v>3309</v>
+      </c>
+      <c r="U1002" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1002" s="4" t="s">
         <v>2512</v>
       </c>
@@ -55541,6 +58095,12 @@
       <c r="K1003" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1003" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1003" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1003" s="4" t="s">
         <v>2514</v>
       </c>
@@ -55571,6 +58131,12 @@
       <c r="K1004" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1004" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1004" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1004" s="4" t="s">
         <v>2516</v>
       </c>
@@ -55601,6 +58167,12 @@
       <c r="K1005" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1005" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1005" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1005" s="4" t="s">
         <v>2518</v>
       </c>
@@ -55631,6 +58203,12 @@
       <c r="K1006" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1006" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1006" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1006" s="4" t="s">
         <v>2520</v>
       </c>
@@ -55661,6 +58239,12 @@
       <c r="K1007" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1007" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1007" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1007" s="4" t="s">
         <v>2522</v>
       </c>
@@ -55687,6 +58271,12 @@
       <c r="K1008" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1008" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1008" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1008" s="4" t="s">
         <v>2524</v>
       </c>
@@ -55717,6 +58307,12 @@
       <c r="K1009" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1009" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1009" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1009" s="4" t="s">
         <v>2526</v>
       </c>
@@ -55747,6 +58343,12 @@
       <c r="K1010" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1010" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1010" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1010" s="4" t="s">
         <v>2528</v>
       </c>
@@ -55777,6 +58379,12 @@
       <c r="K1011" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1011" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1011" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1011" s="4" t="s">
         <v>2530</v>
       </c>
@@ -55807,6 +58415,12 @@
       <c r="K1012" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1012" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1012" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1012" s="4" t="s">
         <v>2532</v>
       </c>
@@ -55837,6 +58451,12 @@
       <c r="K1013" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1013" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1013" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1013" s="4" t="s">
         <v>2534</v>
       </c>
@@ -55863,6 +58483,12 @@
       <c r="K1014" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1014" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1014" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1014" s="4" t="s">
         <v>2536</v>
       </c>
@@ -55893,6 +58519,12 @@
       <c r="K1015" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1015" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1015" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1015" s="4" t="s">
         <v>2538</v>
       </c>
@@ -55923,6 +58555,12 @@
       <c r="K1016" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1016" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1016" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1016" s="4" t="s">
         <v>2540</v>
       </c>
@@ -55953,6 +58591,12 @@
       <c r="K1017" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1017" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1017" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1017" s="4" t="s">
         <v>2542</v>
       </c>
@@ -55983,6 +58627,12 @@
       <c r="K1018" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1018" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1018" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1018" s="4" t="s">
         <v>2544</v>
       </c>
@@ -56013,6 +58663,12 @@
       <c r="K1019" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1019" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1019" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1019" s="4" t="s">
         <v>2546</v>
       </c>
@@ -56039,6 +58695,12 @@
       <c r="K1020" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1020" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1020" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1020" s="4" t="s">
         <v>2548</v>
       </c>
@@ -56069,6 +58731,12 @@
       <c r="K1021" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1021" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1021" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1021" s="4" t="s">
         <v>2550</v>
       </c>
@@ -56099,6 +58767,12 @@
       <c r="K1022" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1022" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1022" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1022" s="4" t="s">
         <v>2552</v>
       </c>
@@ -56129,6 +58803,12 @@
       <c r="K1023" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1023" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1023" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1023" s="4" t="s">
         <v>2554</v>
       </c>
@@ -56159,6 +58839,12 @@
       <c r="K1024" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1024" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1024" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1024" s="4" t="s">
         <v>2556</v>
       </c>
@@ -56189,6 +58875,12 @@
       <c r="K1025" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1025" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1025" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1025" s="4" t="s">
         <v>2558</v>
       </c>
@@ -56215,6 +58907,12 @@
       <c r="K1026" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1026" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1026" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1026" s="4" t="s">
         <v>2560</v>
       </c>
@@ -56245,6 +58943,12 @@
       <c r="K1027" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1027" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1027" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1027" s="4" t="s">
         <v>2562</v>
       </c>
@@ -56275,6 +58979,12 @@
       <c r="K1028" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1028" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1028" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1028" s="4" t="s">
         <v>2564</v>
       </c>
@@ -56305,6 +59015,12 @@
       <c r="K1029" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N1029" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1029" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1029" s="4" t="s">
         <v>2566</v>
       </c>
@@ -56335,6 +59051,12 @@
       <c r="K1030" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1030" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1030" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1030" s="4" t="s">
         <v>2568</v>
       </c>
@@ -56365,6 +59087,12 @@
       <c r="K1031" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N1031" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1031" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1031" s="4" t="s">
         <v>2570</v>
       </c>
@@ -56395,6 +59123,12 @@
       <c r="K1032" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N1032" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1032" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1032" s="4" t="s">
         <v>2572</v>
       </c>
@@ -56425,6 +59159,12 @@
       <c r="K1033" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N1033" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1033" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1033" s="4" t="s">
         <v>2574</v>
       </c>
@@ -56451,6 +59191,12 @@
       <c r="K1034" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1034" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1034" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1034" s="4" t="s">
         <v>2576</v>
       </c>
@@ -56481,6 +59227,12 @@
       <c r="K1035" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1035" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1035" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1035" s="4" t="s">
         <v>2578</v>
       </c>
@@ -56511,6 +59263,12 @@
       <c r="K1036" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1036" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1036" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1036" s="4" t="s">
         <v>2580</v>
       </c>
@@ -56541,6 +59299,12 @@
       <c r="K1037" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1037" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1037" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1037" s="4" t="s">
         <v>2582</v>
       </c>
@@ -56571,6 +59335,12 @@
       <c r="K1038" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1038" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1038" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1038" s="4" t="s">
         <v>2584</v>
       </c>
@@ -56601,6 +59371,12 @@
       <c r="K1039" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1039" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1039" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1039" s="4" t="s">
         <v>2586</v>
       </c>
@@ -56627,6 +59403,12 @@
       <c r="K1040" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1040" s="38">
+        <v>11044</v>
+      </c>
+      <c r="U1040" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1040" s="4" t="s">
         <v>2588</v>
       </c>
@@ -56660,6 +59442,12 @@
       <c r="K1041" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1041" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1041" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1041" s="4" t="s">
         <v>2590</v>
       </c>
@@ -56693,6 +59481,12 @@
       <c r="K1042" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1042" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1042" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1042" s="4" t="s">
         <v>2592</v>
       </c>
@@ -56726,6 +59520,12 @@
       <c r="K1043" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1043" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1043" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1043" s="4" t="s">
         <v>2594</v>
       </c>
@@ -56759,6 +59559,12 @@
       <c r="K1044" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1044" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1044" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1044" s="4" t="s">
         <v>2596</v>
       </c>
@@ -56792,6 +59598,12 @@
       <c r="K1045" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1045" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1045" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1045" s="4" t="s">
         <v>2598</v>
       </c>
@@ -56821,6 +59633,12 @@
       <c r="K1046" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1046" s="38">
+        <v>3203</v>
+      </c>
+      <c r="U1046" s="50">
+        <v>76001</v>
+      </c>
       <c r="Y1046" s="4" t="s">
         <v>2600</v>
       </c>
@@ -56851,6 +59669,12 @@
       <c r="K1047" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1047" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1047" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1047" s="4" t="s">
         <v>2602</v>
       </c>
@@ -56881,6 +59705,12 @@
       <c r="K1048" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1048" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1048" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1048" s="4" t="s">
         <v>2604</v>
       </c>
@@ -56911,6 +59741,12 @@
       <c r="K1049" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1049" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1049" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1049" s="4" t="s">
         <v>2606</v>
       </c>
@@ -56941,6 +59777,12 @@
       <c r="K1050" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1050" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1050" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1050" s="4" t="s">
         <v>2608</v>
       </c>
@@ -56971,6 +59813,12 @@
       <c r="K1051" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1051" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1051" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1051" s="4" t="s">
         <v>2610</v>
       </c>
@@ -56997,6 +59845,12 @@
       <c r="K1052" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1052" s="38">
+        <v>3303</v>
+      </c>
+      <c r="U1052" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1052" s="4" t="s">
         <v>2612</v>
       </c>
@@ -57027,6 +59881,12 @@
       <c r="K1053" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1053" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1053" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1053" s="4" t="s">
         <v>2614</v>
       </c>
@@ -57057,6 +59917,12 @@
       <c r="K1054" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1054" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1054" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1054" s="4" t="s">
         <v>2616</v>
       </c>
@@ -57087,6 +59953,12 @@
       <c r="K1055" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1055" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1055" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1055" s="4" t="s">
         <v>2618</v>
       </c>
@@ -57117,6 +59989,12 @@
       <c r="K1056" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1056" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1056" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1056" s="4" t="s">
         <v>2620</v>
       </c>
@@ -57147,6 +60025,12 @@
       <c r="K1057" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1057" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1057" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1057" s="4" t="s">
         <v>2622</v>
       </c>
@@ -57173,6 +60057,12 @@
       <c r="K1058" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1058" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1058" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1058" s="4" t="s">
         <v>2624</v>
       </c>
@@ -57203,6 +60093,12 @@
       <c r="K1059" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1059" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1059" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1059" s="4" t="s">
         <v>2626</v>
       </c>
@@ -57233,6 +60129,12 @@
       <c r="K1060" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1060" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1060" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1060" s="4" t="s">
         <v>2628</v>
       </c>
@@ -57263,6 +60165,12 @@
       <c r="K1061" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1061" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1061" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1061" s="4" t="s">
         <v>2630</v>
       </c>
@@ -57293,6 +60201,12 @@
       <c r="K1062" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1062" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1062" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1062" s="4" t="s">
         <v>2632</v>
       </c>
@@ -57323,6 +60237,12 @@
       <c r="K1063" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1063" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1063" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1063" s="4" t="s">
         <v>2634</v>
       </c>
@@ -57349,6 +60269,12 @@
       <c r="K1064" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1064" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1064" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1064" s="4" t="s">
         <v>2636</v>
       </c>
@@ -57379,6 +60305,12 @@
       <c r="K1065" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1065" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1065" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1065" s="4" t="s">
         <v>2638</v>
       </c>
@@ -57409,6 +60341,12 @@
       <c r="K1066" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1066" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1066" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1066" s="4" t="s">
         <v>2640</v>
       </c>
@@ -57439,6 +60377,12 @@
       <c r="K1067" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1067" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1067" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1067" s="4" t="s">
         <v>2642</v>
       </c>
@@ -57469,6 +60413,12 @@
       <c r="K1068" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1068" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1068" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1068" s="4" t="s">
         <v>2644</v>
       </c>
@@ -57499,6 +60449,12 @@
       <c r="K1069" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1069" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1069" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1069" s="4" t="s">
         <v>2646</v>
       </c>
@@ -57525,6 +60481,12 @@
       <c r="K1070" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1070" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1070" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1070" s="4" t="s">
         <v>2648</v>
       </c>
@@ -57555,6 +60517,12 @@
       <c r="K1071" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1071" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1071" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1071" s="4" t="s">
         <v>2650</v>
       </c>
@@ -57585,6 +60553,12 @@
       <c r="K1072" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1072" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1072" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1072" s="4" t="s">
         <v>2652</v>
       </c>
@@ -57615,6 +60589,12 @@
       <c r="K1073" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1073" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1073" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1073" s="4" t="s">
         <v>2654</v>
       </c>
@@ -57645,6 +60625,12 @@
       <c r="K1074" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1074" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1074" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1074" s="4" t="s">
         <v>2656</v>
       </c>
@@ -57675,6 +60661,12 @@
       <c r="K1075" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1075" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1075" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1075" s="4" t="s">
         <v>2658</v>
       </c>
@@ -57701,6 +60693,12 @@
       <c r="K1076" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1076" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1076" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1076" s="4" t="s">
         <v>2660</v>
       </c>
@@ -57731,6 +60729,12 @@
       <c r="K1077" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1077" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1077" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1077" s="4" t="s">
         <v>2662</v>
       </c>
@@ -57761,6 +60765,12 @@
       <c r="K1078" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1078" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1078" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1078" s="4" t="s">
         <v>2664</v>
       </c>
@@ -57791,6 +60801,12 @@
       <c r="K1079" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N1079" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1079" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1079" s="4" t="s">
         <v>2666</v>
       </c>
@@ -57821,6 +60837,12 @@
       <c r="K1080" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1080" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1080" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1080" s="4" t="s">
         <v>2668</v>
       </c>
@@ -57851,6 +60873,12 @@
       <c r="K1081" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N1081" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1081" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1081" s="4" t="s">
         <v>2670</v>
       </c>
@@ -57881,6 +60909,12 @@
       <c r="K1082" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N1082" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1082" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1082" s="4" t="s">
         <v>2672</v>
       </c>
@@ -57911,6 +60945,12 @@
       <c r="K1083" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N1083" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1083" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1083" s="4" t="s">
         <v>2674</v>
       </c>
@@ -57937,6 +60977,12 @@
       <c r="K1084" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1084" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1084" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1084" s="4" t="s">
         <v>2676</v>
       </c>
@@ -57967,6 +61013,12 @@
       <c r="K1085" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1085" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1085" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1085" s="4" t="s">
         <v>2678</v>
       </c>
@@ -57997,6 +61049,12 @@
       <c r="K1086" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1086" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1086" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1086" s="4" t="s">
         <v>2680</v>
       </c>
@@ -58027,6 +61085,12 @@
       <c r="K1087" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1087" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1087" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1087" s="4" t="s">
         <v>2682</v>
       </c>
@@ -58057,6 +61121,12 @@
       <c r="K1088" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1088" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1088" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1088" s="4" t="s">
         <v>2684</v>
       </c>
@@ -58087,6 +61157,12 @@
       <c r="K1089" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1089" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1089" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1089" s="4" t="s">
         <v>2686</v>
       </c>
@@ -58113,6 +61189,12 @@
       <c r="K1090" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1090" s="38">
+        <v>11007</v>
+      </c>
+      <c r="U1090" s="50">
+        <v>76011</v>
+      </c>
       <c r="Y1090" s="4" t="s">
         <v>2688</v>
       </c>
@@ -58146,6 +61228,12 @@
       <c r="K1091" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1091" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1091" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1091" s="4" t="s">
         <v>1210</v>
       </c>
@@ -58179,6 +61267,12 @@
       <c r="K1092" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1092" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1092" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1092" s="4" t="s">
         <v>1220</v>
       </c>
@@ -58212,6 +61306,12 @@
       <c r="K1093" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1093" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1093" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1093" s="4" t="s">
         <v>1231</v>
       </c>
@@ -58245,6 +61345,12 @@
       <c r="K1094" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1094" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1094" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1094" s="4" t="s">
         <v>1238</v>
       </c>
@@ -58278,6 +61384,12 @@
       <c r="K1095" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1095" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1095" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1095" s="4" t="s">
         <v>2690</v>
       </c>
@@ -58307,6 +61419,12 @@
       <c r="K1096" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1096" s="38">
+        <v>3209</v>
+      </c>
+      <c r="U1096" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1096" s="4" t="s">
         <v>2692</v>
       </c>
@@ -58337,6 +61455,12 @@
       <c r="K1097" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1097" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1097" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1097" s="4" t="s">
         <v>1212</v>
       </c>
@@ -58367,6 +61491,12 @@
       <c r="K1098" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1098" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1098" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1098" s="4" t="s">
         <v>2694</v>
       </c>
@@ -58397,6 +61527,12 @@
       <c r="K1099" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1099" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1099" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1099" s="4" t="s">
         <v>2696</v>
       </c>
@@ -58427,6 +61563,12 @@
       <c r="K1100" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1100" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1100" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1100" s="4" t="s">
         <v>1240</v>
       </c>
@@ -58457,6 +61599,12 @@
       <c r="K1101" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1101" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1101" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1101" s="4" t="s">
         <v>2698</v>
       </c>
@@ -58483,6 +61631,12 @@
       <c r="K1102" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1102" s="38">
+        <v>3312</v>
+      </c>
+      <c r="U1102" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1102" s="4" t="s">
         <v>2700</v>
       </c>
@@ -58513,6 +61667,12 @@
       <c r="K1103" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1103" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1103" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1103" s="4" t="s">
         <v>2702</v>
       </c>
@@ -58543,6 +61703,12 @@
       <c r="K1104" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1104" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1104" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1104" s="4" t="s">
         <v>2704</v>
       </c>
@@ -58573,6 +61739,12 @@
       <c r="K1105" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1105" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1105" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1105" s="4" t="s">
         <v>2706</v>
       </c>
@@ -58603,6 +61775,12 @@
       <c r="K1106" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1106" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1106" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1106" s="4" t="s">
         <v>2708</v>
       </c>
@@ -58633,6 +61811,12 @@
       <c r="K1107" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1107" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1107" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1107" s="4" t="s">
         <v>2710</v>
       </c>
@@ -58659,6 +61843,12 @@
       <c r="K1108" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1108" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1108" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1108" s="4" t="s">
         <v>2712</v>
       </c>
@@ -58689,6 +61879,12 @@
       <c r="K1109" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1109" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1109" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1109" s="4" t="s">
         <v>2714</v>
       </c>
@@ -58719,6 +61915,12 @@
       <c r="K1110" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1110" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1110" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1110" s="4" t="s">
         <v>2716</v>
       </c>
@@ -58749,6 +61951,12 @@
       <c r="K1111" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1111" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1111" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1111" s="4" t="s">
         <v>2718</v>
       </c>
@@ -58779,6 +61987,12 @@
       <c r="K1112" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1112" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1112" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1112" s="4" t="s">
         <v>2720</v>
       </c>
@@ -58809,6 +62023,12 @@
       <c r="K1113" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1113" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1113" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1113" s="4" t="s">
         <v>2722</v>
       </c>
@@ -58835,6 +62055,12 @@
       <c r="K1114" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1114" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1114" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1114" s="4" t="s">
         <v>2724</v>
       </c>
@@ -58865,6 +62091,12 @@
       <c r="K1115" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1115" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1115" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1115" s="4" t="s">
         <v>2726</v>
       </c>
@@ -58895,6 +62127,12 @@
       <c r="K1116" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1116" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1116" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1116" s="4" t="s">
         <v>2728</v>
       </c>
@@ -58925,6 +62163,12 @@
       <c r="K1117" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1117" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1117" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1117" s="4" t="s">
         <v>2730</v>
       </c>
@@ -58955,6 +62199,12 @@
       <c r="K1118" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1118" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1118" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1118" s="4" t="s">
         <v>2732</v>
       </c>
@@ -58985,6 +62235,12 @@
       <c r="K1119" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1119" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1119" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1119" s="4" t="s">
         <v>2734</v>
       </c>
@@ -59011,6 +62267,12 @@
       <c r="K1120" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1120" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1120" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1120" s="4" t="s">
         <v>2736</v>
       </c>
@@ -59041,6 +62303,12 @@
       <c r="K1121" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1121" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1121" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1121" s="4" t="s">
         <v>2738</v>
       </c>
@@ -59071,6 +62339,12 @@
       <c r="K1122" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1122" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1122" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1122" s="4" t="s">
         <v>2740</v>
       </c>
@@ -59101,6 +62375,12 @@
       <c r="K1123" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1123" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1123" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1123" s="4" t="s">
         <v>2742</v>
       </c>
@@ -59131,6 +62411,12 @@
       <c r="K1124" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1124" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1124" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1124" s="4" t="s">
         <v>2744</v>
       </c>
@@ -59161,6 +62447,12 @@
       <c r="K1125" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1125" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1125" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1125" s="4" t="s">
         <v>2746</v>
       </c>
@@ -59187,6 +62479,12 @@
       <c r="K1126" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1126" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1126" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1126" s="4" t="s">
         <v>2748</v>
       </c>
@@ -59217,6 +62515,12 @@
       <c r="K1127" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1127" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1127" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1127" s="4" t="s">
         <v>2750</v>
       </c>
@@ -59247,6 +62551,12 @@
       <c r="K1128" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1128" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1128" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1128" s="4" t="s">
         <v>2752</v>
       </c>
@@ -59277,6 +62587,12 @@
       <c r="K1129" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N1129" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1129" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1129" s="4" t="s">
         <v>2754</v>
       </c>
@@ -59307,6 +62623,12 @@
       <c r="K1130" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1130" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1130" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1130" s="4" t="s">
         <v>2756</v>
       </c>
@@ -59337,6 +62659,12 @@
       <c r="K1131" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N1131" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1131" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1131" s="4" t="s">
         <v>2758</v>
       </c>
@@ -59367,6 +62695,12 @@
       <c r="K1132" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N1132" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1132" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1132" s="4" t="s">
         <v>2760</v>
       </c>
@@ -59397,6 +62731,12 @@
       <c r="K1133" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N1133" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1133" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1133" s="4" t="s">
         <v>2762</v>
       </c>
@@ -59423,6 +62763,12 @@
       <c r="K1134" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1134" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1134" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1134" s="4" t="s">
         <v>2764</v>
       </c>
@@ -59453,6 +62799,12 @@
       <c r="K1135" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1135" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1135" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1135" s="4" t="s">
         <v>2766</v>
       </c>
@@ -59483,6 +62835,12 @@
       <c r="K1136" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1136" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1136" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1136" s="4" t="s">
         <v>2768</v>
       </c>
@@ -59513,6 +62871,12 @@
       <c r="K1137" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1137" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1137" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1137" s="4" t="s">
         <v>2770</v>
       </c>
@@ -59543,6 +62907,12 @@
       <c r="K1138" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1138" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1138" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1138" s="4" t="s">
         <v>2772</v>
       </c>
@@ -59573,6 +62943,12 @@
       <c r="K1139" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1139" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1139" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1139" s="4" t="s">
         <v>2774</v>
       </c>
@@ -59599,6 +62975,12 @@
       <c r="K1140" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1140" s="38">
+        <v>11022</v>
+      </c>
+      <c r="U1140" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1140" s="4" t="s">
         <v>2776</v>
       </c>
@@ -59632,6 +63014,12 @@
       <c r="K1141" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1141" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1141" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1141" s="4" t="s">
         <v>1159</v>
       </c>
@@ -59665,6 +63053,12 @@
       <c r="K1142" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1142" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1142" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1142" s="4" t="s">
         <v>1169</v>
       </c>
@@ -59698,6 +63092,12 @@
       <c r="K1143" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1143" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1143" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1143" s="4" t="s">
         <v>1180</v>
       </c>
@@ -59731,6 +63131,12 @@
       <c r="K1144" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1144" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1144" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1144" s="4" t="s">
         <v>1187</v>
       </c>
@@ -59764,6 +63170,12 @@
       <c r="K1145" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1145" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1145" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1145" s="4" t="s">
         <v>2778</v>
       </c>
@@ -59793,6 +63205,12 @@
       <c r="K1146" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1146" s="38">
+        <v>3210</v>
+      </c>
+      <c r="U1146" s="61">
+        <v>76001</v>
+      </c>
       <c r="Y1146" s="4" t="s">
         <v>2780</v>
       </c>
@@ -59823,6 +63241,12 @@
       <c r="K1147" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1147" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1147" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1147" s="4" t="s">
         <v>1161</v>
       </c>
@@ -59853,6 +63277,12 @@
       <c r="K1148" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1148" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1148" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1148" s="4" t="s">
         <v>2782</v>
       </c>
@@ -59883,6 +63313,12 @@
       <c r="K1149" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1149" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1149" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1149" s="4" t="s">
         <v>2784</v>
       </c>
@@ -59913,6 +63349,12 @@
       <c r="K1150" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1150" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1150" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1150" s="4" t="s">
         <v>2786</v>
       </c>
@@ -59943,6 +63385,12 @@
       <c r="K1151" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1151" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1151" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1151" s="4" t="s">
         <v>2788</v>
       </c>
@@ -59969,6 +63417,12 @@
       <c r="K1152" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1152" s="38">
+        <v>3311</v>
+      </c>
+      <c r="U1152" s="50">
+        <v>76002</v>
+      </c>
       <c r="Y1152" s="4" t="s">
         <v>2790</v>
       </c>
@@ -59999,6 +63453,12 @@
       <c r="K1153" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1153" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1153" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1153" s="4" t="s">
         <v>2792</v>
       </c>
@@ -60029,6 +63489,12 @@
       <c r="K1154" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1154" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1154" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1154" s="4" t="s">
         <v>2794</v>
       </c>
@@ -60059,6 +63525,12 @@
       <c r="K1155" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1155" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1155" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1155" s="4" t="s">
         <v>2796</v>
       </c>
@@ -60089,6 +63561,12 @@
       <c r="K1156" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1156" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1156" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1156" s="4" t="s">
         <v>2798</v>
       </c>
@@ -60119,6 +63597,12 @@
       <c r="K1157" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1157" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1157" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1157" s="4" t="s">
         <v>2800</v>
       </c>
@@ -60145,6 +63629,12 @@
       <c r="K1158" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1158" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1158" s="50">
+        <v>76003</v>
+      </c>
       <c r="Y1158" s="4" t="s">
         <v>2802</v>
       </c>
@@ -60175,6 +63665,12 @@
       <c r="K1159" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1159" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1159" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1159" s="4" t="s">
         <v>2804</v>
       </c>
@@ -60205,6 +63701,12 @@
       <c r="K1160" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1160" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1160" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1160" s="4" t="s">
         <v>2806</v>
       </c>
@@ -60235,6 +63737,12 @@
       <c r="K1161" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1161" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1161" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1161" s="4" t="s">
         <v>2808</v>
       </c>
@@ -60265,6 +63773,12 @@
       <c r="K1162" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1162" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1162" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1162" s="4" t="s">
         <v>2810</v>
       </c>
@@ -60295,6 +63809,12 @@
       <c r="K1163" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1163" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1163" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1163" s="4" t="s">
         <v>2812</v>
       </c>
@@ -60321,6 +63841,12 @@
       <c r="K1164" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1164" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1164" s="50">
+        <v>76004</v>
+      </c>
       <c r="Y1164" s="4" t="s">
         <v>2814</v>
       </c>
@@ -60351,6 +63877,12 @@
       <c r="K1165" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1165" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1165" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1165" s="4" t="s">
         <v>2816</v>
       </c>
@@ -60381,6 +63913,12 @@
       <c r="K1166" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1166" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1166" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1166" s="4" t="s">
         <v>2818</v>
       </c>
@@ -60411,6 +63949,12 @@
       <c r="K1167" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1167" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1167" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1167" s="4" t="s">
         <v>2820</v>
       </c>
@@ -60441,6 +63985,12 @@
       <c r="K1168" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1168" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1168" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1168" s="4" t="s">
         <v>2822</v>
       </c>
@@ -60471,6 +64021,12 @@
       <c r="K1169" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1169" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1169" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1169" s="4" t="s">
         <v>2824</v>
       </c>
@@ -60497,6 +64053,12 @@
       <c r="K1170" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1170" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1170" s="50">
+        <v>76005</v>
+      </c>
       <c r="Y1170" s="4" t="s">
         <v>2826</v>
       </c>
@@ -60527,6 +64089,12 @@
       <c r="K1171" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1171" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1171" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1171" s="4" t="s">
         <v>2828</v>
       </c>
@@ -60557,6 +64125,12 @@
       <c r="K1172" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1172" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1172" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1172" s="4" t="s">
         <v>2830</v>
       </c>
@@ -60587,6 +64161,12 @@
       <c r="K1173" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1173" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1173" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1173" s="4" t="s">
         <v>2832</v>
       </c>
@@ -60617,6 +64197,12 @@
       <c r="K1174" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1174" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1174" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1174" s="4" t="s">
         <v>2834</v>
       </c>
@@ -60647,6 +64233,12 @@
       <c r="K1175" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1175" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1175" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1175" s="4" t="s">
         <v>2836</v>
       </c>
@@ -60673,6 +64265,12 @@
       <c r="K1176" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1176" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1176" s="50">
+        <v>76006</v>
+      </c>
       <c r="Y1176" s="4" t="s">
         <v>2838</v>
       </c>
@@ -60703,6 +64301,12 @@
       <c r="K1177" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1177" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1177" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1177" s="4" t="s">
         <v>2840</v>
       </c>
@@ -60733,6 +64337,12 @@
       <c r="K1178" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1178" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1178" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1178" s="4" t="s">
         <v>2842</v>
       </c>
@@ -60763,6 +64373,12 @@
       <c r="K1179" s="4" t="s">
         <v>1829</v>
       </c>
+      <c r="N1179" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1179" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1179" s="4" t="s">
         <v>2844</v>
       </c>
@@ -60793,6 +64409,12 @@
       <c r="K1180" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1180" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1180" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1180" s="4" t="s">
         <v>2846</v>
       </c>
@@ -60823,6 +64445,12 @@
       <c r="K1181" s="4" t="s">
         <v>1834</v>
       </c>
+      <c r="N1181" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1181" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1181" s="4" t="s">
         <v>2848</v>
       </c>
@@ -60853,6 +64481,12 @@
       <c r="K1182" s="4" t="s">
         <v>1837</v>
       </c>
+      <c r="N1182" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1182" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1182" s="4" t="s">
         <v>2850</v>
       </c>
@@ -60883,6 +64517,12 @@
       <c r="K1183" s="4" t="s">
         <v>1840</v>
       </c>
+      <c r="N1183" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1183" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1183" s="4" t="s">
         <v>2852</v>
       </c>
@@ -60909,6 +64549,12 @@
       <c r="K1184" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1184" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1184" s="50">
+        <v>76007</v>
+      </c>
       <c r="Y1184" s="4" t="s">
         <v>2854</v>
       </c>
@@ -60939,6 +64585,12 @@
       <c r="K1185" s="4" t="s">
         <v>1747</v>
       </c>
+      <c r="N1185" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1185" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1185" s="4" t="s">
         <v>2856</v>
       </c>
@@ -60969,6 +64621,12 @@
       <c r="K1186" s="4" t="s">
         <v>1750</v>
       </c>
+      <c r="N1186" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1186" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1186" s="4" t="s">
         <v>2858</v>
       </c>
@@ -60999,6 +64657,12 @@
       <c r="K1187" s="4" t="s">
         <v>1753</v>
       </c>
+      <c r="N1187" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1187" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1187" s="4" t="s">
         <v>2860</v>
       </c>
@@ -61029,6 +64693,12 @@
       <c r="K1188" s="4" t="s">
         <v>1756</v>
       </c>
+      <c r="N1188" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1188" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1188" s="4" t="s">
         <v>2862</v>
       </c>
@@ -61059,6 +64729,12 @@
       <c r="K1189" s="4" t="s">
         <v>1759</v>
       </c>
+      <c r="N1189" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1189" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1189" s="4" t="s">
         <v>2864</v>
       </c>
@@ -61085,325 +64761,382 @@
       <c r="K1190" s="4" t="s">
         <v>1762</v>
       </c>
+      <c r="N1190" s="38">
+        <v>11021</v>
+      </c>
+      <c r="U1190" s="50">
+        <v>76008</v>
+      </c>
       <c r="Y1190" s="4" t="s">
         <v>2866</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="V1">
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A381:A488">
+    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A641:A690">
+    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A691:A740">
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A741:A790">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A791:A840">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A841:A890">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A891:A940">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A941:A990">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A991:A1040">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1041:A1090">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1091:A1140">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1141:A1190">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H111:H374">
+    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H375:H380">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H381:H488">
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H597:H601">
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H603:H607">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H609:H613">
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H615:H619">
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H621:H625">
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H627:H633">
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H635:H639">
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H647:H651">
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H653:H657">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H659:H663">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H665:H669">
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H671:H675">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H677:H683">
+    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H685:H689">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H697:H701">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H703:H707">
     <cfRule type="duplicateValues" dxfId="0" priority="98"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A381:A488">
-    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  <conditionalFormatting sqref="H709:H713">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A641:A690">
+  <conditionalFormatting sqref="H715:H719">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H721:H725">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H727:H733">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H735:H739">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H747:H751">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H753:H757">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H759:H763">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H765:H769">
     <cfRule type="duplicateValues" dxfId="0" priority="88"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A691:A740">
+  <conditionalFormatting sqref="H771:H775">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H777:H783">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H785:H789">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H797:H801">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H803:H807">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H809:H813">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H815:H819">
     <cfRule type="duplicateValues" dxfId="0" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A741:A790">
+  <conditionalFormatting sqref="H821:H825">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H827:H833">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H835:H839">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H847:H851">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H853:H857">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H859:H863">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H865:H869">
     <cfRule type="duplicateValues" dxfId="0" priority="72"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A791:A840">
+  <conditionalFormatting sqref="H871:H875">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H877:H883">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H885:H889">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H897:H901">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H903:H907">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H909:H913">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H915:H919">
     <cfRule type="duplicateValues" dxfId="0" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A841:A890">
+  <conditionalFormatting sqref="H921:H925">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H927:H933">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H935:H939">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H947:H951">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H953:H957">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H959:H963">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H965:H969">
     <cfRule type="duplicateValues" dxfId="0" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A891:A940">
+  <conditionalFormatting sqref="H971:H975">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H977:H983">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H985:H989">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H997:H1001">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1003:H1007">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1009:H1013">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1015:H1019">
     <cfRule type="duplicateValues" dxfId="0" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A941:A990">
+  <conditionalFormatting sqref="H1021:H1025">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1027:H1033">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1035:H1039">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1047:H1051">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1053:H1057">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1059:H1063">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1065:H1069">
     <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A991:A1040">
+  <conditionalFormatting sqref="H1071:H1075">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1077:H1083">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1085:H1089">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1097:H1101">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1103:H1107">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1109:H1113">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1115:H1119">
     <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1041:A1090">
+  <conditionalFormatting sqref="H1121:H1125">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1127:H1133">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1135:H1139">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1147:H1151">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1153:H1157">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1159:H1163">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1165:H1169">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1091:A1140">
+  <conditionalFormatting sqref="H1171:H1175">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1177:H1183">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1185:H1189">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U564:U590">
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U591:U596">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U641:U646">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U647:U690">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1141:A1190">
+  <conditionalFormatting sqref="U791:U796">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U797:U840">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U841:U846">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U847:U890">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U891:U896">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U897:U940">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U941:U946">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U947:U990">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H111:H374">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  <conditionalFormatting sqref="U991:U996">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H375:H380">
-    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H381:H488">
-    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H597:H601">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H603:H607">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H609:H613">
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H615:H619">
-    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H621:H625">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H627:H633">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H635:H639">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H647:H651">
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H653:H657">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H659:H663">
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H665:H669">
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H671:H675">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H677:H683">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H685:H689">
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H697:H701">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H703:H707">
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H709:H713">
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H715:H719">
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H721:H725">
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H727:H733">
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H735:H739">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H747:H751">
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H753:H757">
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H759:H763">
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H765:H769">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H771:H775">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H777:H783">
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H785:H789">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H797:H801">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H803:H807">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H809:H813">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H815:H819">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H821:H825">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H827:H833">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H835:H839">
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H847:H851">
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H853:H857">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H859:H863">
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H865:H869">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H871:H875">
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H877:H883">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H885:H889">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H897:H901">
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H903:H907">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H909:H913">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H915:H919">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H921:H925">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H927:H933">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H935:H939">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H947:H951">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H953:H957">
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H959:H963">
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H965:H969">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H971:H975">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H977:H983">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H985:H989">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H997:H1001">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1003:H1007">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1009:H1013">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1015:H1019">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1021:H1025">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1027:H1033">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1035:H1039">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1047:H1051">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1053:H1057">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1059:H1063">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1065:H1069">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1071:H1075">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1077:H1083">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1085:H1089">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1097:H1101">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1103:H1107">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1109:H1113">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1115:H1119">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1121:H1125">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1127:H1133">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1135:H1139">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1147:H1151">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1153:H1157">
+  <conditionalFormatting sqref="U997:U1040">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1159:H1163">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="U1091:U1096">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1165:H1169">
+  <conditionalFormatting sqref="U1097:U1140">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1171:H1175">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="U1141:U1146">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1177:H1183">
+  <conditionalFormatting sqref="U1147:U1190">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1185:H1189">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A1:A380 A489:A640 A1191:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U564:U590">
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A380 A489:A640 A1191:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U1 U2:V380 U489:V563 U591:V1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+  <conditionalFormatting sqref="U1 U2:V380 U489:V563 V591:V596 U597:V640 V641:V690 U691:V790 V791:V1040 U1041:V1090 V1091:V1190 U1191:V1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U381:V440 U447:V488">
-    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U441:V446">
-    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2581,7 +2581,7 @@
     <t>12273_1_1101</t>
   </si>
   <si>
-    <t>1024001_5000|1980000_30|1024081_10|1022505_645</t>
+    <t>1024001_5000|1980000_30|1024081_30|1022505_200</t>
   </si>
   <si>
     <t>解锁&lt;color=#00bfff&gt;[萌宠小队]&lt;/color&gt;游戏建筑</t>
@@ -2590,7 +2590,7 @@
     <t>12207_1101_3</t>
   </si>
   <si>
-    <t>1024005_30|1022502_3|1022505_645</t>
+    <t>1024005_30|1022502_3|1022505_400</t>
   </si>
   <si>
     <t>[萌宠小队]建筑&lt;color=#00bfff&gt;等级达到3级&lt;/color&gt;</t>
@@ -2599,7 +2599,7 @@
     <t>12304_103900_1</t>
   </si>
   <si>
-    <t>1980000_30|1024007_2|1022505_645</t>
+    <t>1980000_30|1024007_2|1022505_644</t>
   </si>
   <si>
     <t>[萌宠小队]游戏&lt;color=#00bfff&gt;技能升级1次&lt;/color&gt;</t>
@@ -2608,7 +2608,7 @@
     <t>12221_103900_2</t>
   </si>
   <si>
-    <t>1980000_50|1024007_2|1024081_10|1022505_645</t>
+    <t>1980000_50|1024007_2|1024081_10|1022505_644</t>
   </si>
   <si>
     <t>在[萌宠小队]SLOT游戏中&lt;color=#00bfff&gt;投注2次&lt;/color&gt;</t>
@@ -2617,7 +2617,7 @@
     <t>12207_1101_4</t>
   </si>
   <si>
-    <t>1024001_5000|1990000_300000|1022505_645</t>
+    <t>1024001_5000|1990000_300000|1022505_644</t>
   </si>
   <si>
     <t>[萌宠小队]建筑&lt;color=#00bfff&gt;等级达到4级&lt;/color&gt;</t>
@@ -2626,19 +2626,19 @@
     <t>12225_103900_1990000_20000</t>
   </si>
   <si>
-    <t>1024005_10|1022502_3|1022505_645</t>
+    <t>1024005_10|1022502_3|1022505_644</t>
   </si>
   <si>
     <t>在[萌宠小队]SLOT游戏中&lt;color=#00bfff&gt;赢取2万金币&lt;/color&gt;</t>
   </si>
   <si>
-    <t>1024014_1|1990000_300000|1022505_645</t>
+    <t>1024014_1|1990000_300000|1022505_644</t>
   </si>
   <si>
     <t>12303_20001_1</t>
   </si>
   <si>
-    <t>1126101_20|1022502_3|1022505_645</t>
+    <t>1126101_20|1022502_3|1022505_644</t>
   </si>
   <si>
     <t>在[雇员]卡池&lt;color=#00bfff&gt;招募1次&lt;/color&gt;</t>
@@ -2647,7 +2647,7 @@
     <t>12259_10_1_1</t>
   </si>
   <si>
-    <t>1980000_30|1990000_300000|1022505_645</t>
+    <t>1980000_30|1990000_300000|1022505_644</t>
   </si>
   <si>
     <t>拥有&lt;color=#00bfff&gt;1个1星的游戏经理&lt;/color&gt;</t>
@@ -10213,6 +10213,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -10220,12 +10226,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2581,7 +2581,7 @@
     <t>12273_1_1101</t>
   </si>
   <si>
-    <t>1024001_5000|1980000_30|1024081_30|1022505_200</t>
+    <t>1024001_5000|1980000_30|1024081_30|1022505_644</t>
   </si>
   <si>
     <t>解锁&lt;color=#00bfff&gt;[萌宠小队]&lt;/color&gt;游戏建筑</t>
@@ -2590,7 +2590,7 @@
     <t>12207_1101_3</t>
   </si>
   <si>
-    <t>1024005_30|1022502_3|1022505_400</t>
+    <t>1024005_30|1022502_3|1022505_644</t>
   </si>
   <si>
     <t>[萌宠小队]建筑&lt;color=#00bfff&gt;等级达到3级&lt;/color&gt;</t>
@@ -10231,12 +10231,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -22947,9 +22947,7 @@
       <c r="I127" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="J127" s="12">
-        <v>5002</v>
-      </c>
+      <c r="J127" s="12"/>
       <c r="K127" s="12" t="s">
         <v>700</v>
       </c>
@@ -23699,9 +23697,7 @@
       <c r="I142" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="J142" s="12">
-        <v>5004</v>
-      </c>
+      <c r="J142" s="12"/>
       <c r="K142" s="12" t="s">
         <v>734</v>
       </c>
@@ -23951,9 +23947,7 @@
       <c r="I147" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="J147" s="12">
-        <v>5003</v>
-      </c>
+      <c r="J147" s="12"/>
       <c r="K147" s="12" t="s">
         <v>749</v>
       </c>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -2617,7 +2617,7 @@
     <t>12207_1101_4</t>
   </si>
   <si>
-    <t>1024001_5000|1990000_300000|1022505_644</t>
+    <t>1024001_5000|1980000_200|1022505_644</t>
   </si>
   <si>
     <t>[萌宠小队]建筑&lt;color=#00bfff&gt;等级达到4级&lt;/color&gt;</t>
@@ -10231,12 +10231,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -10411,6 +10411,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -10418,12 +10424,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -35512,7 +35512,9 @@
         <v>1261</v>
       </c>
       <c r="P391" s="58"/>
-      <c r="Q391" s="59"/>
+      <c r="Q391" s="59">
+        <v>0</v>
+      </c>
       <c r="R391" s="59"/>
       <c r="S391" s="60" t="b">
         <v>0</v>
@@ -35567,7 +35569,9 @@
         <v>1265</v>
       </c>
       <c r="P392" s="58"/>
-      <c r="Q392" s="59"/>
+      <c r="Q392" s="59">
+        <v>0</v>
+      </c>
       <c r="R392" s="59"/>
       <c r="S392" s="60" t="b">
         <v>0</v>
@@ -35622,7 +35626,9 @@
         <v>1265</v>
       </c>
       <c r="P393" s="58"/>
-      <c r="Q393" s="59"/>
+      <c r="Q393" s="59">
+        <v>0</v>
+      </c>
       <c r="R393" s="59"/>
       <c r="S393" s="60" t="b">
         <v>0</v>
@@ -35677,7 +35683,9 @@
         <v>1265</v>
       </c>
       <c r="P394" s="58"/>
-      <c r="Q394" s="59"/>
+      <c r="Q394" s="59">
+        <v>0</v>
+      </c>
       <c r="R394" s="59"/>
       <c r="S394" s="60" t="b">
         <v>0</v>
@@ -35732,7 +35740,9 @@
         <v>1265</v>
       </c>
       <c r="P395" s="58"/>
-      <c r="Q395" s="59"/>
+      <c r="Q395" s="59">
+        <v>0</v>
+      </c>
       <c r="R395" s="59"/>
       <c r="S395" s="60" t="b">
         <v>0</v>
@@ -35785,7 +35795,9 @@
         <v>1265</v>
       </c>
       <c r="P396" s="58"/>
-      <c r="Q396" s="59"/>
+      <c r="Q396" s="59">
+        <v>0</v>
+      </c>
       <c r="R396" s="59"/>
       <c r="S396" s="60" t="b">
         <v>0</v>
@@ -35840,7 +35852,9 @@
         <v>1281</v>
       </c>
       <c r="P397" s="58"/>
-      <c r="Q397" s="59"/>
+      <c r="Q397" s="59">
+        <v>0</v>
+      </c>
       <c r="R397" s="59"/>
       <c r="S397" s="60" t="b">
         <v>0</v>
@@ -35895,7 +35909,9 @@
         <v>1281</v>
       </c>
       <c r="P398" s="58"/>
-      <c r="Q398" s="59"/>
+      <c r="Q398" s="59">
+        <v>0</v>
+      </c>
       <c r="R398" s="59"/>
       <c r="S398" t="b">
         <v>0</v>
@@ -35950,7 +35966,9 @@
         <v>1281</v>
       </c>
       <c r="P399" s="58"/>
-      <c r="Q399" s="59"/>
+      <c r="Q399" s="59">
+        <v>0</v>
+      </c>
       <c r="R399" s="59"/>
       <c r="S399" t="b">
         <v>0</v>
@@ -36005,7 +36023,9 @@
         <v>1289</v>
       </c>
       <c r="P400" s="58"/>
-      <c r="Q400" s="59"/>
+      <c r="Q400" s="59">
+        <v>0</v>
+      </c>
       <c r="R400" s="59"/>
       <c r="S400" t="b">
         <v>0</v>
@@ -36060,7 +36080,9 @@
         <v>1289</v>
       </c>
       <c r="P401" s="58"/>
-      <c r="Q401" s="59"/>
+      <c r="Q401" s="59">
+        <v>0</v>
+      </c>
       <c r="R401" s="59"/>
       <c r="S401" t="b">
         <v>0</v>
@@ -36113,7 +36135,9 @@
         <v>1289</v>
       </c>
       <c r="P402" s="58"/>
-      <c r="Q402" s="59"/>
+      <c r="Q402" s="59">
+        <v>0</v>
+      </c>
       <c r="R402" s="59"/>
       <c r="S402" t="b">
         <v>0</v>
@@ -36169,7 +36193,9 @@
         <v>1297</v>
       </c>
       <c r="P403" s="58"/>
-      <c r="Q403" s="59"/>
+      <c r="Q403" s="59">
+        <v>0</v>
+      </c>
       <c r="R403" s="59"/>
       <c r="S403" t="b">
         <v>0</v>
@@ -36225,7 +36251,9 @@
         <v>1297</v>
       </c>
       <c r="P404" s="58"/>
-      <c r="Q404" s="59"/>
+      <c r="Q404" s="59">
+        <v>0</v>
+      </c>
       <c r="R404" s="59"/>
       <c r="S404" t="b">
         <v>0</v>
@@ -36281,7 +36309,9 @@
         <v>1297</v>
       </c>
       <c r="P405" s="58"/>
-      <c r="Q405" s="59"/>
+      <c r="Q405" s="59">
+        <v>0</v>
+      </c>
       <c r="R405" s="59"/>
       <c r="S405" t="b">
         <v>0</v>
@@ -36337,7 +36367,9 @@
         <v>1305</v>
       </c>
       <c r="P406" s="58"/>
-      <c r="Q406" s="59"/>
+      <c r="Q406" s="59">
+        <v>0</v>
+      </c>
       <c r="R406" s="59"/>
       <c r="S406" t="b">
         <v>0</v>
@@ -36393,7 +36425,9 @@
         <v>1305</v>
       </c>
       <c r="P407" s="58"/>
-      <c r="Q407" s="59"/>
+      <c r="Q407" s="59">
+        <v>0</v>
+      </c>
       <c r="R407" s="59"/>
       <c r="S407" t="b">
         <v>0</v>
@@ -36446,7 +36480,9 @@
         <v>1305</v>
       </c>
       <c r="P408" s="58"/>
-      <c r="Q408" s="59"/>
+      <c r="Q408" s="59">
+        <v>0</v>
+      </c>
       <c r="R408" s="59"/>
       <c r="S408" t="b">
         <v>0</v>
@@ -36502,7 +36538,9 @@
         <v>1313</v>
       </c>
       <c r="P409" s="58"/>
-      <c r="Q409" s="59"/>
+      <c r="Q409" s="59">
+        <v>0</v>
+      </c>
       <c r="R409" s="59"/>
       <c r="S409" t="b">
         <v>0</v>
@@ -36558,7 +36596,9 @@
         <v>1313</v>
       </c>
       <c r="P410" s="58"/>
-      <c r="Q410" s="59"/>
+      <c r="Q410" s="59">
+        <v>0</v>
+      </c>
       <c r="R410" s="59"/>
       <c r="S410" t="b">
         <v>0</v>
@@ -36614,7 +36654,9 @@
         <v>1313</v>
       </c>
       <c r="P411" s="58"/>
-      <c r="Q411" s="59"/>
+      <c r="Q411" s="59">
+        <v>0</v>
+      </c>
       <c r="R411" s="59"/>
       <c r="S411" t="b">
         <v>0</v>
@@ -36670,7 +36712,9 @@
         <v>1321</v>
       </c>
       <c r="P412" s="58"/>
-      <c r="Q412" s="59"/>
+      <c r="Q412" s="59">
+        <v>0</v>
+      </c>
       <c r="R412" s="59"/>
       <c r="S412" t="b">
         <v>0</v>
@@ -36726,7 +36770,9 @@
         <v>1321</v>
       </c>
       <c r="P413" s="58"/>
-      <c r="Q413" s="59"/>
+      <c r="Q413" s="59">
+        <v>0</v>
+      </c>
       <c r="R413" s="59"/>
       <c r="S413" t="b">
         <v>0</v>
@@ -36779,7 +36825,9 @@
         <v>1321</v>
       </c>
       <c r="P414" s="58"/>
-      <c r="Q414" s="59"/>
+      <c r="Q414" s="59">
+        <v>0</v>
+      </c>
       <c r="R414" s="59"/>
       <c r="S414" t="b">
         <v>0</v>
@@ -36835,7 +36883,9 @@
         <v>1329</v>
       </c>
       <c r="P415" s="58"/>
-      <c r="Q415" s="59"/>
+      <c r="Q415" s="59">
+        <v>0</v>
+      </c>
       <c r="R415" s="59"/>
       <c r="S415" t="b">
         <v>0</v>
@@ -36889,7 +36939,9 @@
         <v>1329</v>
       </c>
       <c r="P416" s="58"/>
-      <c r="Q416" s="59"/>
+      <c r="Q416" s="59">
+        <v>0</v>
+      </c>
       <c r="R416" s="59"/>
       <c r="S416" t="b">
         <v>0</v>
@@ -36943,7 +36995,9 @@
         <v>1329</v>
       </c>
       <c r="P417" s="58"/>
-      <c r="Q417" s="59"/>
+      <c r="Q417" s="59">
+        <v>0</v>
+      </c>
       <c r="R417" s="59"/>
       <c r="S417" t="b">
         <v>0</v>
@@ -36997,7 +37051,9 @@
         <v>1337</v>
       </c>
       <c r="P418" s="58"/>
-      <c r="Q418" s="59"/>
+      <c r="Q418" s="59">
+        <v>0</v>
+      </c>
       <c r="R418" s="59"/>
       <c r="S418" t="b">
         <v>0</v>
@@ -37051,7 +37107,9 @@
         <v>1337</v>
       </c>
       <c r="P419" s="58"/>
-      <c r="Q419" s="59"/>
+      <c r="Q419" s="59">
+        <v>0</v>
+      </c>
       <c r="R419" s="59"/>
       <c r="S419" t="b">
         <v>0</v>
@@ -37102,7 +37160,9 @@
         <v>1337</v>
       </c>
       <c r="P420" s="58"/>
-      <c r="Q420" s="59"/>
+      <c r="Q420" s="59">
+        <v>0</v>
+      </c>
       <c r="R420" s="59"/>
       <c r="S420" t="b">
         <v>0</v>
@@ -37156,7 +37216,9 @@
         <v>1345</v>
       </c>
       <c r="P421" s="58"/>
-      <c r="Q421" s="59"/>
+      <c r="Q421" s="59">
+        <v>0</v>
+      </c>
       <c r="R421" s="59"/>
       <c r="S421" t="b">
         <v>0</v>
@@ -37212,7 +37274,9 @@
         <v>1345</v>
       </c>
       <c r="P422" s="58"/>
-      <c r="Q422" s="59"/>
+      <c r="Q422" s="59">
+        <v>0</v>
+      </c>
       <c r="R422" s="59"/>
       <c r="S422" t="b">
         <v>0</v>
@@ -37268,7 +37332,9 @@
         <v>1345</v>
       </c>
       <c r="P423" s="58"/>
-      <c r="Q423" s="59"/>
+      <c r="Q423" s="59">
+        <v>0</v>
+      </c>
       <c r="R423" s="59"/>
       <c r="S423" t="b">
         <v>0</v>
@@ -37324,7 +37390,9 @@
         <v>1353</v>
       </c>
       <c r="P424" s="58"/>
-      <c r="Q424" s="59"/>
+      <c r="Q424" s="59">
+        <v>0</v>
+      </c>
       <c r="R424" s="59"/>
       <c r="S424" t="b">
         <v>0</v>
@@ -37380,7 +37448,9 @@
         <v>1353</v>
       </c>
       <c r="P425" s="58"/>
-      <c r="Q425" s="59"/>
+      <c r="Q425" s="59">
+        <v>0</v>
+      </c>
       <c r="R425" s="59"/>
       <c r="S425" t="b">
         <v>0</v>
@@ -37433,7 +37503,9 @@
         <v>1353</v>
       </c>
       <c r="P426" s="58"/>
-      <c r="Q426" s="59"/>
+      <c r="Q426" s="59">
+        <v>0</v>
+      </c>
       <c r="R426" s="59"/>
       <c r="S426" t="b">
         <v>0</v>
@@ -44163,6 +44235,9 @@
       <c r="N607" s="38">
         <v>3201</v>
       </c>
+      <c r="Q607" s="50">
+        <v>1</v>
+      </c>
       <c r="U607" s="61">
         <v>76001</v>
       </c>
@@ -44202,6 +44277,9 @@
       <c r="N608" s="38">
         <v>3201</v>
       </c>
+      <c r="Q608" s="50">
+        <v>1</v>
+      </c>
       <c r="U608" s="61">
         <v>76001</v>
       </c>
@@ -44241,6 +44319,9 @@
       <c r="N609" s="38">
         <v>3201</v>
       </c>
+      <c r="Q609" s="50">
+        <v>1</v>
+      </c>
       <c r="U609" s="61">
         <v>76001</v>
       </c>
@@ -44280,6 +44361,9 @@
       <c r="N610" s="38">
         <v>3201</v>
       </c>
+      <c r="Q610" s="50">
+        <v>1</v>
+      </c>
       <c r="U610" s="61">
         <v>76001</v>
       </c>
@@ -44319,6 +44403,9 @@
       <c r="N611" s="38">
         <v>3201</v>
       </c>
+      <c r="Q611" s="50">
+        <v>1</v>
+      </c>
       <c r="U611" s="61">
         <v>76001</v>
       </c>
@@ -44354,6 +44441,9 @@
       <c r="N612" s="38">
         <v>3201</v>
       </c>
+      <c r="Q612" s="50">
+        <v>1</v>
+      </c>
       <c r="U612" s="61">
         <v>76001</v>
       </c>
@@ -44390,6 +44480,9 @@
       <c r="N613" s="38">
         <v>3301</v>
       </c>
+      <c r="Q613" s="50">
+        <v>1</v>
+      </c>
       <c r="U613" s="50">
         <v>76002</v>
       </c>
@@ -44426,6 +44519,9 @@
       <c r="N614" s="38">
         <v>3301</v>
       </c>
+      <c r="Q614" s="50">
+        <v>1</v>
+      </c>
       <c r="U614" s="50">
         <v>76002</v>
       </c>
@@ -44462,6 +44558,9 @@
       <c r="N615" s="38">
         <v>3301</v>
       </c>
+      <c r="Q615" s="50">
+        <v>1</v>
+      </c>
       <c r="U615" s="50">
         <v>76002</v>
       </c>
@@ -44498,6 +44597,9 @@
       <c r="N616" s="38">
         <v>3301</v>
       </c>
+      <c r="Q616" s="50">
+        <v>1</v>
+      </c>
       <c r="U616" s="50">
         <v>76002</v>
       </c>
@@ -44534,6 +44636,9 @@
       <c r="N617" s="38">
         <v>3301</v>
       </c>
+      <c r="Q617" s="50">
+        <v>1</v>
+      </c>
       <c r="U617" s="50">
         <v>76002</v>
       </c>
@@ -44566,6 +44671,9 @@
       <c r="N618" s="38">
         <v>3301</v>
       </c>
+      <c r="Q618" s="50">
+        <v>1</v>
+      </c>
       <c r="U618" s="50">
         <v>76002</v>
       </c>
@@ -44602,6 +44710,9 @@
       <c r="N619" s="38">
         <v>11041</v>
       </c>
+      <c r="Q619" s="50">
+        <v>1</v>
+      </c>
       <c r="U619" s="50">
         <v>76003</v>
       </c>
@@ -44638,6 +44749,9 @@
       <c r="N620" s="38">
         <v>11041</v>
       </c>
+      <c r="Q620" s="50">
+        <v>1</v>
+      </c>
       <c r="U620" s="50">
         <v>76003</v>
       </c>
@@ -44674,6 +44788,9 @@
       <c r="N621" s="38">
         <v>11041</v>
       </c>
+      <c r="Q621" s="50">
+        <v>1</v>
+      </c>
       <c r="U621" s="50">
         <v>76003</v>
       </c>
@@ -44710,6 +44827,9 @@
       <c r="N622" s="38">
         <v>11041</v>
       </c>
+      <c r="Q622" s="50">
+        <v>1</v>
+      </c>
       <c r="U622" s="50">
         <v>76003</v>
       </c>
@@ -44746,6 +44866,9 @@
       <c r="N623" s="38">
         <v>11041</v>
       </c>
+      <c r="Q623" s="50">
+        <v>1</v>
+      </c>
       <c r="U623" s="50">
         <v>76003</v>
       </c>
@@ -44778,6 +44901,9 @@
       <c r="N624" s="38">
         <v>11041</v>
       </c>
+      <c r="Q624" s="50">
+        <v>1</v>
+      </c>
       <c r="U624" s="50">
         <v>76003</v>
       </c>
@@ -44814,6 +44940,9 @@
       <c r="N625" s="38">
         <v>11041</v>
       </c>
+      <c r="Q625" s="50">
+        <v>1</v>
+      </c>
       <c r="U625" s="50">
         <v>76004</v>
       </c>
@@ -44850,6 +44979,9 @@
       <c r="N626" s="38">
         <v>11041</v>
       </c>
+      <c r="Q626" s="50">
+        <v>1</v>
+      </c>
       <c r="U626" s="50">
         <v>76004</v>
       </c>
@@ -44886,6 +45018,9 @@
       <c r="N627" s="38">
         <v>11041</v>
       </c>
+      <c r="Q627" s="50">
+        <v>1</v>
+      </c>
       <c r="U627" s="50">
         <v>76004</v>
       </c>
@@ -44922,6 +45057,9 @@
       <c r="N628" s="38">
         <v>11041</v>
       </c>
+      <c r="Q628" s="50">
+        <v>1</v>
+      </c>
       <c r="U628" s="50">
         <v>76004</v>
       </c>
@@ -44958,6 +45096,9 @@
       <c r="N629" s="38">
         <v>11041</v>
       </c>
+      <c r="Q629" s="50">
+        <v>1</v>
+      </c>
       <c r="U629" s="50">
         <v>76004</v>
       </c>
@@ -44990,6 +45131,9 @@
       <c r="N630" s="38">
         <v>11041</v>
       </c>
+      <c r="Q630" s="50">
+        <v>1</v>
+      </c>
       <c r="U630" s="50">
         <v>76004</v>
       </c>
@@ -45026,6 +45170,9 @@
       <c r="N631" s="38">
         <v>11041</v>
       </c>
+      <c r="Q631" s="50">
+        <v>1</v>
+      </c>
       <c r="U631" s="50">
         <v>76005</v>
       </c>
@@ -45062,6 +45209,9 @@
       <c r="N632" s="38">
         <v>11041</v>
       </c>
+      <c r="Q632" s="50">
+        <v>1</v>
+      </c>
       <c r="U632" s="50">
         <v>76005</v>
       </c>
@@ -45098,6 +45248,9 @@
       <c r="N633" s="38">
         <v>11041</v>
       </c>
+      <c r="Q633" s="50">
+        <v>1</v>
+      </c>
       <c r="U633" s="50">
         <v>76005</v>
       </c>
@@ -45134,6 +45287,9 @@
       <c r="N634" s="38">
         <v>11041</v>
       </c>
+      <c r="Q634" s="50">
+        <v>1</v>
+      </c>
       <c r="U634" s="50">
         <v>76005</v>
       </c>
@@ -45170,6 +45326,9 @@
       <c r="N635" s="38">
         <v>11041</v>
       </c>
+      <c r="Q635" s="50">
+        <v>1</v>
+      </c>
       <c r="U635" s="50">
         <v>76005</v>
       </c>
@@ -45202,6 +45361,9 @@
       <c r="N636" s="38">
         <v>11041</v>
       </c>
+      <c r="Q636" s="50">
+        <v>1</v>
+      </c>
       <c r="U636" s="50">
         <v>76005</v>
       </c>
@@ -45238,6 +45400,9 @@
       <c r="N637" s="38">
         <v>11041</v>
       </c>
+      <c r="Q637" s="50">
+        <v>1</v>
+      </c>
       <c r="U637" s="50">
         <v>76006</v>
       </c>
@@ -45274,6 +45439,9 @@
       <c r="N638" s="38">
         <v>11041</v>
       </c>
+      <c r="Q638" s="50">
+        <v>1</v>
+      </c>
       <c r="U638" s="50">
         <v>76006</v>
       </c>
@@ -45310,6 +45478,9 @@
       <c r="N639" s="38">
         <v>11041</v>
       </c>
+      <c r="Q639" s="50">
+        <v>1</v>
+      </c>
       <c r="U639" s="50">
         <v>76006</v>
       </c>
@@ -45346,6 +45517,9 @@
       <c r="N640" s="38">
         <v>11041</v>
       </c>
+      <c r="Q640" s="50">
+        <v>1</v>
+      </c>
       <c r="U640" s="50">
         <v>76006</v>
       </c>
@@ -45382,6 +45556,9 @@
       <c r="N641" s="38">
         <v>11041</v>
       </c>
+      <c r="Q641" s="50">
+        <v>1</v>
+      </c>
       <c r="U641" s="50">
         <v>76006</v>
       </c>
@@ -45414,6 +45591,9 @@
       <c r="N642" s="38">
         <v>11041</v>
       </c>
+      <c r="Q642" s="50">
+        <v>1</v>
+      </c>
       <c r="U642" s="50">
         <v>76006</v>
       </c>
@@ -45450,6 +45630,9 @@
       <c r="N643" s="38">
         <v>11041</v>
       </c>
+      <c r="Q643" s="50">
+        <v>1</v>
+      </c>
       <c r="U643" s="50">
         <v>76007</v>
       </c>
@@ -45486,6 +45669,9 @@
       <c r="N644" s="38">
         <v>11041</v>
       </c>
+      <c r="Q644" s="50">
+        <v>1</v>
+      </c>
       <c r="U644" s="50">
         <v>76007</v>
       </c>
@@ -45522,6 +45708,9 @@
       <c r="N645" s="38">
         <v>11041</v>
       </c>
+      <c r="Q645" s="50">
+        <v>1</v>
+      </c>
       <c r="U645" s="50">
         <v>76007</v>
       </c>
@@ -45558,6 +45747,9 @@
       <c r="N646" s="38">
         <v>11041</v>
       </c>
+      <c r="Q646" s="50">
+        <v>1</v>
+      </c>
       <c r="U646" s="50">
         <v>76007</v>
       </c>
@@ -45594,6 +45786,9 @@
       <c r="N647" s="38">
         <v>11041</v>
       </c>
+      <c r="Q647" s="50">
+        <v>1</v>
+      </c>
       <c r="U647" s="50">
         <v>76007</v>
       </c>
@@ -45630,6 +45825,9 @@
       <c r="N648" s="38">
         <v>11041</v>
       </c>
+      <c r="Q648" s="50">
+        <v>1</v>
+      </c>
       <c r="U648" s="50">
         <v>76007</v>
       </c>
@@ -45666,6 +45864,9 @@
       <c r="N649" s="38">
         <v>11041</v>
       </c>
+      <c r="Q649" s="50">
+        <v>1</v>
+      </c>
       <c r="U649" s="50">
         <v>76007</v>
       </c>
@@ -45698,6 +45899,9 @@
       <c r="N650" s="38">
         <v>11041</v>
       </c>
+      <c r="Q650" s="50">
+        <v>1</v>
+      </c>
       <c r="U650" s="50">
         <v>76007</v>
       </c>
@@ -45734,6 +45938,9 @@
       <c r="N651" s="38">
         <v>11041</v>
       </c>
+      <c r="Q651" s="50">
+        <v>1</v>
+      </c>
       <c r="U651" s="50">
         <v>76008</v>
       </c>
@@ -45770,6 +45977,9 @@
       <c r="N652" s="38">
         <v>11041</v>
       </c>
+      <c r="Q652" s="50">
+        <v>1</v>
+      </c>
       <c r="U652" s="50">
         <v>76008</v>
       </c>
@@ -45806,6 +46016,9 @@
       <c r="N653" s="38">
         <v>11041</v>
       </c>
+      <c r="Q653" s="50">
+        <v>1</v>
+      </c>
       <c r="U653" s="50">
         <v>76008</v>
       </c>
@@ -45842,6 +46055,9 @@
       <c r="N654" s="38">
         <v>11041</v>
       </c>
+      <c r="Q654" s="50">
+        <v>1</v>
+      </c>
       <c r="U654" s="50">
         <v>76008</v>
       </c>
@@ -45878,6 +46094,9 @@
       <c r="N655" s="38">
         <v>11041</v>
       </c>
+      <c r="Q655" s="50">
+        <v>1</v>
+      </c>
       <c r="U655" s="50">
         <v>76008</v>
       </c>
@@ -45910,6 +46129,9 @@
       <c r="N656" s="38">
         <v>11041</v>
       </c>
+      <c r="Q656" s="50">
+        <v>1</v>
+      </c>
       <c r="U656" s="50">
         <v>76008</v>
       </c>
@@ -45949,6 +46171,9 @@
       <c r="N657" s="38">
         <v>3202</v>
       </c>
+      <c r="Q657" s="50">
+        <v>1</v>
+      </c>
       <c r="U657" s="61">
         <v>76001</v>
       </c>
@@ -45988,6 +46213,9 @@
       <c r="N658" s="38">
         <v>3202</v>
       </c>
+      <c r="Q658" s="50">
+        <v>1</v>
+      </c>
       <c r="U658" s="61">
         <v>76001</v>
       </c>
@@ -46027,6 +46255,9 @@
       <c r="N659" s="38">
         <v>3202</v>
       </c>
+      <c r="Q659" s="50">
+        <v>1</v>
+      </c>
       <c r="U659" s="61">
         <v>76001</v>
       </c>
@@ -46066,6 +46297,9 @@
       <c r="N660" s="38">
         <v>3202</v>
       </c>
+      <c r="Q660" s="50">
+        <v>1</v>
+      </c>
       <c r="U660" s="61">
         <v>76001</v>
       </c>
@@ -46105,6 +46339,9 @@
       <c r="N661" s="38">
         <v>3202</v>
       </c>
+      <c r="Q661" s="50">
+        <v>1</v>
+      </c>
       <c r="U661" s="61">
         <v>76001</v>
       </c>
@@ -46140,6 +46377,9 @@
       <c r="N662" s="38">
         <v>3202</v>
       </c>
+      <c r="Q662" s="50">
+        <v>1</v>
+      </c>
       <c r="U662" s="61">
         <v>76001</v>
       </c>
@@ -46176,6 +46416,9 @@
       <c r="N663" s="38">
         <v>3302</v>
       </c>
+      <c r="Q663" s="50">
+        <v>1</v>
+      </c>
       <c r="U663" s="50">
         <v>76002</v>
       </c>
@@ -46212,6 +46455,9 @@
       <c r="N664" s="38">
         <v>3302</v>
       </c>
+      <c r="Q664" s="50">
+        <v>1</v>
+      </c>
       <c r="U664" s="50">
         <v>76002</v>
       </c>
@@ -46248,6 +46494,9 @@
       <c r="N665" s="38">
         <v>3302</v>
       </c>
+      <c r="Q665" s="50">
+        <v>1</v>
+      </c>
       <c r="U665" s="50">
         <v>76002</v>
       </c>
@@ -46284,6 +46533,9 @@
       <c r="N666" s="38">
         <v>3302</v>
       </c>
+      <c r="Q666" s="50">
+        <v>1</v>
+      </c>
       <c r="U666" s="50">
         <v>76002</v>
       </c>
@@ -46320,6 +46572,9 @@
       <c r="N667" s="38">
         <v>3302</v>
       </c>
+      <c r="Q667" s="50">
+        <v>1</v>
+      </c>
       <c r="U667" s="50">
         <v>76002</v>
       </c>
@@ -46352,6 +46607,9 @@
       <c r="N668" s="38">
         <v>3302</v>
       </c>
+      <c r="Q668" s="50">
+        <v>1</v>
+      </c>
       <c r="U668" s="50">
         <v>76002</v>
       </c>
@@ -46388,6 +46646,9 @@
       <c r="N669" s="38">
         <v>11042</v>
       </c>
+      <c r="Q669" s="50">
+        <v>1</v>
+      </c>
       <c r="U669" s="50">
         <v>76003</v>
       </c>
@@ -46424,6 +46685,9 @@
       <c r="N670" s="38">
         <v>11042</v>
       </c>
+      <c r="Q670" s="50">
+        <v>1</v>
+      </c>
       <c r="U670" s="50">
         <v>76003</v>
       </c>
@@ -46460,6 +46724,9 @@
       <c r="N671" s="38">
         <v>11042</v>
       </c>
+      <c r="Q671" s="50">
+        <v>1</v>
+      </c>
       <c r="U671" s="50">
         <v>76003</v>
       </c>
@@ -46496,6 +46763,9 @@
       <c r="N672" s="38">
         <v>11042</v>
       </c>
+      <c r="Q672" s="50">
+        <v>1</v>
+      </c>
       <c r="U672" s="50">
         <v>76003</v>
       </c>
@@ -46532,6 +46802,9 @@
       <c r="N673" s="38">
         <v>11042</v>
       </c>
+      <c r="Q673" s="50">
+        <v>1</v>
+      </c>
       <c r="U673" s="50">
         <v>76003</v>
       </c>
@@ -46564,6 +46837,9 @@
       <c r="N674" s="38">
         <v>11042</v>
       </c>
+      <c r="Q674" s="50">
+        <v>1</v>
+      </c>
       <c r="U674" s="50">
         <v>76003</v>
       </c>
@@ -46600,6 +46876,9 @@
       <c r="N675" s="38">
         <v>11042</v>
       </c>
+      <c r="Q675" s="50">
+        <v>1</v>
+      </c>
       <c r="U675" s="50">
         <v>76004</v>
       </c>
@@ -46636,6 +46915,9 @@
       <c r="N676" s="38">
         <v>11042</v>
       </c>
+      <c r="Q676" s="50">
+        <v>1</v>
+      </c>
       <c r="U676" s="50">
         <v>76004</v>
       </c>
@@ -46672,6 +46954,9 @@
       <c r="N677" s="38">
         <v>11042</v>
       </c>
+      <c r="Q677" s="50">
+        <v>1</v>
+      </c>
       <c r="U677" s="50">
         <v>76004</v>
       </c>
@@ -46708,6 +46993,9 @@
       <c r="N678" s="38">
         <v>11042</v>
       </c>
+      <c r="Q678" s="50">
+        <v>1</v>
+      </c>
       <c r="U678" s="50">
         <v>76004</v>
       </c>
@@ -46744,6 +47032,9 @@
       <c r="N679" s="38">
         <v>11042</v>
       </c>
+      <c r="Q679" s="50">
+        <v>1</v>
+      </c>
       <c r="U679" s="50">
         <v>76004</v>
       </c>
@@ -46776,6 +47067,9 @@
       <c r="N680" s="38">
         <v>11042</v>
       </c>
+      <c r="Q680" s="50">
+        <v>1</v>
+      </c>
       <c r="U680" s="50">
         <v>76004</v>
       </c>
@@ -46812,6 +47106,9 @@
       <c r="N681" s="38">
         <v>11042</v>
       </c>
+      <c r="Q681" s="50">
+        <v>1</v>
+      </c>
       <c r="U681" s="50">
         <v>76005</v>
       </c>
@@ -46848,6 +47145,9 @@
       <c r="N682" s="38">
         <v>11042</v>
       </c>
+      <c r="Q682" s="50">
+        <v>1</v>
+      </c>
       <c r="U682" s="50">
         <v>76005</v>
       </c>
@@ -46884,6 +47184,9 @@
       <c r="N683" s="38">
         <v>11042</v>
       </c>
+      <c r="Q683" s="50">
+        <v>1</v>
+      </c>
       <c r="U683" s="50">
         <v>76005</v>
       </c>
@@ -46920,6 +47223,9 @@
       <c r="N684" s="38">
         <v>11042</v>
       </c>
+      <c r="Q684" s="50">
+        <v>1</v>
+      </c>
       <c r="U684" s="50">
         <v>76005</v>
       </c>
@@ -46956,6 +47262,9 @@
       <c r="N685" s="38">
         <v>11042</v>
       </c>
+      <c r="Q685" s="50">
+        <v>1</v>
+      </c>
       <c r="U685" s="50">
         <v>76005</v>
       </c>
@@ -46988,6 +47297,9 @@
       <c r="N686" s="38">
         <v>11042</v>
       </c>
+      <c r="Q686" s="50">
+        <v>1</v>
+      </c>
       <c r="U686" s="50">
         <v>76005</v>
       </c>
@@ -47024,6 +47336,9 @@
       <c r="N687" s="38">
         <v>11042</v>
       </c>
+      <c r="Q687" s="50">
+        <v>1</v>
+      </c>
       <c r="U687" s="50">
         <v>76006</v>
       </c>
@@ -47060,6 +47375,9 @@
       <c r="N688" s="38">
         <v>11042</v>
       </c>
+      <c r="Q688" s="50">
+        <v>1</v>
+      </c>
       <c r="U688" s="50">
         <v>76006</v>
       </c>
@@ -47096,6 +47414,9 @@
       <c r="N689" s="38">
         <v>11042</v>
       </c>
+      <c r="Q689" s="50">
+        <v>1</v>
+      </c>
       <c r="U689" s="50">
         <v>76006</v>
       </c>
@@ -47132,6 +47453,9 @@
       <c r="N690" s="38">
         <v>11042</v>
       </c>
+      <c r="Q690" s="50">
+        <v>1</v>
+      </c>
       <c r="U690" s="50">
         <v>76006</v>
       </c>
@@ -47168,6 +47492,9 @@
       <c r="N691" s="38">
         <v>11042</v>
       </c>
+      <c r="Q691" s="50">
+        <v>1</v>
+      </c>
       <c r="U691" s="50">
         <v>76006</v>
       </c>
@@ -47200,6 +47527,9 @@
       <c r="N692" s="38">
         <v>11042</v>
       </c>
+      <c r="Q692" s="50">
+        <v>1</v>
+      </c>
       <c r="U692" s="50">
         <v>76006</v>
       </c>
@@ -47236,6 +47566,9 @@
       <c r="N693" s="38">
         <v>11042</v>
       </c>
+      <c r="Q693" s="50">
+        <v>1</v>
+      </c>
       <c r="U693" s="50">
         <v>76007</v>
       </c>
@@ -47272,6 +47605,9 @@
       <c r="N694" s="38">
         <v>11042</v>
       </c>
+      <c r="Q694" s="50">
+        <v>1</v>
+      </c>
       <c r="U694" s="50">
         <v>76007</v>
       </c>
@@ -47308,6 +47644,9 @@
       <c r="N695" s="38">
         <v>11042</v>
       </c>
+      <c r="Q695" s="50">
+        <v>1</v>
+      </c>
       <c r="U695" s="50">
         <v>76007</v>
       </c>
@@ -47344,6 +47683,9 @@
       <c r="N696" s="38">
         <v>11042</v>
       </c>
+      <c r="Q696" s="50">
+        <v>1</v>
+      </c>
       <c r="U696" s="50">
         <v>76007</v>
       </c>
@@ -47380,6 +47722,9 @@
       <c r="N697" s="38">
         <v>11042</v>
       </c>
+      <c r="Q697" s="50">
+        <v>1</v>
+      </c>
       <c r="U697" s="50">
         <v>76007</v>
       </c>
@@ -47416,6 +47761,9 @@
       <c r="N698" s="38">
         <v>11042</v>
       </c>
+      <c r="Q698" s="50">
+        <v>1</v>
+      </c>
       <c r="U698" s="50">
         <v>76007</v>
       </c>
@@ -47452,6 +47800,9 @@
       <c r="N699" s="38">
         <v>11042</v>
       </c>
+      <c r="Q699" s="50">
+        <v>1</v>
+      </c>
       <c r="U699" s="50">
         <v>76007</v>
       </c>
@@ -47484,6 +47835,9 @@
       <c r="N700" s="38">
         <v>11042</v>
       </c>
+      <c r="Q700" s="50">
+        <v>1</v>
+      </c>
       <c r="U700" s="50">
         <v>76007</v>
       </c>
@@ -47520,6 +47874,9 @@
       <c r="N701" s="38">
         <v>11042</v>
       </c>
+      <c r="Q701" s="50">
+        <v>1</v>
+      </c>
       <c r="U701" s="50">
         <v>76008</v>
       </c>
@@ -47556,6 +47913,9 @@
       <c r="N702" s="38">
         <v>11042</v>
       </c>
+      <c r="Q702" s="50">
+        <v>1</v>
+      </c>
       <c r="U702" s="50">
         <v>76008</v>
       </c>
@@ -47592,6 +47952,9 @@
       <c r="N703" s="38">
         <v>11042</v>
       </c>
+      <c r="Q703" s="50">
+        <v>1</v>
+      </c>
       <c r="U703" s="50">
         <v>76008</v>
       </c>
@@ -47628,6 +47991,9 @@
       <c r="N704" s="38">
         <v>11042</v>
       </c>
+      <c r="Q704" s="50">
+        <v>1</v>
+      </c>
       <c r="U704" s="50">
         <v>76008</v>
       </c>
@@ -47664,6 +48030,9 @@
       <c r="N705" s="38">
         <v>11042</v>
       </c>
+      <c r="Q705" s="50">
+        <v>1</v>
+      </c>
       <c r="U705" s="50">
         <v>76008</v>
       </c>
@@ -47696,6 +48065,9 @@
       <c r="N706" s="38">
         <v>11042</v>
       </c>
+      <c r="Q706" s="50">
+        <v>1</v>
+      </c>
       <c r="U706" s="50">
         <v>76008</v>
       </c>
@@ -47735,6 +48107,9 @@
       <c r="N707" s="38">
         <v>3205</v>
       </c>
+      <c r="Q707" s="50">
+        <v>1</v>
+      </c>
       <c r="U707" s="50">
         <v>76001</v>
       </c>
@@ -47774,6 +48149,9 @@
       <c r="N708" s="38">
         <v>3205</v>
       </c>
+      <c r="Q708" s="50">
+        <v>1</v>
+      </c>
       <c r="U708" s="50">
         <v>76001</v>
       </c>
@@ -47813,6 +48191,9 @@
       <c r="N709" s="38">
         <v>3205</v>
       </c>
+      <c r="Q709" s="50">
+        <v>1</v>
+      </c>
       <c r="U709" s="50">
         <v>76001</v>
       </c>
@@ -47852,6 +48233,9 @@
       <c r="N710" s="38">
         <v>3205</v>
       </c>
+      <c r="Q710" s="50">
+        <v>1</v>
+      </c>
       <c r="U710" s="50">
         <v>76001</v>
       </c>
@@ -47891,6 +48275,9 @@
       <c r="N711" s="38">
         <v>3205</v>
       </c>
+      <c r="Q711" s="50">
+        <v>1</v>
+      </c>
       <c r="U711" s="50">
         <v>76001</v>
       </c>
@@ -47926,6 +48313,9 @@
       <c r="N712" s="38">
         <v>3205</v>
       </c>
+      <c r="Q712" s="50">
+        <v>1</v>
+      </c>
       <c r="U712" s="50">
         <v>76001</v>
       </c>
@@ -47962,6 +48352,9 @@
       <c r="N713" s="38">
         <v>3308</v>
       </c>
+      <c r="Q713" s="50">
+        <v>1</v>
+      </c>
       <c r="U713" s="50">
         <v>76002</v>
       </c>
@@ -47998,6 +48391,9 @@
       <c r="N714" s="38">
         <v>3308</v>
       </c>
+      <c r="Q714" s="50">
+        <v>1</v>
+      </c>
       <c r="U714" s="50">
         <v>76002</v>
       </c>
@@ -48034,6 +48430,9 @@
       <c r="N715" s="38">
         <v>3308</v>
       </c>
+      <c r="Q715" s="50">
+        <v>1</v>
+      </c>
       <c r="U715" s="50">
         <v>76002</v>
       </c>
@@ -48070,6 +48469,9 @@
       <c r="N716" s="38">
         <v>3308</v>
       </c>
+      <c r="Q716" s="50">
+        <v>1</v>
+      </c>
       <c r="U716" s="50">
         <v>76002</v>
       </c>
@@ -48106,6 +48508,9 @@
       <c r="N717" s="38">
         <v>3308</v>
       </c>
+      <c r="Q717" s="50">
+        <v>1</v>
+      </c>
       <c r="U717" s="50">
         <v>76002</v>
       </c>
@@ -48138,6 +48543,9 @@
       <c r="N718" s="38">
         <v>3308</v>
       </c>
+      <c r="Q718" s="50">
+        <v>1</v>
+      </c>
       <c r="U718" s="50">
         <v>76002</v>
       </c>
@@ -48174,6 +48582,9 @@
       <c r="N719" s="38">
         <v>11003</v>
       </c>
+      <c r="Q719" s="50">
+        <v>1</v>
+      </c>
       <c r="U719" s="50">
         <v>76003</v>
       </c>
@@ -48210,6 +48621,9 @@
       <c r="N720" s="38">
         <v>11003</v>
       </c>
+      <c r="Q720" s="50">
+        <v>1</v>
+      </c>
       <c r="U720" s="50">
         <v>76003</v>
       </c>
@@ -48246,6 +48660,9 @@
       <c r="N721" s="38">
         <v>11003</v>
       </c>
+      <c r="Q721" s="50">
+        <v>1</v>
+      </c>
       <c r="U721" s="50">
         <v>76003</v>
       </c>
@@ -48282,6 +48699,9 @@
       <c r="N722" s="38">
         <v>11003</v>
       </c>
+      <c r="Q722" s="50">
+        <v>1</v>
+      </c>
       <c r="U722" s="50">
         <v>76003</v>
       </c>
@@ -48318,6 +48738,9 @@
       <c r="N723" s="38">
         <v>11003</v>
       </c>
+      <c r="Q723" s="50">
+        <v>1</v>
+      </c>
       <c r="U723" s="50">
         <v>76003</v>
       </c>
@@ -48350,6 +48773,9 @@
       <c r="N724" s="38">
         <v>11003</v>
       </c>
+      <c r="Q724" s="50">
+        <v>1</v>
+      </c>
       <c r="U724" s="50">
         <v>76003</v>
       </c>
@@ -48386,6 +48812,9 @@
       <c r="N725" s="38">
         <v>11003</v>
       </c>
+      <c r="Q725" s="50">
+        <v>1</v>
+      </c>
       <c r="U725" s="50">
         <v>76004</v>
       </c>
@@ -48422,6 +48851,9 @@
       <c r="N726" s="38">
         <v>11003</v>
       </c>
+      <c r="Q726" s="50">
+        <v>1</v>
+      </c>
       <c r="U726" s="50">
         <v>76004</v>
       </c>
@@ -48458,6 +48890,9 @@
       <c r="N727" s="38">
         <v>11003</v>
       </c>
+      <c r="Q727" s="50">
+        <v>1</v>
+      </c>
       <c r="U727" s="50">
         <v>76004</v>
       </c>
@@ -48494,6 +48929,9 @@
       <c r="N728" s="38">
         <v>11003</v>
       </c>
+      <c r="Q728" s="50">
+        <v>1</v>
+      </c>
       <c r="U728" s="50">
         <v>76004</v>
       </c>
@@ -48530,6 +48968,9 @@
       <c r="N729" s="38">
         <v>11003</v>
       </c>
+      <c r="Q729" s="50">
+        <v>1</v>
+      </c>
       <c r="U729" s="50">
         <v>76004</v>
       </c>
@@ -48562,6 +49003,9 @@
       <c r="N730" s="38">
         <v>11003</v>
       </c>
+      <c r="Q730" s="50">
+        <v>1</v>
+      </c>
       <c r="U730" s="50">
         <v>76004</v>
       </c>
@@ -48598,6 +49042,9 @@
       <c r="N731" s="38">
         <v>11003</v>
       </c>
+      <c r="Q731" s="50">
+        <v>1</v>
+      </c>
       <c r="U731" s="50">
         <v>76009</v>
       </c>
@@ -48634,6 +49081,9 @@
       <c r="N732" s="38">
         <v>11003</v>
       </c>
+      <c r="Q732" s="50">
+        <v>1</v>
+      </c>
       <c r="U732" s="50">
         <v>76009</v>
       </c>
@@ -48670,6 +49120,9 @@
       <c r="N733" s="38">
         <v>11003</v>
       </c>
+      <c r="Q733" s="50">
+        <v>1</v>
+      </c>
       <c r="U733" s="50">
         <v>76009</v>
       </c>
@@ -48706,6 +49159,9 @@
       <c r="N734" s="38">
         <v>11003</v>
       </c>
+      <c r="Q734" s="50">
+        <v>1</v>
+      </c>
       <c r="U734" s="50">
         <v>76009</v>
       </c>
@@ -48742,6 +49198,9 @@
       <c r="N735" s="38">
         <v>11003</v>
       </c>
+      <c r="Q735" s="50">
+        <v>1</v>
+      </c>
       <c r="U735" s="50">
         <v>76009</v>
       </c>
@@ -48774,6 +49233,9 @@
       <c r="N736" s="38">
         <v>11003</v>
       </c>
+      <c r="Q736" s="50">
+        <v>1</v>
+      </c>
       <c r="U736" s="50">
         <v>76009</v>
       </c>
@@ -48810,6 +49272,9 @@
       <c r="N737" s="38">
         <v>11003</v>
       </c>
+      <c r="Q737" s="50">
+        <v>1</v>
+      </c>
       <c r="U737" s="50">
         <v>76006</v>
       </c>
@@ -48846,6 +49311,9 @@
       <c r="N738" s="38">
         <v>11003</v>
       </c>
+      <c r="Q738" s="50">
+        <v>1</v>
+      </c>
       <c r="U738" s="50">
         <v>76006</v>
       </c>
@@ -48882,6 +49350,9 @@
       <c r="N739" s="38">
         <v>11003</v>
       </c>
+      <c r="Q739" s="50">
+        <v>1</v>
+      </c>
       <c r="U739" s="50">
         <v>76006</v>
       </c>
@@ -48918,6 +49389,9 @@
       <c r="N740" s="38">
         <v>11003</v>
       </c>
+      <c r="Q740" s="50">
+        <v>1</v>
+      </c>
       <c r="U740" s="50">
         <v>76006</v>
       </c>
@@ -48954,6 +49428,9 @@
       <c r="N741" s="38">
         <v>11003</v>
       </c>
+      <c r="Q741" s="50">
+        <v>1</v>
+      </c>
       <c r="U741" s="50">
         <v>76006</v>
       </c>
@@ -48986,6 +49463,9 @@
       <c r="N742" s="38">
         <v>11003</v>
       </c>
+      <c r="Q742" s="50">
+        <v>1</v>
+      </c>
       <c r="U742" s="50">
         <v>76006</v>
       </c>
@@ -49022,6 +49502,9 @@
       <c r="N743" s="38">
         <v>11003</v>
       </c>
+      <c r="Q743" s="50">
+        <v>1</v>
+      </c>
       <c r="U743" s="50">
         <v>76007</v>
       </c>
@@ -49058,6 +49541,9 @@
       <c r="N744" s="38">
         <v>11003</v>
       </c>
+      <c r="Q744" s="50">
+        <v>1</v>
+      </c>
       <c r="U744" s="50">
         <v>76007</v>
       </c>
@@ -49094,6 +49580,9 @@
       <c r="N745" s="38">
         <v>11003</v>
       </c>
+      <c r="Q745" s="50">
+        <v>1</v>
+      </c>
       <c r="U745" s="50">
         <v>76007</v>
       </c>
@@ -49130,6 +49619,9 @@
       <c r="N746" s="38">
         <v>11003</v>
       </c>
+      <c r="Q746" s="50">
+        <v>1</v>
+      </c>
       <c r="U746" s="50">
         <v>76007</v>
       </c>
@@ -49166,6 +49658,9 @@
       <c r="N747" s="38">
         <v>11003</v>
       </c>
+      <c r="Q747" s="50">
+        <v>1</v>
+      </c>
       <c r="U747" s="50">
         <v>76007</v>
       </c>
@@ -49202,6 +49697,9 @@
       <c r="N748" s="38">
         <v>11003</v>
       </c>
+      <c r="Q748" s="50">
+        <v>1</v>
+      </c>
       <c r="U748" s="50">
         <v>76007</v>
       </c>
@@ -49238,6 +49736,9 @@
       <c r="N749" s="38">
         <v>11003</v>
       </c>
+      <c r="Q749" s="50">
+        <v>1</v>
+      </c>
       <c r="U749" s="50">
         <v>76007</v>
       </c>
@@ -49270,6 +49771,9 @@
       <c r="N750" s="38">
         <v>11003</v>
       </c>
+      <c r="Q750" s="50">
+        <v>1</v>
+      </c>
       <c r="U750" s="50">
         <v>76007</v>
       </c>
@@ -49306,6 +49810,9 @@
       <c r="N751" s="38">
         <v>11003</v>
       </c>
+      <c r="Q751" s="50">
+        <v>1</v>
+      </c>
       <c r="U751" s="50">
         <v>76008</v>
       </c>
@@ -49342,6 +49849,9 @@
       <c r="N752" s="38">
         <v>11003</v>
       </c>
+      <c r="Q752" s="50">
+        <v>1</v>
+      </c>
       <c r="U752" s="50">
         <v>76008</v>
       </c>
@@ -49378,6 +49888,9 @@
       <c r="N753" s="38">
         <v>11003</v>
       </c>
+      <c r="Q753" s="50">
+        <v>1</v>
+      </c>
       <c r="U753" s="50">
         <v>76008</v>
       </c>
@@ -49414,6 +49927,9 @@
       <c r="N754" s="38">
         <v>11003</v>
       </c>
+      <c r="Q754" s="50">
+        <v>1</v>
+      </c>
       <c r="U754" s="50">
         <v>76008</v>
       </c>
@@ -49450,6 +49966,9 @@
       <c r="N755" s="38">
         <v>11003</v>
       </c>
+      <c r="Q755" s="50">
+        <v>1</v>
+      </c>
       <c r="U755" s="50">
         <v>76008</v>
       </c>
@@ -49482,6 +50001,9 @@
       <c r="N756" s="38">
         <v>11003</v>
       </c>
+      <c r="Q756" s="50">
+        <v>1</v>
+      </c>
       <c r="U756" s="50">
         <v>76008</v>
       </c>
@@ -49521,6 +50043,9 @@
       <c r="N757" s="38">
         <v>3206</v>
       </c>
+      <c r="Q757" s="50">
+        <v>1</v>
+      </c>
       <c r="U757" s="50">
         <v>76001</v>
       </c>
@@ -49560,6 +50085,9 @@
       <c r="N758" s="38">
         <v>3206</v>
       </c>
+      <c r="Q758" s="50">
+        <v>1</v>
+      </c>
       <c r="U758" s="50">
         <v>76001</v>
       </c>
@@ -49599,6 +50127,9 @@
       <c r="N759" s="38">
         <v>3206</v>
       </c>
+      <c r="Q759" s="50">
+        <v>1</v>
+      </c>
       <c r="U759" s="50">
         <v>76001</v>
       </c>
@@ -49638,6 +50169,9 @@
       <c r="N760" s="38">
         <v>3206</v>
       </c>
+      <c r="Q760" s="50">
+        <v>1</v>
+      </c>
       <c r="U760" s="50">
         <v>76001</v>
       </c>
@@ -49677,6 +50211,9 @@
       <c r="N761" s="38">
         <v>3206</v>
       </c>
+      <c r="Q761" s="50">
+        <v>1</v>
+      </c>
       <c r="U761" s="50">
         <v>76001</v>
       </c>
@@ -49712,6 +50249,9 @@
       <c r="N762" s="38">
         <v>3206</v>
       </c>
+      <c r="Q762" s="50">
+        <v>1</v>
+      </c>
       <c r="U762" s="50">
         <v>76001</v>
       </c>
@@ -49748,6 +50288,9 @@
       <c r="N763" s="38">
         <v>3307</v>
       </c>
+      <c r="Q763" s="50">
+        <v>1</v>
+      </c>
       <c r="U763" s="50">
         <v>76002</v>
       </c>
@@ -49784,6 +50327,9 @@
       <c r="N764" s="38">
         <v>3307</v>
       </c>
+      <c r="Q764" s="50">
+        <v>1</v>
+      </c>
       <c r="U764" s="50">
         <v>76002</v>
       </c>
@@ -49820,6 +50366,9 @@
       <c r="N765" s="38">
         <v>3307</v>
       </c>
+      <c r="Q765" s="50">
+        <v>1</v>
+      </c>
       <c r="U765" s="50">
         <v>76002</v>
       </c>
@@ -49856,6 +50405,9 @@
       <c r="N766" s="38">
         <v>3307</v>
       </c>
+      <c r="Q766" s="50">
+        <v>1</v>
+      </c>
       <c r="U766" s="50">
         <v>76002</v>
       </c>
@@ -49892,6 +50444,9 @@
       <c r="N767" s="38">
         <v>3307</v>
       </c>
+      <c r="Q767" s="50">
+        <v>1</v>
+      </c>
       <c r="U767" s="50">
         <v>76002</v>
       </c>
@@ -49924,6 +50479,9 @@
       <c r="N768" s="38">
         <v>3307</v>
       </c>
+      <c r="Q768" s="50">
+        <v>1</v>
+      </c>
       <c r="U768" s="50">
         <v>76002</v>
       </c>
@@ -49960,6 +50518,9 @@
       <c r="N769" s="38">
         <v>11012</v>
       </c>
+      <c r="Q769" s="50">
+        <v>1</v>
+      </c>
       <c r="U769" s="50">
         <v>76003</v>
       </c>
@@ -49996,6 +50557,9 @@
       <c r="N770" s="38">
         <v>11012</v>
       </c>
+      <c r="Q770" s="50">
+        <v>1</v>
+      </c>
       <c r="U770" s="50">
         <v>76003</v>
       </c>
@@ -50032,6 +50596,9 @@
       <c r="N771" s="38">
         <v>11012</v>
       </c>
+      <c r="Q771" s="50">
+        <v>1</v>
+      </c>
       <c r="U771" s="50">
         <v>76003</v>
       </c>
@@ -50068,6 +50635,9 @@
       <c r="N772" s="38">
         <v>11012</v>
       </c>
+      <c r="Q772" s="50">
+        <v>1</v>
+      </c>
       <c r="U772" s="50">
         <v>76003</v>
       </c>
@@ -50104,6 +50674,9 @@
       <c r="N773" s="38">
         <v>11012</v>
       </c>
+      <c r="Q773" s="50">
+        <v>1</v>
+      </c>
       <c r="U773" s="50">
         <v>76003</v>
       </c>
@@ -50136,6 +50709,9 @@
       <c r="N774" s="38">
         <v>11012</v>
       </c>
+      <c r="Q774" s="50">
+        <v>1</v>
+      </c>
       <c r="U774" s="50">
         <v>76003</v>
       </c>
@@ -50172,6 +50748,9 @@
       <c r="N775" s="38">
         <v>11012</v>
       </c>
+      <c r="Q775" s="50">
+        <v>1</v>
+      </c>
       <c r="U775" s="50">
         <v>76004</v>
       </c>
@@ -50208,6 +50787,9 @@
       <c r="N776" s="38">
         <v>11012</v>
       </c>
+      <c r="Q776" s="50">
+        <v>1</v>
+      </c>
       <c r="U776" s="50">
         <v>76004</v>
       </c>
@@ -50244,6 +50826,9 @@
       <c r="N777" s="38">
         <v>11012</v>
       </c>
+      <c r="Q777" s="50">
+        <v>1</v>
+      </c>
       <c r="U777" s="50">
         <v>76004</v>
       </c>
@@ -50280,6 +50865,9 @@
       <c r="N778" s="38">
         <v>11012</v>
       </c>
+      <c r="Q778" s="50">
+        <v>1</v>
+      </c>
       <c r="U778" s="50">
         <v>76004</v>
       </c>
@@ -50316,6 +50904,9 @@
       <c r="N779" s="38">
         <v>11012</v>
       </c>
+      <c r="Q779" s="50">
+        <v>1</v>
+      </c>
       <c r="U779" s="50">
         <v>76004</v>
       </c>
@@ -50348,6 +50939,9 @@
       <c r="N780" s="38">
         <v>11012</v>
       </c>
+      <c r="Q780" s="50">
+        <v>1</v>
+      </c>
       <c r="U780" s="50">
         <v>76004</v>
       </c>
@@ -50384,6 +50978,9 @@
       <c r="N781" s="38">
         <v>11012</v>
       </c>
+      <c r="Q781" s="50">
+        <v>1</v>
+      </c>
       <c r="U781" s="50">
         <v>76010</v>
       </c>
@@ -50420,6 +51017,9 @@
       <c r="N782" s="38">
         <v>11012</v>
       </c>
+      <c r="Q782" s="50">
+        <v>1</v>
+      </c>
       <c r="U782" s="50">
         <v>76010</v>
       </c>
@@ -50456,6 +51056,9 @@
       <c r="N783" s="38">
         <v>11012</v>
       </c>
+      <c r="Q783" s="50">
+        <v>1</v>
+      </c>
       <c r="U783" s="50">
         <v>76010</v>
       </c>
@@ -50492,6 +51095,9 @@
       <c r="N784" s="38">
         <v>11012</v>
       </c>
+      <c r="Q784" s="50">
+        <v>1</v>
+      </c>
       <c r="U784" s="50">
         <v>76010</v>
       </c>
@@ -50528,6 +51134,9 @@
       <c r="N785" s="38">
         <v>11012</v>
       </c>
+      <c r="Q785" s="50">
+        <v>1</v>
+      </c>
       <c r="U785" s="50">
         <v>76010</v>
       </c>
@@ -50560,6 +51169,9 @@
       <c r="N786" s="38">
         <v>11012</v>
       </c>
+      <c r="Q786" s="50">
+        <v>1</v>
+      </c>
       <c r="U786" s="50">
         <v>76010</v>
       </c>
@@ -50596,6 +51208,9 @@
       <c r="N787" s="38">
         <v>11012</v>
       </c>
+      <c r="Q787" s="50">
+        <v>1</v>
+      </c>
       <c r="U787" s="50">
         <v>76006</v>
       </c>
@@ -50632,6 +51247,9 @@
       <c r="N788" s="38">
         <v>11012</v>
       </c>
+      <c r="Q788" s="50">
+        <v>1</v>
+      </c>
       <c r="U788" s="50">
         <v>76006</v>
       </c>
@@ -50668,6 +51286,9 @@
       <c r="N789" s="38">
         <v>11012</v>
       </c>
+      <c r="Q789" s="50">
+        <v>1</v>
+      </c>
       <c r="U789" s="50">
         <v>76006</v>
       </c>
@@ -50704,6 +51325,9 @@
       <c r="N790" s="38">
         <v>11012</v>
       </c>
+      <c r="Q790" s="50">
+        <v>1</v>
+      </c>
       <c r="U790" s="50">
         <v>76006</v>
       </c>
@@ -50740,6 +51364,9 @@
       <c r="N791" s="38">
         <v>11012</v>
       </c>
+      <c r="Q791" s="50">
+        <v>1</v>
+      </c>
       <c r="U791" s="50">
         <v>76006</v>
       </c>
@@ -50772,6 +51399,9 @@
       <c r="N792" s="38">
         <v>11012</v>
       </c>
+      <c r="Q792" s="50">
+        <v>1</v>
+      </c>
       <c r="U792" s="50">
         <v>76006</v>
       </c>
@@ -50808,6 +51438,9 @@
       <c r="N793" s="38">
         <v>11012</v>
       </c>
+      <c r="Q793" s="50">
+        <v>1</v>
+      </c>
       <c r="U793" s="50">
         <v>76007</v>
       </c>
@@ -50844,6 +51477,9 @@
       <c r="N794" s="38">
         <v>11012</v>
       </c>
+      <c r="Q794" s="50">
+        <v>1</v>
+      </c>
       <c r="U794" s="50">
         <v>76007</v>
       </c>
@@ -50880,6 +51516,9 @@
       <c r="N795" s="38">
         <v>11012</v>
       </c>
+      <c r="Q795" s="50">
+        <v>1</v>
+      </c>
       <c r="U795" s="50">
         <v>76007</v>
       </c>
@@ -50916,6 +51555,9 @@
       <c r="N796" s="38">
         <v>11012</v>
       </c>
+      <c r="Q796" s="50">
+        <v>1</v>
+      </c>
       <c r="U796" s="50">
         <v>76007</v>
       </c>
@@ -50952,6 +51594,9 @@
       <c r="N797" s="38">
         <v>11012</v>
       </c>
+      <c r="Q797" s="50">
+        <v>1</v>
+      </c>
       <c r="U797" s="50">
         <v>76007</v>
       </c>
@@ -50988,6 +51633,9 @@
       <c r="N798" s="38">
         <v>11012</v>
       </c>
+      <c r="Q798" s="50">
+        <v>1</v>
+      </c>
       <c r="U798" s="50">
         <v>76007</v>
       </c>
@@ -51024,6 +51672,9 @@
       <c r="N799" s="38">
         <v>11012</v>
       </c>
+      <c r="Q799" s="50">
+        <v>1</v>
+      </c>
       <c r="U799" s="50">
         <v>76007</v>
       </c>
@@ -51056,6 +51707,9 @@
       <c r="N800" s="38">
         <v>11012</v>
       </c>
+      <c r="Q800" s="50">
+        <v>1</v>
+      </c>
       <c r="U800" s="50">
         <v>76007</v>
       </c>
@@ -51092,6 +51746,9 @@
       <c r="N801" s="38">
         <v>11012</v>
       </c>
+      <c r="Q801" s="50">
+        <v>1</v>
+      </c>
       <c r="U801" s="50">
         <v>76009</v>
       </c>
@@ -51128,6 +51785,9 @@
       <c r="N802" s="38">
         <v>11012</v>
       </c>
+      <c r="Q802" s="50">
+        <v>1</v>
+      </c>
       <c r="U802" s="50">
         <v>76009</v>
       </c>
@@ -51164,6 +51824,9 @@
       <c r="N803" s="38">
         <v>11012</v>
       </c>
+      <c r="Q803" s="50">
+        <v>1</v>
+      </c>
       <c r="U803" s="50">
         <v>76009</v>
       </c>
@@ -51200,6 +51863,9 @@
       <c r="N804" s="38">
         <v>11012</v>
       </c>
+      <c r="Q804" s="50">
+        <v>1</v>
+      </c>
       <c r="U804" s="50">
         <v>76009</v>
       </c>
@@ -51236,6 +51902,9 @@
       <c r="N805" s="38">
         <v>11012</v>
       </c>
+      <c r="Q805" s="50">
+        <v>1</v>
+      </c>
       <c r="U805" s="50">
         <v>76009</v>
       </c>
@@ -51268,6 +51937,9 @@
       <c r="N806" s="38">
         <v>11012</v>
       </c>
+      <c r="Q806" s="50">
+        <v>1</v>
+      </c>
       <c r="U806" s="50">
         <v>76009</v>
       </c>
@@ -51307,6 +51979,9 @@
       <c r="N807" s="38">
         <v>3207</v>
       </c>
+      <c r="Q807" s="50">
+        <v>1</v>
+      </c>
       <c r="U807" s="61">
         <v>76001</v>
       </c>
@@ -51346,6 +52021,9 @@
       <c r="N808" s="38">
         <v>3207</v>
       </c>
+      <c r="Q808" s="50">
+        <v>1</v>
+      </c>
       <c r="U808" s="61">
         <v>76001</v>
       </c>
@@ -51385,6 +52063,9 @@
       <c r="N809" s="38">
         <v>3207</v>
       </c>
+      <c r="Q809" s="50">
+        <v>1</v>
+      </c>
       <c r="U809" s="61">
         <v>76001</v>
       </c>
@@ -51424,6 +52105,9 @@
       <c r="N810" s="38">
         <v>3207</v>
       </c>
+      <c r="Q810" s="50">
+        <v>1</v>
+      </c>
       <c r="U810" s="61">
         <v>76001</v>
       </c>
@@ -51463,6 +52147,9 @@
       <c r="N811" s="38">
         <v>3207</v>
       </c>
+      <c r="Q811" s="50">
+        <v>1</v>
+      </c>
       <c r="U811" s="61">
         <v>76001</v>
       </c>
@@ -51498,6 +52185,9 @@
       <c r="N812" s="38">
         <v>3207</v>
       </c>
+      <c r="Q812" s="50">
+        <v>1</v>
+      </c>
       <c r="U812" s="61">
         <v>76001</v>
       </c>
@@ -51534,6 +52224,9 @@
       <c r="N813" s="38">
         <v>3306</v>
       </c>
+      <c r="Q813" s="50">
+        <v>1</v>
+      </c>
       <c r="U813" s="50">
         <v>76002</v>
       </c>
@@ -51570,6 +52263,9 @@
       <c r="N814" s="38">
         <v>3306</v>
       </c>
+      <c r="Q814" s="50">
+        <v>1</v>
+      </c>
       <c r="U814" s="50">
         <v>76002</v>
       </c>
@@ -51606,6 +52302,9 @@
       <c r="N815" s="38">
         <v>3306</v>
       </c>
+      <c r="Q815" s="50">
+        <v>1</v>
+      </c>
       <c r="U815" s="50">
         <v>76002</v>
       </c>
@@ -51642,6 +52341,9 @@
       <c r="N816" s="38">
         <v>3306</v>
       </c>
+      <c r="Q816" s="50">
+        <v>1</v>
+      </c>
       <c r="U816" s="50">
         <v>76002</v>
       </c>
@@ -51678,6 +52380,9 @@
       <c r="N817" s="38">
         <v>3306</v>
       </c>
+      <c r="Q817" s="50">
+        <v>1</v>
+      </c>
       <c r="U817" s="50">
         <v>76002</v>
       </c>
@@ -51710,6 +52415,9 @@
       <c r="N818" s="38">
         <v>3306</v>
       </c>
+      <c r="Q818" s="50">
+        <v>1</v>
+      </c>
       <c r="U818" s="50">
         <v>76002</v>
       </c>
@@ -51746,6 +52454,9 @@
       <c r="N819" s="38">
         <v>11028</v>
       </c>
+      <c r="Q819" s="50">
+        <v>1</v>
+      </c>
       <c r="U819" s="50">
         <v>76003</v>
       </c>
@@ -51782,6 +52493,9 @@
       <c r="N820" s="38">
         <v>11028</v>
       </c>
+      <c r="Q820" s="50">
+        <v>1</v>
+      </c>
       <c r="U820" s="50">
         <v>76003</v>
       </c>
@@ -51818,6 +52532,9 @@
       <c r="N821" s="38">
         <v>11028</v>
       </c>
+      <c r="Q821" s="50">
+        <v>1</v>
+      </c>
       <c r="U821" s="50">
         <v>76003</v>
       </c>
@@ -51854,6 +52571,9 @@
       <c r="N822" s="38">
         <v>11028</v>
       </c>
+      <c r="Q822" s="50">
+        <v>1</v>
+      </c>
       <c r="U822" s="50">
         <v>76003</v>
       </c>
@@ -51890,6 +52610,9 @@
       <c r="N823" s="38">
         <v>11028</v>
       </c>
+      <c r="Q823" s="50">
+        <v>1</v>
+      </c>
       <c r="U823" s="50">
         <v>76003</v>
       </c>
@@ -51922,6 +52645,9 @@
       <c r="N824" s="38">
         <v>11028</v>
       </c>
+      <c r="Q824" s="50">
+        <v>1</v>
+      </c>
       <c r="U824" s="50">
         <v>76003</v>
       </c>
@@ -51958,6 +52684,9 @@
       <c r="N825" s="38">
         <v>11028</v>
       </c>
+      <c r="Q825" s="50">
+        <v>1</v>
+      </c>
       <c r="U825" s="50">
         <v>76004</v>
       </c>
@@ -51994,6 +52723,9 @@
       <c r="N826" s="38">
         <v>11028</v>
       </c>
+      <c r="Q826" s="50">
+        <v>1</v>
+      </c>
       <c r="U826" s="50">
         <v>76004</v>
       </c>
@@ -52030,6 +52762,9 @@
       <c r="N827" s="38">
         <v>11028</v>
       </c>
+      <c r="Q827" s="50">
+        <v>1</v>
+      </c>
       <c r="U827" s="50">
         <v>76004</v>
       </c>
@@ -52066,6 +52801,9 @@
       <c r="N828" s="38">
         <v>11028</v>
       </c>
+      <c r="Q828" s="50">
+        <v>1</v>
+      </c>
       <c r="U828" s="50">
         <v>76004</v>
       </c>
@@ -52102,6 +52840,9 @@
       <c r="N829" s="38">
         <v>11028</v>
       </c>
+      <c r="Q829" s="50">
+        <v>1</v>
+      </c>
       <c r="U829" s="50">
         <v>76004</v>
       </c>
@@ -52134,6 +52875,9 @@
       <c r="N830" s="38">
         <v>11028</v>
       </c>
+      <c r="Q830" s="50">
+        <v>1</v>
+      </c>
       <c r="U830" s="50">
         <v>76004</v>
       </c>
@@ -52170,6 +52914,9 @@
       <c r="N831" s="38">
         <v>11028</v>
       </c>
+      <c r="Q831" s="50">
+        <v>1</v>
+      </c>
       <c r="U831" s="50">
         <v>76005</v>
       </c>
@@ -52206,6 +52953,9 @@
       <c r="N832" s="38">
         <v>11028</v>
       </c>
+      <c r="Q832" s="50">
+        <v>1</v>
+      </c>
       <c r="U832" s="50">
         <v>76005</v>
       </c>
@@ -52242,6 +52992,9 @@
       <c r="N833" s="38">
         <v>11028</v>
       </c>
+      <c r="Q833" s="50">
+        <v>1</v>
+      </c>
       <c r="U833" s="50">
         <v>76005</v>
       </c>
@@ -52278,6 +53031,9 @@
       <c r="N834" s="38">
         <v>11028</v>
       </c>
+      <c r="Q834" s="50">
+        <v>1</v>
+      </c>
       <c r="U834" s="50">
         <v>76005</v>
       </c>
@@ -52314,6 +53070,9 @@
       <c r="N835" s="38">
         <v>11028</v>
       </c>
+      <c r="Q835" s="50">
+        <v>1</v>
+      </c>
       <c r="U835" s="50">
         <v>76005</v>
       </c>
@@ -52346,6 +53105,9 @@
       <c r="N836" s="38">
         <v>11028</v>
       </c>
+      <c r="Q836" s="50">
+        <v>1</v>
+      </c>
       <c r="U836" s="50">
         <v>76005</v>
       </c>
@@ -52382,6 +53144,9 @@
       <c r="N837" s="38">
         <v>11028</v>
       </c>
+      <c r="Q837" s="50">
+        <v>1</v>
+      </c>
       <c r="U837" s="50">
         <v>76006</v>
       </c>
@@ -52418,6 +53183,9 @@
       <c r="N838" s="38">
         <v>11028</v>
       </c>
+      <c r="Q838" s="50">
+        <v>1</v>
+      </c>
       <c r="U838" s="50">
         <v>76006</v>
       </c>
@@ -52454,6 +53222,9 @@
       <c r="N839" s="38">
         <v>11028</v>
       </c>
+      <c r="Q839" s="50">
+        <v>1</v>
+      </c>
       <c r="U839" s="50">
         <v>76006</v>
       </c>
@@ -52490,6 +53261,9 @@
       <c r="N840" s="38">
         <v>11028</v>
       </c>
+      <c r="Q840" s="50">
+        <v>1</v>
+      </c>
       <c r="U840" s="50">
         <v>76006</v>
       </c>
@@ -52526,6 +53300,9 @@
       <c r="N841" s="38">
         <v>11028</v>
       </c>
+      <c r="Q841" s="50">
+        <v>1</v>
+      </c>
       <c r="U841" s="50">
         <v>76006</v>
       </c>
@@ -52558,6 +53335,9 @@
       <c r="N842" s="38">
         <v>11028</v>
       </c>
+      <c r="Q842" s="50">
+        <v>1</v>
+      </c>
       <c r="U842" s="50">
         <v>76006</v>
       </c>
@@ -52594,6 +53374,9 @@
       <c r="N843" s="38">
         <v>11028</v>
       </c>
+      <c r="Q843" s="50">
+        <v>1</v>
+      </c>
       <c r="U843" s="50">
         <v>76007</v>
       </c>
@@ -52630,6 +53413,9 @@
       <c r="N844" s="38">
         <v>11028</v>
       </c>
+      <c r="Q844" s="50">
+        <v>1</v>
+      </c>
       <c r="U844" s="50">
         <v>76007</v>
       </c>
@@ -52666,6 +53452,9 @@
       <c r="N845" s="38">
         <v>11028</v>
       </c>
+      <c r="Q845" s="50">
+        <v>1</v>
+      </c>
       <c r="U845" s="50">
         <v>76007</v>
       </c>
@@ -52702,6 +53491,9 @@
       <c r="N846" s="38">
         <v>11028</v>
       </c>
+      <c r="Q846" s="50">
+        <v>1</v>
+      </c>
       <c r="U846" s="50">
         <v>76007</v>
       </c>
@@ -52738,6 +53530,9 @@
       <c r="N847" s="38">
         <v>11028</v>
       </c>
+      <c r="Q847" s="50">
+        <v>1</v>
+      </c>
       <c r="U847" s="50">
         <v>76007</v>
       </c>
@@ -52774,6 +53569,9 @@
       <c r="N848" s="38">
         <v>11028</v>
       </c>
+      <c r="Q848" s="50">
+        <v>1</v>
+      </c>
       <c r="U848" s="50">
         <v>76007</v>
       </c>
@@ -52810,6 +53608,9 @@
       <c r="N849" s="38">
         <v>11028</v>
       </c>
+      <c r="Q849" s="50">
+        <v>1</v>
+      </c>
       <c r="U849" s="50">
         <v>76007</v>
       </c>
@@ -52842,6 +53643,9 @@
       <c r="N850" s="38">
         <v>11028</v>
       </c>
+      <c r="Q850" s="50">
+        <v>1</v>
+      </c>
       <c r="U850" s="50">
         <v>76007</v>
       </c>
@@ -52878,6 +53682,9 @@
       <c r="N851" s="38">
         <v>11028</v>
       </c>
+      <c r="Q851" s="50">
+        <v>1</v>
+      </c>
       <c r="U851" s="50">
         <v>76008</v>
       </c>
@@ -52914,6 +53721,9 @@
       <c r="N852" s="38">
         <v>11028</v>
       </c>
+      <c r="Q852" s="50">
+        <v>1</v>
+      </c>
       <c r="U852" s="50">
         <v>76008</v>
       </c>
@@ -52950,6 +53760,9 @@
       <c r="N853" s="38">
         <v>11028</v>
       </c>
+      <c r="Q853" s="50">
+        <v>1</v>
+      </c>
       <c r="U853" s="50">
         <v>76008</v>
       </c>
@@ -52986,6 +53799,9 @@
       <c r="N854" s="38">
         <v>11028</v>
       </c>
+      <c r="Q854" s="50">
+        <v>1</v>
+      </c>
       <c r="U854" s="50">
         <v>76008</v>
       </c>
@@ -53022,6 +53838,9 @@
       <c r="N855" s="38">
         <v>11028</v>
       </c>
+      <c r="Q855" s="50">
+        <v>1</v>
+      </c>
       <c r="U855" s="50">
         <v>76008</v>
       </c>
@@ -53054,6 +53873,9 @@
       <c r="N856" s="38">
         <v>11028</v>
       </c>
+      <c r="Q856" s="50">
+        <v>1</v>
+      </c>
       <c r="U856" s="50">
         <v>76008</v>
       </c>
@@ -53093,6 +53915,9 @@
       <c r="N857" s="38">
         <v>3208</v>
       </c>
+      <c r="Q857" s="50">
+        <v>1</v>
+      </c>
       <c r="U857" s="61">
         <v>76001</v>
       </c>
@@ -53132,6 +53957,9 @@
       <c r="N858" s="38">
         <v>3208</v>
       </c>
+      <c r="Q858" s="50">
+        <v>1</v>
+      </c>
       <c r="U858" s="61">
         <v>76001</v>
       </c>
@@ -53171,6 +53999,9 @@
       <c r="N859" s="38">
         <v>3208</v>
       </c>
+      <c r="Q859" s="50">
+        <v>1</v>
+      </c>
       <c r="U859" s="61">
         <v>76001</v>
       </c>
@@ -53210,6 +54041,9 @@
       <c r="N860" s="38">
         <v>3208</v>
       </c>
+      <c r="Q860" s="50">
+        <v>1</v>
+      </c>
       <c r="U860" s="61">
         <v>76001</v>
       </c>
@@ -53249,6 +54083,9 @@
       <c r="N861" s="38">
         <v>3208</v>
       </c>
+      <c r="Q861" s="50">
+        <v>1</v>
+      </c>
       <c r="U861" s="61">
         <v>76001</v>
       </c>
@@ -53284,6 +54121,9 @@
       <c r="N862" s="38">
         <v>3208</v>
       </c>
+      <c r="Q862" s="50">
+        <v>1</v>
+      </c>
       <c r="U862" s="61">
         <v>76001</v>
       </c>
@@ -53320,6 +54160,9 @@
       <c r="N863" s="38">
         <v>3305</v>
       </c>
+      <c r="Q863" s="50">
+        <v>1</v>
+      </c>
       <c r="U863" s="50">
         <v>76002</v>
       </c>
@@ -53356,6 +54199,9 @@
       <c r="N864" s="38">
         <v>3305</v>
       </c>
+      <c r="Q864" s="50">
+        <v>1</v>
+      </c>
       <c r="U864" s="50">
         <v>76002</v>
       </c>
@@ -53392,6 +54238,9 @@
       <c r="N865" s="38">
         <v>3305</v>
       </c>
+      <c r="Q865" s="50">
+        <v>1</v>
+      </c>
       <c r="U865" s="50">
         <v>76002</v>
       </c>
@@ -53428,6 +54277,9 @@
       <c r="N866" s="38">
         <v>3305</v>
       </c>
+      <c r="Q866" s="50">
+        <v>1</v>
+      </c>
       <c r="U866" s="50">
         <v>76002</v>
       </c>
@@ -53464,6 +54316,9 @@
       <c r="N867" s="38">
         <v>3305</v>
       </c>
+      <c r="Q867" s="50">
+        <v>1</v>
+      </c>
       <c r="U867" s="50">
         <v>76002</v>
       </c>
@@ -53496,6 +54351,9 @@
       <c r="N868" s="38">
         <v>3305</v>
       </c>
+      <c r="Q868" s="50">
+        <v>1</v>
+      </c>
       <c r="U868" s="50">
         <v>76002</v>
       </c>
@@ -53532,6 +54390,9 @@
       <c r="N869" s="38">
         <v>11043</v>
       </c>
+      <c r="Q869" s="50">
+        <v>1</v>
+      </c>
       <c r="U869" s="50">
         <v>76003</v>
       </c>
@@ -53568,6 +54429,9 @@
       <c r="N870" s="38">
         <v>11043</v>
       </c>
+      <c r="Q870" s="50">
+        <v>1</v>
+      </c>
       <c r="U870" s="50">
         <v>76003</v>
       </c>
@@ -53604,6 +54468,9 @@
       <c r="N871" s="38">
         <v>11043</v>
       </c>
+      <c r="Q871" s="50">
+        <v>1</v>
+      </c>
       <c r="U871" s="50">
         <v>76003</v>
       </c>
@@ -53640,6 +54507,9 @@
       <c r="N872" s="38">
         <v>11043</v>
       </c>
+      <c r="Q872" s="50">
+        <v>1</v>
+      </c>
       <c r="U872" s="50">
         <v>76003</v>
       </c>
@@ -53676,6 +54546,9 @@
       <c r="N873" s="38">
         <v>11043</v>
       </c>
+      <c r="Q873" s="50">
+        <v>1</v>
+      </c>
       <c r="U873" s="50">
         <v>76003</v>
       </c>
@@ -53708,6 +54581,9 @@
       <c r="N874" s="38">
         <v>11043</v>
       </c>
+      <c r="Q874" s="50">
+        <v>1</v>
+      </c>
       <c r="U874" s="50">
         <v>76003</v>
       </c>
@@ -53744,6 +54620,9 @@
       <c r="N875" s="38">
         <v>11043</v>
       </c>
+      <c r="Q875" s="50">
+        <v>1</v>
+      </c>
       <c r="U875" s="50">
         <v>76004</v>
       </c>
@@ -53780,6 +54659,9 @@
       <c r="N876" s="38">
         <v>11043</v>
       </c>
+      <c r="Q876" s="50">
+        <v>1</v>
+      </c>
       <c r="U876" s="50">
         <v>76004</v>
       </c>
@@ -53816,6 +54698,9 @@
       <c r="N877" s="38">
         <v>11043</v>
       </c>
+      <c r="Q877" s="50">
+        <v>1</v>
+      </c>
       <c r="U877" s="50">
         <v>76004</v>
       </c>
@@ -53852,6 +54737,9 @@
       <c r="N878" s="38">
         <v>11043</v>
       </c>
+      <c r="Q878" s="50">
+        <v>1</v>
+      </c>
       <c r="U878" s="50">
         <v>76004</v>
       </c>
@@ -53888,6 +54776,9 @@
       <c r="N879" s="38">
         <v>11043</v>
       </c>
+      <c r="Q879" s="50">
+        <v>1</v>
+      </c>
       <c r="U879" s="50">
         <v>76004</v>
       </c>
@@ -53920,6 +54811,9 @@
       <c r="N880" s="38">
         <v>11043</v>
       </c>
+      <c r="Q880" s="50">
+        <v>1</v>
+      </c>
       <c r="U880" s="50">
         <v>76004</v>
       </c>
@@ -53956,6 +54850,9 @@
       <c r="N881" s="38">
         <v>11043</v>
       </c>
+      <c r="Q881" s="50">
+        <v>1</v>
+      </c>
       <c r="U881" s="50">
         <v>76005</v>
       </c>
@@ -53992,6 +54889,9 @@
       <c r="N882" s="38">
         <v>11043</v>
       </c>
+      <c r="Q882" s="50">
+        <v>1</v>
+      </c>
       <c r="U882" s="50">
         <v>76005</v>
       </c>
@@ -54028,6 +54928,9 @@
       <c r="N883" s="38">
         <v>11043</v>
       </c>
+      <c r="Q883" s="50">
+        <v>1</v>
+      </c>
       <c r="U883" s="50">
         <v>76005</v>
       </c>
@@ -54064,6 +54967,9 @@
       <c r="N884" s="38">
         <v>11043</v>
       </c>
+      <c r="Q884" s="50">
+        <v>1</v>
+      </c>
       <c r="U884" s="50">
         <v>76005</v>
       </c>
@@ -54100,6 +55006,9 @@
       <c r="N885" s="38">
         <v>11043</v>
       </c>
+      <c r="Q885" s="50">
+        <v>1</v>
+      </c>
       <c r="U885" s="50">
         <v>76005</v>
       </c>
@@ -54132,6 +55041,9 @@
       <c r="N886" s="38">
         <v>11043</v>
       </c>
+      <c r="Q886" s="50">
+        <v>1</v>
+      </c>
       <c r="U886" s="50">
         <v>76005</v>
       </c>
@@ -54168,6 +55080,9 @@
       <c r="N887" s="38">
         <v>11043</v>
       </c>
+      <c r="Q887" s="50">
+        <v>1</v>
+      </c>
       <c r="U887" s="50">
         <v>76006</v>
       </c>
@@ -54204,6 +55119,9 @@
       <c r="N888" s="38">
         <v>11043</v>
       </c>
+      <c r="Q888" s="50">
+        <v>1</v>
+      </c>
       <c r="U888" s="50">
         <v>76006</v>
       </c>
@@ -54240,6 +55158,9 @@
       <c r="N889" s="38">
         <v>11043</v>
       </c>
+      <c r="Q889" s="50">
+        <v>1</v>
+      </c>
       <c r="U889" s="50">
         <v>76006</v>
       </c>
@@ -54276,6 +55197,9 @@
       <c r="N890" s="38">
         <v>11043</v>
       </c>
+      <c r="Q890" s="50">
+        <v>1</v>
+      </c>
       <c r="U890" s="50">
         <v>76006</v>
       </c>
@@ -54312,6 +55236,9 @@
       <c r="N891" s="38">
         <v>11043</v>
       </c>
+      <c r="Q891" s="50">
+        <v>1</v>
+      </c>
       <c r="U891" s="50">
         <v>76006</v>
       </c>
@@ -54344,6 +55271,9 @@
       <c r="N892" s="38">
         <v>11043</v>
       </c>
+      <c r="Q892" s="50">
+        <v>1</v>
+      </c>
       <c r="U892" s="50">
         <v>76006</v>
       </c>
@@ -54380,6 +55310,9 @@
       <c r="N893" s="38">
         <v>11043</v>
       </c>
+      <c r="Q893" s="50">
+        <v>1</v>
+      </c>
       <c r="U893" s="50">
         <v>76007</v>
       </c>
@@ -54416,6 +55349,9 @@
       <c r="N894" s="38">
         <v>11043</v>
       </c>
+      <c r="Q894" s="50">
+        <v>1</v>
+      </c>
       <c r="U894" s="50">
         <v>76007</v>
       </c>
@@ -54452,6 +55388,9 @@
       <c r="N895" s="38">
         <v>11043</v>
       </c>
+      <c r="Q895" s="50">
+        <v>1</v>
+      </c>
       <c r="U895" s="50">
         <v>76007</v>
       </c>
@@ -54488,6 +55427,9 @@
       <c r="N896" s="38">
         <v>11043</v>
       </c>
+      <c r="Q896" s="50">
+        <v>1</v>
+      </c>
       <c r="U896" s="50">
         <v>76007</v>
       </c>
@@ -54524,6 +55466,9 @@
       <c r="N897" s="38">
         <v>11043</v>
       </c>
+      <c r="Q897" s="50">
+        <v>1</v>
+      </c>
       <c r="U897" s="50">
         <v>76007</v>
       </c>
@@ -54560,6 +55505,9 @@
       <c r="N898" s="38">
         <v>11043</v>
       </c>
+      <c r="Q898" s="50">
+        <v>1</v>
+      </c>
       <c r="U898" s="50">
         <v>76007</v>
       </c>
@@ -54596,6 +55544,9 @@
       <c r="N899" s="38">
         <v>11043</v>
       </c>
+      <c r="Q899" s="50">
+        <v>1</v>
+      </c>
       <c r="U899" s="50">
         <v>76007</v>
       </c>
@@ -54628,6 +55579,9 @@
       <c r="N900" s="38">
         <v>11043</v>
       </c>
+      <c r="Q900" s="50">
+        <v>1</v>
+      </c>
       <c r="U900" s="50">
         <v>76007</v>
       </c>
@@ -54664,6 +55618,9 @@
       <c r="N901" s="38">
         <v>11043</v>
       </c>
+      <c r="Q901" s="50">
+        <v>1</v>
+      </c>
       <c r="U901" s="50">
         <v>76008</v>
       </c>
@@ -54700,6 +55657,9 @@
       <c r="N902" s="38">
         <v>11043</v>
       </c>
+      <c r="Q902" s="50">
+        <v>1</v>
+      </c>
       <c r="U902" s="50">
         <v>76008</v>
       </c>
@@ -54736,6 +55696,9 @@
       <c r="N903" s="38">
         <v>11043</v>
       </c>
+      <c r="Q903" s="50">
+        <v>1</v>
+      </c>
       <c r="U903" s="50">
         <v>76008</v>
       </c>
@@ -54772,6 +55735,9 @@
       <c r="N904" s="38">
         <v>11043</v>
       </c>
+      <c r="Q904" s="50">
+        <v>1</v>
+      </c>
       <c r="U904" s="50">
         <v>76008</v>
       </c>
@@ -54808,6 +55774,9 @@
       <c r="N905" s="38">
         <v>11043</v>
       </c>
+      <c r="Q905" s="50">
+        <v>1</v>
+      </c>
       <c r="U905" s="50">
         <v>76008</v>
       </c>
@@ -54840,6 +55809,9 @@
       <c r="N906" s="38">
         <v>11043</v>
       </c>
+      <c r="Q906" s="50">
+        <v>1</v>
+      </c>
       <c r="U906" s="50">
         <v>76008</v>
       </c>
@@ -54879,6 +55851,9 @@
       <c r="N907" s="38">
         <v>3204</v>
       </c>
+      <c r="Q907" s="50">
+        <v>1</v>
+      </c>
       <c r="U907" s="61">
         <v>76001</v>
       </c>
@@ -54918,6 +55893,9 @@
       <c r="N908" s="38">
         <v>3204</v>
       </c>
+      <c r="Q908" s="50">
+        <v>1</v>
+      </c>
       <c r="U908" s="61">
         <v>76001</v>
       </c>
@@ -54957,6 +55935,9 @@
       <c r="N909" s="38">
         <v>3204</v>
       </c>
+      <c r="Q909" s="50">
+        <v>1</v>
+      </c>
       <c r="U909" s="61">
         <v>76001</v>
       </c>
@@ -54996,6 +55977,9 @@
       <c r="N910" s="38">
         <v>3204</v>
       </c>
+      <c r="Q910" s="50">
+        <v>1</v>
+      </c>
       <c r="U910" s="61">
         <v>76001</v>
       </c>
@@ -55035,6 +56019,9 @@
       <c r="N911" s="38">
         <v>3204</v>
       </c>
+      <c r="Q911" s="50">
+        <v>1</v>
+      </c>
       <c r="U911" s="61">
         <v>76001</v>
       </c>
@@ -55070,6 +56057,9 @@
       <c r="N912" s="38">
         <v>3204</v>
       </c>
+      <c r="Q912" s="50">
+        <v>1</v>
+      </c>
       <c r="U912" s="61">
         <v>76001</v>
       </c>
@@ -55106,6 +56096,9 @@
       <c r="N913" s="38">
         <v>3304</v>
       </c>
+      <c r="Q913" s="50">
+        <v>1</v>
+      </c>
       <c r="U913" s="50">
         <v>76002</v>
       </c>
@@ -55142,6 +56135,9 @@
       <c r="N914" s="38">
         <v>3304</v>
       </c>
+      <c r="Q914" s="50">
+        <v>1</v>
+      </c>
       <c r="U914" s="50">
         <v>76002</v>
       </c>
@@ -55178,6 +56174,9 @@
       <c r="N915" s="38">
         <v>3304</v>
       </c>
+      <c r="Q915" s="50">
+        <v>1</v>
+      </c>
       <c r="U915" s="50">
         <v>76002</v>
       </c>
@@ -55214,6 +56213,9 @@
       <c r="N916" s="38">
         <v>3304</v>
       </c>
+      <c r="Q916" s="50">
+        <v>1</v>
+      </c>
       <c r="U916" s="50">
         <v>76002</v>
       </c>
@@ -55250,6 +56252,9 @@
       <c r="N917" s="38">
         <v>3304</v>
       </c>
+      <c r="Q917" s="50">
+        <v>1</v>
+      </c>
       <c r="U917" s="50">
         <v>76002</v>
       </c>
@@ -55282,6 +56287,9 @@
       <c r="N918" s="38">
         <v>3304</v>
       </c>
+      <c r="Q918" s="50">
+        <v>1</v>
+      </c>
       <c r="U918" s="50">
         <v>76002</v>
       </c>
@@ -55318,6 +56326,9 @@
       <c r="N919" s="38">
         <v>11027</v>
       </c>
+      <c r="Q919" s="50">
+        <v>1</v>
+      </c>
       <c r="U919" s="50">
         <v>76003</v>
       </c>
@@ -55354,6 +56365,9 @@
       <c r="N920" s="38">
         <v>11027</v>
       </c>
+      <c r="Q920" s="50">
+        <v>1</v>
+      </c>
       <c r="U920" s="50">
         <v>76003</v>
       </c>
@@ -55390,6 +56404,9 @@
       <c r="N921" s="38">
         <v>11027</v>
       </c>
+      <c r="Q921" s="50">
+        <v>1</v>
+      </c>
       <c r="U921" s="50">
         <v>76003</v>
       </c>
@@ -55426,6 +56443,9 @@
       <c r="N922" s="38">
         <v>11027</v>
       </c>
+      <c r="Q922" s="50">
+        <v>1</v>
+      </c>
       <c r="U922" s="50">
         <v>76003</v>
       </c>
@@ -55462,6 +56482,9 @@
       <c r="N923" s="38">
         <v>11027</v>
       </c>
+      <c r="Q923" s="50">
+        <v>1</v>
+      </c>
       <c r="U923" s="50">
         <v>76003</v>
       </c>
@@ -55494,6 +56517,9 @@
       <c r="N924" s="38">
         <v>11027</v>
       </c>
+      <c r="Q924" s="50">
+        <v>1</v>
+      </c>
       <c r="U924" s="50">
         <v>76003</v>
       </c>
@@ -55530,6 +56556,9 @@
       <c r="N925" s="38">
         <v>11027</v>
       </c>
+      <c r="Q925" s="50">
+        <v>1</v>
+      </c>
       <c r="U925" s="50">
         <v>76004</v>
       </c>
@@ -55566,6 +56595,9 @@
       <c r="N926" s="38">
         <v>11027</v>
       </c>
+      <c r="Q926" s="50">
+        <v>1</v>
+      </c>
       <c r="U926" s="50">
         <v>76004</v>
       </c>
@@ -55602,6 +56634,9 @@
       <c r="N927" s="38">
         <v>11027</v>
       </c>
+      <c r="Q927" s="50">
+        <v>1</v>
+      </c>
       <c r="U927" s="50">
         <v>76004</v>
       </c>
@@ -55638,6 +56673,9 @@
       <c r="N928" s="38">
         <v>11027</v>
       </c>
+      <c r="Q928" s="50">
+        <v>1</v>
+      </c>
       <c r="U928" s="50">
         <v>76004</v>
       </c>
@@ -55674,6 +56712,9 @@
       <c r="N929" s="38">
         <v>11027</v>
       </c>
+      <c r="Q929" s="50">
+        <v>1</v>
+      </c>
       <c r="U929" s="50">
         <v>76004</v>
       </c>
@@ -55706,6 +56747,9 @@
       <c r="N930" s="38">
         <v>11027</v>
       </c>
+      <c r="Q930" s="50">
+        <v>1</v>
+      </c>
       <c r="U930" s="50">
         <v>76004</v>
       </c>
@@ -55742,6 +56786,9 @@
       <c r="N931" s="38">
         <v>11027</v>
       </c>
+      <c r="Q931" s="50">
+        <v>1</v>
+      </c>
       <c r="U931" s="50">
         <v>76005</v>
       </c>
@@ -55778,6 +56825,9 @@
       <c r="N932" s="38">
         <v>11027</v>
       </c>
+      <c r="Q932" s="50">
+        <v>1</v>
+      </c>
       <c r="U932" s="50">
         <v>76005</v>
       </c>
@@ -55814,6 +56864,9 @@
       <c r="N933" s="38">
         <v>11027</v>
       </c>
+      <c r="Q933" s="50">
+        <v>1</v>
+      </c>
       <c r="U933" s="50">
         <v>76005</v>
       </c>
@@ -55850,6 +56903,9 @@
       <c r="N934" s="38">
         <v>11027</v>
       </c>
+      <c r="Q934" s="50">
+        <v>1</v>
+      </c>
       <c r="U934" s="50">
         <v>76005</v>
       </c>
@@ -55886,6 +56942,9 @@
       <c r="N935" s="38">
         <v>11027</v>
       </c>
+      <c r="Q935" s="50">
+        <v>1</v>
+      </c>
       <c r="U935" s="50">
         <v>76005</v>
       </c>
@@ -55918,6 +56977,9 @@
       <c r="N936" s="38">
         <v>11027</v>
       </c>
+      <c r="Q936" s="50">
+        <v>1</v>
+      </c>
       <c r="U936" s="50">
         <v>76005</v>
       </c>
@@ -55954,6 +57016,9 @@
       <c r="N937" s="38">
         <v>11027</v>
       </c>
+      <c r="Q937" s="50">
+        <v>1</v>
+      </c>
       <c r="U937" s="50">
         <v>76006</v>
       </c>
@@ -55990,6 +57055,9 @@
       <c r="N938" s="38">
         <v>11027</v>
       </c>
+      <c r="Q938" s="50">
+        <v>1</v>
+      </c>
       <c r="U938" s="50">
         <v>76006</v>
       </c>
@@ -56026,6 +57094,9 @@
       <c r="N939" s="38">
         <v>11027</v>
       </c>
+      <c r="Q939" s="50">
+        <v>1</v>
+      </c>
       <c r="U939" s="50">
         <v>76006</v>
       </c>
@@ -56062,6 +57133,9 @@
       <c r="N940" s="38">
         <v>11027</v>
       </c>
+      <c r="Q940" s="50">
+        <v>1</v>
+      </c>
       <c r="U940" s="50">
         <v>76006</v>
       </c>
@@ -56098,6 +57172,9 @@
       <c r="N941" s="38">
         <v>11027</v>
       </c>
+      <c r="Q941" s="50">
+        <v>1</v>
+      </c>
       <c r="U941" s="50">
         <v>76006</v>
       </c>
@@ -56130,6 +57207,9 @@
       <c r="N942" s="38">
         <v>11027</v>
       </c>
+      <c r="Q942" s="50">
+        <v>1</v>
+      </c>
       <c r="U942" s="50">
         <v>76006</v>
       </c>
@@ -56166,6 +57246,9 @@
       <c r="N943" s="38">
         <v>11027</v>
       </c>
+      <c r="Q943" s="50">
+        <v>1</v>
+      </c>
       <c r="U943" s="50">
         <v>76007</v>
       </c>
@@ -56202,6 +57285,9 @@
       <c r="N944" s="38">
         <v>11027</v>
       </c>
+      <c r="Q944" s="50">
+        <v>1</v>
+      </c>
       <c r="U944" s="50">
         <v>76007</v>
       </c>
@@ -56238,6 +57324,9 @@
       <c r="N945" s="38">
         <v>11027</v>
       </c>
+      <c r="Q945" s="50">
+        <v>1</v>
+      </c>
       <c r="U945" s="50">
         <v>76007</v>
       </c>
@@ -56274,6 +57363,9 @@
       <c r="N946" s="38">
         <v>11027</v>
       </c>
+      <c r="Q946" s="50">
+        <v>1</v>
+      </c>
       <c r="U946" s="50">
         <v>76007</v>
       </c>
@@ -56310,6 +57402,9 @@
       <c r="N947" s="38">
         <v>11027</v>
       </c>
+      <c r="Q947" s="50">
+        <v>1</v>
+      </c>
       <c r="U947" s="50">
         <v>76007</v>
       </c>
@@ -56346,6 +57441,9 @@
       <c r="N948" s="38">
         <v>11027</v>
       </c>
+      <c r="Q948" s="50">
+        <v>1</v>
+      </c>
       <c r="U948" s="50">
         <v>76007</v>
       </c>
@@ -56382,6 +57480,9 @@
       <c r="N949" s="38">
         <v>11027</v>
       </c>
+      <c r="Q949" s="50">
+        <v>1</v>
+      </c>
       <c r="U949" s="50">
         <v>76007</v>
       </c>
@@ -56414,6 +57515,9 @@
       <c r="N950" s="38">
         <v>11027</v>
       </c>
+      <c r="Q950" s="50">
+        <v>1</v>
+      </c>
       <c r="U950" s="50">
         <v>76007</v>
       </c>
@@ -56450,6 +57554,9 @@
       <c r="N951" s="38">
         <v>11027</v>
       </c>
+      <c r="Q951" s="50">
+        <v>1</v>
+      </c>
       <c r="U951" s="50">
         <v>76008</v>
       </c>
@@ -56486,6 +57593,9 @@
       <c r="N952" s="38">
         <v>11027</v>
       </c>
+      <c r="Q952" s="50">
+        <v>1</v>
+      </c>
       <c r="U952" s="50">
         <v>76008</v>
       </c>
@@ -56522,6 +57632,9 @@
       <c r="N953" s="38">
         <v>11027</v>
       </c>
+      <c r="Q953" s="50">
+        <v>1</v>
+      </c>
       <c r="U953" s="50">
         <v>76008</v>
       </c>
@@ -56558,6 +57671,9 @@
       <c r="N954" s="38">
         <v>11027</v>
       </c>
+      <c r="Q954" s="50">
+        <v>1</v>
+      </c>
       <c r="U954" s="50">
         <v>76008</v>
       </c>
@@ -56594,6 +57710,9 @@
       <c r="N955" s="38">
         <v>11027</v>
       </c>
+      <c r="Q955" s="50">
+        <v>1</v>
+      </c>
       <c r="U955" s="50">
         <v>76008</v>
       </c>
@@ -56626,6 +57745,9 @@
       <c r="N956" s="38">
         <v>11027</v>
       </c>
+      <c r="Q956" s="50">
+        <v>1</v>
+      </c>
       <c r="U956" s="50">
         <v>76008</v>
       </c>
@@ -56665,6 +57787,9 @@
       <c r="N957" s="38">
         <v>3211</v>
       </c>
+      <c r="Q957" s="50">
+        <v>1</v>
+      </c>
       <c r="U957" s="61">
         <v>76001</v>
       </c>
@@ -56704,6 +57829,9 @@
       <c r="N958" s="38">
         <v>3211</v>
       </c>
+      <c r="Q958" s="50">
+        <v>1</v>
+      </c>
       <c r="U958" s="61">
         <v>76001</v>
       </c>
@@ -56743,6 +57871,9 @@
       <c r="N959" s="38">
         <v>3211</v>
       </c>
+      <c r="Q959" s="50">
+        <v>1</v>
+      </c>
       <c r="U959" s="61">
         <v>76001</v>
       </c>
@@ -56782,6 +57913,9 @@
       <c r="N960" s="38">
         <v>3211</v>
       </c>
+      <c r="Q960" s="50">
+        <v>1</v>
+      </c>
       <c r="U960" s="61">
         <v>76001</v>
       </c>
@@ -56821,6 +57955,9 @@
       <c r="N961" s="38">
         <v>3211</v>
       </c>
+      <c r="Q961" s="50">
+        <v>1</v>
+      </c>
       <c r="U961" s="61">
         <v>76001</v>
       </c>
@@ -56856,6 +57993,9 @@
       <c r="N962" s="38">
         <v>3211</v>
       </c>
+      <c r="Q962" s="50">
+        <v>1</v>
+      </c>
       <c r="U962" s="61">
         <v>76001</v>
       </c>
@@ -56892,6 +58032,9 @@
       <c r="N963" s="38">
         <v>3310</v>
       </c>
+      <c r="Q963" s="50">
+        <v>1</v>
+      </c>
       <c r="U963" s="50">
         <v>76002</v>
       </c>
@@ -56928,6 +58071,9 @@
       <c r="N964" s="38">
         <v>3310</v>
       </c>
+      <c r="Q964" s="50">
+        <v>1</v>
+      </c>
       <c r="U964" s="50">
         <v>76002</v>
       </c>
@@ -56964,6 +58110,9 @@
       <c r="N965" s="38">
         <v>3310</v>
       </c>
+      <c r="Q965" s="50">
+        <v>1</v>
+      </c>
       <c r="U965" s="50">
         <v>76002</v>
       </c>
@@ -57000,6 +58149,9 @@
       <c r="N966" s="38">
         <v>3310</v>
       </c>
+      <c r="Q966" s="50">
+        <v>1</v>
+      </c>
       <c r="U966" s="50">
         <v>76002</v>
       </c>
@@ -57036,6 +58188,9 @@
       <c r="N967" s="38">
         <v>3310</v>
       </c>
+      <c r="Q967" s="50">
+        <v>1</v>
+      </c>
       <c r="U967" s="50">
         <v>76002</v>
       </c>
@@ -57068,6 +58223,9 @@
       <c r="N968" s="38">
         <v>3310</v>
       </c>
+      <c r="Q968" s="50">
+        <v>1</v>
+      </c>
       <c r="U968" s="50">
         <v>76002</v>
       </c>
@@ -57104,6 +58262,9 @@
       <c r="N969" s="38">
         <v>11045</v>
       </c>
+      <c r="Q969" s="50">
+        <v>1</v>
+      </c>
       <c r="U969" s="50">
         <v>76003</v>
       </c>
@@ -57140,6 +58301,9 @@
       <c r="N970" s="38">
         <v>11045</v>
       </c>
+      <c r="Q970" s="50">
+        <v>1</v>
+      </c>
       <c r="U970" s="50">
         <v>76003</v>
       </c>
@@ -57176,6 +58340,9 @@
       <c r="N971" s="38">
         <v>11045</v>
       </c>
+      <c r="Q971" s="50">
+        <v>1</v>
+      </c>
       <c r="U971" s="50">
         <v>76003</v>
       </c>
@@ -57212,6 +58379,9 @@
       <c r="N972" s="38">
         <v>11045</v>
       </c>
+      <c r="Q972" s="50">
+        <v>1</v>
+      </c>
       <c r="U972" s="50">
         <v>76003</v>
       </c>
@@ -57248,6 +58418,9 @@
       <c r="N973" s="38">
         <v>11045</v>
       </c>
+      <c r="Q973" s="50">
+        <v>1</v>
+      </c>
       <c r="U973" s="50">
         <v>76003</v>
       </c>
@@ -57280,6 +58453,9 @@
       <c r="N974" s="38">
         <v>11045</v>
       </c>
+      <c r="Q974" s="50">
+        <v>1</v>
+      </c>
       <c r="U974" s="50">
         <v>76003</v>
       </c>
@@ -57316,6 +58492,9 @@
       <c r="N975" s="38">
         <v>11045</v>
       </c>
+      <c r="Q975" s="50">
+        <v>1</v>
+      </c>
       <c r="U975" s="50">
         <v>76004</v>
       </c>
@@ -57352,6 +58531,9 @@
       <c r="N976" s="38">
         <v>11045</v>
       </c>
+      <c r="Q976" s="50">
+        <v>1</v>
+      </c>
       <c r="U976" s="50">
         <v>76004</v>
       </c>
@@ -57388,6 +58570,9 @@
       <c r="N977" s="38">
         <v>11045</v>
       </c>
+      <c r="Q977" s="50">
+        <v>1</v>
+      </c>
       <c r="U977" s="50">
         <v>76004</v>
       </c>
@@ -57424,6 +58609,9 @@
       <c r="N978" s="38">
         <v>11045</v>
       </c>
+      <c r="Q978" s="50">
+        <v>1</v>
+      </c>
       <c r="U978" s="50">
         <v>76004</v>
       </c>
@@ -57460,6 +58648,9 @@
       <c r="N979" s="38">
         <v>11045</v>
       </c>
+      <c r="Q979" s="50">
+        <v>1</v>
+      </c>
       <c r="U979" s="50">
         <v>76004</v>
       </c>
@@ -57492,6 +58683,9 @@
       <c r="N980" s="38">
         <v>11045</v>
       </c>
+      <c r="Q980" s="50">
+        <v>1</v>
+      </c>
       <c r="U980" s="50">
         <v>76004</v>
       </c>
@@ -57528,6 +58722,9 @@
       <c r="N981" s="38">
         <v>11045</v>
       </c>
+      <c r="Q981" s="50">
+        <v>1</v>
+      </c>
       <c r="U981" s="50">
         <v>76005</v>
       </c>
@@ -57564,6 +58761,9 @@
       <c r="N982" s="38">
         <v>11045</v>
       </c>
+      <c r="Q982" s="50">
+        <v>1</v>
+      </c>
       <c r="U982" s="50">
         <v>76005</v>
       </c>
@@ -57600,6 +58800,9 @@
       <c r="N983" s="38">
         <v>11045</v>
       </c>
+      <c r="Q983" s="50">
+        <v>1</v>
+      </c>
       <c r="U983" s="50">
         <v>76005</v>
       </c>
@@ -57636,6 +58839,9 @@
       <c r="N984" s="38">
         <v>11045</v>
       </c>
+      <c r="Q984" s="50">
+        <v>1</v>
+      </c>
       <c r="U984" s="50">
         <v>76005</v>
       </c>
@@ -57672,6 +58878,9 @@
       <c r="N985" s="38">
         <v>11045</v>
       </c>
+      <c r="Q985" s="50">
+        <v>1</v>
+      </c>
       <c r="U985" s="50">
         <v>76005</v>
       </c>
@@ -57704,6 +58913,9 @@
       <c r="N986" s="38">
         <v>11045</v>
       </c>
+      <c r="Q986" s="50">
+        <v>1</v>
+      </c>
       <c r="U986" s="50">
         <v>76005</v>
       </c>
@@ -57740,6 +58952,9 @@
       <c r="N987" s="38">
         <v>11045</v>
       </c>
+      <c r="Q987" s="50">
+        <v>1</v>
+      </c>
       <c r="U987" s="50">
         <v>76006</v>
       </c>
@@ -57776,6 +58991,9 @@
       <c r="N988" s="38">
         <v>11045</v>
       </c>
+      <c r="Q988" s="50">
+        <v>1</v>
+      </c>
       <c r="U988" s="50">
         <v>76006</v>
       </c>
@@ -57812,6 +59030,9 @@
       <c r="N989" s="38">
         <v>11045</v>
       </c>
+      <c r="Q989" s="50">
+        <v>1</v>
+      </c>
       <c r="U989" s="50">
         <v>76006</v>
       </c>
@@ -57848,6 +59069,9 @@
       <c r="N990" s="38">
         <v>11045</v>
       </c>
+      <c r="Q990" s="50">
+        <v>1</v>
+      </c>
       <c r="U990" s="50">
         <v>76006</v>
       </c>
@@ -57884,6 +59108,9 @@
       <c r="N991" s="38">
         <v>11045</v>
       </c>
+      <c r="Q991" s="50">
+        <v>1</v>
+      </c>
       <c r="U991" s="50">
         <v>76006</v>
       </c>
@@ -57916,6 +59143,9 @@
       <c r="N992" s="38">
         <v>11045</v>
       </c>
+      <c r="Q992" s="50">
+        <v>1</v>
+      </c>
       <c r="U992" s="50">
         <v>76006</v>
       </c>
@@ -57952,6 +59182,9 @@
       <c r="N993" s="38">
         <v>11045</v>
       </c>
+      <c r="Q993" s="50">
+        <v>1</v>
+      </c>
       <c r="U993" s="50">
         <v>76007</v>
       </c>
@@ -57988,6 +59221,9 @@
       <c r="N994" s="38">
         <v>11045</v>
       </c>
+      <c r="Q994" s="50">
+        <v>1</v>
+      </c>
       <c r="U994" s="50">
         <v>76007</v>
       </c>
@@ -58024,6 +59260,9 @@
       <c r="N995" s="38">
         <v>11045</v>
       </c>
+      <c r="Q995" s="50">
+        <v>1</v>
+      </c>
       <c r="U995" s="50">
         <v>76007</v>
       </c>
@@ -58060,6 +59299,9 @@
       <c r="N996" s="38">
         <v>11045</v>
       </c>
+      <c r="Q996" s="50">
+        <v>1</v>
+      </c>
       <c r="U996" s="50">
         <v>76007</v>
       </c>
@@ -58096,6 +59338,9 @@
       <c r="N997" s="38">
         <v>11045</v>
       </c>
+      <c r="Q997" s="50">
+        <v>1</v>
+      </c>
       <c r="U997" s="50">
         <v>76007</v>
       </c>
@@ -58132,6 +59377,9 @@
       <c r="N998" s="38">
         <v>11045</v>
       </c>
+      <c r="Q998" s="50">
+        <v>1</v>
+      </c>
       <c r="U998" s="50">
         <v>76007</v>
       </c>
@@ -58168,6 +59416,9 @@
       <c r="N999" s="38">
         <v>11045</v>
       </c>
+      <c r="Q999" s="50">
+        <v>1</v>
+      </c>
       <c r="U999" s="50">
         <v>76007</v>
       </c>
@@ -58200,6 +59451,9 @@
       <c r="N1000" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1000" s="50">
+        <v>1</v>
+      </c>
       <c r="U1000" s="50">
         <v>76007</v>
       </c>
@@ -58236,6 +59490,9 @@
       <c r="N1001" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1001" s="50">
+        <v>1</v>
+      </c>
       <c r="U1001" s="50">
         <v>76008</v>
       </c>
@@ -58272,6 +59529,9 @@
       <c r="N1002" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1002" s="50">
+        <v>1</v>
+      </c>
       <c r="U1002" s="50">
         <v>76008</v>
       </c>
@@ -58308,6 +59568,9 @@
       <c r="N1003" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1003" s="50">
+        <v>1</v>
+      </c>
       <c r="U1003" s="50">
         <v>76008</v>
       </c>
@@ -58344,6 +59607,9 @@
       <c r="N1004" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1004" s="50">
+        <v>1</v>
+      </c>
       <c r="U1004" s="50">
         <v>76008</v>
       </c>
@@ -58380,6 +59646,9 @@
       <c r="N1005" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1005" s="50">
+        <v>1</v>
+      </c>
       <c r="U1005" s="50">
         <v>76008</v>
       </c>
@@ -58412,6 +59681,9 @@
       <c r="N1006" s="38">
         <v>11045</v>
       </c>
+      <c r="Q1006" s="50">
+        <v>1</v>
+      </c>
       <c r="U1006" s="50">
         <v>76008</v>
       </c>
@@ -58451,6 +59723,9 @@
       <c r="N1007" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1007" s="50">
+        <v>1</v>
+      </c>
       <c r="U1007" s="61">
         <v>76001</v>
       </c>
@@ -58490,6 +59765,9 @@
       <c r="N1008" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1008" s="50">
+        <v>1</v>
+      </c>
       <c r="U1008" s="61">
         <v>76001</v>
       </c>
@@ -58529,6 +59807,9 @@
       <c r="N1009" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1009" s="50">
+        <v>1</v>
+      </c>
       <c r="U1009" s="61">
         <v>76001</v>
       </c>
@@ -58568,6 +59849,9 @@
       <c r="N1010" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1010" s="50">
+        <v>1</v>
+      </c>
       <c r="U1010" s="61">
         <v>76001</v>
       </c>
@@ -58607,6 +59891,9 @@
       <c r="N1011" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1011" s="50">
+        <v>1</v>
+      </c>
       <c r="U1011" s="61">
         <v>76001</v>
       </c>
@@ -58642,6 +59929,9 @@
       <c r="N1012" s="38">
         <v>3212</v>
       </c>
+      <c r="Q1012" s="50">
+        <v>1</v>
+      </c>
       <c r="U1012" s="61">
         <v>76001</v>
       </c>
@@ -58678,6 +59968,9 @@
       <c r="N1013" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1013" s="50">
+        <v>1</v>
+      </c>
       <c r="U1013" s="50">
         <v>76002</v>
       </c>
@@ -58714,6 +60007,9 @@
       <c r="N1014" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1014" s="50">
+        <v>1</v>
+      </c>
       <c r="U1014" s="50">
         <v>76002</v>
       </c>
@@ -58750,6 +60046,9 @@
       <c r="N1015" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1015" s="50">
+        <v>1</v>
+      </c>
       <c r="U1015" s="50">
         <v>76002</v>
       </c>
@@ -58786,6 +60085,9 @@
       <c r="N1016" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1016" s="50">
+        <v>1</v>
+      </c>
       <c r="U1016" s="50">
         <v>76002</v>
       </c>
@@ -58822,6 +60124,9 @@
       <c r="N1017" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1017" s="50">
+        <v>1</v>
+      </c>
       <c r="U1017" s="50">
         <v>76002</v>
       </c>
@@ -58854,6 +60159,9 @@
       <c r="N1018" s="38">
         <v>3309</v>
       </c>
+      <c r="Q1018" s="50">
+        <v>1</v>
+      </c>
       <c r="U1018" s="50">
         <v>76002</v>
       </c>
@@ -58890,6 +60198,9 @@
       <c r="N1019" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1019" s="50">
+        <v>1</v>
+      </c>
       <c r="U1019" s="50">
         <v>76003</v>
       </c>
@@ -58926,6 +60237,9 @@
       <c r="N1020" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1020" s="50">
+        <v>1</v>
+      </c>
       <c r="U1020" s="50">
         <v>76003</v>
       </c>
@@ -58962,6 +60276,9 @@
       <c r="N1021" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1021" s="50">
+        <v>1</v>
+      </c>
       <c r="U1021" s="50">
         <v>76003</v>
       </c>
@@ -58998,6 +60315,9 @@
       <c r="N1022" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1022" s="50">
+        <v>1</v>
+      </c>
       <c r="U1022" s="50">
         <v>76003</v>
       </c>
@@ -59034,6 +60354,9 @@
       <c r="N1023" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1023" s="50">
+        <v>1</v>
+      </c>
       <c r="U1023" s="50">
         <v>76003</v>
       </c>
@@ -59066,6 +60389,9 @@
       <c r="N1024" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1024" s="50">
+        <v>1</v>
+      </c>
       <c r="U1024" s="50">
         <v>76003</v>
       </c>
@@ -59102,6 +60428,9 @@
       <c r="N1025" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1025" s="50">
+        <v>1</v>
+      </c>
       <c r="U1025" s="50">
         <v>76004</v>
       </c>
@@ -59138,6 +60467,9 @@
       <c r="N1026" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1026" s="50">
+        <v>1</v>
+      </c>
       <c r="U1026" s="50">
         <v>76004</v>
       </c>
@@ -59174,6 +60506,9 @@
       <c r="N1027" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1027" s="50">
+        <v>1</v>
+      </c>
       <c r="U1027" s="50">
         <v>76004</v>
       </c>
@@ -59210,6 +60545,9 @@
       <c r="N1028" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1028" s="50">
+        <v>1</v>
+      </c>
       <c r="U1028" s="50">
         <v>76004</v>
       </c>
@@ -59246,6 +60584,9 @@
       <c r="N1029" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1029" s="50">
+        <v>1</v>
+      </c>
       <c r="U1029" s="50">
         <v>76004</v>
       </c>
@@ -59278,6 +60619,9 @@
       <c r="N1030" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1030" s="50">
+        <v>1</v>
+      </c>
       <c r="U1030" s="50">
         <v>76004</v>
       </c>
@@ -59314,6 +60658,9 @@
       <c r="N1031" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1031" s="50">
+        <v>1</v>
+      </c>
       <c r="U1031" s="50">
         <v>76005</v>
       </c>
@@ -59350,6 +60697,9 @@
       <c r="N1032" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1032" s="50">
+        <v>1</v>
+      </c>
       <c r="U1032" s="50">
         <v>76005</v>
       </c>
@@ -59386,6 +60736,9 @@
       <c r="N1033" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1033" s="50">
+        <v>1</v>
+      </c>
       <c r="U1033" s="50">
         <v>76005</v>
       </c>
@@ -59422,6 +60775,9 @@
       <c r="N1034" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1034" s="50">
+        <v>1</v>
+      </c>
       <c r="U1034" s="50">
         <v>76005</v>
       </c>
@@ -59458,6 +60814,9 @@
       <c r="N1035" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1035" s="50">
+        <v>1</v>
+      </c>
       <c r="U1035" s="50">
         <v>76005</v>
       </c>
@@ -59490,6 +60849,9 @@
       <c r="N1036" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1036" s="50">
+        <v>1</v>
+      </c>
       <c r="U1036" s="50">
         <v>76005</v>
       </c>
@@ -59526,6 +60888,9 @@
       <c r="N1037" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1037" s="50">
+        <v>1</v>
+      </c>
       <c r="U1037" s="50">
         <v>76006</v>
       </c>
@@ -59562,6 +60927,9 @@
       <c r="N1038" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1038" s="50">
+        <v>1</v>
+      </c>
       <c r="U1038" s="50">
         <v>76006</v>
       </c>
@@ -59598,6 +60966,9 @@
       <c r="N1039" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1039" s="50">
+        <v>1</v>
+      </c>
       <c r="U1039" s="50">
         <v>76006</v>
       </c>
@@ -59634,6 +61005,9 @@
       <c r="N1040" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1040" s="50">
+        <v>1</v>
+      </c>
       <c r="U1040" s="50">
         <v>76006</v>
       </c>
@@ -59670,6 +61044,9 @@
       <c r="N1041" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1041" s="50">
+        <v>1</v>
+      </c>
       <c r="U1041" s="50">
         <v>76006</v>
       </c>
@@ -59702,6 +61079,9 @@
       <c r="N1042" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1042" s="50">
+        <v>1</v>
+      </c>
       <c r="U1042" s="50">
         <v>76006</v>
       </c>
@@ -59738,6 +61118,9 @@
       <c r="N1043" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1043" s="50">
+        <v>1</v>
+      </c>
       <c r="U1043" s="50">
         <v>76007</v>
       </c>
@@ -59774,6 +61157,9 @@
       <c r="N1044" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1044" s="50">
+        <v>1</v>
+      </c>
       <c r="U1044" s="50">
         <v>76007</v>
       </c>
@@ -59810,6 +61196,9 @@
       <c r="N1045" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1045" s="50">
+        <v>1</v>
+      </c>
       <c r="U1045" s="50">
         <v>76007</v>
       </c>
@@ -59846,6 +61235,9 @@
       <c r="N1046" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1046" s="50">
+        <v>1</v>
+      </c>
       <c r="U1046" s="50">
         <v>76007</v>
       </c>
@@ -59882,6 +61274,9 @@
       <c r="N1047" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1047" s="50">
+        <v>1</v>
+      </c>
       <c r="U1047" s="50">
         <v>76007</v>
       </c>
@@ -59918,6 +61313,9 @@
       <c r="N1048" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1048" s="50">
+        <v>1</v>
+      </c>
       <c r="U1048" s="50">
         <v>76007</v>
       </c>
@@ -59954,6 +61352,9 @@
       <c r="N1049" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1049" s="50">
+        <v>1</v>
+      </c>
       <c r="U1049" s="50">
         <v>76007</v>
       </c>
@@ -59986,6 +61387,9 @@
       <c r="N1050" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1050" s="50">
+        <v>1</v>
+      </c>
       <c r="U1050" s="50">
         <v>76007</v>
       </c>
@@ -60022,6 +61426,9 @@
       <c r="N1051" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1051" s="50">
+        <v>1</v>
+      </c>
       <c r="U1051" s="50">
         <v>76008</v>
       </c>
@@ -60058,6 +61465,9 @@
       <c r="N1052" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1052" s="50">
+        <v>1</v>
+      </c>
       <c r="U1052" s="50">
         <v>76008</v>
       </c>
@@ -60094,6 +61504,9 @@
       <c r="N1053" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1053" s="50">
+        <v>1</v>
+      </c>
       <c r="U1053" s="50">
         <v>76008</v>
       </c>
@@ -60130,6 +61543,9 @@
       <c r="N1054" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1054" s="50">
+        <v>1</v>
+      </c>
       <c r="U1054" s="50">
         <v>76008</v>
       </c>
@@ -60166,6 +61582,9 @@
       <c r="N1055" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1055" s="50">
+        <v>1</v>
+      </c>
       <c r="U1055" s="50">
         <v>76008</v>
       </c>
@@ -60198,6 +61617,9 @@
       <c r="N1056" s="38">
         <v>11044</v>
       </c>
+      <c r="Q1056" s="50">
+        <v>1</v>
+      </c>
       <c r="U1056" s="50">
         <v>76008</v>
       </c>
@@ -60237,6 +61659,9 @@
       <c r="N1057" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1057" s="50">
+        <v>1</v>
+      </c>
       <c r="U1057" s="50">
         <v>76001</v>
       </c>
@@ -60276,6 +61701,9 @@
       <c r="N1058" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1058" s="50">
+        <v>1</v>
+      </c>
       <c r="U1058" s="50">
         <v>76001</v>
       </c>
@@ -60315,6 +61743,9 @@
       <c r="N1059" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1059" s="50">
+        <v>1</v>
+      </c>
       <c r="U1059" s="50">
         <v>76001</v>
       </c>
@@ -60354,6 +61785,9 @@
       <c r="N1060" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1060" s="50">
+        <v>1</v>
+      </c>
       <c r="U1060" s="50">
         <v>76001</v>
       </c>
@@ -60393,6 +61827,9 @@
       <c r="N1061" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1061" s="50">
+        <v>1</v>
+      </c>
       <c r="U1061" s="50">
         <v>76001</v>
       </c>
@@ -60428,6 +61865,9 @@
       <c r="N1062" s="38">
         <v>3203</v>
       </c>
+      <c r="Q1062" s="50">
+        <v>1</v>
+      </c>
       <c r="U1062" s="50">
         <v>76001</v>
       </c>
@@ -60464,6 +61904,9 @@
       <c r="N1063" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1063" s="50">
+        <v>1</v>
+      </c>
       <c r="U1063" s="50">
         <v>76002</v>
       </c>
@@ -60500,6 +61943,9 @@
       <c r="N1064" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1064" s="50">
+        <v>1</v>
+      </c>
       <c r="U1064" s="50">
         <v>76002</v>
       </c>
@@ -60536,6 +61982,9 @@
       <c r="N1065" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1065" s="50">
+        <v>1</v>
+      </c>
       <c r="U1065" s="50">
         <v>76002</v>
       </c>
@@ -60572,6 +62021,9 @@
       <c r="N1066" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1066" s="50">
+        <v>1</v>
+      </c>
       <c r="U1066" s="50">
         <v>76002</v>
       </c>
@@ -60608,6 +62060,9 @@
       <c r="N1067" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1067" s="50">
+        <v>1</v>
+      </c>
       <c r="U1067" s="50">
         <v>76002</v>
       </c>
@@ -60640,6 +62095,9 @@
       <c r="N1068" s="38">
         <v>3303</v>
       </c>
+      <c r="Q1068" s="50">
+        <v>1</v>
+      </c>
       <c r="U1068" s="50">
         <v>76002</v>
       </c>
@@ -60676,6 +62134,9 @@
       <c r="N1069" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1069" s="50">
+        <v>1</v>
+      </c>
       <c r="U1069" s="50">
         <v>76003</v>
       </c>
@@ -60712,6 +62173,9 @@
       <c r="N1070" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1070" s="50">
+        <v>1</v>
+      </c>
       <c r="U1070" s="50">
         <v>76003</v>
       </c>
@@ -60748,6 +62212,9 @@
       <c r="N1071" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1071" s="50">
+        <v>1</v>
+      </c>
       <c r="U1071" s="50">
         <v>76003</v>
       </c>
@@ -60784,6 +62251,9 @@
       <c r="N1072" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1072" s="50">
+        <v>1</v>
+      </c>
       <c r="U1072" s="50">
         <v>76003</v>
       </c>
@@ -60820,6 +62290,9 @@
       <c r="N1073" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1073" s="50">
+        <v>1</v>
+      </c>
       <c r="U1073" s="50">
         <v>76003</v>
       </c>
@@ -60852,6 +62325,9 @@
       <c r="N1074" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1074" s="50">
+        <v>1</v>
+      </c>
       <c r="U1074" s="50">
         <v>76003</v>
       </c>
@@ -60888,6 +62364,9 @@
       <c r="N1075" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1075" s="50">
+        <v>1</v>
+      </c>
       <c r="U1075" s="50">
         <v>76004</v>
       </c>
@@ -60924,6 +62403,9 @@
       <c r="N1076" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1076" s="50">
+        <v>1</v>
+      </c>
       <c r="U1076" s="50">
         <v>76004</v>
       </c>
@@ -60960,6 +62442,9 @@
       <c r="N1077" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1077" s="50">
+        <v>1</v>
+      </c>
       <c r="U1077" s="50">
         <v>76004</v>
       </c>
@@ -60996,6 +62481,9 @@
       <c r="N1078" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1078" s="50">
+        <v>1</v>
+      </c>
       <c r="U1078" s="50">
         <v>76004</v>
       </c>
@@ -61032,6 +62520,9 @@
       <c r="N1079" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1079" s="50">
+        <v>1</v>
+      </c>
       <c r="U1079" s="50">
         <v>76004</v>
       </c>
@@ -61064,6 +62555,9 @@
       <c r="N1080" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1080" s="50">
+        <v>1</v>
+      </c>
       <c r="U1080" s="50">
         <v>76004</v>
       </c>
@@ -61100,6 +62594,9 @@
       <c r="N1081" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1081" s="50">
+        <v>1</v>
+      </c>
       <c r="U1081" s="50">
         <v>76005</v>
       </c>
@@ -61136,6 +62633,9 @@
       <c r="N1082" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1082" s="50">
+        <v>1</v>
+      </c>
       <c r="U1082" s="50">
         <v>76005</v>
       </c>
@@ -61172,6 +62672,9 @@
       <c r="N1083" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1083" s="50">
+        <v>1</v>
+      </c>
       <c r="U1083" s="50">
         <v>76005</v>
       </c>
@@ -61208,6 +62711,9 @@
       <c r="N1084" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1084" s="50">
+        <v>1</v>
+      </c>
       <c r="U1084" s="50">
         <v>76005</v>
       </c>
@@ -61244,6 +62750,9 @@
       <c r="N1085" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1085" s="50">
+        <v>1</v>
+      </c>
       <c r="U1085" s="50">
         <v>76005</v>
       </c>
@@ -61276,6 +62785,9 @@
       <c r="N1086" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1086" s="50">
+        <v>1</v>
+      </c>
       <c r="U1086" s="50">
         <v>76005</v>
       </c>
@@ -61312,6 +62824,9 @@
       <c r="N1087" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1087" s="50">
+        <v>1</v>
+      </c>
       <c r="U1087" s="50">
         <v>76006</v>
       </c>
@@ -61348,6 +62863,9 @@
       <c r="N1088" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1088" s="50">
+        <v>1</v>
+      </c>
       <c r="U1088" s="50">
         <v>76006</v>
       </c>
@@ -61384,6 +62902,9 @@
       <c r="N1089" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1089" s="50">
+        <v>1</v>
+      </c>
       <c r="U1089" s="50">
         <v>76006</v>
       </c>
@@ -61420,6 +62941,9 @@
       <c r="N1090" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1090" s="50">
+        <v>1</v>
+      </c>
       <c r="U1090" s="50">
         <v>76006</v>
       </c>
@@ -61456,6 +62980,9 @@
       <c r="N1091" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1091" s="50">
+        <v>1</v>
+      </c>
       <c r="U1091" s="50">
         <v>76006</v>
       </c>
@@ -61488,6 +63015,9 @@
       <c r="N1092" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1092" s="50">
+        <v>1</v>
+      </c>
       <c r="U1092" s="50">
         <v>76006</v>
       </c>
@@ -61524,6 +63054,9 @@
       <c r="N1093" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1093" s="50">
+        <v>1</v>
+      </c>
       <c r="U1093" s="50">
         <v>76007</v>
       </c>
@@ -61560,6 +63093,9 @@
       <c r="N1094" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1094" s="50">
+        <v>1</v>
+      </c>
       <c r="U1094" s="50">
         <v>76007</v>
       </c>
@@ -61596,6 +63132,9 @@
       <c r="N1095" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1095" s="50">
+        <v>1</v>
+      </c>
       <c r="U1095" s="50">
         <v>76007</v>
       </c>
@@ -61632,6 +63171,9 @@
       <c r="N1096" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1096" s="50">
+        <v>1</v>
+      </c>
       <c r="U1096" s="50">
         <v>76007</v>
       </c>
@@ -61668,6 +63210,9 @@
       <c r="N1097" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1097" s="50">
+        <v>1</v>
+      </c>
       <c r="U1097" s="50">
         <v>76007</v>
       </c>
@@ -61704,6 +63249,9 @@
       <c r="N1098" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1098" s="50">
+        <v>1</v>
+      </c>
       <c r="U1098" s="50">
         <v>76007</v>
       </c>
@@ -61740,6 +63288,9 @@
       <c r="N1099" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1099" s="50">
+        <v>1</v>
+      </c>
       <c r="U1099" s="50">
         <v>76007</v>
       </c>
@@ -61772,6 +63323,9 @@
       <c r="N1100" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1100" s="50">
+        <v>1</v>
+      </c>
       <c r="U1100" s="50">
         <v>76007</v>
       </c>
@@ -61808,6 +63362,9 @@
       <c r="N1101" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1101" s="50">
+        <v>1</v>
+      </c>
       <c r="U1101" s="50">
         <v>76011</v>
       </c>
@@ -61844,6 +63401,9 @@
       <c r="N1102" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1102" s="50">
+        <v>1</v>
+      </c>
       <c r="U1102" s="50">
         <v>76011</v>
       </c>
@@ -61880,6 +63440,9 @@
       <c r="N1103" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1103" s="50">
+        <v>1</v>
+      </c>
       <c r="U1103" s="50">
         <v>76011</v>
       </c>
@@ -61916,6 +63479,9 @@
       <c r="N1104" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1104" s="50">
+        <v>1</v>
+      </c>
       <c r="U1104" s="50">
         <v>76011</v>
       </c>
@@ -61952,6 +63518,9 @@
       <c r="N1105" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1105" s="50">
+        <v>1</v>
+      </c>
       <c r="U1105" s="50">
         <v>76011</v>
       </c>
@@ -61984,6 +63553,9 @@
       <c r="N1106" s="38">
         <v>11007</v>
       </c>
+      <c r="Q1106" s="50">
+        <v>1</v>
+      </c>
       <c r="U1106" s="50">
         <v>76011</v>
       </c>
@@ -62023,6 +63595,9 @@
       <c r="N1107" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1107" s="50">
+        <v>1</v>
+      </c>
       <c r="U1107" s="61">
         <v>76001</v>
       </c>
@@ -62062,6 +63637,9 @@
       <c r="N1108" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1108" s="50">
+        <v>1</v>
+      </c>
       <c r="U1108" s="61">
         <v>76001</v>
       </c>
@@ -62101,6 +63679,9 @@
       <c r="N1109" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1109" s="50">
+        <v>1</v>
+      </c>
       <c r="U1109" s="61">
         <v>76001</v>
       </c>
@@ -62140,6 +63721,9 @@
       <c r="N1110" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1110" s="50">
+        <v>1</v>
+      </c>
       <c r="U1110" s="61">
         <v>76001</v>
       </c>
@@ -62179,6 +63763,9 @@
       <c r="N1111" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1111" s="50">
+        <v>1</v>
+      </c>
       <c r="U1111" s="61">
         <v>76001</v>
       </c>
@@ -62214,6 +63801,9 @@
       <c r="N1112" s="38">
         <v>3209</v>
       </c>
+      <c r="Q1112" s="50">
+        <v>1</v>
+      </c>
       <c r="U1112" s="61">
         <v>76001</v>
       </c>
@@ -62250,6 +63840,9 @@
       <c r="N1113" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1113" s="50">
+        <v>1</v>
+      </c>
       <c r="U1113" s="50">
         <v>76002</v>
       </c>
@@ -62286,6 +63879,9 @@
       <c r="N1114" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1114" s="50">
+        <v>1</v>
+      </c>
       <c r="U1114" s="50">
         <v>76002</v>
       </c>
@@ -62322,6 +63918,9 @@
       <c r="N1115" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1115" s="50">
+        <v>1</v>
+      </c>
       <c r="U1115" s="50">
         <v>76002</v>
       </c>
@@ -62358,6 +63957,9 @@
       <c r="N1116" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1116" s="50">
+        <v>1</v>
+      </c>
       <c r="U1116" s="50">
         <v>76002</v>
       </c>
@@ -62394,6 +63996,9 @@
       <c r="N1117" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1117" s="50">
+        <v>1</v>
+      </c>
       <c r="U1117" s="50">
         <v>76002</v>
       </c>
@@ -62426,6 +64031,9 @@
       <c r="N1118" s="38">
         <v>3312</v>
       </c>
+      <c r="Q1118" s="50">
+        <v>1</v>
+      </c>
       <c r="U1118" s="50">
         <v>76002</v>
       </c>
@@ -62462,6 +64070,9 @@
       <c r="N1119" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1119" s="50">
+        <v>1</v>
+      </c>
       <c r="U1119" s="50">
         <v>76003</v>
       </c>
@@ -62498,6 +64109,9 @@
       <c r="N1120" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1120" s="50">
+        <v>1</v>
+      </c>
       <c r="U1120" s="50">
         <v>76003</v>
       </c>
@@ -62534,6 +64148,9 @@
       <c r="N1121" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1121" s="50">
+        <v>1</v>
+      </c>
       <c r="U1121" s="50">
         <v>76003</v>
       </c>
@@ -62570,6 +64187,9 @@
       <c r="N1122" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1122" s="50">
+        <v>1</v>
+      </c>
       <c r="U1122" s="50">
         <v>76003</v>
       </c>
@@ -62606,6 +64226,9 @@
       <c r="N1123" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1123" s="50">
+        <v>1</v>
+      </c>
       <c r="U1123" s="50">
         <v>76003</v>
       </c>
@@ -62638,6 +64261,9 @@
       <c r="N1124" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1124" s="50">
+        <v>1</v>
+      </c>
       <c r="U1124" s="50">
         <v>76003</v>
       </c>
@@ -62674,6 +64300,9 @@
       <c r="N1125" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1125" s="50">
+        <v>1</v>
+      </c>
       <c r="U1125" s="50">
         <v>76004</v>
       </c>
@@ -62710,6 +64339,9 @@
       <c r="N1126" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1126" s="50">
+        <v>1</v>
+      </c>
       <c r="U1126" s="50">
         <v>76004</v>
       </c>
@@ -62746,6 +64378,9 @@
       <c r="N1127" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1127" s="50">
+        <v>1</v>
+      </c>
       <c r="U1127" s="50">
         <v>76004</v>
       </c>
@@ -62782,6 +64417,9 @@
       <c r="N1128" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1128" s="50">
+        <v>1</v>
+      </c>
       <c r="U1128" s="50">
         <v>76004</v>
       </c>
@@ -62818,6 +64456,9 @@
       <c r="N1129" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1129" s="50">
+        <v>1</v>
+      </c>
       <c r="U1129" s="50">
         <v>76004</v>
       </c>
@@ -62850,6 +64491,9 @@
       <c r="N1130" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1130" s="50">
+        <v>1</v>
+      </c>
       <c r="U1130" s="50">
         <v>76004</v>
       </c>
@@ -62886,6 +64530,9 @@
       <c r="N1131" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1131" s="50">
+        <v>1</v>
+      </c>
       <c r="U1131" s="50">
         <v>76005</v>
       </c>
@@ -62922,6 +64569,9 @@
       <c r="N1132" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1132" s="50">
+        <v>1</v>
+      </c>
       <c r="U1132" s="50">
         <v>76005</v>
       </c>
@@ -62958,6 +64608,9 @@
       <c r="N1133" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1133" s="50">
+        <v>1</v>
+      </c>
       <c r="U1133" s="50">
         <v>76005</v>
       </c>
@@ -62994,6 +64647,9 @@
       <c r="N1134" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1134" s="50">
+        <v>1</v>
+      </c>
       <c r="U1134" s="50">
         <v>76005</v>
       </c>
@@ -63030,6 +64686,9 @@
       <c r="N1135" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1135" s="50">
+        <v>1</v>
+      </c>
       <c r="U1135" s="50">
         <v>76005</v>
       </c>
@@ -63062,6 +64721,9 @@
       <c r="N1136" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1136" s="50">
+        <v>1</v>
+      </c>
       <c r="U1136" s="50">
         <v>76005</v>
       </c>
@@ -63098,6 +64760,9 @@
       <c r="N1137" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1137" s="50">
+        <v>1</v>
+      </c>
       <c r="U1137" s="50">
         <v>76006</v>
       </c>
@@ -63134,6 +64799,9 @@
       <c r="N1138" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1138" s="50">
+        <v>1</v>
+      </c>
       <c r="U1138" s="50">
         <v>76006</v>
       </c>
@@ -63170,6 +64838,9 @@
       <c r="N1139" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1139" s="50">
+        <v>1</v>
+      </c>
       <c r="U1139" s="50">
         <v>76006</v>
       </c>
@@ -63206,6 +64877,9 @@
       <c r="N1140" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1140" s="50">
+        <v>1</v>
+      </c>
       <c r="U1140" s="50">
         <v>76006</v>
       </c>
@@ -63242,6 +64916,9 @@
       <c r="N1141" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1141" s="50">
+        <v>1</v>
+      </c>
       <c r="U1141" s="50">
         <v>76006</v>
       </c>
@@ -63274,6 +64951,9 @@
       <c r="N1142" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1142" s="50">
+        <v>1</v>
+      </c>
       <c r="U1142" s="50">
         <v>76006</v>
       </c>
@@ -63310,6 +64990,9 @@
       <c r="N1143" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1143" s="50">
+        <v>1</v>
+      </c>
       <c r="U1143" s="50">
         <v>76007</v>
       </c>
@@ -63346,6 +65029,9 @@
       <c r="N1144" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1144" s="50">
+        <v>1</v>
+      </c>
       <c r="U1144" s="50">
         <v>76007</v>
       </c>
@@ -63382,6 +65068,9 @@
       <c r="N1145" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1145" s="50">
+        <v>1</v>
+      </c>
       <c r="U1145" s="50">
         <v>76007</v>
       </c>
@@ -63418,6 +65107,9 @@
       <c r="N1146" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1146" s="50">
+        <v>1</v>
+      </c>
       <c r="U1146" s="50">
         <v>76007</v>
       </c>
@@ -63454,6 +65146,9 @@
       <c r="N1147" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1147" s="50">
+        <v>1</v>
+      </c>
       <c r="U1147" s="50">
         <v>76007</v>
       </c>
@@ -63490,6 +65185,9 @@
       <c r="N1148" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1148" s="50">
+        <v>1</v>
+      </c>
       <c r="U1148" s="50">
         <v>76007</v>
       </c>
@@ -63526,6 +65224,9 @@
       <c r="N1149" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1149" s="50">
+        <v>1</v>
+      </c>
       <c r="U1149" s="50">
         <v>76007</v>
       </c>
@@ -63558,6 +65259,9 @@
       <c r="N1150" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1150" s="50">
+        <v>1</v>
+      </c>
       <c r="U1150" s="50">
         <v>76007</v>
       </c>
@@ -63594,6 +65298,9 @@
       <c r="N1151" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1151" s="50">
+        <v>1</v>
+      </c>
       <c r="U1151" s="50">
         <v>76008</v>
       </c>
@@ -63630,6 +65337,9 @@
       <c r="N1152" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1152" s="50">
+        <v>1</v>
+      </c>
       <c r="U1152" s="50">
         <v>76008</v>
       </c>
@@ -63666,6 +65376,9 @@
       <c r="N1153" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1153" s="50">
+        <v>1</v>
+      </c>
       <c r="U1153" s="50">
         <v>76008</v>
       </c>
@@ -63702,6 +65415,9 @@
       <c r="N1154" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1154" s="50">
+        <v>1</v>
+      </c>
       <c r="U1154" s="50">
         <v>76008</v>
       </c>
@@ -63738,6 +65454,9 @@
       <c r="N1155" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1155" s="50">
+        <v>1</v>
+      </c>
       <c r="U1155" s="50">
         <v>76008</v>
       </c>
@@ -63770,6 +65489,9 @@
       <c r="N1156" s="38">
         <v>11022</v>
       </c>
+      <c r="Q1156" s="50">
+        <v>1</v>
+      </c>
       <c r="U1156" s="50">
         <v>76008</v>
       </c>
@@ -63809,6 +65531,9 @@
       <c r="N1157" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1157" s="50">
+        <v>1</v>
+      </c>
       <c r="U1157" s="61">
         <v>76001</v>
       </c>
@@ -63848,6 +65573,9 @@
       <c r="N1158" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1158" s="50">
+        <v>1</v>
+      </c>
       <c r="U1158" s="61">
         <v>76001</v>
       </c>
@@ -63887,6 +65615,9 @@
       <c r="N1159" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1159" s="50">
+        <v>1</v>
+      </c>
       <c r="U1159" s="61">
         <v>76001</v>
       </c>
@@ -63926,6 +65657,9 @@
       <c r="N1160" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1160" s="50">
+        <v>1</v>
+      </c>
       <c r="U1160" s="61">
         <v>76001</v>
       </c>
@@ -63965,6 +65699,9 @@
       <c r="N1161" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1161" s="50">
+        <v>1</v>
+      </c>
       <c r="U1161" s="61">
         <v>76001</v>
       </c>
@@ -64000,6 +65737,9 @@
       <c r="N1162" s="38">
         <v>3210</v>
       </c>
+      <c r="Q1162" s="50">
+        <v>1</v>
+      </c>
       <c r="U1162" s="61">
         <v>76001</v>
       </c>
@@ -64036,6 +65776,9 @@
       <c r="N1163" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1163" s="50">
+        <v>1</v>
+      </c>
       <c r="U1163" s="50">
         <v>76002</v>
       </c>
@@ -64072,6 +65815,9 @@
       <c r="N1164" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1164" s="50">
+        <v>1</v>
+      </c>
       <c r="U1164" s="50">
         <v>76002</v>
       </c>
@@ -64108,6 +65854,9 @@
       <c r="N1165" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1165" s="50">
+        <v>1</v>
+      </c>
       <c r="U1165" s="50">
         <v>76002</v>
       </c>
@@ -64144,6 +65893,9 @@
       <c r="N1166" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1166" s="50">
+        <v>1</v>
+      </c>
       <c r="U1166" s="50">
         <v>76002</v>
       </c>
@@ -64180,6 +65932,9 @@
       <c r="N1167" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1167" s="50">
+        <v>1</v>
+      </c>
       <c r="U1167" s="50">
         <v>76002</v>
       </c>
@@ -64212,6 +65967,9 @@
       <c r="N1168" s="38">
         <v>3311</v>
       </c>
+      <c r="Q1168" s="50">
+        <v>1</v>
+      </c>
       <c r="U1168" s="50">
         <v>76002</v>
       </c>
@@ -64248,6 +66006,9 @@
       <c r="N1169" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1169" s="50">
+        <v>1</v>
+      </c>
       <c r="U1169" s="50">
         <v>76003</v>
       </c>
@@ -64284,6 +66045,9 @@
       <c r="N1170" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1170" s="50">
+        <v>1</v>
+      </c>
       <c r="U1170" s="50">
         <v>76003</v>
       </c>
@@ -64320,6 +66084,9 @@
       <c r="N1171" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1171" s="50">
+        <v>1</v>
+      </c>
       <c r="U1171" s="50">
         <v>76003</v>
       </c>
@@ -64356,6 +66123,9 @@
       <c r="N1172" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1172" s="50">
+        <v>1</v>
+      </c>
       <c r="U1172" s="50">
         <v>76003</v>
       </c>
@@ -64392,6 +66162,9 @@
       <c r="N1173" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1173" s="50">
+        <v>1</v>
+      </c>
       <c r="U1173" s="50">
         <v>76003</v>
       </c>
@@ -64424,6 +66197,9 @@
       <c r="N1174" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1174" s="50">
+        <v>1</v>
+      </c>
       <c r="U1174" s="50">
         <v>76003</v>
       </c>
@@ -64460,6 +66236,9 @@
       <c r="N1175" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1175" s="50">
+        <v>1</v>
+      </c>
       <c r="U1175" s="50">
         <v>76004</v>
       </c>
@@ -64496,6 +66275,9 @@
       <c r="N1176" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1176" s="50">
+        <v>1</v>
+      </c>
       <c r="U1176" s="50">
         <v>76004</v>
       </c>
@@ -64532,6 +66314,9 @@
       <c r="N1177" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1177" s="50">
+        <v>1</v>
+      </c>
       <c r="U1177" s="50">
         <v>76004</v>
       </c>
@@ -64568,6 +66353,9 @@
       <c r="N1178" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1178" s="50">
+        <v>1</v>
+      </c>
       <c r="U1178" s="50">
         <v>76004</v>
       </c>
@@ -64604,6 +66392,9 @@
       <c r="N1179" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1179" s="50">
+        <v>1</v>
+      </c>
       <c r="U1179" s="50">
         <v>76004</v>
       </c>
@@ -64636,6 +66427,9 @@
       <c r="N1180" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1180" s="50">
+        <v>1</v>
+      </c>
       <c r="U1180" s="50">
         <v>76004</v>
       </c>
@@ -64672,6 +66466,9 @@
       <c r="N1181" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1181" s="50">
+        <v>1</v>
+      </c>
       <c r="U1181" s="50">
         <v>76005</v>
       </c>
@@ -64708,6 +66505,9 @@
       <c r="N1182" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1182" s="50">
+        <v>1</v>
+      </c>
       <c r="U1182" s="50">
         <v>76005</v>
       </c>
@@ -64744,6 +66544,9 @@
       <c r="N1183" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1183" s="50">
+        <v>1</v>
+      </c>
       <c r="U1183" s="50">
         <v>76005</v>
       </c>
@@ -64780,6 +66583,9 @@
       <c r="N1184" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1184" s="50">
+        <v>1</v>
+      </c>
       <c r="U1184" s="50">
         <v>76005</v>
       </c>
@@ -64816,6 +66622,9 @@
       <c r="N1185" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1185" s="50">
+        <v>1</v>
+      </c>
       <c r="U1185" s="50">
         <v>76005</v>
       </c>
@@ -64848,6 +66657,9 @@
       <c r="N1186" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1186" s="50">
+        <v>1</v>
+      </c>
       <c r="U1186" s="50">
         <v>76005</v>
       </c>
@@ -64884,6 +66696,9 @@
       <c r="N1187" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1187" s="50">
+        <v>1</v>
+      </c>
       <c r="U1187" s="50">
         <v>76006</v>
       </c>
@@ -64920,6 +66735,9 @@
       <c r="N1188" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1188" s="50">
+        <v>1</v>
+      </c>
       <c r="U1188" s="50">
         <v>76006</v>
       </c>
@@ -64956,6 +66774,9 @@
       <c r="N1189" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1189" s="50">
+        <v>1</v>
+      </c>
       <c r="U1189" s="50">
         <v>76006</v>
       </c>
@@ -64992,6 +66813,9 @@
       <c r="N1190" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1190" s="50">
+        <v>1</v>
+      </c>
       <c r="U1190" s="50">
         <v>76006</v>
       </c>
@@ -65028,6 +66852,9 @@
       <c r="N1191" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1191" s="50">
+        <v>1</v>
+      </c>
       <c r="U1191" s="50">
         <v>76006</v>
       </c>
@@ -65060,6 +66887,9 @@
       <c r="N1192" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1192" s="50">
+        <v>1</v>
+      </c>
       <c r="U1192" s="50">
         <v>76006</v>
       </c>
@@ -65096,6 +66926,9 @@
       <c r="N1193" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1193" s="50">
+        <v>1</v>
+      </c>
       <c r="U1193" s="50">
         <v>76007</v>
       </c>
@@ -65132,6 +66965,9 @@
       <c r="N1194" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1194" s="50">
+        <v>1</v>
+      </c>
       <c r="U1194" s="50">
         <v>76007</v>
       </c>
@@ -65168,6 +67004,9 @@
       <c r="N1195" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1195" s="50">
+        <v>1</v>
+      </c>
       <c r="U1195" s="50">
         <v>76007</v>
       </c>
@@ -65204,6 +67043,9 @@
       <c r="N1196" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1196" s="50">
+        <v>1</v>
+      </c>
       <c r="U1196" s="50">
         <v>76007</v>
       </c>
@@ -65240,6 +67082,9 @@
       <c r="N1197" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1197" s="50">
+        <v>1</v>
+      </c>
       <c r="U1197" s="50">
         <v>76007</v>
       </c>
@@ -65276,6 +67121,9 @@
       <c r="N1198" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1198" s="50">
+        <v>1</v>
+      </c>
       <c r="U1198" s="50">
         <v>76007</v>
       </c>
@@ -65312,6 +67160,9 @@
       <c r="N1199" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1199" s="50">
+        <v>1</v>
+      </c>
       <c r="U1199" s="50">
         <v>76007</v>
       </c>
@@ -65344,6 +67195,9 @@
       <c r="N1200" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1200" s="50">
+        <v>1</v>
+      </c>
       <c r="U1200" s="50">
         <v>76007</v>
       </c>
@@ -65380,6 +67234,9 @@
       <c r="N1201" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1201" s="50">
+        <v>1</v>
+      </c>
       <c r="U1201" s="50">
         <v>76008</v>
       </c>
@@ -65416,6 +67273,9 @@
       <c r="N1202" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1202" s="50">
+        <v>1</v>
+      </c>
       <c r="U1202" s="50">
         <v>76008</v>
       </c>
@@ -65452,6 +67312,9 @@
       <c r="N1203" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1203" s="50">
+        <v>1</v>
+      </c>
       <c r="U1203" s="50">
         <v>76008</v>
       </c>
@@ -65488,6 +67351,9 @@
       <c r="N1204" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1204" s="50">
+        <v>1</v>
+      </c>
       <c r="U1204" s="50">
         <v>76008</v>
       </c>
@@ -65524,6 +67390,9 @@
       <c r="N1205" s="38">
         <v>11021</v>
       </c>
+      <c r="Q1205" s="50">
+        <v>1</v>
+      </c>
       <c r="U1205" s="50">
         <v>76008</v>
       </c>
@@ -65555,6 +67424,9 @@
       </c>
       <c r="N1206" s="38">
         <v>11021</v>
+      </c>
+      <c r="Q1206" s="50">
+        <v>1</v>
       </c>
       <c r="U1206" s="50">
         <v>76008</v>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -5656,7 +5656,7 @@
     <t>试炼任务</t>
   </si>
   <si>
-    <t>12601_100300_5_400</t>
+    <t>12601_100300_400</t>
   </si>
   <si>
     <t>1960000_50</t>
@@ -5665,7 +5665,7 @@
     <t>5局收益达到400</t>
   </si>
   <si>
-    <t>12601_100300_5_600</t>
+    <t>12601_100300_600</t>
   </si>
   <si>
     <t>1960000_100</t>
@@ -5674,7 +5674,7 @@
     <t>5局收益达到600</t>
   </si>
   <si>
-    <t>12601_100300_5_800</t>
+    <t>12601_100300_800</t>
   </si>
   <si>
     <t>1960000_200</t>
@@ -5683,91 +5683,91 @@
     <t>5局收益达到800</t>
   </si>
   <si>
-    <t>12602_100300_100_2_1</t>
+    <t>12602_2_1</t>
   </si>
   <si>
     <t>100局触发一次樱桃</t>
   </si>
   <si>
-    <t>12602_100300_100_2_2</t>
+    <t>12602_2_2</t>
   </si>
   <si>
     <t>100局触发二次樱桃</t>
   </si>
   <si>
-    <t>12602_100300_100_2_3</t>
+    <t>12602_2_3</t>
   </si>
   <si>
     <t>100局触发三次樱桃</t>
   </si>
   <si>
-    <t>12603_100300_30_2_1</t>
+    <t>12603_100300_1</t>
   </si>
   <si>
     <t>30局触发1次2倍奖励</t>
   </si>
   <si>
-    <t>12603_100300_30_2_2</t>
+    <t>12603_100300_2</t>
   </si>
   <si>
     <t>30局触发2次2倍奖励</t>
   </si>
   <si>
-    <t>12603_100300_30_2_3</t>
+    <t>12603_100300_3</t>
   </si>
   <si>
     <t>30局触发3次2倍奖励</t>
   </si>
   <si>
-    <t>12604_100300_5_1</t>
+    <t>12604_100300_1</t>
   </si>
   <si>
     <t>5局内中奖1次</t>
   </si>
   <si>
-    <t>12604_100300_5_2</t>
+    <t>12604_100300_2</t>
   </si>
   <si>
     <t>5局内中奖2次</t>
   </si>
   <si>
-    <t>12604_100300_5_3</t>
+    <t>12604_100300_3</t>
   </si>
   <si>
     <t>5局内中奖3次</t>
   </si>
   <si>
-    <t>12603_100300_50_5_1</t>
+    <t>12611_100300_1</t>
   </si>
   <si>
     <t>50局触发1次5倍奖励</t>
   </si>
   <si>
-    <t>12603_100300_50_5_2</t>
+    <t>12611_100300_2</t>
   </si>
   <si>
     <t>50局触发2次5倍奖励</t>
   </si>
   <si>
-    <t>12603_100300_50_5_3</t>
+    <t>12611_100300_3</t>
   </si>
   <si>
     <t>50局触发3次5倍奖励</t>
   </si>
   <si>
-    <t>12605_100300_5_4_1</t>
+    <t>12605_4_1</t>
   </si>
   <si>
     <t>5局出现铃铛图标1次</t>
   </si>
   <si>
-    <t>12605_100300_5_4_2</t>
+    <t>12605_4_2</t>
   </si>
   <si>
     <t>5局出现铃铛图标2次</t>
   </si>
   <si>
-    <t>12605_100300_5_4_3</t>
+    <t>12605_4_3</t>
   </si>
   <si>
     <t>5局出现铃铛图标3次</t>
@@ -5793,7 +5793,7 @@
     </r>
   </si>
   <si>
-    <t>12601_100300_5_1000</t>
+    <t>12601_100300_1000</t>
   </si>
   <si>
     <r>
@@ -5816,13 +5816,13 @@
     </r>
   </si>
   <si>
-    <t>12601_100300_5_1200</t>
+    <t>12601_100300_1200</t>
   </si>
   <si>
     <t>自由搭配，5局总收益≥1200</t>
   </si>
   <si>
-    <t>12606_100300_3_200</t>
+    <t>12606_100300_200</t>
   </si>
   <si>
     <r>
@@ -5845,7 +5845,7 @@
     </r>
   </si>
   <si>
-    <t>12606_100300_3_300</t>
+    <t>12606_100300_300</t>
   </si>
   <si>
     <r>
@@ -5868,7 +5868,7 @@
     </r>
   </si>
   <si>
-    <t>12606_100300_3_400</t>
+    <t>12606_100300_400</t>
   </si>
   <si>
     <r>
@@ -10351,12 +10351,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="27945" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -10723,12 +10723,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -10736,6 +10730,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -24239,7 +24239,7 @@
       <c r="M135" s="12"/>
       <c r="N135" s="13"/>
       <c r="O135" s="10">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="P135" s="10"/>
       <c r="Q135" s="8"/>

--- a/table/resources/sample/task.xlsx
+++ b/table/resources/sample/task.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SSS\游戏配置表\common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\common\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="task" sheetId="1" r:id="rId1"/>
@@ -9502,19 +9502,19 @@
     <t>在slot游戏中触发50次免费旋转</t>
   </si>
   <si>
-    <t>12231_0_30</t>
+    <t>12231_30</t>
   </si>
   <si>
     <t>抽卡次数30次</t>
   </si>
   <si>
-    <t>12231_0_60</t>
+    <t>12231_60</t>
   </si>
   <si>
     <t>抽卡次数60次</t>
   </si>
   <si>
-    <t>12231_0_100</t>
+    <t>12231_100</t>
   </si>
   <si>
     <t>抽卡次数100次</t>
